--- a/rtss-mexico/src/main/resources/latinamerica/Latin-America-Urbanization.xlsx
+++ b/rtss-mexico/src/main/resources/latinamerica/Latin-America-Urbanization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-mexico\src\main\resources\latinamerica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B989A0A5-AD96-4E84-9872-10CF459A22BF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D971E15-B926-4DA6-B8D6-2E0641B8FE32}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13185" yWindow="600" windowWidth="21915" windowHeight="22275" activeTab="9" xr2:uid="{CF6A2AB8-34C5-4CDB-9A0B-0A9EB6FB1FEF}"/>
+    <workbookView xWindow="13605" yWindow="1065" windowWidth="26520" windowHeight="22275" activeTab="9" xr2:uid="{CF6A2AB8-34C5-4CDB-9A0B-0A9EB6FB1FEF}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="112">
   <si>
     <t>Boletín demográfico. Año 38, no. 75, Jan 2005, стр. 26</t>
   </si>
@@ -374,6 +374,12 @@
   <si>
     <t>100+ тыс</t>
   </si>
+  <si>
+    <t>Для СССР и РСФСР см. urbanization.xlsx</t>
+  </si>
+  <si>
+    <t>РСФСР</t>
+  </si>
 </sst>
 </file>
 
@@ -382,7 +388,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,6 +454,12 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -498,7 +510,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -524,9 +536,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -549,6 +558,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -885,9 +899,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A5BC77-576E-4DC4-B117-3E379681AD07}">
-  <dimension ref="A2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>110</v>
+      </c>
+    </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3"/>
     </row>
@@ -898,15 +917,15 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC336925-0078-4AF9-986A-8BA8236BAFF3}">
-  <dimension ref="A1:AE114"/>
+  <dimension ref="A1:AF132"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:26" ht="15">
+    <row r="1" spans="1:28" ht="15">
       <c r="A1" s="11" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="15">
+    <row r="3" spans="1:28" ht="15">
       <c r="A3" s="16" t="s">
         <v>38</v>
       </c>
@@ -985,8 +1004,14 @@
       <c r="Z3" s="16" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:26" ht="15">
+      <c r="AA3" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB3" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" ht="15">
       <c r="A4">
         <v>1895</v>
       </c>
@@ -1018,11 +1043,11 @@
       <c r="Y4" s="16"/>
       <c r="Z4" s="16"/>
     </row>
-    <row r="5" spans="1:26" ht="15">
+    <row r="5" spans="1:28" ht="15">
       <c r="A5">
-        <v>1899</v>
-      </c>
-      <c r="B5" s="16"/>
+        <v>1897</v>
+      </c>
+      <c r="B5" s="1"/>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -1047,16 +1072,20 @@
       <c r="X5" s="16"/>
       <c r="Y5" s="16"/>
       <c r="Z5" s="16"/>
-    </row>
-    <row r="6" spans="1:26" ht="15">
+      <c r="AA5">
+        <v>15</v>
+      </c>
+      <c r="AB5">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="15">
       <c r="A6">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
-      <c r="D6" s="1">
-        <v>26.9</v>
-      </c>
+      <c r="D6" s="16"/>
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
@@ -1080,13 +1109,15 @@
       <c r="Y6" s="16"/>
       <c r="Z6" s="16"/>
     </row>
-    <row r="7" spans="1:26" ht="15">
+    <row r="7" spans="1:28" ht="15">
       <c r="A7">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
+      <c r="D7" s="1">
+        <v>26.9</v>
+      </c>
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
@@ -1110,9 +1141,9 @@
       <c r="Y7" s="16"/>
       <c r="Z7" s="16"/>
     </row>
-    <row r="8" spans="1:26" ht="15">
+    <row r="8" spans="1:28" ht="15">
       <c r="A8">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -1128,9 +1159,7 @@
       <c r="M8" s="16"/>
       <c r="N8" s="16"/>
       <c r="O8" s="16"/>
-      <c r="P8" s="1">
-        <v>33</v>
-      </c>
+      <c r="P8" s="16"/>
       <c r="Q8" s="16"/>
       <c r="R8" s="16"/>
       <c r="S8" s="16"/>
@@ -1142,9 +1171,9 @@
       <c r="Y8" s="16"/>
       <c r="Z8" s="16"/>
     </row>
-    <row r="9" spans="1:26" ht="15">
+    <row r="9" spans="1:28" ht="15">
       <c r="A9">
-        <v>1910</v>
+        <v>1906</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -1160,7 +1189,9 @@
       <c r="M9" s="16"/>
       <c r="N9" s="16"/>
       <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
+      <c r="P9" s="1">
+        <v>33</v>
+      </c>
       <c r="Q9" s="16"/>
       <c r="R9" s="16"/>
       <c r="S9" s="16"/>
@@ -1172,9 +1203,9 @@
       <c r="Y9" s="16"/>
       <c r="Z9" s="16"/>
     </row>
-    <row r="10" spans="1:26" ht="15">
+    <row r="10" spans="1:28" ht="15">
       <c r="A10">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -1202,13 +1233,11 @@
       <c r="Y10" s="16"/>
       <c r="Z10" s="16"/>
     </row>
-    <row r="11" spans="1:26" ht="15">
+    <row r="11" spans="1:28" ht="15">
       <c r="A11">
-        <v>1914</v>
-      </c>
-      <c r="B11" s="1">
-        <v>52.7</v>
-      </c>
+        <v>1911</v>
+      </c>
+      <c r="B11" s="16"/>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
@@ -1234,9 +1263,9 @@
       <c r="Y11" s="16"/>
       <c r="Z11" s="16"/>
     </row>
-    <row r="12" spans="1:26" ht="15">
+    <row r="12" spans="1:28" ht="15">
       <c r="A12">
-        <v>1920</v>
+        <v>1913</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -1247,16 +1276,12 @@
       <c r="H12" s="16"/>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
-      <c r="K12" s="1">
-        <v>16.100000000000001</v>
-      </c>
+      <c r="K12" s="16"/>
       <c r="L12" s="16"/>
       <c r="M12" s="16"/>
       <c r="N12" s="16"/>
       <c r="O12" s="16"/>
-      <c r="P12" s="1">
-        <v>34.200000000000003</v>
-      </c>
+      <c r="P12" s="16"/>
       <c r="Q12" s="16"/>
       <c r="R12" s="16"/>
       <c r="S12" s="16"/>
@@ -1267,20 +1292,23 @@
       <c r="X12" s="16"/>
       <c r="Y12" s="16"/>
       <c r="Z12" s="16"/>
-    </row>
-    <row r="13" spans="1:26" ht="15">
+      <c r="AA12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" ht="15">
       <c r="A13">
-        <v>1921</v>
-      </c>
-      <c r="B13" s="16"/>
+        <v>1914</v>
+      </c>
+      <c r="B13" s="1">
+        <v>52.7</v>
+      </c>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
-      <c r="H13" s="1">
-        <v>26.6</v>
-      </c>
+      <c r="H13" s="16"/>
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
       <c r="K13" s="16"/>
@@ -1300,9 +1328,9 @@
       <c r="Y13" s="16"/>
       <c r="Z13" s="16"/>
     </row>
-    <row r="14" spans="1:26" ht="15">
+    <row r="14" spans="1:28" ht="15">
       <c r="A14">
-        <v>1930</v>
+        <v>1920</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
@@ -1313,36 +1341,36 @@
       <c r="H14" s="16"/>
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
+      <c r="K14" s="1">
+        <v>16.100000000000001</v>
+      </c>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
       <c r="N14" s="16"/>
-      <c r="O14" s="1">
-        <v>33.5</v>
-      </c>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="1">
-        <v>30.1</v>
-      </c>
+      <c r="O14" s="16"/>
+      <c r="P14" s="1">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="Q14" s="16"/>
       <c r="R14" s="16"/>
       <c r="S14" s="16"/>
-      <c r="T14" s="1">
-        <v>38.299999999999997</v>
-      </c>
+      <c r="T14" s="16"/>
       <c r="U14" s="16"/>
       <c r="V14" s="16"/>
       <c r="W14" s="16"/>
-      <c r="X14" s="1">
-        <v>49.4</v>
-      </c>
-      <c r="Y14" s="1">
-        <v>30.3</v>
-      </c>
+      <c r="X14" s="16"/>
+      <c r="Y14" s="16"/>
       <c r="Z14" s="16"/>
-    </row>
-    <row r="15" spans="1:26" ht="15">
+      <c r="AA14">
+        <v>15</v>
+      </c>
+      <c r="AB14">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" ht="15">
       <c r="A15">
-        <v>1931</v>
+        <v>1921</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -1350,7 +1378,9 @@
       <c r="E15" s="16"/>
       <c r="F15" s="16"/>
       <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
+      <c r="H15" s="1">
+        <v>26.6</v>
+      </c>
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
       <c r="K15" s="16"/>
@@ -1370,9 +1400,9 @@
       <c r="Y15" s="16"/>
       <c r="Z15" s="16"/>
     </row>
-    <row r="16" spans="1:26" ht="15">
+    <row r="16" spans="1:28" ht="15">
       <c r="A16">
-        <v>1935</v>
+        <v>1926</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -1380,12 +1410,10 @@
       <c r="E16" s="16"/>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
+      <c r="H16" s="1"/>
       <c r="I16" s="16"/>
       <c r="J16" s="16"/>
-      <c r="K16" s="1">
-        <v>18</v>
-      </c>
+      <c r="K16" s="16"/>
       <c r="L16" s="16"/>
       <c r="M16" s="16"/>
       <c r="N16" s="16"/>
@@ -1401,18 +1429,22 @@
       <c r="X16" s="16"/>
       <c r="Y16" s="16"/>
       <c r="Z16" s="16"/>
-    </row>
-    <row r="17" spans="1:26" ht="15">
+      <c r="AA16">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="AB16">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" ht="15">
       <c r="A17">
-        <v>1936</v>
+        <v>1930</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
-      <c r="F17" s="1">
-        <v>35</v>
-      </c>
+      <c r="F17" s="16"/>
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
       <c r="I17" s="16"/>
@@ -1421,22 +1453,32 @@
       <c r="L17" s="16"/>
       <c r="M17" s="16"/>
       <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
+      <c r="O17" s="1">
+        <v>33.5</v>
+      </c>
       <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
+      <c r="Q17" s="1">
+        <v>30.1</v>
+      </c>
       <c r="R17" s="16"/>
       <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
+      <c r="T17" s="1">
+        <v>38.299999999999997</v>
+      </c>
       <c r="U17" s="16"/>
       <c r="V17" s="16"/>
       <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="16"/>
+      <c r="X17" s="1">
+        <v>49.4</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>30.3</v>
+      </c>
       <c r="Z17" s="16"/>
     </row>
-    <row r="18" spans="1:26" ht="15">
+    <row r="18" spans="1:28" ht="15">
       <c r="A18">
-        <v>1938</v>
+        <v>1931</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -1448,9 +1490,7 @@
       <c r="I18" s="16"/>
       <c r="J18" s="16"/>
       <c r="K18" s="16"/>
-      <c r="L18" s="1">
-        <v>29.1</v>
-      </c>
+      <c r="L18" s="16"/>
       <c r="M18" s="16"/>
       <c r="N18" s="16"/>
       <c r="O18" s="16"/>
@@ -1466,9 +1506,9 @@
       <c r="Y18" s="16"/>
       <c r="Z18" s="16"/>
     </row>
-    <row r="19" spans="1:26" ht="15">
+    <row r="19" spans="1:28" ht="15">
       <c r="A19">
-        <v>1939</v>
+        <v>1935</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -1479,7 +1519,9 @@
       <c r="H19" s="16"/>
       <c r="I19" s="16"/>
       <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
+      <c r="K19" s="1">
+        <v>18</v>
+      </c>
       <c r="L19" s="16"/>
       <c r="M19" s="16"/>
       <c r="N19" s="16"/>
@@ -1496,189 +1538,197 @@
       <c r="Y19" s="16"/>
       <c r="Z19" s="16"/>
     </row>
-    <row r="20" spans="1:26" ht="15">
-      <c r="A20" s="12">
+    <row r="20" spans="1:28" ht="15">
+      <c r="A20">
+        <v>1936</v>
+      </c>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="1">
+        <v>35</v>
+      </c>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+      <c r="T20" s="16"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="16"/>
+      <c r="W20" s="16"/>
+      <c r="X20" s="16"/>
+      <c r="Y20" s="16"/>
+      <c r="Z20" s="16"/>
+    </row>
+    <row r="21" spans="1:28" ht="15">
+      <c r="A21">
+        <v>1937</v>
+      </c>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="16"/>
+      <c r="S21" s="16"/>
+      <c r="T21" s="16"/>
+      <c r="U21" s="16"/>
+      <c r="V21" s="16"/>
+      <c r="W21" s="16"/>
+      <c r="X21" s="16"/>
+      <c r="Y21" s="16"/>
+      <c r="Z21" s="16"/>
+      <c r="AA21">
+        <v>31.2</v>
+      </c>
+      <c r="AB21">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" ht="15">
+      <c r="A22">
+        <v>1938</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="1">
+        <v>29.1</v>
+      </c>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="16"/>
+      <c r="V22" s="16"/>
+      <c r="W22" s="16"/>
+      <c r="X22" s="16"/>
+      <c r="Y22" s="16"/>
+      <c r="Z22" s="16"/>
+    </row>
+    <row r="23" spans="1:28" ht="15">
+      <c r="A23">
+        <v>1939</v>
+      </c>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="16"/>
+      <c r="S23" s="16"/>
+      <c r="T23" s="16"/>
+      <c r="U23" s="16"/>
+      <c r="V23" s="16"/>
+      <c r="W23" s="16"/>
+      <c r="X23" s="16"/>
+      <c r="Y23" s="16"/>
+      <c r="Z23" s="16"/>
+      <c r="AA23">
+        <v>31.7</v>
+      </c>
+      <c r="AB23">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" ht="15">
+      <c r="A24" s="12">
         <v>1940</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="1">
-        <v>31.2</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="1">
-        <v>26.7</v>
-      </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="1">
-        <v>35.1</v>
-      </c>
-      <c r="P20" s="1">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="R20" s="2"/>
-      <c r="S20" s="12">
-        <v>36.1</v>
-      </c>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="1">
-        <v>52.4</v>
-      </c>
-      <c r="Y20" s="2"/>
-      <c r="Z20" s="2"/>
-    </row>
-    <row r="21" spans="1:26" ht="15">
-      <c r="A21">
-        <v>1941</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="1">
-        <v>39</v>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="12"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2"/>
-    </row>
-    <row r="22" spans="1:26" ht="15">
-      <c r="A22">
-        <v>1943</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="1">
-        <v>54.6</v>
-      </c>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
-      <c r="Y22" s="2"/>
-      <c r="Z22" s="1">
-        <v>18.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" ht="15">
-      <c r="A23">
-        <v>1945</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="1">
-        <v>29</v>
-      </c>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="12"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
-      <c r="Y23" s="2"/>
-      <c r="Z23" s="2"/>
-    </row>
-    <row r="24" spans="1:26" ht="15">
-      <c r="A24">
-        <v>1946</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+      <c r="E24" s="1">
+        <v>31.2</v>
+      </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
+      <c r="H24" s="1">
+        <v>26.7</v>
+      </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
+      <c r="O24" s="1">
+        <v>35.1</v>
+      </c>
+      <c r="P24" s="1">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>33.799999999999997</v>
+      </c>
       <c r="R24" s="2"/>
-      <c r="S24" s="12"/>
+      <c r="S24" s="12">
+        <v>36.1</v>
+      </c>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
       <c r="V24" s="2"/>
       <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
+      <c r="X24" s="1">
+        <v>52.4</v>
+      </c>
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="15">
+    <row r="25" spans="1:28" ht="15">
       <c r="A25">
-        <v>1947</v>
-      </c>
-      <c r="B25" s="1">
-        <v>62.5</v>
-      </c>
+        <v>1941</v>
+      </c>
+      <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
+      <c r="F25" s="1">
+        <v>39</v>
+      </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -1700,1479 +1750,1469 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" spans="1:28" ht="15">
       <c r="A26">
+        <v>1943</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="1">
+        <v>54.6</v>
+      </c>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="12"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="2"/>
+      <c r="Z26" s="1">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" ht="15">
+      <c r="A27">
+        <v>1945</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="1">
+        <v>29</v>
+      </c>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="2"/>
+      <c r="Z27" s="2"/>
+    </row>
+    <row r="28" spans="1:28" ht="15">
+      <c r="A28">
+        <v>1946</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="12"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="2"/>
+      <c r="Z28" s="2"/>
+    </row>
+    <row r="29" spans="1:28" ht="15">
+      <c r="A29">
+        <v>1947</v>
+      </c>
+      <c r="B29" s="1">
+        <v>62.5</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="2"/>
+      <c r="Z29" s="2"/>
+    </row>
+    <row r="30" spans="1:28">
+      <c r="A30">
         <v>1950</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B30" s="1">
         <v>62.5</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C30" s="1">
         <v>56.5</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D30" s="1">
         <v>33.9</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E30" s="1">
         <v>36.5</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F30" s="1">
         <v>53.7</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G30" s="1">
         <v>12.2</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H30" s="1">
         <v>25</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I30" s="1">
         <v>28.1</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J30" s="1">
         <v>31</v>
       </c>
-      <c r="K26" s="1">
+      <c r="K30" s="1">
         <v>23.9</v>
       </c>
-      <c r="L26" s="1">
+      <c r="L30" s="1">
         <v>42.7</v>
       </c>
-      <c r="M26" s="1">
+      <c r="M30" s="1">
         <v>33.5</v>
       </c>
-      <c r="N26" s="1">
+      <c r="N30" s="1">
         <v>55.1</v>
       </c>
-      <c r="O26" s="1">
+      <c r="O30" s="1">
         <v>36.200000000000003</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P30" s="1">
         <v>34.9</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="Q30" s="1">
         <v>36</v>
       </c>
-      <c r="R26" s="1">
+      <c r="R30" s="1">
         <v>34.6</v>
       </c>
-      <c r="S26" s="1">
+      <c r="S30" s="1">
         <v>35.299999999999997</v>
       </c>
-      <c r="T26" s="1">
+      <c r="T30" s="1">
         <v>36.5</v>
       </c>
-      <c r="U26" s="1">
+      <c r="U30" s="1">
         <v>47</v>
       </c>
-      <c r="V26" s="1">
+      <c r="V30" s="1">
         <v>78</v>
       </c>
-      <c r="W26" s="1">
+      <c r="W30" s="1">
         <v>52</v>
       </c>
-      <c r="X26" s="1">
+      <c r="X30" s="1">
         <v>60.7</v>
       </c>
-      <c r="Y26" s="1">
+      <c r="Y30" s="1">
         <v>28.5</v>
       </c>
-      <c r="Z26" s="1">
+      <c r="Z30" s="1">
         <v>26.7</v>
       </c>
     </row>
-    <row r="27" spans="1:26">
-      <c r="A27">
+    <row r="31" spans="1:28">
+      <c r="A31">
+        <v>1959</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31">
+        <v>47.9</v>
+      </c>
+      <c r="AB31">
+        <v>52.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28">
+      <c r="A32">
         <v>1960</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B32" s="1">
         <v>73.8</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C32" s="1">
         <v>53.8</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D32" s="1">
         <v>39.299999999999997</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E32" s="1">
         <v>43</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F32" s="1">
         <v>67.400000000000006</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G32" s="1">
         <v>15.6</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H32" s="1">
         <v>33.6</v>
       </c>
-      <c r="I27" s="1">
+      <c r="I32" s="1">
         <v>29</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J32" s="1">
         <v>30.4</v>
       </c>
-      <c r="K27" s="1">
+      <c r="K32" s="1">
         <v>30.5</v>
       </c>
-      <c r="L27" s="1">
+      <c r="L32" s="1">
         <v>52.1</v>
       </c>
-      <c r="M27" s="1">
+      <c r="M32" s="1">
         <v>34.5</v>
       </c>
-      <c r="N27" s="1">
+      <c r="N32" s="1">
         <v>54.9</v>
       </c>
-      <c r="O27" s="1">
+      <c r="O32" s="1">
         <v>43.7</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P32" s="1">
         <v>40.9</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="Q32" s="1">
         <v>41.5</v>
       </c>
-      <c r="R27" s="1">
+      <c r="R32" s="1">
         <v>35.799999999999997</v>
       </c>
-      <c r="S27" s="1">
+      <c r="S32" s="1">
         <v>47.4</v>
       </c>
-      <c r="T27" s="1">
+      <c r="T32" s="1">
         <v>38.5</v>
       </c>
-      <c r="U27" s="1">
+      <c r="U32" s="1">
         <v>47.2</v>
       </c>
-      <c r="V27" s="1">
+      <c r="V32" s="1">
         <v>81</v>
       </c>
-      <c r="W27" s="1">
+      <c r="W32" s="1">
         <v>63.6</v>
       </c>
-      <c r="X27" s="1">
+      <c r="X32" s="1">
         <v>68.2</v>
       </c>
-      <c r="Y27" s="1">
+      <c r="Y32" s="1">
         <v>35.299999999999997</v>
       </c>
-      <c r="Z27" s="1">
+      <c r="Z32" s="1">
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:26">
-      <c r="A28">
+    <row r="33" spans="1:28">
+      <c r="A33">
         <v>1970</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B33" s="1">
         <v>79</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C33" s="1">
         <v>51.2</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D33" s="1">
         <v>41.7</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E33" s="1">
         <v>55.9</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F33" s="1">
         <v>77.2</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G33" s="1">
         <v>20.2</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H33" s="1">
         <v>36.4</v>
       </c>
-      <c r="I28" s="1">
+      <c r="I33" s="1">
         <v>29.5</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J33" s="1">
         <v>37.200000000000003</v>
       </c>
-      <c r="K28" s="1">
+      <c r="K33" s="1">
         <v>39.700000000000003</v>
       </c>
-      <c r="L28" s="1">
+      <c r="L33" s="1">
         <v>59.1</v>
       </c>
-      <c r="M28" s="1">
+      <c r="M33" s="1">
         <v>40.6</v>
       </c>
-      <c r="N28" s="1">
+      <c r="N33" s="1">
         <v>60.7</v>
       </c>
-      <c r="O28" s="1">
+      <c r="O33" s="1">
         <v>51.4</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P33" s="1">
         <v>47.7</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="Q33" s="1">
         <v>47.6</v>
       </c>
-      <c r="R28" s="1">
+      <c r="R33" s="1">
         <v>37.1</v>
       </c>
-      <c r="S28" s="1">
+      <c r="S33" s="1">
         <v>59.5</v>
       </c>
-      <c r="T28" s="1">
+      <c r="T33" s="1">
         <v>39.5</v>
       </c>
-      <c r="U28" s="1">
+      <c r="U33" s="1">
         <v>46</v>
       </c>
-      <c r="V28" s="1">
+      <c r="V33" s="1">
         <v>83.3</v>
       </c>
-      <c r="W28" s="1">
+      <c r="W33" s="1">
         <v>67.3</v>
       </c>
-      <c r="X28" s="1">
+      <c r="X33" s="1">
         <v>75.099999999999994</v>
       </c>
-      <c r="Y28" s="1">
+      <c r="Y33" s="1">
         <v>41.4</v>
       </c>
-      <c r="Z28" s="1">
+      <c r="Z33" s="1">
         <v>41.5</v>
       </c>
-    </row>
-    <row r="29" spans="1:26">
-      <c r="A29">
+      <c r="AA33" s="1">
+        <v>56.3</v>
+      </c>
+      <c r="AB33" s="1">
+        <v>62.3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28">
+      <c r="A34">
+        <v>1979</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1"/>
+      <c r="Z34" s="1"/>
+      <c r="AA34" s="1">
+        <v>62.3</v>
+      </c>
+      <c r="AB34">
+        <v>69.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28">
+      <c r="A35">
         <v>1980</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B35" s="1">
         <v>83</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C35" s="1">
         <v>49.3</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D35" s="1">
         <v>50.5</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E35" s="1">
         <v>67.599999999999994</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F35" s="1">
         <v>84</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G35" s="1">
         <v>24.5</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H35" s="1">
         <v>32.700000000000003</v>
       </c>
-      <c r="I29" s="1">
+      <c r="I35" s="1">
         <v>30.6</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J35" s="1">
         <v>38.700000000000003</v>
       </c>
-      <c r="K29" s="1">
+      <c r="K35" s="1">
         <v>52</v>
       </c>
-      <c r="L29" s="1">
+      <c r="L35" s="1">
         <v>67.2</v>
       </c>
-      <c r="M29" s="1">
+      <c r="M35" s="1">
         <v>44.5</v>
       </c>
-      <c r="N29" s="1">
+      <c r="N35" s="1">
         <v>69</v>
       </c>
-      <c r="O29" s="1">
+      <c r="O35" s="1">
         <v>58.4</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P35" s="1">
         <v>50.3</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="Q35" s="1">
         <v>50.4</v>
       </c>
-      <c r="R29" s="1">
+      <c r="R35" s="1">
         <v>42.8</v>
       </c>
-      <c r="S29" s="1">
+      <c r="S35" s="1">
         <v>65.2</v>
       </c>
-      <c r="T29" s="1">
+      <c r="T35" s="1">
         <v>41.6</v>
       </c>
-      <c r="U29" s="1">
+      <c r="U35" s="1">
         <v>54.9</v>
       </c>
-      <c r="V29" s="1">
+      <c r="V35" s="1">
         <v>87.3</v>
       </c>
-      <c r="W29" s="1">
+      <c r="W35" s="1">
         <v>70.599999999999994</v>
       </c>
-      <c r="X29" s="1">
+      <c r="X35" s="1">
         <v>82.2</v>
       </c>
-      <c r="Y29" s="1">
+      <c r="Y35" s="1">
         <v>49</v>
       </c>
-      <c r="Z29" s="1">
+      <c r="Z35" s="1">
         <v>46.8</v>
       </c>
     </row>
-    <row r="30" spans="1:26">
-      <c r="A30">
+    <row r="36" spans="1:28">
+      <c r="A36">
+        <v>1989</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="AB36">
+        <v>73.599999999999994</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28">
+      <c r="A37">
         <v>1990</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B37" s="1">
         <v>87.3</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C37" s="1">
         <v>47.6</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D37" s="1">
         <v>57.5</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E37" s="1">
         <v>78.400000000000006</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F37" s="1">
         <v>84.4</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G37" s="1">
         <v>29.5</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H37" s="1">
         <v>35</v>
       </c>
-      <c r="I30" s="1">
+      <c r="I37" s="1">
         <v>33.200000000000003</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J37" s="1">
         <v>47.5</v>
       </c>
-      <c r="K30" s="1">
+      <c r="K37" s="1">
         <v>56.1</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L37" s="1">
         <v>71</v>
       </c>
-      <c r="M30" s="1">
+      <c r="M37" s="1">
         <v>46.8</v>
       </c>
-      <c r="N30" s="1">
+      <c r="N37" s="1">
         <v>73.599999999999994</v>
       </c>
-      <c r="O30" s="1">
+      <c r="O37" s="1">
         <v>65.599999999999994</v>
       </c>
-      <c r="P30" s="1">
+      <c r="P37" s="1">
         <v>54.4</v>
       </c>
-      <c r="Q30" s="1">
+      <c r="Q37" s="1">
         <v>53.7</v>
       </c>
-      <c r="R30" s="1">
+      <c r="R37" s="1">
         <v>50.3</v>
       </c>
-      <c r="S30" s="1">
+      <c r="S37" s="1">
         <v>70.099999999999994</v>
       </c>
-      <c r="T30" s="1">
+      <c r="T37" s="1">
         <v>50.4</v>
       </c>
-      <c r="U30" s="1">
+      <c r="U37" s="1">
         <v>65.400000000000006</v>
       </c>
-      <c r="V30" s="1">
+      <c r="V37" s="1">
         <v>90.8</v>
       </c>
-      <c r="W30" s="1">
+      <c r="W37" s="1">
         <v>74.400000000000006</v>
       </c>
-      <c r="X30" s="1">
+      <c r="X37" s="1">
         <v>83.5</v>
       </c>
-      <c r="Y30" s="1">
+      <c r="Y37" s="1">
         <v>55.1</v>
       </c>
-      <c r="Z30" s="1">
+      <c r="Z37" s="1">
         <v>51.5</v>
       </c>
     </row>
-    <row r="31" spans="1:26">
-      <c r="A31">
+    <row r="38" spans="1:28">
+      <c r="A38">
         <v>2000</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B38" s="1">
         <v>90.5</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C38" s="1">
         <v>47.9</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D38" s="1">
         <v>62.4</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E38" s="1">
         <v>81.2</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F38" s="1">
         <v>86.9</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G38" s="1">
         <v>35.6</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H38" s="1">
         <v>46.1</v>
       </c>
-      <c r="I31" s="1">
+      <c r="I38" s="1">
         <v>36.200000000000003</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J38" s="1">
         <v>45.5</v>
       </c>
-      <c r="K31" s="1">
+      <c r="K38" s="1">
         <v>58.2</v>
       </c>
-      <c r="L31" s="1">
+      <c r="L38" s="1">
         <v>74.900000000000006</v>
       </c>
-      <c r="M31" s="1">
+      <c r="M38" s="1">
         <v>59</v>
       </c>
-      <c r="N31" s="1">
+      <c r="N38" s="1">
         <v>75.2</v>
       </c>
-      <c r="O31" s="1">
+      <c r="O38" s="1">
         <v>69.8</v>
       </c>
-      <c r="P31" s="1">
+      <c r="P38" s="1">
         <v>56.1</v>
       </c>
-      <c r="Q31" s="1">
+      <c r="Q38" s="1">
         <v>65.599999999999994</v>
       </c>
-      <c r="R31" s="1">
+      <c r="R38" s="1">
         <v>58.7</v>
       </c>
-      <c r="S31" s="1">
+      <c r="S38" s="1">
         <v>72.8</v>
       </c>
-      <c r="T31" s="1">
+      <c r="T38" s="1">
         <v>58.4</v>
       </c>
-      <c r="U31" s="1">
+      <c r="U38" s="1">
         <v>74.099999999999994</v>
       </c>
-      <c r="V31" s="1">
+      <c r="V38" s="1">
         <v>91.9</v>
       </c>
-      <c r="W31" s="1">
+      <c r="W38" s="1">
         <v>75</v>
       </c>
-      <c r="X31" s="1">
+      <c r="X38" s="1">
         <v>86.6</v>
       </c>
-      <c r="Y31" s="1">
+      <c r="Y38" s="1">
         <v>61.4</v>
       </c>
-      <c r="Z31" s="1">
+      <c r="Z38" s="1">
         <v>52.1</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="15">
-      <c r="A35" s="11" t="s">
+    <row r="42" spans="1:28" ht="15">
+      <c r="A42" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="15">
-      <c r="A37" s="16" t="s">
+    <row r="44" spans="1:28" ht="15">
+      <c r="A44" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B44" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C44" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D44" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="16" t="s">
+      <c r="E44" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F37" s="16" t="s">
+      <c r="F44" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="G37" s="16" t="s">
+      <c r="G44" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H37" s="16" t="s">
+      <c r="H44" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="I37" s="16" t="s">
+      <c r="I44" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="J37" s="16" t="s">
+      <c r="J44" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="K37" s="16" t="s">
+      <c r="K44" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="L37" s="16" t="s">
+      <c r="L44" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="M37" s="16" t="s">
+      <c r="M44" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="N37" s="16" t="s">
+      <c r="N44" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="O37" s="16" t="s">
+      <c r="O44" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="P37" s="16" t="s">
+      <c r="P44" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="Q37" s="16" t="s">
+      <c r="Q44" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="R37" s="16" t="s">
+      <c r="R44" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="S37" s="16" t="s">
+      <c r="S44" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="T37" s="16" t="s">
+      <c r="T44" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="U37" s="16" t="s">
+      <c r="U44" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="V37" s="16" t="s">
+      <c r="V44" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="W37" s="16" t="s">
+      <c r="W44" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="X37" s="16" t="s">
+      <c r="X44" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="Y37" s="16" t="s">
+      <c r="Y44" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="Z37" s="16" t="s">
+      <c r="Z44" s="16" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="38" spans="1:26">
-      <c r="A38">
+      <c r="AA44" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB44" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" ht="15">
+      <c r="A45" s="31">
+        <v>1926</v>
+      </c>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="16"/>
+      <c r="Q45" s="16"/>
+      <c r="R45" s="16"/>
+      <c r="S45" s="16"/>
+      <c r="T45" s="16"/>
+      <c r="U45" s="16"/>
+      <c r="V45" s="16"/>
+      <c r="W45" s="16"/>
+      <c r="X45" s="16"/>
+      <c r="Y45" s="16"/>
+      <c r="Z45" s="16"/>
+      <c r="AA45" s="1">
+        <v>36</v>
+      </c>
+      <c r="AB45" s="1">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28">
+      <c r="A46">
         <v>1950</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B46" s="1">
         <v>64.3</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C46" s="1">
         <v>56.5</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D46" s="1">
         <v>25.6</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E46" s="1">
         <v>30.1</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F46" s="1">
         <v>51.8</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G46" s="1">
         <v>9.6999999999999993</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H46" s="1">
         <v>26.8</v>
       </c>
-      <c r="I38" s="1">
+      <c r="I46" s="1">
         <v>28.1</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J46" s="1">
         <v>17.2</v>
       </c>
-      <c r="K38" s="1">
+      <c r="K46" s="1">
         <v>21.6</v>
       </c>
-      <c r="L38" s="1">
+      <c r="L46" s="1">
         <v>33.700000000000003</v>
       </c>
-      <c r="M38" s="1">
+      <c r="M46" s="1">
         <v>29.9</v>
       </c>
-      <c r="N38" s="1">
+      <c r="N46" s="1">
         <v>51.4</v>
       </c>
-      <c r="O38" s="1">
+      <c r="O46" s="1">
         <v>42</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P46" s="1">
         <v>28</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="Q46" s="1">
         <v>35.5</v>
       </c>
-      <c r="R38" s="1">
+      <c r="R46" s="1">
         <v>31.3</v>
       </c>
-      <c r="S38" s="1">
+      <c r="S46" s="1">
         <v>26.9</v>
       </c>
-      <c r="T38" s="1">
+      <c r="T46" s="1">
         <v>27.9</v>
       </c>
-      <c r="U38" s="1">
+      <c r="U46" s="1">
         <v>47</v>
       </c>
-      <c r="V38" s="1">
+      <c r="V46" s="1">
         <v>78.3</v>
       </c>
-      <c r="W38" s="1">
+      <c r="W46" s="1">
         <v>52</v>
       </c>
-      <c r="X38" s="1">
+      <c r="X46" s="1">
         <v>58.8</v>
       </c>
-      <c r="Y38" s="1">
+      <c r="Y46" s="1">
         <v>28.2</v>
       </c>
-      <c r="Z38" s="1">
+      <c r="Z46" s="1">
         <v>26.7</v>
       </c>
     </row>
-    <row r="39" spans="1:26">
-      <c r="A39">
+    <row r="47" spans="1:28">
+      <c r="A47">
+        <v>1959</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="1"/>
+      <c r="W47" s="1"/>
+      <c r="X47" s="1"/>
+      <c r="Y47" s="1"/>
+      <c r="Z47" s="1"/>
+      <c r="AA47" s="1">
+        <v>57.2</v>
+      </c>
+      <c r="AB47" s="1">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28">
+      <c r="A48">
         <v>1960</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B48" s="1">
         <v>75</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C48" s="1">
         <v>53.8</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D48" s="1">
         <v>39.299999999999997</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E48" s="1">
         <v>38.1</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F48" s="1">
         <v>64.900000000000006</v>
       </c>
-      <c r="G39" s="1">
+      <c r="G48" s="1">
         <v>15.6</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H48" s="1">
         <v>31.5</v>
       </c>
-      <c r="I39" s="1">
+      <c r="I48" s="1">
         <v>29</v>
       </c>
-      <c r="J39" s="1">
+      <c r="J48" s="1">
         <v>22</v>
       </c>
-      <c r="K39" s="1">
+      <c r="K48" s="1">
         <v>29.1</v>
       </c>
-      <c r="L39" s="1">
+      <c r="L48" s="1">
         <v>50.3</v>
       </c>
-      <c r="M39" s="1">
+      <c r="M48" s="1">
         <v>32.200000000000003</v>
       </c>
-      <c r="N39" s="1">
+      <c r="N48" s="1">
         <v>54.9</v>
       </c>
-      <c r="O39" s="1">
+      <c r="O48" s="1">
         <v>49.6</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P48" s="1">
         <v>35.6</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="Q48" s="1">
         <v>41.5</v>
       </c>
-      <c r="R39" s="1">
+      <c r="R48" s="1">
         <v>35.1</v>
       </c>
-      <c r="S39" s="1">
+      <c r="S48" s="1">
         <v>40.6</v>
       </c>
-      <c r="T39" s="1">
+      <c r="T48" s="1">
         <v>31.8</v>
       </c>
-      <c r="U39" s="1">
+      <c r="U48" s="1">
         <v>47.2</v>
       </c>
-      <c r="V39" s="1">
+      <c r="V48" s="1">
         <v>78.3</v>
       </c>
-      <c r="W39" s="1">
+      <c r="W48" s="1">
         <v>63.6</v>
       </c>
-      <c r="X39" s="1">
+      <c r="X48" s="1">
         <v>64.7</v>
       </c>
-      <c r="Y39" s="1">
+      <c r="Y48" s="1">
         <v>36</v>
       </c>
-      <c r="Z39" s="1">
+      <c r="Z48" s="1">
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:26">
-      <c r="A40">
+    <row r="49" spans="1:32">
+      <c r="A49">
         <v>1970</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B49" s="1">
         <v>79.2</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C49" s="1">
         <v>51.2</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D49" s="1">
         <v>43.5</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E49" s="1">
         <v>51.1</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F49" s="1">
         <v>74.599999999999994</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G49" s="1">
         <v>18.600000000000001</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H49" s="1">
         <v>33.700000000000003</v>
       </c>
-      <c r="I40" s="1">
+      <c r="I49" s="1">
         <v>29.5</v>
       </c>
-      <c r="J40" s="1">
+      <c r="J49" s="1">
         <v>32.299999999999997</v>
       </c>
-      <c r="K40" s="1">
+      <c r="K49" s="1">
         <v>39</v>
       </c>
-      <c r="L40" s="1">
+      <c r="L49" s="1">
         <v>57.3</v>
       </c>
-      <c r="M40" s="1">
+      <c r="M49" s="1">
         <v>39.4</v>
       </c>
-      <c r="N40" s="1">
+      <c r="N49" s="1">
         <v>58.3</v>
       </c>
-      <c r="O40" s="1">
+      <c r="O49" s="1">
         <v>58</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P49" s="1">
         <v>46.2</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="Q49" s="1">
         <v>47.3</v>
       </c>
-      <c r="R40" s="1">
+      <c r="R49" s="1">
         <v>36.5</v>
       </c>
-      <c r="S40" s="1">
+      <c r="S49" s="1">
         <v>52.4</v>
       </c>
-      <c r="T40" s="1">
+      <c r="T49" s="1">
         <v>34.6</v>
       </c>
-      <c r="U40" s="1">
+      <c r="U49" s="1">
         <v>46</v>
       </c>
-      <c r="V40" s="1">
+      <c r="V49" s="1">
         <v>81.599999999999994</v>
       </c>
-      <c r="W40" s="1">
+      <c r="W49" s="1">
         <v>67.3</v>
       </c>
-      <c r="X40" s="1">
+      <c r="X49" s="1">
         <v>71.8</v>
       </c>
-      <c r="Y40" s="1">
+      <c r="Y49" s="1">
         <v>42.1</v>
       </c>
-      <c r="Z40" s="1">
+      <c r="Z49" s="1">
         <v>41.5</v>
       </c>
-    </row>
-    <row r="41" spans="1:26">
-      <c r="A41">
+      <c r="AA49" s="1">
+        <v>65.7</v>
+      </c>
+      <c r="AB49" s="1">
+        <v>69.7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:32">
+      <c r="A50">
         <v>1980</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B50" s="1">
         <v>83.5</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C50" s="1">
         <v>49.3</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D50" s="1">
         <v>50.5</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E50" s="1">
         <v>64.900000000000006</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F50" s="1">
         <v>81.900000000000006</v>
       </c>
-      <c r="G41" s="1">
+      <c r="G50" s="1">
         <v>23.1</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H50" s="1">
         <v>35.9</v>
       </c>
-      <c r="I41" s="1">
+      <c r="I50" s="1">
         <v>30.6</v>
       </c>
-      <c r="J41" s="1">
+      <c r="J50" s="1">
         <v>39.700000000000003</v>
       </c>
-      <c r="K41" s="1">
+      <c r="K50" s="1">
         <v>51.4</v>
       </c>
-      <c r="L41" s="1">
+      <c r="L50" s="1">
         <v>65.8</v>
       </c>
-      <c r="M41" s="1">
+      <c r="M50" s="1">
         <v>43.4</v>
       </c>
-      <c r="N41" s="1">
+      <c r="N50" s="1">
         <v>66.099999999999994</v>
       </c>
-      <c r="O41" s="1">
+      <c r="O50" s="1">
         <v>65.3</v>
       </c>
-      <c r="P41" s="1">
+      <c r="P50" s="1">
         <v>50.3</v>
       </c>
-      <c r="Q41" s="1">
+      <c r="Q50" s="1">
         <v>50</v>
       </c>
-      <c r="R41" s="1">
+      <c r="R50" s="1">
         <v>42.9</v>
       </c>
-      <c r="S41" s="1">
+      <c r="S50" s="1">
         <v>59.2</v>
       </c>
-      <c r="T41" s="1">
+      <c r="T50" s="1">
         <v>41.6</v>
       </c>
-      <c r="U41" s="1">
+      <c r="U50" s="1">
         <v>54.9</v>
       </c>
-      <c r="V41" s="1">
+      <c r="V50" s="1">
         <v>84.4</v>
       </c>
-      <c r="W41" s="1">
+      <c r="W50" s="1">
         <v>70.599999999999994</v>
       </c>
-      <c r="X41" s="1">
+      <c r="X50" s="1">
         <v>78.599999999999994</v>
       </c>
-      <c r="Y41" s="1">
+      <c r="Y50" s="1">
         <v>51.1</v>
       </c>
-      <c r="Z41" s="1">
+      <c r="Z50" s="1">
         <v>46.8</v>
       </c>
     </row>
-    <row r="42" spans="1:26">
-      <c r="A42">
+    <row r="51" spans="1:32">
+      <c r="A51">
         <v>1990</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B51" s="1">
         <v>87.2</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C51" s="1">
         <v>47.6</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D51" s="1">
         <v>57.5</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E51" s="1">
         <v>73.099999999999994</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F51" s="1">
         <v>85.7</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G51" s="1">
         <v>23.1</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H51" s="1">
         <v>38.1</v>
       </c>
-      <c r="I42" s="1">
+      <c r="I51" s="1">
         <v>33.200000000000003</v>
       </c>
-      <c r="J42" s="1">
+      <c r="J51" s="1">
         <v>39.4</v>
       </c>
-      <c r="K42" s="1">
+      <c r="K51" s="1">
         <v>55.9</v>
       </c>
-      <c r="L42" s="1">
+      <c r="L51" s="1">
         <v>70</v>
       </c>
-      <c r="M42" s="1">
+      <c r="M51" s="1">
         <v>58.8</v>
       </c>
-      <c r="N42" s="1">
+      <c r="N51" s="1">
         <v>66.099999999999994</v>
       </c>
-      <c r="O42" s="1">
+      <c r="O51" s="1">
         <v>71.400000000000006</v>
       </c>
-      <c r="P42" s="1">
+      <c r="P51" s="1">
         <v>53.4</v>
       </c>
-      <c r="Q42" s="1">
+      <c r="Q51" s="1">
         <v>53.5</v>
       </c>
-      <c r="R42" s="1">
+      <c r="R51" s="1">
         <v>48.5</v>
       </c>
-      <c r="S42" s="1">
+      <c r="S51" s="1">
         <v>66</v>
       </c>
-      <c r="T42" s="1">
+      <c r="T51" s="1">
         <v>47.6</v>
       </c>
-      <c r="U42" s="1">
+      <c r="U51" s="1">
         <v>65.400000000000006</v>
       </c>
-      <c r="V42" s="1">
+      <c r="V51" s="1">
         <v>84.7</v>
       </c>
-      <c r="W42" s="1">
+      <c r="W51" s="1">
         <v>74.400000000000006</v>
       </c>
-      <c r="X42" s="1">
+      <c r="X51" s="1">
         <v>83.9</v>
       </c>
-      <c r="Y42" s="1">
+      <c r="Y51" s="1">
         <v>56.3</v>
       </c>
-      <c r="Z42" s="1">
+      <c r="Z51" s="1">
         <v>51.5</v>
       </c>
     </row>
-    <row r="43" spans="1:26">
-      <c r="A43">
+    <row r="52" spans="1:32">
+      <c r="A52">
         <v>2000</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B52" s="1">
         <v>89.1</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C52" s="1">
         <v>49.6</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D52" s="1">
         <v>62.7</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E52" s="1">
         <v>79.5</v>
       </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1">
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1">
         <v>47.7</v>
       </c>
-      <c r="I43" s="1">
+      <c r="I52" s="1">
         <v>36.200000000000003</v>
       </c>
-      <c r="J43" s="1">
+      <c r="J52" s="1">
         <v>43.9</v>
       </c>
-      <c r="K43" s="1">
+      <c r="K52" s="1">
         <v>63</v>
       </c>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1">
+      <c r="L52" s="1"/>
+      <c r="M52" s="1">
         <v>54.2</v>
       </c>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1">
+      <c r="N52" s="1"/>
+      <c r="O52" s="1">
         <v>74.5</v>
       </c>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1">
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1">
         <v>61.6</v>
       </c>
-      <c r="R43" s="1">
+      <c r="R52" s="1">
         <v>54.2</v>
       </c>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1">
+      <c r="S52" s="1"/>
+      <c r="T52" s="1"/>
+      <c r="U52" s="1">
         <v>74.099999999999994</v>
       </c>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1">
+      <c r="V52" s="1"/>
+      <c r="W52" s="1">
         <v>75</v>
       </c>
-      <c r="X43" s="1">
+      <c r="X52" s="1">
         <v>86</v>
       </c>
-      <c r="Y43" s="1">
+      <c r="Y52" s="1">
         <v>61.6</v>
       </c>
-      <c r="Z43" s="1">
+      <c r="Z52" s="1">
         <v>52.1</v>
       </c>
     </row>
-    <row r="47" spans="1:26" ht="15">
-      <c r="A47" s="11" t="s">
+    <row r="56" spans="1:32" ht="15">
+      <c r="A56" s="11" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="1:31" ht="15">
-      <c r="A49" s="16" t="s">
+    <row r="58" spans="1:32" ht="15">
+      <c r="A58" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B58" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C58" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D58" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E49" s="16" t="s">
+      <c r="E58" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="F49" s="16" t="s">
+      <c r="F58" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G49" s="16" t="s">
+      <c r="G58" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="H49" s="16" t="s">
+      <c r="H58" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I49" s="16" t="s">
+      <c r="I58" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="J49" s="16" t="s">
+      <c r="J58" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="K49" s="16" t="s">
+      <c r="K58" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="L49" s="16" t="s">
+      <c r="L58" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="M49" s="16" t="s">
+      <c r="M58" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="N49" s="16" t="s">
+      <c r="N58" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="O49" s="16" t="s">
+      <c r="O58" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="P49" s="16" t="s">
+      <c r="P58" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="Q49" s="16" t="s">
+      <c r="Q58" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="R49" s="16" t="s">
+      <c r="R58" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="S49" s="16" t="s">
+      <c r="S58" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="T49" s="16" t="s">
+      <c r="T58" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="U49" s="16" t="s">
+      <c r="U58" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="V49" s="16" t="s">
+      <c r="V58" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="W49" s="16" t="s">
+      <c r="W58" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="X49" s="16" t="s">
+      <c r="X58" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="Y49" s="16" t="s">
+      <c r="Y58" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="Z49" s="16" t="s">
+      <c r="Z58" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="AA49" s="16" t="s">
+      <c r="AA58" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="AB49" s="16" t="s">
+      <c r="AB58" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="AC49" s="16" t="s">
+      <c r="AC58" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="AD49" s="16" t="s">
+      <c r="AD58" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AE49" s="16" t="s">
+      <c r="AE58" s="16" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="50" spans="1:31">
-      <c r="A50" s="12">
+      <c r="AF58" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:32">
+      <c r="A59" s="12">
         <v>1865</v>
       </c>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="12"/>
-      <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
-      <c r="L50" s="12"/>
-      <c r="M50" s="12"/>
-      <c r="N50" s="12"/>
-      <c r="O50" s="12"/>
-      <c r="P50" s="12"/>
-      <c r="Q50" s="12"/>
-      <c r="R50" s="12"/>
-      <c r="S50" s="12"/>
-      <c r="T50" s="12"/>
-      <c r="U50" s="12"/>
-      <c r="V50" s="12"/>
-      <c r="W50" s="12"/>
-      <c r="X50" s="12"/>
-      <c r="Y50" s="12"/>
-      <c r="Z50" s="12"/>
-      <c r="AA50" s="12"/>
-      <c r="AB50" s="13">
-        <v>15.973962510368438</v>
-      </c>
-      <c r="AC50" s="12"/>
-      <c r="AD50" s="12"/>
-      <c r="AE50" s="12"/>
-    </row>
-    <row r="51" spans="1:31">
-      <c r="A51" s="12">
-        <v>1869</v>
-      </c>
-      <c r="B51" s="13">
-        <v>24.82533867257391</v>
-      </c>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="12"/>
-      <c r="L51" s="12"/>
-      <c r="M51" s="12"/>
-      <c r="N51" s="12"/>
-      <c r="O51" s="12"/>
-      <c r="P51" s="12"/>
-      <c r="Q51" s="12"/>
-      <c r="R51" s="12"/>
-      <c r="S51" s="12"/>
-      <c r="T51" s="12"/>
-      <c r="U51" s="12"/>
-      <c r="V51" s="12"/>
-      <c r="W51" s="12"/>
-      <c r="X51" s="12"/>
-      <c r="Y51" s="12"/>
-      <c r="Z51" s="12"/>
-      <c r="AA51" s="12"/>
-      <c r="AB51" s="12"/>
-      <c r="AC51" s="12"/>
-      <c r="AD51" s="12"/>
-      <c r="AE51" s="12"/>
-    </row>
-    <row r="52" spans="1:31">
-      <c r="A52" s="12">
-        <v>1875</v>
-      </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="12"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="12"/>
-      <c r="M52" s="12"/>
-      <c r="N52" s="12"/>
-      <c r="O52" s="12"/>
-      <c r="P52" s="12"/>
-      <c r="Q52" s="12"/>
-      <c r="R52" s="12"/>
-      <c r="S52" s="12"/>
-      <c r="T52" s="12"/>
-      <c r="U52" s="12"/>
-      <c r="V52" s="12"/>
-      <c r="W52" s="12"/>
-      <c r="X52" s="12"/>
-      <c r="Y52" s="12"/>
-      <c r="Z52" s="12"/>
-      <c r="AA52" s="12"/>
-      <c r="AB52" s="13">
-        <v>17.277987023903513</v>
-      </c>
-      <c r="AC52" s="12"/>
-      <c r="AD52" s="12"/>
-      <c r="AE52" s="12"/>
-    </row>
-    <row r="53" spans="1:31">
-      <c r="A53" s="12">
-        <v>1876</v>
-      </c>
-      <c r="B53" s="13"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="12"/>
-      <c r="J53" s="12"/>
-      <c r="K53" s="12"/>
-      <c r="L53" s="12"/>
-      <c r="M53" s="12"/>
-      <c r="N53" s="12"/>
-      <c r="O53" s="12"/>
-      <c r="P53" s="12"/>
-      <c r="Q53" s="12"/>
-      <c r="R53" s="12"/>
-      <c r="S53" s="12"/>
-      <c r="T53" s="12"/>
-      <c r="U53" s="12"/>
-      <c r="V53" s="13">
-        <v>7.4535049753510974</v>
-      </c>
-      <c r="W53" s="12"/>
-      <c r="X53" s="12"/>
-      <c r="Y53" s="12"/>
-      <c r="Z53" s="12"/>
-      <c r="AA53" s="12"/>
-      <c r="AB53" s="13"/>
-      <c r="AC53" s="12"/>
-      <c r="AD53" s="12"/>
-      <c r="AE53" s="12"/>
-    </row>
-    <row r="54" spans="1:31">
-      <c r="A54" s="12">
-        <v>1885</v>
-      </c>
-      <c r="B54" s="13"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
-      <c r="M54" s="12"/>
-      <c r="N54" s="12"/>
-      <c r="O54" s="12"/>
-      <c r="P54" s="12"/>
-      <c r="Q54" s="12"/>
-      <c r="R54" s="12"/>
-      <c r="S54" s="12"/>
-      <c r="T54" s="12"/>
-      <c r="U54" s="12"/>
-      <c r="V54" s="12"/>
-      <c r="W54" s="12"/>
-      <c r="X54" s="12"/>
-      <c r="Y54" s="12"/>
-      <c r="Z54" s="12"/>
-      <c r="AA54" s="12"/>
-      <c r="AB54" s="13">
-        <v>19.212369940391472</v>
-      </c>
-      <c r="AC54" s="12"/>
-      <c r="AD54" s="12"/>
-      <c r="AE54" s="12"/>
-    </row>
-    <row r="55" spans="1:31">
-      <c r="A55" s="12">
-        <v>1895</v>
-      </c>
-      <c r="B55" s="13">
-        <v>31.833737851496533</v>
-      </c>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
-      <c r="K55" s="12"/>
-      <c r="L55" s="12"/>
-      <c r="M55" s="12"/>
-      <c r="N55" s="12"/>
-      <c r="O55" s="12"/>
-      <c r="P55" s="12"/>
-      <c r="Q55" s="12"/>
-      <c r="R55" s="12"/>
-      <c r="S55" s="12"/>
-      <c r="T55" s="12"/>
-      <c r="U55" s="12"/>
-      <c r="V55" s="12"/>
-      <c r="W55" s="12"/>
-      <c r="X55" s="12"/>
-      <c r="Y55" s="12"/>
-      <c r="Z55" s="12"/>
-      <c r="AA55" s="12"/>
-      <c r="AB55" s="13">
-        <v>24.121981380841554</v>
-      </c>
-      <c r="AC55" s="12"/>
-      <c r="AD55" s="12"/>
-      <c r="AE55" s="12"/>
-    </row>
-    <row r="56" spans="1:31">
-      <c r="A56" s="12">
-        <v>1900</v>
-      </c>
-      <c r="B56" s="13"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="13">
-        <v>8.5972647960386706</v>
-      </c>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="12"/>
-      <c r="M56" s="12"/>
-      <c r="N56" s="12"/>
-      <c r="O56" s="12"/>
-      <c r="P56" s="12"/>
-      <c r="Q56" s="12"/>
-      <c r="R56" s="1">
-        <v>21.466933269210756</v>
-      </c>
-      <c r="S56" s="12"/>
-      <c r="T56" s="12"/>
-      <c r="U56" s="12"/>
-      <c r="V56" s="12"/>
-      <c r="W56" s="12"/>
-      <c r="X56" s="12"/>
-      <c r="Y56" s="12"/>
-      <c r="Z56" s="12"/>
-      <c r="AA56" s="12"/>
-      <c r="AB56" s="13"/>
-      <c r="AC56" s="12"/>
-      <c r="AD56" s="12"/>
-      <c r="AE56" s="12"/>
-    </row>
-    <row r="57" spans="1:31">
-      <c r="A57" s="12">
-        <v>1907</v>
-      </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
-      <c r="K57" s="12"/>
-      <c r="L57" s="12"/>
-      <c r="M57" s="12"/>
-      <c r="N57" s="12"/>
-      <c r="O57" s="12"/>
-      <c r="P57" s="12"/>
-      <c r="Q57" s="12"/>
-      <c r="R57" s="12"/>
-      <c r="S57" s="12"/>
-      <c r="T57" s="12"/>
-      <c r="U57" s="12"/>
-      <c r="V57" s="12"/>
-      <c r="W57" s="12"/>
-      <c r="X57" s="12"/>
-      <c r="Y57" s="12"/>
-      <c r="Z57" s="12"/>
-      <c r="AA57" s="12"/>
-      <c r="AB57" s="13">
-        <v>27.698910521277391</v>
-      </c>
-      <c r="AC57" s="12"/>
-      <c r="AD57" s="12"/>
-      <c r="AE57" s="12"/>
-    </row>
-    <row r="58" spans="1:31">
-      <c r="A58" s="12">
-        <v>1910</v>
-      </c>
-      <c r="B58" s="13"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
-      <c r="K58" s="12"/>
-      <c r="L58" s="12"/>
-      <c r="M58" s="12"/>
-      <c r="N58" s="12"/>
-      <c r="O58" s="12"/>
-      <c r="P58" s="12"/>
-      <c r="Q58" s="12"/>
-      <c r="R58" s="12">
-        <v>24.7</v>
-      </c>
-      <c r="S58" s="12"/>
-      <c r="T58" s="12"/>
-      <c r="U58" s="12"/>
-      <c r="V58" s="12"/>
-      <c r="W58" s="12"/>
-      <c r="X58" s="12"/>
-      <c r="Y58" s="12"/>
-      <c r="Z58" s="12"/>
-      <c r="AA58" s="12"/>
-      <c r="AB58" s="13"/>
-      <c r="AC58" s="12"/>
-      <c r="AD58" s="12"/>
-      <c r="AE58" s="12"/>
-    </row>
-    <row r="59" spans="1:31">
-      <c r="A59" s="12">
-        <v>1914</v>
-      </c>
-      <c r="B59" s="13">
-        <v>38.26516565069636</v>
-      </c>
+      <c r="B59" s="12"/>
       <c r="C59" s="12"/>
       <c r="D59" s="12"/>
       <c r="E59" s="12"/>
@@ -3198,16 +3238,20 @@
       <c r="Y59" s="12"/>
       <c r="Z59" s="12"/>
       <c r="AA59" s="12"/>
-      <c r="AB59" s="12"/>
+      <c r="AB59" s="13">
+        <v>15.973962510368438</v>
+      </c>
       <c r="AC59" s="12"/>
       <c r="AD59" s="12"/>
       <c r="AE59" s="12"/>
     </row>
-    <row r="60" spans="1:31" ht="13.5" customHeight="1">
+    <row r="60" spans="1:32">
       <c r="A60" s="12">
-        <v>1919</v>
-      </c>
-      <c r="B60" s="12"/>
+        <v>1869</v>
+      </c>
+      <c r="B60" s="13">
+        <v>24.82533867257391</v>
+      </c>
       <c r="C60" s="12"/>
       <c r="D60" s="12"/>
       <c r="E60" s="12"/>
@@ -3222,9 +3266,7 @@
       <c r="N60" s="12"/>
       <c r="O60" s="12"/>
       <c r="P60" s="12"/>
-      <c r="Q60" s="13">
-        <v>27.859047616410361</v>
-      </c>
+      <c r="Q60" s="12"/>
       <c r="R60" s="12"/>
       <c r="S60" s="12"/>
       <c r="T60" s="12"/>
@@ -3240,478 +3282,436 @@
       <c r="AD60" s="12"/>
       <c r="AE60" s="12"/>
     </row>
-    <row r="61" spans="1:31">
-      <c r="A61" s="14">
+    <row r="61" spans="1:32">
+      <c r="A61" s="12">
+        <v>1875</v>
+      </c>
+      <c r="B61" s="13"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12"/>
+      <c r="J61" s="12"/>
+      <c r="K61" s="12"/>
+      <c r="L61" s="12"/>
+      <c r="M61" s="12"/>
+      <c r="N61" s="12"/>
+      <c r="O61" s="12"/>
+      <c r="P61" s="12"/>
+      <c r="Q61" s="12"/>
+      <c r="R61" s="12"/>
+      <c r="S61" s="12"/>
+      <c r="T61" s="12"/>
+      <c r="U61" s="12"/>
+      <c r="V61" s="12"/>
+      <c r="W61" s="12"/>
+      <c r="X61" s="12"/>
+      <c r="Y61" s="12"/>
+      <c r="Z61" s="12"/>
+      <c r="AA61" s="12"/>
+      <c r="AB61" s="13">
+        <v>17.277987023903513</v>
+      </c>
+      <c r="AC61" s="12"/>
+      <c r="AD61" s="12"/>
+      <c r="AE61" s="12"/>
+    </row>
+    <row r="62" spans="1:32">
+      <c r="A62" s="12">
+        <v>1876</v>
+      </c>
+      <c r="B62" s="13"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12"/>
+      <c r="L62" s="12"/>
+      <c r="M62" s="12"/>
+      <c r="N62" s="12"/>
+      <c r="O62" s="12"/>
+      <c r="P62" s="12"/>
+      <c r="Q62" s="12"/>
+      <c r="R62" s="12"/>
+      <c r="S62" s="12"/>
+      <c r="T62" s="12"/>
+      <c r="U62" s="12"/>
+      <c r="V62" s="13">
+        <v>7.4535049753510974</v>
+      </c>
+      <c r="W62" s="12"/>
+      <c r="X62" s="12"/>
+      <c r="Y62" s="12"/>
+      <c r="Z62" s="12"/>
+      <c r="AA62" s="12"/>
+      <c r="AB62" s="13"/>
+      <c r="AC62" s="12"/>
+      <c r="AD62" s="12"/>
+      <c r="AE62" s="12"/>
+    </row>
+    <row r="63" spans="1:32">
+      <c r="A63" s="12">
+        <v>1885</v>
+      </c>
+      <c r="B63" s="13"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12"/>
+      <c r="J63" s="12"/>
+      <c r="K63" s="12"/>
+      <c r="L63" s="12"/>
+      <c r="M63" s="12"/>
+      <c r="N63" s="12"/>
+      <c r="O63" s="12"/>
+      <c r="P63" s="12"/>
+      <c r="Q63" s="12"/>
+      <c r="R63" s="12"/>
+      <c r="S63" s="12"/>
+      <c r="T63" s="12"/>
+      <c r="U63" s="12"/>
+      <c r="V63" s="12"/>
+      <c r="W63" s="12"/>
+      <c r="X63" s="12"/>
+      <c r="Y63" s="12"/>
+      <c r="Z63" s="12"/>
+      <c r="AA63" s="12"/>
+      <c r="AB63" s="13">
+        <v>19.212369940391472</v>
+      </c>
+      <c r="AC63" s="12"/>
+      <c r="AD63" s="12"/>
+      <c r="AE63" s="12"/>
+    </row>
+    <row r="64" spans="1:32">
+      <c r="A64" s="12">
+        <v>1895</v>
+      </c>
+      <c r="B64" s="13">
+        <v>31.833737851496533</v>
+      </c>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+      <c r="I64" s="12"/>
+      <c r="J64" s="12"/>
+      <c r="K64" s="12"/>
+      <c r="L64" s="12"/>
+      <c r="M64" s="12"/>
+      <c r="N64" s="12"/>
+      <c r="O64" s="12"/>
+      <c r="P64" s="12"/>
+      <c r="Q64" s="12"/>
+      <c r="R64" s="12"/>
+      <c r="S64" s="12"/>
+      <c r="T64" s="12"/>
+      <c r="U64" s="12"/>
+      <c r="V64" s="12"/>
+      <c r="W64" s="12"/>
+      <c r="X64" s="12"/>
+      <c r="Y64" s="12"/>
+      <c r="Z64" s="12"/>
+      <c r="AA64" s="12"/>
+      <c r="AB64" s="13">
+        <v>24.121981380841554</v>
+      </c>
+      <c r="AC64" s="12"/>
+      <c r="AD64" s="12"/>
+      <c r="AE64" s="12"/>
+    </row>
+    <row r="65" spans="1:32">
+      <c r="A65" s="12">
+        <v>1900</v>
+      </c>
+      <c r="B65" s="13"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="13">
+        <v>8.5972647960386706</v>
+      </c>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
+      <c r="I65" s="12"/>
+      <c r="J65" s="12"/>
+      <c r="K65" s="12"/>
+      <c r="L65" s="12"/>
+      <c r="M65" s="12"/>
+      <c r="N65" s="12"/>
+      <c r="O65" s="12"/>
+      <c r="P65" s="12"/>
+      <c r="Q65" s="12"/>
+      <c r="R65" s="1">
+        <v>21.466933269210756</v>
+      </c>
+      <c r="S65" s="12"/>
+      <c r="T65" s="12"/>
+      <c r="U65" s="12"/>
+      <c r="V65" s="12"/>
+      <c r="W65" s="12"/>
+      <c r="X65" s="12"/>
+      <c r="Y65" s="12"/>
+      <c r="Z65" s="12"/>
+      <c r="AA65" s="12"/>
+      <c r="AB65" s="13"/>
+      <c r="AC65" s="12"/>
+      <c r="AD65" s="12"/>
+      <c r="AE65" s="12"/>
+    </row>
+    <row r="66" spans="1:32">
+      <c r="A66" s="12">
+        <v>1907</v>
+      </c>
+      <c r="B66" s="13"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="12"/>
+      <c r="L66" s="12"/>
+      <c r="M66" s="12"/>
+      <c r="N66" s="12"/>
+      <c r="O66" s="12"/>
+      <c r="P66" s="12"/>
+      <c r="Q66" s="12"/>
+      <c r="R66" s="12"/>
+      <c r="S66" s="12"/>
+      <c r="T66" s="12"/>
+      <c r="U66" s="12"/>
+      <c r="V66" s="12"/>
+      <c r="W66" s="12"/>
+      <c r="X66" s="12"/>
+      <c r="Y66" s="12"/>
+      <c r="Z66" s="12"/>
+      <c r="AA66" s="12"/>
+      <c r="AB66" s="13">
+        <v>27.698910521277391</v>
+      </c>
+      <c r="AC66" s="12"/>
+      <c r="AD66" s="12"/>
+      <c r="AE66" s="12"/>
+    </row>
+    <row r="67" spans="1:32">
+      <c r="A67" s="12">
+        <v>1910</v>
+      </c>
+      <c r="B67" s="13"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
+      <c r="I67" s="12"/>
+      <c r="J67" s="12"/>
+      <c r="K67" s="12"/>
+      <c r="L67" s="12"/>
+      <c r="M67" s="12"/>
+      <c r="N67" s="12"/>
+      <c r="O67" s="12"/>
+      <c r="P67" s="12"/>
+      <c r="Q67" s="12"/>
+      <c r="R67" s="12">
+        <v>24.7</v>
+      </c>
+      <c r="S67" s="12"/>
+      <c r="T67" s="12"/>
+      <c r="U67" s="12"/>
+      <c r="V67" s="12"/>
+      <c r="W67" s="12"/>
+      <c r="X67" s="12"/>
+      <c r="Y67" s="12"/>
+      <c r="Z67" s="12"/>
+      <c r="AA67" s="12"/>
+      <c r="AB67" s="13"/>
+      <c r="AC67" s="12"/>
+      <c r="AD67" s="12"/>
+      <c r="AE67" s="12"/>
+    </row>
+    <row r="68" spans="1:32">
+      <c r="A68" s="12">
+        <v>1913</v>
+      </c>
+      <c r="B68" s="13"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
+      <c r="I68" s="12"/>
+      <c r="J68" s="12"/>
+      <c r="K68" s="12"/>
+      <c r="L68" s="12"/>
+      <c r="M68" s="12"/>
+      <c r="N68" s="12"/>
+      <c r="O68" s="12"/>
+      <c r="P68" s="12"/>
+      <c r="Q68" s="12"/>
+      <c r="R68" s="12"/>
+      <c r="S68" s="12"/>
+      <c r="T68" s="12"/>
+      <c r="U68" s="12"/>
+      <c r="V68" s="12"/>
+      <c r="W68" s="12"/>
+      <c r="X68" s="12"/>
+      <c r="Y68" s="12"/>
+      <c r="Z68" s="12"/>
+      <c r="AA68" s="12"/>
+      <c r="AB68" s="13"/>
+      <c r="AC68" s="12"/>
+      <c r="AD68" s="12"/>
+      <c r="AE68" s="12"/>
+    </row>
+    <row r="69" spans="1:32">
+      <c r="A69" s="12">
+        <v>1914</v>
+      </c>
+      <c r="B69" s="13">
+        <v>38.26516565069636</v>
+      </c>
+      <c r="C69" s="12"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+      <c r="I69" s="12"/>
+      <c r="J69" s="12"/>
+      <c r="K69" s="12"/>
+      <c r="L69" s="12"/>
+      <c r="M69" s="12"/>
+      <c r="N69" s="12"/>
+      <c r="O69" s="12"/>
+      <c r="P69" s="12"/>
+      <c r="Q69" s="12"/>
+      <c r="R69" s="12"/>
+      <c r="S69" s="12"/>
+      <c r="T69" s="12"/>
+      <c r="U69" s="12"/>
+      <c r="V69" s="12"/>
+      <c r="W69" s="12"/>
+      <c r="X69" s="12"/>
+      <c r="Y69" s="12"/>
+      <c r="Z69" s="12"/>
+      <c r="AA69" s="12"/>
+      <c r="AB69" s="12"/>
+      <c r="AC69" s="12"/>
+      <c r="AD69" s="12"/>
+      <c r="AE69" s="12"/>
+    </row>
+    <row r="70" spans="1:32" ht="13.5" customHeight="1">
+      <c r="A70" s="12">
+        <v>1919</v>
+      </c>
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
+      <c r="I70" s="12"/>
+      <c r="J70" s="12"/>
+      <c r="K70" s="12"/>
+      <c r="L70" s="12"/>
+      <c r="M70" s="12"/>
+      <c r="N70" s="12"/>
+      <c r="O70" s="12"/>
+      <c r="P70" s="12"/>
+      <c r="Q70" s="13">
+        <v>27.859047616410361</v>
+      </c>
+      <c r="R70" s="12"/>
+      <c r="S70" s="12"/>
+      <c r="T70" s="12"/>
+      <c r="U70" s="12"/>
+      <c r="V70" s="12"/>
+      <c r="W70" s="12"/>
+      <c r="X70" s="12"/>
+      <c r="Y70" s="12"/>
+      <c r="Z70" s="12"/>
+      <c r="AA70" s="12"/>
+      <c r="AB70" s="12"/>
+      <c r="AC70" s="12"/>
+      <c r="AD70" s="12"/>
+      <c r="AE70" s="12"/>
+    </row>
+    <row r="71" spans="1:32">
+      <c r="A71" s="14">
         <v>1920</v>
-      </c>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14">
-        <v>13</v>
-      </c>
-      <c r="H61" s="14">
-        <v>11</v>
-      </c>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="14"/>
-      <c r="N61" s="15">
-        <v>5.3757551709299012</v>
-      </c>
-      <c r="O61" s="14">
-        <v>7</v>
-      </c>
-      <c r="P61" s="14"/>
-      <c r="Q61" s="14"/>
-      <c r="R61" s="14"/>
-      <c r="S61" s="15">
-        <v>4.3936290090937495</v>
-      </c>
-      <c r="T61" s="14"/>
-      <c r="U61" s="14"/>
-      <c r="V61" s="14">
-        <v>6</v>
-      </c>
-      <c r="W61" s="14"/>
-      <c r="X61" s="14"/>
-      <c r="Y61" s="14"/>
-      <c r="Z61" s="14"/>
-      <c r="AA61" s="14">
-        <v>30</v>
-      </c>
-      <c r="AB61" s="15">
-        <v>27.96247421409107</v>
-      </c>
-      <c r="AC61" s="14">
-        <v>10</v>
-      </c>
-      <c r="AD61" s="14"/>
-      <c r="AE61" s="14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:31">
-      <c r="A62" s="14">
-        <v>1921</v>
-      </c>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="14"/>
-      <c r="N62" s="15"/>
-      <c r="O62" s="14"/>
-      <c r="P62" s="14"/>
-      <c r="Q62" s="14"/>
-      <c r="R62" s="1">
-        <v>30.616554018692632</v>
-      </c>
-      <c r="S62" s="15"/>
-      <c r="T62" s="14"/>
-      <c r="U62" s="14"/>
-      <c r="V62" s="14"/>
-      <c r="W62" s="14"/>
-      <c r="X62" s="14"/>
-      <c r="Y62" s="14"/>
-      <c r="Z62" s="14"/>
-      <c r="AA62" s="14"/>
-      <c r="AB62" s="15"/>
-      <c r="AC62" s="14"/>
-      <c r="AD62" s="14">
-        <v>10.3</v>
-      </c>
-      <c r="AE62" s="14"/>
-    </row>
-    <row r="63" spans="1:31">
-      <c r="A63" s="14">
-        <v>1927</v>
-      </c>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="14"/>
-      <c r="J63" s="14"/>
-      <c r="K63" s="14"/>
-      <c r="L63" s="14"/>
-      <c r="M63" s="14"/>
-      <c r="N63" s="14"/>
-      <c r="O63" s="14"/>
-      <c r="P63" s="15">
-        <v>18.87623959756025</v>
-      </c>
-      <c r="Q63" s="14"/>
-      <c r="R63" s="14"/>
-      <c r="S63" s="14"/>
-      <c r="T63" s="14"/>
-      <c r="U63" s="14"/>
-      <c r="V63" s="14"/>
-      <c r="W63" s="14"/>
-      <c r="X63" s="14"/>
-      <c r="Y63" s="14"/>
-      <c r="Z63" s="14"/>
-      <c r="AA63" s="14"/>
-      <c r="AB63" s="14"/>
-      <c r="AC63" s="14"/>
-      <c r="AD63" s="14"/>
-      <c r="AE63" s="14"/>
-    </row>
-    <row r="64" spans="1:31">
-      <c r="A64" s="14">
-        <v>1930</v>
-      </c>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14">
-        <v>14</v>
-      </c>
-      <c r="H64" s="14">
-        <v>13</v>
-      </c>
-      <c r="I64" s="14"/>
-      <c r="J64" s="14"/>
-      <c r="K64" s="14"/>
-      <c r="L64" s="14"/>
-      <c r="M64" s="14"/>
-      <c r="N64" s="14"/>
-      <c r="O64" s="14">
-        <v>10</v>
-      </c>
-      <c r="P64" s="14"/>
-      <c r="Q64" s="14"/>
-      <c r="R64" s="14">
-        <v>28.5</v>
-      </c>
-      <c r="S64" s="14"/>
-      <c r="T64" s="15">
-        <v>24.338525446181379</v>
-      </c>
-      <c r="U64" s="14"/>
-      <c r="V64" s="14">
-        <v>10</v>
-      </c>
-      <c r="W64" s="15">
-        <v>10.216396011882644</v>
-      </c>
-      <c r="X64" s="14"/>
-      <c r="Y64" s="14"/>
-      <c r="Z64" s="14"/>
-      <c r="AA64" s="14">
-        <v>35</v>
-      </c>
-      <c r="AB64" s="15">
-        <v>32.849564250969983</v>
-      </c>
-      <c r="AC64" s="14">
-        <v>13</v>
-      </c>
-      <c r="AD64" s="14"/>
-      <c r="AE64" s="14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="1:31">
-      <c r="A65" s="14">
-        <v>1931</v>
-      </c>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="14"/>
-      <c r="K65" s="14"/>
-      <c r="L65" s="14"/>
-      <c r="M65" s="14"/>
-      <c r="N65" s="14"/>
-      <c r="O65" s="14"/>
-      <c r="P65" s="14"/>
-      <c r="Q65" s="15">
-        <v>29.864393399462539</v>
-      </c>
-      <c r="R65" s="14"/>
-      <c r="S65" s="14"/>
-      <c r="T65" s="14"/>
-      <c r="U65" s="14"/>
-      <c r="V65" s="14"/>
-      <c r="W65" s="14"/>
-      <c r="X65" s="14"/>
-      <c r="Y65" s="14"/>
-      <c r="Z65" s="14"/>
-      <c r="AA65" s="14"/>
-      <c r="AB65" s="14"/>
-      <c r="AC65" s="14"/>
-      <c r="AD65" s="14"/>
-      <c r="AE65" s="14"/>
-    </row>
-    <row r="66" spans="1:31">
-      <c r="A66" s="14">
-        <v>1935</v>
-      </c>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="14"/>
-      <c r="J66" s="14"/>
-      <c r="K66" s="14"/>
-      <c r="L66" s="14"/>
-      <c r="M66" s="14"/>
-      <c r="N66" s="15">
-        <v>7.1153704466016006</v>
-      </c>
-      <c r="O66" s="14"/>
-      <c r="P66" s="14"/>
-      <c r="Q66" s="14"/>
-      <c r="R66" s="14"/>
-      <c r="S66" s="14"/>
-      <c r="T66" s="14"/>
-      <c r="U66" s="14"/>
-      <c r="V66" s="14"/>
-      <c r="W66" s="14"/>
-      <c r="X66" s="14"/>
-      <c r="Y66" s="14"/>
-      <c r="Z66" s="14"/>
-      <c r="AA66" s="14"/>
-      <c r="AB66" s="14"/>
-      <c r="AC66" s="14"/>
-      <c r="AD66" s="14"/>
-      <c r="AE66" s="14"/>
-    </row>
-    <row r="67" spans="1:31">
-      <c r="A67" s="14">
-        <v>1936</v>
-      </c>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="15">
-        <v>19.091253072290105</v>
-      </c>
-      <c r="I67" s="14"/>
-      <c r="J67" s="14"/>
-      <c r="K67" s="14"/>
-      <c r="L67" s="14"/>
-      <c r="M67" s="14"/>
-      <c r="N67" s="14"/>
-      <c r="O67" s="14"/>
-      <c r="P67" s="14"/>
-      <c r="Q67" s="14"/>
-      <c r="R67" s="14"/>
-      <c r="S67" s="14"/>
-      <c r="T67" s="14"/>
-      <c r="U67" s="14"/>
-      <c r="V67" s="14"/>
-      <c r="W67" s="14"/>
-      <c r="X67" s="14"/>
-      <c r="Y67" s="14"/>
-      <c r="Z67" s="14"/>
-      <c r="AA67" s="14"/>
-      <c r="AB67" s="14"/>
-      <c r="AC67" s="14"/>
-      <c r="AD67" s="14"/>
-      <c r="AE67" s="14"/>
-    </row>
-    <row r="68" spans="1:31">
-      <c r="A68" s="14">
-        <v>1937</v>
-      </c>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="15"/>
-      <c r="I68" s="14"/>
-      <c r="J68" s="14"/>
-      <c r="K68" s="14"/>
-      <c r="L68" s="14"/>
-      <c r="M68" s="14"/>
-      <c r="N68" s="14"/>
-      <c r="O68" s="14"/>
-      <c r="P68" s="14"/>
-      <c r="Q68" s="14"/>
-      <c r="R68" s="14"/>
-      <c r="S68" s="14"/>
-      <c r="T68" s="14"/>
-      <c r="U68" s="15">
-        <v>11.197210631902117</v>
-      </c>
-      <c r="V68" s="14"/>
-      <c r="W68" s="14"/>
-      <c r="X68" s="14"/>
-      <c r="Y68" s="14"/>
-      <c r="Z68" s="14"/>
-      <c r="AA68" s="14"/>
-      <c r="AB68" s="14"/>
-      <c r="AC68" s="14"/>
-      <c r="AD68" s="14"/>
-      <c r="AE68" s="14"/>
-    </row>
-    <row r="69" spans="1:31">
-      <c r="A69" s="14">
-        <v>1938</v>
-      </c>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="14"/>
-      <c r="J69" s="14"/>
-      <c r="K69" s="14"/>
-      <c r="L69" s="14"/>
-      <c r="M69" s="14"/>
-      <c r="N69" s="14"/>
-      <c r="O69" s="15">
-        <v>14.737441012312832</v>
-      </c>
-      <c r="P69" s="14"/>
-      <c r="Q69" s="14"/>
-      <c r="R69" s="14"/>
-      <c r="S69" s="14"/>
-      <c r="T69" s="14"/>
-      <c r="U69" s="14"/>
-      <c r="V69" s="14"/>
-      <c r="W69" s="14"/>
-      <c r="X69" s="14"/>
-      <c r="Y69" s="14"/>
-      <c r="Z69" s="14"/>
-      <c r="AA69" s="14"/>
-      <c r="AB69" s="14"/>
-      <c r="AC69" s="14"/>
-      <c r="AD69" s="14"/>
-      <c r="AE69" s="14"/>
-    </row>
-    <row r="70" spans="1:31">
-      <c r="A70" s="14">
-        <v>1940</v>
-      </c>
-      <c r="B70" s="14">
-        <v>41</v>
-      </c>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="15">
-        <v>14.979631374994044</v>
-      </c>
-      <c r="H70" s="14"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="14"/>
-      <c r="K70" s="15">
-        <v>5.7838535408498206</v>
-      </c>
-      <c r="L70" s="14">
-        <v>6.1</v>
-      </c>
-      <c r="M70" s="14"/>
-      <c r="N70" s="14"/>
-      <c r="O70" s="14"/>
-      <c r="P70" s="14"/>
-      <c r="Q70" s="14">
-        <v>30</v>
-      </c>
-      <c r="R70" s="14"/>
-      <c r="S70" s="15">
-        <v>7.5335821390138475</v>
-      </c>
-      <c r="T70" s="15">
-        <v>27.583662937332001</v>
-      </c>
-      <c r="U70" s="14"/>
-      <c r="V70" s="15">
-        <v>14.12009761005495</v>
-      </c>
-      <c r="W70" s="14"/>
-      <c r="X70" s="14"/>
-      <c r="Y70" s="14"/>
-      <c r="Z70" s="14"/>
-      <c r="AA70" s="14">
-        <v>38</v>
-      </c>
-      <c r="AB70" s="15">
-        <v>36.418648287591672</v>
-      </c>
-      <c r="AC70" s="14">
-        <v>16</v>
-      </c>
-      <c r="AD70" s="14"/>
-      <c r="AE70" s="14">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="71" spans="1:31">
-      <c r="A71" s="14">
-        <v>1941</v>
       </c>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
       <c r="D71" s="14"/>
       <c r="E71" s="14"/>
       <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="15">
-        <v>18.100000000000001</v>
+      <c r="G71" s="14">
+        <v>13</v>
+      </c>
+      <c r="H71" s="14">
+        <v>11</v>
       </c>
       <c r="I71" s="14"/>
       <c r="J71" s="14"/>
       <c r="K71" s="14"/>
       <c r="L71" s="14"/>
       <c r="M71" s="14"/>
-      <c r="N71" s="14"/>
-      <c r="O71" s="14"/>
+      <c r="N71" s="15">
+        <v>5.3757551709299012</v>
+      </c>
+      <c r="O71" s="14">
+        <v>7</v>
+      </c>
       <c r="P71" s="14"/>
       <c r="Q71" s="14"/>
       <c r="R71" s="14"/>
-      <c r="S71" s="14"/>
+      <c r="S71" s="15">
+        <v>4.3936290090937495</v>
+      </c>
       <c r="T71" s="14"/>
       <c r="U71" s="14"/>
-      <c r="V71" s="14"/>
+      <c r="V71" s="14">
+        <v>6</v>
+      </c>
       <c r="W71" s="14"/>
       <c r="X71" s="14"/>
       <c r="Y71" s="14"/>
       <c r="Z71" s="14"/>
-      <c r="AA71" s="14"/>
-      <c r="AB71" s="14"/>
-      <c r="AC71" s="14"/>
+      <c r="AA71" s="14">
+        <v>30</v>
+      </c>
+      <c r="AB71" s="15">
+        <v>27.96247421409107</v>
+      </c>
+      <c r="AC71" s="14">
+        <v>10</v>
+      </c>
       <c r="AD71" s="14"/>
-      <c r="AE71" s="14"/>
-    </row>
-    <row r="72" spans="1:31">
+      <c r="AE71" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:32">
       <c r="A72" s="14">
-        <v>1943</v>
+        <v>1921</v>
       </c>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
@@ -3725,14 +3725,14 @@
       <c r="K72" s="14"/>
       <c r="L72" s="14"/>
       <c r="M72" s="14"/>
-      <c r="N72" s="14"/>
+      <c r="N72" s="15"/>
       <c r="O72" s="14"/>
       <c r="P72" s="14"/>
-      <c r="Q72" s="15">
-        <v>33.361821561291613</v>
-      </c>
-      <c r="R72" s="14"/>
-      <c r="S72" s="14"/>
+      <c r="Q72" s="14"/>
+      <c r="R72" s="1">
+        <v>30.616554018692632</v>
+      </c>
+      <c r="S72" s="15"/>
       <c r="T72" s="14"/>
       <c r="U72" s="14"/>
       <c r="V72" s="14"/>
@@ -3741,20 +3741,18 @@
       <c r="Y72" s="14"/>
       <c r="Z72" s="14"/>
       <c r="AA72" s="14"/>
-      <c r="AB72" s="14"/>
+      <c r="AB72" s="15"/>
       <c r="AC72" s="14"/>
       <c r="AD72" s="14">
-        <v>16.3</v>
+        <v>10.3</v>
       </c>
       <c r="AE72" s="14"/>
     </row>
-    <row r="73" spans="1:31">
+    <row r="73" spans="1:32">
       <c r="A73" s="14">
-        <v>1947</v>
-      </c>
-      <c r="B73" s="15">
-        <v>49.068352134448176</v>
-      </c>
+        <v>1926</v>
+      </c>
+      <c r="B73" s="14"/>
       <c r="C73" s="14"/>
       <c r="D73" s="14"/>
       <c r="E73" s="14"/>
@@ -3766,12 +3764,12 @@
       <c r="K73" s="14"/>
       <c r="L73" s="14"/>
       <c r="M73" s="14"/>
-      <c r="N73" s="14"/>
+      <c r="N73" s="15"/>
       <c r="O73" s="14"/>
       <c r="P73" s="14"/>
       <c r="Q73" s="14"/>
-      <c r="R73" s="14"/>
-      <c r="S73" s="14"/>
+      <c r="R73" s="1"/>
+      <c r="S73" s="15"/>
       <c r="T73" s="14"/>
       <c r="U73" s="14"/>
       <c r="V73" s="14"/>
@@ -3780,1250 +3778,1395 @@
       <c r="Y73" s="14"/>
       <c r="Z73" s="14"/>
       <c r="AA73" s="14"/>
-      <c r="AB73" s="14"/>
+      <c r="AB73" s="15"/>
       <c r="AC73" s="14"/>
       <c r="AD73" s="14"/>
-      <c r="AE73" s="14"/>
-    </row>
-    <row r="74" spans="1:31">
+      <c r="AE73" s="14">
+        <v>12.1</v>
+      </c>
+      <c r="AF73">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:32">
       <c r="A74" s="14">
+        <v>1927</v>
+      </c>
+      <c r="B74" s="14"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+      <c r="K74" s="14"/>
+      <c r="L74" s="14"/>
+      <c r="M74" s="14"/>
+      <c r="N74" s="14"/>
+      <c r="O74" s="14"/>
+      <c r="P74" s="15">
+        <v>18.87623959756025</v>
+      </c>
+      <c r="Q74" s="14"/>
+      <c r="R74" s="14"/>
+      <c r="S74" s="14"/>
+      <c r="T74" s="14"/>
+      <c r="U74" s="14"/>
+      <c r="V74" s="14"/>
+      <c r="W74" s="14"/>
+      <c r="X74" s="14"/>
+      <c r="Y74" s="14"/>
+      <c r="Z74" s="14"/>
+      <c r="AA74" s="14"/>
+      <c r="AB74" s="14"/>
+      <c r="AC74" s="14"/>
+      <c r="AD74" s="14"/>
+      <c r="AE74" s="14"/>
+    </row>
+    <row r="75" spans="1:32">
+      <c r="A75" s="14">
+        <v>1930</v>
+      </c>
+      <c r="B75" s="14"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14">
+        <v>14</v>
+      </c>
+      <c r="H75" s="14">
+        <v>13</v>
+      </c>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+      <c r="K75" s="14"/>
+      <c r="L75" s="14"/>
+      <c r="M75" s="14"/>
+      <c r="N75" s="14"/>
+      <c r="O75" s="14">
+        <v>10</v>
+      </c>
+      <c r="P75" s="14"/>
+      <c r="Q75" s="14"/>
+      <c r="R75" s="14">
+        <v>28.5</v>
+      </c>
+      <c r="S75" s="14"/>
+      <c r="T75" s="15">
+        <v>24.338525446181379</v>
+      </c>
+      <c r="U75" s="14"/>
+      <c r="V75" s="14">
+        <v>10</v>
+      </c>
+      <c r="W75" s="15">
+        <v>10.216396011882644</v>
+      </c>
+      <c r="X75" s="14"/>
+      <c r="Y75" s="14"/>
+      <c r="Z75" s="14"/>
+      <c r="AA75" s="14">
+        <v>35</v>
+      </c>
+      <c r="AB75" s="15">
+        <v>32.849564250969983</v>
+      </c>
+      <c r="AC75" s="14">
+        <v>13</v>
+      </c>
+      <c r="AD75" s="14"/>
+      <c r="AE75" s="14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:32">
+      <c r="A76" s="14">
+        <v>1931</v>
+      </c>
+      <c r="B76" s="14"/>
+      <c r="C76" s="14"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="14"/>
+      <c r="H76" s="14"/>
+      <c r="I76" s="14"/>
+      <c r="J76" s="14"/>
+      <c r="K76" s="14"/>
+      <c r="L76" s="14"/>
+      <c r="M76" s="14"/>
+      <c r="N76" s="14"/>
+      <c r="O76" s="14"/>
+      <c r="P76" s="14"/>
+      <c r="Q76" s="15">
+        <v>29.864393399462539</v>
+      </c>
+      <c r="R76" s="14"/>
+      <c r="S76" s="14"/>
+      <c r="T76" s="14"/>
+      <c r="U76" s="14"/>
+      <c r="V76" s="14"/>
+      <c r="W76" s="14"/>
+      <c r="X76" s="14"/>
+      <c r="Y76" s="14"/>
+      <c r="Z76" s="14"/>
+      <c r="AA76" s="14"/>
+      <c r="AB76" s="14"/>
+      <c r="AC76" s="14"/>
+      <c r="AD76" s="14"/>
+      <c r="AE76" s="14"/>
+    </row>
+    <row r="77" spans="1:32">
+      <c r="A77" s="14">
+        <v>1935</v>
+      </c>
+      <c r="B77" s="14"/>
+      <c r="C77" s="14"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="14"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
+      <c r="K77" s="14"/>
+      <c r="L77" s="14"/>
+      <c r="M77" s="14"/>
+      <c r="N77" s="15">
+        <v>7.1153704466016006</v>
+      </c>
+      <c r="O77" s="14"/>
+      <c r="P77" s="14"/>
+      <c r="Q77" s="14"/>
+      <c r="R77" s="14"/>
+      <c r="S77" s="14"/>
+      <c r="T77" s="14"/>
+      <c r="U77" s="14"/>
+      <c r="V77" s="14"/>
+      <c r="W77" s="14"/>
+      <c r="X77" s="14"/>
+      <c r="Y77" s="14"/>
+      <c r="Z77" s="14"/>
+      <c r="AA77" s="14"/>
+      <c r="AB77" s="14"/>
+      <c r="AC77" s="14"/>
+      <c r="AD77" s="14"/>
+      <c r="AE77" s="14"/>
+    </row>
+    <row r="78" spans="1:32">
+      <c r="A78" s="14">
+        <v>1936</v>
+      </c>
+      <c r="B78" s="14"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="14"/>
+      <c r="H78" s="15">
+        <v>19.091253072290105</v>
+      </c>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+      <c r="K78" s="14"/>
+      <c r="L78" s="14"/>
+      <c r="M78" s="14"/>
+      <c r="N78" s="14"/>
+      <c r="O78" s="14"/>
+      <c r="P78" s="14"/>
+      <c r="Q78" s="14"/>
+      <c r="R78" s="14"/>
+      <c r="S78" s="14"/>
+      <c r="T78" s="14"/>
+      <c r="U78" s="14"/>
+      <c r="V78" s="14"/>
+      <c r="W78" s="14"/>
+      <c r="X78" s="14"/>
+      <c r="Y78" s="14"/>
+      <c r="Z78" s="14"/>
+      <c r="AA78" s="14"/>
+      <c r="AB78" s="14"/>
+      <c r="AC78" s="14"/>
+      <c r="AD78" s="14"/>
+      <c r="AE78" s="14"/>
+    </row>
+    <row r="79" spans="1:32">
+      <c r="A79" s="14">
+        <v>1937</v>
+      </c>
+      <c r="B79" s="14"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="14"/>
+      <c r="H79" s="15"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+      <c r="K79" s="14"/>
+      <c r="L79" s="14"/>
+      <c r="M79" s="14"/>
+      <c r="N79" s="14"/>
+      <c r="O79" s="14"/>
+      <c r="P79" s="14"/>
+      <c r="Q79" s="14"/>
+      <c r="R79" s="14"/>
+      <c r="S79" s="14"/>
+      <c r="T79" s="14"/>
+      <c r="U79" s="15">
+        <v>11.197210631902117</v>
+      </c>
+      <c r="V79" s="14"/>
+      <c r="W79" s="14"/>
+      <c r="X79" s="14"/>
+      <c r="Y79" s="14"/>
+      <c r="Z79" s="14"/>
+      <c r="AA79" s="14"/>
+      <c r="AB79" s="14"/>
+      <c r="AC79" s="14"/>
+      <c r="AD79" s="14"/>
+      <c r="AE79" s="14"/>
+    </row>
+    <row r="80" spans="1:32">
+      <c r="A80" s="14">
+        <v>1938</v>
+      </c>
+      <c r="B80" s="14"/>
+      <c r="C80" s="14"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="14"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="14"/>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="14"/>
+      <c r="K80" s="14"/>
+      <c r="L80" s="14"/>
+      <c r="M80" s="14"/>
+      <c r="N80" s="14"/>
+      <c r="O80" s="15">
+        <v>14.737441012312832</v>
+      </c>
+      <c r="P80" s="14"/>
+      <c r="Q80" s="14"/>
+      <c r="R80" s="14"/>
+      <c r="S80" s="14"/>
+      <c r="T80" s="14"/>
+      <c r="U80" s="14"/>
+      <c r="V80" s="14"/>
+      <c r="W80" s="14"/>
+      <c r="X80" s="14"/>
+      <c r="Y80" s="14"/>
+      <c r="Z80" s="14"/>
+      <c r="AA80" s="14"/>
+      <c r="AB80" s="14"/>
+      <c r="AC80" s="14"/>
+      <c r="AD80" s="14"/>
+      <c r="AE80" s="14"/>
+    </row>
+    <row r="81" spans="1:32">
+      <c r="A81" s="14">
+        <v>1939</v>
+      </c>
+      <c r="B81" s="14"/>
+      <c r="C81" s="14"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="14"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+      <c r="K81" s="14"/>
+      <c r="L81" s="14"/>
+      <c r="M81" s="14"/>
+      <c r="N81" s="14"/>
+      <c r="O81" s="15"/>
+      <c r="P81" s="14"/>
+      <c r="Q81" s="14"/>
+      <c r="R81" s="14"/>
+      <c r="S81" s="14"/>
+      <c r="T81" s="14"/>
+      <c r="U81" s="14"/>
+      <c r="V81" s="14"/>
+      <c r="W81" s="14"/>
+      <c r="X81" s="14"/>
+      <c r="Y81" s="14"/>
+      <c r="Z81" s="14"/>
+      <c r="AA81" s="14"/>
+      <c r="AB81" s="14"/>
+      <c r="AC81" s="14"/>
+      <c r="AD81" s="14"/>
+      <c r="AE81" s="14"/>
+    </row>
+    <row r="82" spans="1:32">
+      <c r="A82" s="14">
+        <v>1940</v>
+      </c>
+      <c r="B82" s="14">
+        <v>41</v>
+      </c>
+      <c r="C82" s="14"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="15">
+        <v>14.979631374994044</v>
+      </c>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+      <c r="K82" s="15">
+        <v>5.7838535408498206</v>
+      </c>
+      <c r="L82" s="14">
+        <v>6.1</v>
+      </c>
+      <c r="M82" s="14"/>
+      <c r="N82" s="14"/>
+      <c r="O82" s="14"/>
+      <c r="P82" s="14"/>
+      <c r="Q82" s="14">
+        <v>30</v>
+      </c>
+      <c r="R82" s="14"/>
+      <c r="S82" s="15">
+        <v>7.5335821390138475</v>
+      </c>
+      <c r="T82" s="15">
+        <v>27.583662937332001</v>
+      </c>
+      <c r="U82" s="14"/>
+      <c r="V82" s="15">
+        <v>14.12009761005495</v>
+      </c>
+      <c r="W82" s="14"/>
+      <c r="X82" s="14"/>
+      <c r="Y82" s="14"/>
+      <c r="Z82" s="14"/>
+      <c r="AA82" s="14">
+        <v>38</v>
+      </c>
+      <c r="AB82" s="15">
+        <v>36.418648287591672</v>
+      </c>
+      <c r="AC82" s="14">
+        <v>16</v>
+      </c>
+      <c r="AD82" s="14"/>
+      <c r="AE82" s="14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:32">
+      <c r="A83" s="14">
+        <v>1941</v>
+      </c>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
+      <c r="H83" s="15">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14"/>
+      <c r="K83" s="14"/>
+      <c r="L83" s="14"/>
+      <c r="M83" s="14"/>
+      <c r="N83" s="14"/>
+      <c r="O83" s="14"/>
+      <c r="P83" s="14"/>
+      <c r="Q83" s="14"/>
+      <c r="R83" s="14"/>
+      <c r="S83" s="14"/>
+      <c r="T83" s="14"/>
+      <c r="U83" s="14"/>
+      <c r="V83" s="14"/>
+      <c r="W83" s="14"/>
+      <c r="X83" s="14"/>
+      <c r="Y83" s="14"/>
+      <c r="Z83" s="14"/>
+      <c r="AA83" s="14"/>
+      <c r="AB83" s="14"/>
+      <c r="AC83" s="14"/>
+      <c r="AD83" s="14"/>
+      <c r="AE83" s="14"/>
+    </row>
+    <row r="84" spans="1:32">
+      <c r="A84" s="14">
+        <v>1943</v>
+      </c>
+      <c r="B84" s="14"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+      <c r="K84" s="14"/>
+      <c r="L84" s="14"/>
+      <c r="M84" s="14"/>
+      <c r="N84" s="14"/>
+      <c r="O84" s="14"/>
+      <c r="P84" s="14"/>
+      <c r="Q84" s="15">
+        <v>33.361821561291613</v>
+      </c>
+      <c r="R84" s="14"/>
+      <c r="S84" s="14"/>
+      <c r="T84" s="14"/>
+      <c r="U84" s="14"/>
+      <c r="V84" s="14"/>
+      <c r="W84" s="14"/>
+      <c r="X84" s="14"/>
+      <c r="Y84" s="14"/>
+      <c r="Z84" s="14"/>
+      <c r="AA84" s="14"/>
+      <c r="AB84" s="14"/>
+      <c r="AC84" s="14"/>
+      <c r="AD84" s="14">
+        <v>16.3</v>
+      </c>
+      <c r="AE84" s="14"/>
+    </row>
+    <row r="85" spans="1:32">
+      <c r="A85" s="14">
+        <v>1947</v>
+      </c>
+      <c r="B85" s="15">
+        <v>49.068352134448176</v>
+      </c>
+      <c r="C85" s="14"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+      <c r="K85" s="14"/>
+      <c r="L85" s="14"/>
+      <c r="M85" s="14"/>
+      <c r="N85" s="14"/>
+      <c r="O85" s="14"/>
+      <c r="P85" s="14"/>
+      <c r="Q85" s="14"/>
+      <c r="R85" s="14"/>
+      <c r="S85" s="14"/>
+      <c r="T85" s="14"/>
+      <c r="U85" s="14"/>
+      <c r="V85" s="14"/>
+      <c r="W85" s="14"/>
+      <c r="X85" s="14"/>
+      <c r="Y85" s="14"/>
+      <c r="Z85" s="14"/>
+      <c r="AA85" s="14"/>
+      <c r="AB85" s="14"/>
+      <c r="AC85" s="14"/>
+      <c r="AD85" s="14"/>
+      <c r="AE85" s="14"/>
+    </row>
+    <row r="86" spans="1:32">
+      <c r="A86" s="14">
         <v>1950</v>
       </c>
-      <c r="B74" s="15">
+      <c r="B86" s="15">
         <v>50.7</v>
       </c>
-      <c r="C74" s="15">
+      <c r="C86" s="15">
         <v>54.4</v>
       </c>
-      <c r="D74" s="15">
+      <c r="D86" s="15">
         <v>45.5</v>
       </c>
-      <c r="E74" s="15">
+      <c r="E86" s="15">
         <v>37</v>
       </c>
-      <c r="F74" s="15">
+      <c r="F86" s="15">
         <v>19.7</v>
       </c>
-      <c r="G74" s="15">
+      <c r="G86" s="15">
         <v>22</v>
       </c>
-      <c r="H74" s="15">
+      <c r="H86" s="15">
         <v>38.700000000000003</v>
       </c>
-      <c r="I74" s="15">
+      <c r="I86" s="15">
         <v>24.5</v>
       </c>
-      <c r="J74" s="15">
+      <c r="J86" s="15">
         <v>5.5</v>
       </c>
-      <c r="K74" s="15">
+      <c r="K86" s="15">
         <v>13.8</v>
       </c>
-      <c r="L74" s="15">
+      <c r="L86" s="15">
         <v>6.8</v>
       </c>
-      <c r="M74" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="N74" s="15">
+      <c r="M86" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="N86" s="15">
         <v>11.1</v>
       </c>
-      <c r="O74" s="15">
+      <c r="O86" s="15">
         <v>22.5</v>
       </c>
-      <c r="P74" s="15">
+      <c r="P86" s="15">
         <v>18.399999999999999</v>
       </c>
-      <c r="Q74" s="15">
+      <c r="Q86" s="15">
         <v>38.299999999999997</v>
       </c>
-      <c r="R74" s="15">
+      <c r="R86" s="15">
         <v>29.3</v>
       </c>
-      <c r="S74" s="15">
+      <c r="S86" s="15">
         <v>15.2</v>
       </c>
-      <c r="T74" s="15">
+      <c r="T86" s="15">
         <v>28.2</v>
       </c>
-      <c r="U74" s="15">
+      <c r="U86" s="15">
         <v>19.600000000000001</v>
       </c>
-      <c r="V74" s="15">
+      <c r="V86" s="15">
         <v>15.9</v>
       </c>
-      <c r="W74" s="15">
+      <c r="W86" s="15">
         <v>14.7</v>
       </c>
-      <c r="X74" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y74" s="15">
+      <c r="X86" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y86" s="15">
         <v>32</v>
       </c>
-      <c r="Z74" s="15">
+      <c r="Z86" s="15">
         <v>22.1</v>
       </c>
-      <c r="AA74" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB74" s="15">
+      <c r="AA86" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB86" s="15">
         <v>47.1</v>
       </c>
-      <c r="AC74" s="15">
+      <c r="AC86" s="15">
         <v>18</v>
       </c>
-      <c r="AD74" s="15">
+      <c r="AD86" s="15">
         <v>16.399999999999999</v>
       </c>
-      <c r="AE74" s="15">
+      <c r="AE86" s="15">
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:31">
-      <c r="A75" s="14">
+    <row r="87" spans="1:32">
+      <c r="A87" s="14">
+        <v>1959</v>
+      </c>
+      <c r="B87" s="15"/>
+      <c r="C87" s="15"/>
+      <c r="D87" s="15"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="15"/>
+      <c r="G87" s="15"/>
+      <c r="H87" s="15"/>
+      <c r="I87" s="15"/>
+      <c r="J87" s="15"/>
+      <c r="K87" s="15"/>
+      <c r="L87" s="15"/>
+      <c r="M87" s="15"/>
+      <c r="N87" s="15"/>
+      <c r="O87" s="15"/>
+      <c r="P87" s="15"/>
+      <c r="Q87" s="15"/>
+      <c r="R87" s="15"/>
+      <c r="S87" s="15"/>
+      <c r="T87" s="15"/>
+      <c r="U87" s="15"/>
+      <c r="V87" s="15"/>
+      <c r="W87" s="15"/>
+      <c r="X87" s="15"/>
+      <c r="Y87" s="15"/>
+      <c r="Z87" s="15"/>
+      <c r="AA87" s="15"/>
+      <c r="AB87" s="15"/>
+      <c r="AC87" s="15"/>
+      <c r="AD87" s="15"/>
+      <c r="AE87" s="15">
+        <v>35.6</v>
+      </c>
+      <c r="AF87" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="88" spans="1:32">
+      <c r="A88" s="14">
         <v>1960</v>
       </c>
-      <c r="B75" s="15">
+      <c r="B88" s="15">
         <v>60</v>
       </c>
-      <c r="C75" s="15">
+      <c r="C88" s="15">
         <v>62.1</v>
       </c>
-      <c r="D75" s="15">
+      <c r="D88" s="15">
         <v>46.2</v>
       </c>
-      <c r="E75" s="15">
+      <c r="E88" s="15">
         <v>44.3</v>
       </c>
-      <c r="F75" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="G75" s="15">
+      <c r="F88" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="G88" s="15">
         <v>29</v>
       </c>
-      <c r="H75" s="15">
+      <c r="H88" s="15">
         <v>52.7</v>
       </c>
-      <c r="I75" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="J75" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="K75" s="15">
+      <c r="I88" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="J88" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="K88" s="15">
         <v>19.3</v>
       </c>
-      <c r="L75" s="15">
+      <c r="L88" s="15">
         <v>11.5</v>
       </c>
-      <c r="M75" s="15">
+      <c r="M88" s="15">
         <v>30.3</v>
       </c>
-      <c r="N75" s="15">
+      <c r="N88" s="15">
         <v>18.7</v>
       </c>
-      <c r="O75" s="15">
+      <c r="O88" s="15">
         <v>37.200000000000003</v>
       </c>
-      <c r="P75" s="15">
+      <c r="P88" s="15">
         <v>22.8</v>
       </c>
-      <c r="Q75" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="R75" s="15">
+      <c r="Q88" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="R88" s="15">
         <v>37</v>
       </c>
-      <c r="S75" s="15">
+      <c r="S88" s="15">
         <v>23</v>
       </c>
-      <c r="T75" s="15">
+      <c r="T88" s="15">
         <v>34.6</v>
       </c>
-      <c r="U75" s="15">
+      <c r="U88" s="15">
         <v>23</v>
       </c>
-      <c r="V75" s="15">
+      <c r="V88" s="15">
         <v>30.7</v>
       </c>
-      <c r="W75" s="15">
+      <c r="W88" s="15">
         <v>19.5</v>
       </c>
-      <c r="X75" s="15">
+      <c r="X88" s="15">
         <v>25.6</v>
       </c>
-      <c r="Y75" s="15">
+      <c r="Y88" s="15">
         <v>37.6</v>
       </c>
-      <c r="Z75" s="15">
+      <c r="Z88" s="15">
         <v>36.799999999999997</v>
       </c>
-      <c r="AA75" s="15">
+      <c r="AA88" s="15">
         <v>66.900000000000006</v>
       </c>
-      <c r="AB75" s="15">
+      <c r="AB88" s="15">
         <v>55.1</v>
       </c>
-      <c r="AC75" s="15">
+      <c r="AC88" s="15">
         <v>27.7</v>
       </c>
-      <c r="AD75" s="15">
+      <c r="AD88" s="15">
         <v>24.9</v>
       </c>
-      <c r="AE75" s="15">
+      <c r="AE88" s="15">
         <v>36</v>
       </c>
     </row>
-    <row r="76" spans="1:31">
-      <c r="A76">
+    <row r="89" spans="1:32">
+      <c r="A89">
         <v>1970</v>
       </c>
-      <c r="B76" s="1">
+      <c r="B89" s="1">
         <v>66.900000000000006</v>
       </c>
-      <c r="C76" s="1">
+      <c r="C89" s="1">
         <v>60.1</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D89" s="1">
         <v>47</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E89" s="1">
         <v>36.200000000000003</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F89" s="1">
         <v>34.1</v>
       </c>
-      <c r="G76" s="1">
+      <c r="G89" s="1">
         <v>40.700000000000003</v>
       </c>
-      <c r="H76" s="1">
+      <c r="H89" s="1">
         <v>63.3</v>
       </c>
-      <c r="I76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="1">
+      <c r="I89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="1">
         <v>13.7</v>
       </c>
-      <c r="K76" s="1">
+      <c r="K89" s="1">
         <v>22.2</v>
       </c>
-      <c r="L76" s="1">
+      <c r="L89" s="1">
         <v>20.5</v>
       </c>
-      <c r="M76" s="1">
+      <c r="M89" s="1">
         <v>31.9</v>
       </c>
-      <c r="N76" s="1">
+      <c r="N89" s="1">
         <v>30.5</v>
       </c>
-      <c r="O76" s="1">
+      <c r="O89" s="1">
         <v>45.6</v>
       </c>
-      <c r="P76" s="1">
+      <c r="P89" s="1">
         <v>30.8</v>
       </c>
-      <c r="Q76" s="1">
+      <c r="Q89" s="1">
         <v>43.8</v>
       </c>
-      <c r="R76" s="1">
+      <c r="R89" s="1">
         <v>45.7</v>
       </c>
-      <c r="S76" s="1">
+      <c r="S89" s="1">
         <v>29.6</v>
       </c>
-      <c r="T76" s="1">
+      <c r="T89" s="1">
         <v>39.1</v>
       </c>
-      <c r="U76" s="1">
+      <c r="U89" s="1">
         <v>27.6</v>
       </c>
-      <c r="V76" s="1">
+      <c r="V89" s="1">
         <v>43</v>
       </c>
-      <c r="W76" s="1">
+      <c r="W89" s="1">
         <v>21.9</v>
       </c>
-      <c r="X76" s="1">
+      <c r="X89" s="1">
         <v>27</v>
       </c>
-      <c r="Y76" s="1">
+      <c r="Y89" s="1">
         <v>40.5</v>
       </c>
-      <c r="Z76" s="1">
+      <c r="Z89" s="1">
         <v>37.4</v>
       </c>
-      <c r="AA76" s="1">
+      <c r="AA89" s="1">
         <v>69.900000000000006</v>
       </c>
-      <c r="AB76" s="1">
+      <c r="AB89" s="1">
         <v>62</v>
       </c>
-      <c r="AC76" s="1">
+      <c r="AC89" s="1">
         <v>35.299999999999997</v>
       </c>
-      <c r="AD76" s="1">
+      <c r="AD89" s="1">
         <v>32.1</v>
       </c>
-    </row>
-    <row r="77" spans="1:31">
-      <c r="A77">
+      <c r="AE89" s="1">
+        <v>44.3</v>
+      </c>
+      <c r="AF89" s="1">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:32">
+      <c r="A90">
+        <v>1979</v>
+      </c>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="L90" s="1"/>
+      <c r="M90" s="1"/>
+      <c r="N90" s="1"/>
+      <c r="O90" s="1"/>
+      <c r="P90" s="1"/>
+      <c r="Q90" s="1"/>
+      <c r="R90" s="1"/>
+      <c r="S90" s="1"/>
+      <c r="T90" s="1"/>
+      <c r="U90" s="1"/>
+      <c r="V90" s="1"/>
+      <c r="W90" s="1"/>
+      <c r="X90" s="1"/>
+      <c r="Y90" s="1"/>
+      <c r="Z90" s="1"/>
+      <c r="AA90" s="1"/>
+      <c r="AB90" s="1"/>
+      <c r="AC90" s="1"/>
+      <c r="AD90" s="1"/>
+      <c r="AE90" s="1">
+        <v>54.9</v>
+      </c>
+      <c r="AF90" s="30">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="91" spans="1:32">
+      <c r="A91">
         <v>1980</v>
       </c>
-      <c r="B77" s="1">
+      <c r="B91" s="1">
         <v>71.2</v>
       </c>
-      <c r="C77" s="1">
+      <c r="C91" s="1">
         <v>64.599999999999994</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D91" s="1">
         <v>46.6</v>
       </c>
-      <c r="E77" s="1">
+      <c r="E91" s="1">
         <v>27.9</v>
       </c>
-      <c r="F77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G77" s="1">
+      <c r="F91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="1">
         <v>52.3</v>
       </c>
-      <c r="H77" s="1">
+      <c r="H91" s="1">
         <v>70.5</v>
       </c>
-      <c r="I77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J77" s="1">
+      <c r="I91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="1">
         <v>17.399999999999999</v>
       </c>
-      <c r="K77" s="1">
+      <c r="K91" s="1">
         <v>22</v>
       </c>
-      <c r="L77" s="1">
+      <c r="L91" s="1">
         <v>28</v>
       </c>
-      <c r="M77" s="1">
+      <c r="M91" s="1">
         <v>33</v>
       </c>
-      <c r="N77" s="1">
+      <c r="N91" s="1">
         <v>41.9</v>
       </c>
-      <c r="O77" s="1">
+      <c r="O91" s="1">
         <v>55.1</v>
       </c>
-      <c r="P77" s="1">
+      <c r="P91" s="1">
         <v>33.799999999999997</v>
       </c>
-      <c r="Q77" s="1">
+      <c r="Q91" s="1">
         <v>47.9</v>
       </c>
-      <c r="R77" s="1">
+      <c r="R91" s="1">
         <v>52.8</v>
       </c>
-      <c r="S77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="T77" s="1">
+      <c r="S91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="1">
         <v>43.8</v>
       </c>
-      <c r="U77" s="1">
+      <c r="U91" s="1">
         <v>33.1</v>
       </c>
-      <c r="V77" s="1">
+      <c r="V91" s="1">
         <v>51.1</v>
       </c>
-      <c r="W77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="X77" s="1">
+      <c r="W91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="1">
         <v>25.7</v>
       </c>
-      <c r="Y77" s="1">
+      <c r="Y91" s="1">
         <v>37.9</v>
       </c>
-      <c r="Z77" s="1">
+      <c r="Z91" s="1">
         <v>40.799999999999997</v>
       </c>
-      <c r="AA77" s="1">
+      <c r="AA91" s="1">
         <v>71.8</v>
       </c>
-      <c r="AB77" s="1">
+      <c r="AB91" s="1">
         <v>68.599999999999994</v>
       </c>
-      <c r="AC77" s="1">
+      <c r="AC91" s="1">
         <v>42.5</v>
       </c>
-      <c r="AD77" s="1">
+      <c r="AD91" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="78" spans="1:31">
-      <c r="A78">
+    <row r="92" spans="1:32">
+      <c r="A92">
+        <v>1989</v>
+      </c>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="1"/>
+      <c r="M92" s="1"/>
+      <c r="N92" s="1"/>
+      <c r="O92" s="1"/>
+      <c r="P92" s="1"/>
+      <c r="Q92" s="1"/>
+      <c r="R92" s="1"/>
+      <c r="S92" s="1"/>
+      <c r="T92" s="1"/>
+      <c r="U92" s="1"/>
+      <c r="V92" s="1"/>
+      <c r="W92" s="1"/>
+      <c r="X92" s="1"/>
+      <c r="Y92" s="1"/>
+      <c r="Z92" s="1"/>
+      <c r="AA92" s="1"/>
+      <c r="AB92" s="1"/>
+      <c r="AC92" s="1"/>
+      <c r="AD92" s="1"/>
+    </row>
+    <row r="93" spans="1:32">
+      <c r="A93">
         <v>1990</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B93" s="1">
         <v>74.900000000000006</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F78" s="1">
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F93" s="1">
         <v>49.6</v>
       </c>
-      <c r="G78" s="1">
+      <c r="G93" s="1">
         <v>58.9</v>
       </c>
-      <c r="H78" s="1">
+      <c r="H93" s="1">
         <v>71.7</v>
       </c>
-      <c r="I78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K78" s="1">
+      <c r="I93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K93" s="1">
         <v>23.7</v>
       </c>
-      <c r="L78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N78" s="1">
+      <c r="L93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N93" s="1">
         <v>45.2</v>
       </c>
-      <c r="O78" s="1">
+      <c r="O93" s="1">
         <v>59.2</v>
       </c>
-      <c r="P78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="R78" s="1">
+      <c r="P93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R93" s="1">
         <v>57.1</v>
       </c>
-      <c r="S78" s="1">
+      <c r="S93" s="1">
         <v>41</v>
       </c>
-      <c r="T78" s="1">
+      <c r="T93" s="1">
         <v>47</v>
       </c>
-      <c r="U78" s="1">
+      <c r="U93" s="1">
         <v>39</v>
       </c>
-      <c r="V78" s="1">
+      <c r="V93" s="1">
         <v>56.8</v>
       </c>
-      <c r="W78" s="1">
+      <c r="W93" s="1">
         <v>35.5</v>
       </c>
-      <c r="X78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA78" s="1">
+      <c r="X93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA93" s="1">
         <v>74.3</v>
       </c>
-      <c r="AB78" s="1">
+      <c r="AB93" s="1">
         <v>72.5</v>
       </c>
-      <c r="AC78" s="1">
+      <c r="AC93" s="1">
         <v>48</v>
       </c>
-      <c r="AD78" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:31">
-      <c r="A79">
+      <c r="AD93" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:32">
+      <c r="A94">
         <v>2000</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B94" s="1">
         <v>76.599999999999994</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F79" s="1">
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="1">
         <v>54.4</v>
       </c>
-      <c r="G79" s="1">
+      <c r="G94" s="1">
         <v>64.599999999999994</v>
       </c>
-      <c r="H79" s="1">
+      <c r="H94" s="1">
         <v>74.3</v>
       </c>
-      <c r="I79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J79" s="1">
+      <c r="I94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="1">
         <v>34.1</v>
       </c>
-      <c r="K79" s="1">
+      <c r="K94" s="1">
         <v>30.7</v>
       </c>
-      <c r="L79" s="1">
+      <c r="L94" s="1">
         <v>32.5</v>
       </c>
-      <c r="M79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N79" s="1">
+      <c r="M94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="1">
         <v>52.6</v>
       </c>
-      <c r="O79" s="1">
+      <c r="O94" s="1">
         <v>65</v>
       </c>
-      <c r="P79" s="1">
+      <c r="P94" s="1">
         <v>49.2</v>
       </c>
-      <c r="Q79" s="1">
+      <c r="Q94" s="1">
         <v>54.5</v>
       </c>
-      <c r="R79" s="1">
+      <c r="R94" s="1">
         <v>60.5</v>
       </c>
-      <c r="S79" s="1">
+      <c r="S94" s="1">
         <v>41.4</v>
       </c>
-      <c r="T79" s="1">
+      <c r="T94" s="1">
         <v>57.3</v>
       </c>
-      <c r="U79" s="1">
+      <c r="U94" s="1">
         <v>44.8</v>
       </c>
-      <c r="V79" s="1">
+      <c r="V94" s="1">
         <v>62.1</v>
       </c>
-      <c r="W79" s="1">
+      <c r="W94" s="1">
         <v>44</v>
       </c>
-      <c r="X79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA79" s="1">
+      <c r="X94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA94" s="1">
         <v>72</v>
       </c>
-      <c r="AB79" s="1">
+      <c r="AB94" s="1">
         <v>76.900000000000006</v>
       </c>
-      <c r="AC79" s="1">
+      <c r="AC94" s="1">
         <v>54.3</v>
       </c>
-      <c r="AD79" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="80" spans="1:31">
-      <c r="A80">
+      <c r="AD94" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:32">
+      <c r="A95">
         <v>2010</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B95" s="1">
         <v>79.8</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F80" s="1">
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F95" s="1">
         <v>59.4</v>
       </c>
-      <c r="G80" s="1">
+      <c r="G95" s="1">
         <v>70.599999999999994</v>
       </c>
-      <c r="H80" s="1">
+      <c r="H95" s="1">
         <v>78</v>
       </c>
-      <c r="I80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="1">
+      <c r="I95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L95" s="1">
         <v>42.4</v>
       </c>
-      <c r="M80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="1">
+      <c r="M95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N95" s="1">
         <v>64.2</v>
       </c>
-      <c r="O80" s="1">
+      <c r="O95" s="1">
         <v>64.900000000000006</v>
       </c>
-      <c r="P80" s="1">
+      <c r="P95" s="1">
         <v>58.7</v>
       </c>
-      <c r="Q80" s="1">
+      <c r="Q95" s="1">
         <v>55.2</v>
       </c>
-      <c r="R80" s="1">
+      <c r="R95" s="1">
         <v>70.2</v>
       </c>
-      <c r="S80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="T80" s="1">
+      <c r="S95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T95" s="1">
         <v>60.1</v>
       </c>
-      <c r="U80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="V80" s="1">
+      <c r="U95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="V95" s="1">
         <v>69.3</v>
       </c>
-      <c r="W80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="X80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA80" s="1">
+      <c r="W95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA95" s="1">
         <v>77.8</v>
       </c>
-      <c r="AB80" s="1">
+      <c r="AB95" s="1">
         <v>80.3</v>
       </c>
-      <c r="AC80" s="1">
+      <c r="AC95" s="1">
         <v>64.400000000000006</v>
       </c>
-      <c r="AD80" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:25" ht="15">
-      <c r="A84" s="11" t="s">
+      <c r="AD95" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:26" ht="15">
+      <c r="A99" s="11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="15">
-      <c r="A86" s="16" t="s">
+    <row r="101" spans="1:26" ht="15">
+      <c r="A101" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B86" s="16" t="s">
+      <c r="B101" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C86" s="16" t="s">
+      <c r="C101" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D86" s="16" t="s">
+      <c r="D101" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E86" s="16" t="s">
+      <c r="E101" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F86" s="16" t="s">
+      <c r="F101" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="G86" s="16" t="s">
+      <c r="G101" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H86" s="16" t="s">
+      <c r="H101" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="I86" s="16" t="s">
+      <c r="I101" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="J86" s="16" t="s">
+      <c r="J101" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="K86" s="16" t="s">
+      <c r="K101" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="L86" s="16" t="s">
+      <c r="L101" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="M86" s="16" t="s">
+      <c r="M101" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="N86" s="16" t="s">
+      <c r="N101" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="O86" s="16" t="s">
+      <c r="O101" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="P86" s="16" t="s">
+      <c r="P101" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="Q86" s="16" t="s">
+      <c r="Q101" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="R86" s="16" t="s">
+      <c r="R101" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="S86" s="16" t="s">
+      <c r="S101" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="T86" s="16" t="s">
+      <c r="T101" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="U86" s="16" t="s">
+      <c r="U101" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="V86" s="16" t="s">
+      <c r="V101" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="W86" s="16" t="s">
+      <c r="W101" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="X86" s="16" t="s">
+      <c r="X101" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="Y86" s="16" t="s">
+      <c r="Y101" s="16" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="87" spans="1:25" ht="15">
-      <c r="A87" s="12">
+      <c r="Z101" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="102" spans="1:26" ht="15">
+      <c r="A102" s="12">
         <v>1865</v>
-      </c>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
-      <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" s="2"/>
-      <c r="Q87" s="2"/>
-      <c r="R87" s="2"/>
-      <c r="S87" s="2"/>
-      <c r="T87" s="2"/>
-      <c r="U87" s="2"/>
-      <c r="V87" s="1">
-        <v>10.981226600587174</v>
-      </c>
-      <c r="W87" s="2"/>
-      <c r="X87" s="2"/>
-      <c r="Y87" s="2"/>
-    </row>
-    <row r="88" spans="1:25" ht="15">
-      <c r="A88" s="12">
-        <v>1869</v>
-      </c>
-      <c r="B88" s="1">
-        <v>16.412235273528619</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
-      <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
-      <c r="P88" s="2"/>
-      <c r="Q88" s="2"/>
-      <c r="R88" s="2"/>
-      <c r="S88" s="2"/>
-      <c r="T88" s="2"/>
-      <c r="U88" s="2"/>
-      <c r="V88" s="2"/>
-      <c r="W88" s="2"/>
-      <c r="X88" s="2"/>
-      <c r="Y88" s="2"/>
-    </row>
-    <row r="89" spans="1:25" ht="15">
-      <c r="A89" s="12">
-        <v>1875</v>
-      </c>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
-      <c r="L89" s="2"/>
-      <c r="M89" s="2"/>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
-      <c r="P89" s="2"/>
-      <c r="Q89" s="2"/>
-      <c r="R89" s="2"/>
-      <c r="S89" s="2"/>
-      <c r="T89" s="2"/>
-      <c r="U89" s="2"/>
-      <c r="V89" s="1">
-        <v>11.841254044492914</v>
-      </c>
-      <c r="W89" s="2"/>
-      <c r="X89" s="2"/>
-      <c r="Y89" s="2"/>
-    </row>
-    <row r="90" spans="1:25" ht="15">
-      <c r="A90" s="12">
-        <v>1876</v>
-      </c>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
-      <c r="L90" s="2"/>
-      <c r="M90" s="2"/>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
-      <c r="P90" s="2"/>
-      <c r="Q90" s="2"/>
-      <c r="R90" s="1">
-        <v>3.760059812397142</v>
-      </c>
-      <c r="S90" s="2"/>
-      <c r="T90" s="2"/>
-      <c r="U90" s="2"/>
-      <c r="V90" s="2"/>
-      <c r="W90" s="2"/>
-      <c r="X90" s="2"/>
-      <c r="Y90" s="2"/>
-    </row>
-    <row r="91" spans="1:25" ht="15">
-      <c r="A91" s="12">
-        <v>1885</v>
-      </c>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
-      <c r="L91" s="2"/>
-      <c r="M91" s="2"/>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
-      <c r="P91" s="2"/>
-      <c r="Q91" s="2"/>
-      <c r="R91" s="2"/>
-      <c r="S91" s="2"/>
-      <c r="T91" s="2"/>
-      <c r="U91" s="2"/>
-      <c r="V91" s="1">
-        <v>12.749795119459268</v>
-      </c>
-      <c r="W91" s="2"/>
-      <c r="X91" s="2"/>
-      <c r="Y91" s="2"/>
-    </row>
-    <row r="92" spans="1:25" ht="15">
-      <c r="A92" s="12">
-        <v>1895</v>
-      </c>
-      <c r="B92" s="1">
-        <v>24.590995853004024</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
-      <c r="L92" s="2"/>
-      <c r="M92" s="2"/>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
-      <c r="P92" s="2"/>
-      <c r="Q92" s="2"/>
-      <c r="R92" s="2"/>
-      <c r="S92" s="2"/>
-      <c r="T92" s="2"/>
-      <c r="U92" s="2"/>
-      <c r="V92" s="1">
-        <v>15.576245989559462</v>
-      </c>
-      <c r="W92" s="2"/>
-      <c r="X92" s="2"/>
-      <c r="Y92" s="2"/>
-    </row>
-    <row r="93" spans="1:25" ht="15">
-      <c r="A93" s="12">
-        <v>1900</v>
-      </c>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1">
-        <v>3.1064017920301814</v>
-      </c>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
-      <c r="L93" s="2"/>
-      <c r="M93" s="2"/>
-      <c r="N93" s="20"/>
-      <c r="O93" s="2"/>
-      <c r="P93" s="2"/>
-      <c r="Q93" s="2"/>
-      <c r="R93" s="2"/>
-      <c r="S93" s="2"/>
-      <c r="T93" s="2"/>
-      <c r="U93" s="2"/>
-      <c r="V93" s="2"/>
-      <c r="W93" s="2"/>
-      <c r="X93" s="2"/>
-      <c r="Y93" s="2"/>
-    </row>
-    <row r="94" spans="1:25" ht="15">
-      <c r="A94" s="12">
-        <v>1907</v>
-      </c>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="12"/>
-      <c r="K94" s="12"/>
-      <c r="L94" s="12"/>
-      <c r="M94" s="12"/>
-      <c r="N94" s="12"/>
-      <c r="O94" s="12"/>
-      <c r="P94" s="12"/>
-      <c r="Q94" s="2"/>
-      <c r="R94" s="2"/>
-      <c r="S94" s="2"/>
-      <c r="T94" s="2"/>
-      <c r="U94" s="2"/>
-      <c r="V94" s="1">
-        <v>17.093485515276829</v>
-      </c>
-      <c r="W94" s="2"/>
-      <c r="X94" s="2"/>
-      <c r="Y94" s="2"/>
-    </row>
-    <row r="95" spans="1:25" ht="15">
-      <c r="A95">
-        <v>1914</v>
-      </c>
-      <c r="B95" s="1">
-        <v>32.61908297746789</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="12"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="2"/>
-      <c r="R95" s="2"/>
-      <c r="S95" s="2"/>
-      <c r="T95" s="2"/>
-      <c r="U95" s="2"/>
-      <c r="V95" s="1">
-        <v>18.489934280279929</v>
-      </c>
-      <c r="W95" s="2"/>
-      <c r="X95" s="2"/>
-    </row>
-    <row r="96" spans="1:25" ht="15">
-      <c r="A96">
-        <v>1919</v>
-      </c>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-      <c r="J96" s="12"/>
-      <c r="K96" s="12"/>
-      <c r="L96" s="12"/>
-      <c r="M96" s="13">
-        <v>16.136633940278379</v>
-      </c>
-      <c r="N96" s="12"/>
-      <c r="O96" s="12"/>
-      <c r="P96" s="12"/>
-      <c r="Q96" s="2"/>
-      <c r="R96" s="2"/>
-      <c r="S96" s="2"/>
-      <c r="T96" s="2"/>
-      <c r="U96" s="2"/>
-      <c r="V96" s="2"/>
-      <c r="W96" s="2"/>
-      <c r="X96" s="2"/>
-    </row>
-    <row r="97" spans="1:25" ht="15">
-      <c r="A97">
-        <v>1920</v>
-      </c>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="K97" s="12"/>
-      <c r="L97" s="12"/>
-      <c r="M97" s="12"/>
-      <c r="N97" s="12"/>
-      <c r="O97" s="12">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="P97" s="12"/>
-      <c r="Q97" s="2"/>
-      <c r="R97" s="2"/>
-      <c r="S97" s="2"/>
-      <c r="T97" s="2"/>
-      <c r="U97" s="2"/>
-      <c r="V97" s="1">
-        <v>20.291115180623258</v>
-      </c>
-      <c r="W97" s="2"/>
-      <c r="X97" s="2"/>
-    </row>
-    <row r="98" spans="1:25" ht="15">
-      <c r="A98">
-        <v>1927</v>
-      </c>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
-      <c r="J98" s="12"/>
-      <c r="K98" s="12"/>
-      <c r="L98" s="13">
-        <v>15.938107074083186</v>
-      </c>
-      <c r="M98" s="12"/>
-      <c r="N98" s="12"/>
-      <c r="O98" s="12"/>
-      <c r="P98" s="12"/>
-      <c r="Q98" s="2"/>
-      <c r="R98" s="2"/>
-      <c r="S98" s="2"/>
-      <c r="T98" s="2"/>
-      <c r="U98" s="2"/>
-      <c r="V98" s="2"/>
-      <c r="W98" s="2"/>
-      <c r="X98" s="2"/>
-    </row>
-    <row r="99" spans="1:25" ht="15">
-      <c r="A99">
-        <v>1930</v>
-      </c>
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
-      <c r="J99" s="12"/>
-      <c r="K99" s="12"/>
-      <c r="L99" s="12"/>
-      <c r="M99" s="12"/>
-      <c r="N99" s="12"/>
-      <c r="O99" s="12"/>
-      <c r="P99" s="13">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" s="2"/>
-      <c r="S99" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="T99" s="2"/>
-      <c r="U99" s="2"/>
-      <c r="V99" s="1">
-        <v>22.93503473513946</v>
-      </c>
-      <c r="W99" s="2"/>
-      <c r="X99" s="2"/>
-    </row>
-    <row r="100" spans="1:25" ht="15">
-      <c r="A100">
-        <v>1931</v>
-      </c>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="2"/>
-      <c r="J100" s="12"/>
-      <c r="K100" s="12"/>
-      <c r="L100" s="12"/>
-      <c r="M100" s="13">
-        <v>20.751529902502156</v>
-      </c>
-      <c r="N100" s="12"/>
-      <c r="O100" s="12"/>
-      <c r="P100" s="12"/>
-      <c r="Q100" s="2"/>
-      <c r="R100" s="2"/>
-      <c r="S100" s="2"/>
-      <c r="T100" s="2"/>
-      <c r="U100" s="2"/>
-      <c r="V100" s="2"/>
-      <c r="W100" s="2"/>
-      <c r="X100" s="2"/>
-    </row>
-    <row r="101" spans="1:25" ht="15">
-      <c r="A101">
-        <v>1935</v>
-      </c>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="2"/>
-      <c r="J101" s="12">
-        <v>4.7</v>
-      </c>
-      <c r="K101" s="12"/>
-      <c r="L101" s="12"/>
-      <c r="M101" s="12"/>
-      <c r="N101" s="12"/>
-      <c r="O101" s="12"/>
-      <c r="P101" s="12"/>
-      <c r="Q101" s="2"/>
-      <c r="R101" s="2"/>
-      <c r="S101" s="2"/>
-      <c r="T101" s="2"/>
-      <c r="U101" s="2"/>
-      <c r="V101" s="2"/>
-      <c r="W101" s="2"/>
-      <c r="X101" s="2"/>
-    </row>
-    <row r="102" spans="1:25" ht="15">
-      <c r="A102">
-        <v>1936</v>
       </c>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
-      <c r="E102" s="1">
-        <v>10.959868289448146</v>
-      </c>
+      <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
-      <c r="J102" s="12"/>
-      <c r="K102" s="12"/>
-      <c r="L102" s="12"/>
-      <c r="M102" s="12"/>
-      <c r="N102" s="12"/>
-      <c r="O102" s="12"/>
-      <c r="P102" s="12"/>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2"/>
+      <c r="L102" s="2"/>
+      <c r="M102" s="2"/>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" s="2"/>
       <c r="Q102" s="2"/>
       <c r="R102" s="2"/>
       <c r="S102" s="2"/>
       <c r="T102" s="2"/>
       <c r="U102" s="2"/>
-      <c r="V102" s="2"/>
+      <c r="V102" s="1">
+        <v>10.981226600587174</v>
+      </c>
       <c r="W102" s="2"/>
       <c r="X102" s="2"/>
-    </row>
-    <row r="103" spans="1:25" ht="15">
-      <c r="A103">
-        <v>1938</v>
-      </c>
-      <c r="B103" s="2"/>
+      <c r="Y102" s="2"/>
+    </row>
+    <row r="103" spans="1:26" ht="15">
+      <c r="A103" s="12">
+        <v>1869</v>
+      </c>
+      <c r="B103" s="1">
+        <v>16.412235273528619</v>
+      </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
@@ -5031,15 +5174,13 @@
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
-      <c r="J103" s="13"/>
-      <c r="K103" s="13">
-        <v>9.4609561958101622</v>
-      </c>
-      <c r="L103" s="12"/>
-      <c r="M103" s="12"/>
-      <c r="N103" s="12"/>
-      <c r="O103" s="12"/>
-      <c r="P103" s="12"/>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2"/>
+      <c r="L103" s="2"/>
+      <c r="M103" s="2"/>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" s="2"/>
       <c r="Q103" s="2"/>
       <c r="R103" s="2"/>
       <c r="S103" s="2"/>
@@ -5048,82 +5189,73 @@
       <c r="V103" s="2"/>
       <c r="W103" s="2"/>
       <c r="X103" s="2"/>
-    </row>
-    <row r="104" spans="1:25" ht="15">
-      <c r="A104">
-        <v>1940</v>
+      <c r="Y103" s="2"/>
+    </row>
+    <row r="104" spans="1:26" ht="15">
+      <c r="A104" s="12">
+        <v>1875</v>
       </c>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
-      <c r="D104" s="1">
-        <v>10.943696108636283</v>
-      </c>
+      <c r="D104" s="2"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
-      <c r="H104" s="1">
-        <v>5.6620215161447227</v>
-      </c>
+      <c r="H104" s="2"/>
       <c r="I104" s="2"/>
-      <c r="J104" s="12"/>
-      <c r="K104" s="12"/>
-      <c r="L104" s="12"/>
-      <c r="M104" s="12"/>
-      <c r="N104" s="12">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="O104" s="12">
-        <v>7.5</v>
-      </c>
-      <c r="P104" s="13">
-        <v>19.7</v>
-      </c>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
+      <c r="M104" s="2"/>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" s="2"/>
       <c r="Q104" s="2"/>
-      <c r="R104" s="1">
-        <v>8.3848383858999256</v>
-      </c>
+      <c r="R104" s="2"/>
       <c r="S104" s="2"/>
       <c r="T104" s="2"/>
       <c r="U104" s="2"/>
       <c r="V104" s="1">
-        <v>24.839719568216751</v>
+        <v>11.841254044492914</v>
       </c>
       <c r="W104" s="2"/>
       <c r="X104" s="2"/>
-    </row>
-    <row r="105" spans="1:25" ht="15">
-      <c r="A105">
-        <v>1941</v>
+      <c r="Y104" s="2"/>
+    </row>
+    <row r="105" spans="1:26" ht="15">
+      <c r="A105" s="12">
+        <v>1876</v>
       </c>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
-      <c r="E105" s="1">
-        <v>12.354575557604816</v>
-      </c>
+      <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
-      <c r="J105" s="12"/>
-      <c r="K105" s="12"/>
-      <c r="L105" s="12"/>
-      <c r="M105" s="12"/>
-      <c r="N105" s="12"/>
-      <c r="O105" s="12"/>
-      <c r="P105" s="12"/>
+      <c r="J105" s="2"/>
+      <c r="K105" s="2"/>
+      <c r="L105" s="2"/>
+      <c r="M105" s="2"/>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" s="2"/>
       <c r="Q105" s="2"/>
-      <c r="R105" s="2"/>
+      <c r="R105" s="1">
+        <v>3.760059812397142</v>
+      </c>
       <c r="S105" s="2"/>
       <c r="T105" s="2"/>
       <c r="U105" s="2"/>
       <c r="V105" s="2"/>
       <c r="W105" s="2"/>
       <c r="X105" s="2"/>
-    </row>
-    <row r="106" spans="1:25" ht="15">
-      <c r="A106">
-        <v>1943</v>
+      <c r="Y105" s="2"/>
+    </row>
+    <row r="106" spans="1:26" ht="15">
+      <c r="A106" s="12">
+        <v>1885</v>
       </c>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -5133,30 +5265,31 @@
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
-      <c r="J106" s="12"/>
-      <c r="K106" s="12"/>
-      <c r="L106" s="12"/>
-      <c r="M106" s="13">
-        <v>22.055413091163864</v>
-      </c>
-      <c r="N106" s="12"/>
-      <c r="O106" s="12"/>
-      <c r="P106" s="12"/>
+      <c r="J106" s="2"/>
+      <c r="K106" s="2"/>
+      <c r="L106" s="2"/>
+      <c r="M106" s="2"/>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" s="2"/>
       <c r="Q106" s="2"/>
       <c r="R106" s="2"/>
       <c r="S106" s="2"/>
       <c r="T106" s="2"/>
       <c r="U106" s="2"/>
-      <c r="V106" s="2"/>
+      <c r="V106" s="1">
+        <v>12.749795119459268</v>
+      </c>
       <c r="W106" s="2"/>
       <c r="X106" s="2"/>
-    </row>
-    <row r="107" spans="1:25" ht="15">
-      <c r="A107">
-        <v>1947</v>
+      <c r="Y106" s="2"/>
+    </row>
+    <row r="107" spans="1:26" ht="15">
+      <c r="A107" s="12">
+        <v>1895</v>
       </c>
       <c r="B107" s="1">
-        <v>39.999919465588746</v>
+        <v>24.590995853004024</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
@@ -5177,526 +5310,1113 @@
       <c r="S107" s="2"/>
       <c r="T107" s="2"/>
       <c r="U107" s="2"/>
-      <c r="V107" s="2"/>
+      <c r="V107" s="1">
+        <v>15.576245989559462</v>
+      </c>
       <c r="W107" s="2"/>
       <c r="X107" s="2"/>
-    </row>
-    <row r="108" spans="1:25">
-      <c r="A108">
+      <c r="Y107" s="2"/>
+    </row>
+    <row r="108" spans="1:26" ht="15">
+      <c r="A108" s="12">
+        <v>1900</v>
+      </c>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1">
+        <v>3.1064017920301814</v>
+      </c>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+      <c r="I108" s="2"/>
+      <c r="J108" s="2"/>
+      <c r="K108" s="2"/>
+      <c r="L108" s="2"/>
+      <c r="M108" s="2"/>
+      <c r="N108" s="19"/>
+      <c r="O108" s="2"/>
+      <c r="P108" s="2"/>
+      <c r="Q108" s="2"/>
+      <c r="R108" s="2"/>
+      <c r="S108" s="2"/>
+      <c r="T108" s="2"/>
+      <c r="U108" s="2"/>
+      <c r="V108" s="2"/>
+      <c r="W108" s="2"/>
+      <c r="X108" s="2"/>
+      <c r="Y108" s="2"/>
+    </row>
+    <row r="109" spans="1:26" ht="15">
+      <c r="A109" s="12">
+        <v>1907</v>
+      </c>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
+      <c r="I109" s="2"/>
+      <c r="J109" s="12"/>
+      <c r="K109" s="12"/>
+      <c r="L109" s="12"/>
+      <c r="M109" s="12"/>
+      <c r="N109" s="12"/>
+      <c r="O109" s="12"/>
+      <c r="P109" s="12"/>
+      <c r="Q109" s="2"/>
+      <c r="R109" s="2"/>
+      <c r="S109" s="2"/>
+      <c r="T109" s="2"/>
+      <c r="U109" s="2"/>
+      <c r="V109" s="1">
+        <v>17.093485515276829</v>
+      </c>
+      <c r="W109" s="2"/>
+      <c r="X109" s="2"/>
+      <c r="Y109" s="2"/>
+    </row>
+    <row r="110" spans="1:26" ht="15">
+      <c r="A110">
+        <v>1914</v>
+      </c>
+      <c r="B110" s="1">
+        <v>32.61908297746789</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+      <c r="I110" s="2"/>
+      <c r="J110" s="12"/>
+      <c r="K110" s="12"/>
+      <c r="L110" s="12"/>
+      <c r="M110" s="12"/>
+      <c r="N110" s="12"/>
+      <c r="O110" s="12"/>
+      <c r="P110" s="12"/>
+      <c r="Q110" s="2"/>
+      <c r="R110" s="2"/>
+      <c r="S110" s="2"/>
+      <c r="T110" s="2"/>
+      <c r="U110" s="2"/>
+      <c r="V110" s="1">
+        <v>18.489934280279929</v>
+      </c>
+      <c r="W110" s="2"/>
+      <c r="X110" s="2"/>
+    </row>
+    <row r="111" spans="1:26" ht="15">
+      <c r="A111">
+        <v>1919</v>
+      </c>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
+      <c r="I111" s="2"/>
+      <c r="J111" s="12"/>
+      <c r="K111" s="12"/>
+      <c r="L111" s="12"/>
+      <c r="M111" s="13">
+        <v>16.136633940278379</v>
+      </c>
+      <c r="N111" s="12"/>
+      <c r="O111" s="12"/>
+      <c r="P111" s="12"/>
+      <c r="Q111" s="2"/>
+      <c r="R111" s="2"/>
+      <c r="S111" s="2"/>
+      <c r="T111" s="2"/>
+      <c r="U111" s="2"/>
+      <c r="V111" s="2"/>
+      <c r="W111" s="2"/>
+      <c r="X111" s="2"/>
+    </row>
+    <row r="112" spans="1:26" ht="15">
+      <c r="A112">
+        <v>1920</v>
+      </c>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+      <c r="I112" s="2"/>
+      <c r="J112" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="K112" s="12"/>
+      <c r="L112" s="12"/>
+      <c r="M112" s="12"/>
+      <c r="N112" s="12"/>
+      <c r="O112" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P112" s="12"/>
+      <c r="Q112" s="2"/>
+      <c r="R112" s="2"/>
+      <c r="S112" s="2"/>
+      <c r="T112" s="2"/>
+      <c r="U112" s="2"/>
+      <c r="V112" s="1">
+        <v>20.291115180623258</v>
+      </c>
+      <c r="W112" s="2"/>
+      <c r="X112" s="2"/>
+    </row>
+    <row r="113" spans="1:26" ht="15">
+      <c r="A113">
+        <v>1926</v>
+      </c>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2"/>
+      <c r="I113" s="2"/>
+      <c r="J113" s="12"/>
+      <c r="K113" s="12"/>
+      <c r="L113" s="12"/>
+      <c r="M113" s="12"/>
+      <c r="N113" s="12"/>
+      <c r="O113" s="12"/>
+      <c r="P113" s="12"/>
+      <c r="Q113" s="2"/>
+      <c r="R113" s="2"/>
+      <c r="S113" s="2"/>
+      <c r="T113" s="2"/>
+      <c r="U113" s="2"/>
+      <c r="V113" s="1"/>
+      <c r="W113" s="2"/>
+      <c r="X113" s="2"/>
+      <c r="Y113" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="Z113" s="1">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:26" ht="15">
+      <c r="A114">
+        <v>1927</v>
+      </c>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="2"/>
+      <c r="J114" s="12"/>
+      <c r="K114" s="12"/>
+      <c r="L114" s="13">
+        <v>15.938107074083186</v>
+      </c>
+      <c r="M114" s="12"/>
+      <c r="N114" s="12"/>
+      <c r="O114" s="12"/>
+      <c r="P114" s="12"/>
+      <c r="Q114" s="2"/>
+      <c r="R114" s="2"/>
+      <c r="S114" s="2"/>
+      <c r="T114" s="2"/>
+      <c r="U114" s="2"/>
+      <c r="V114" s="2"/>
+      <c r="W114" s="2"/>
+      <c r="X114" s="2"/>
+    </row>
+    <row r="115" spans="1:26" ht="15">
+      <c r="A115">
+        <v>1930</v>
+      </c>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
+      <c r="I115" s="2"/>
+      <c r="J115" s="12"/>
+      <c r="K115" s="12"/>
+      <c r="L115" s="12"/>
+      <c r="M115" s="12"/>
+      <c r="N115" s="12"/>
+      <c r="O115" s="12"/>
+      <c r="P115" s="13">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" s="2"/>
+      <c r="S115" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="T115" s="2"/>
+      <c r="U115" s="2"/>
+      <c r="V115" s="1">
+        <v>22.93503473513946</v>
+      </c>
+      <c r="W115" s="2"/>
+      <c r="X115" s="2"/>
+    </row>
+    <row r="116" spans="1:26" ht="15">
+      <c r="A116">
+        <v>1931</v>
+      </c>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
+      <c r="I116" s="2"/>
+      <c r="J116" s="12"/>
+      <c r="K116" s="12"/>
+      <c r="L116" s="12"/>
+      <c r="M116" s="13">
+        <v>20.751529902502156</v>
+      </c>
+      <c r="N116" s="12"/>
+      <c r="O116" s="12"/>
+      <c r="P116" s="12"/>
+      <c r="Q116" s="2"/>
+      <c r="R116" s="2"/>
+      <c r="S116" s="2"/>
+      <c r="T116" s="2"/>
+      <c r="U116" s="2"/>
+      <c r="V116" s="2"/>
+      <c r="W116" s="2"/>
+      <c r="X116" s="2"/>
+    </row>
+    <row r="117" spans="1:26" ht="15">
+      <c r="A117">
+        <v>1935</v>
+      </c>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+      <c r="I117" s="2"/>
+      <c r="J117" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="K117" s="12"/>
+      <c r="L117" s="12"/>
+      <c r="M117" s="12"/>
+      <c r="N117" s="12"/>
+      <c r="O117" s="12"/>
+      <c r="P117" s="12"/>
+      <c r="Q117" s="2"/>
+      <c r="R117" s="2"/>
+      <c r="S117" s="2"/>
+      <c r="T117" s="2"/>
+      <c r="U117" s="2"/>
+      <c r="V117" s="2"/>
+      <c r="W117" s="2"/>
+      <c r="X117" s="2"/>
+    </row>
+    <row r="118" spans="1:26" ht="15">
+      <c r="A118">
+        <v>1936</v>
+      </c>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="1">
+        <v>10.959868289448146</v>
+      </c>
+      <c r="F118" s="2"/>
+      <c r="G118" s="2"/>
+      <c r="H118" s="2"/>
+      <c r="I118" s="2"/>
+      <c r="J118" s="12"/>
+      <c r="K118" s="12"/>
+      <c r="L118" s="12"/>
+      <c r="M118" s="12"/>
+      <c r="N118" s="12"/>
+      <c r="O118" s="12"/>
+      <c r="P118" s="12"/>
+      <c r="Q118" s="2"/>
+      <c r="R118" s="2"/>
+      <c r="S118" s="2"/>
+      <c r="T118" s="2"/>
+      <c r="U118" s="2"/>
+      <c r="V118" s="2"/>
+      <c r="W118" s="2"/>
+      <c r="X118" s="2"/>
+    </row>
+    <row r="119" spans="1:26" ht="15">
+      <c r="A119">
+        <v>1938</v>
+      </c>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="2"/>
+      <c r="H119" s="2"/>
+      <c r="I119" s="2"/>
+      <c r="J119" s="13"/>
+      <c r="K119" s="13">
+        <v>9.4609561958101622</v>
+      </c>
+      <c r="L119" s="12"/>
+      <c r="M119" s="12"/>
+      <c r="N119" s="12"/>
+      <c r="O119" s="12"/>
+      <c r="P119" s="12"/>
+      <c r="Q119" s="2"/>
+      <c r="R119" s="2"/>
+      <c r="S119" s="2"/>
+      <c r="T119" s="2"/>
+      <c r="U119" s="2"/>
+      <c r="V119" s="2"/>
+      <c r="W119" s="2"/>
+      <c r="X119" s="2"/>
+    </row>
+    <row r="120" spans="1:26" ht="15">
+      <c r="A120">
+        <v>1940</v>
+      </c>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="1">
+        <v>10.943696108636283</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+      <c r="H120" s="1">
+        <v>5.6620215161447227</v>
+      </c>
+      <c r="I120" s="2"/>
+      <c r="J120" s="12"/>
+      <c r="K120" s="12"/>
+      <c r="L120" s="12"/>
+      <c r="M120" s="12"/>
+      <c r="N120" s="12">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="O120" s="12">
+        <v>7.5</v>
+      </c>
+      <c r="P120" s="13">
+        <v>19.7</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" s="1">
+        <v>8.3848383858999256</v>
+      </c>
+      <c r="S120" s="2"/>
+      <c r="T120" s="2"/>
+      <c r="U120" s="2"/>
+      <c r="V120" s="1">
+        <v>24.839719568216751</v>
+      </c>
+      <c r="W120" s="2"/>
+      <c r="X120" s="2"/>
+    </row>
+    <row r="121" spans="1:26" ht="15">
+      <c r="A121">
+        <v>1941</v>
+      </c>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="1">
+        <v>12.354575557604816</v>
+      </c>
+      <c r="F121" s="2"/>
+      <c r="G121" s="2"/>
+      <c r="H121" s="2"/>
+      <c r="I121" s="2"/>
+      <c r="J121" s="12"/>
+      <c r="K121" s="12"/>
+      <c r="L121" s="12"/>
+      <c r="M121" s="12"/>
+      <c r="N121" s="12"/>
+      <c r="O121" s="12"/>
+      <c r="P121" s="12"/>
+      <c r="Q121" s="2"/>
+      <c r="R121" s="2"/>
+      <c r="S121" s="2"/>
+      <c r="T121" s="2"/>
+      <c r="U121" s="2"/>
+      <c r="V121" s="2"/>
+      <c r="W121" s="2"/>
+      <c r="X121" s="2"/>
+    </row>
+    <row r="122" spans="1:26" ht="15">
+      <c r="A122">
+        <v>1943</v>
+      </c>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+      <c r="H122" s="2"/>
+      <c r="I122" s="2"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+      <c r="L122" s="12"/>
+      <c r="M122" s="13">
+        <v>22.055413091163864</v>
+      </c>
+      <c r="N122" s="12"/>
+      <c r="O122" s="12"/>
+      <c r="P122" s="12"/>
+      <c r="Q122" s="2"/>
+      <c r="R122" s="2"/>
+      <c r="S122" s="2"/>
+      <c r="T122" s="2"/>
+      <c r="U122" s="2"/>
+      <c r="V122" s="2"/>
+      <c r="W122" s="2"/>
+      <c r="X122" s="2"/>
+    </row>
+    <row r="123" spans="1:26" ht="15">
+      <c r="A123">
+        <v>1947</v>
+      </c>
+      <c r="B123" s="1">
+        <v>39.999919465588746</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+      <c r="F123" s="2"/>
+      <c r="G123" s="2"/>
+      <c r="H123" s="2"/>
+      <c r="I123" s="2"/>
+      <c r="J123" s="2"/>
+      <c r="K123" s="2"/>
+      <c r="L123" s="2"/>
+      <c r="M123" s="2"/>
+      <c r="N123" s="2"/>
+      <c r="O123" s="2"/>
+      <c r="P123" s="2"/>
+      <c r="Q123" s="2"/>
+      <c r="R123" s="2"/>
+      <c r="S123" s="2"/>
+      <c r="T123" s="2"/>
+      <c r="U123" s="2"/>
+      <c r="V123" s="2"/>
+      <c r="W123" s="2"/>
+      <c r="X123" s="2"/>
+    </row>
+    <row r="124" spans="1:26">
+      <c r="A124">
         <v>1950</v>
       </c>
-      <c r="B108" s="1">
+      <c r="B124" s="1">
         <v>43.2</v>
       </c>
-      <c r="C108" s="1">
+      <c r="C124" s="1">
         <v>10.6</v>
       </c>
-      <c r="D108" s="1">
+      <c r="D124" s="1">
         <v>16.600000000000001</v>
       </c>
-      <c r="E108" s="1">
+      <c r="E124" s="1">
         <v>24.9</v>
       </c>
-      <c r="F108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G108" s="1">
+      <c r="F124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G124" s="1">
         <v>4.7</v>
       </c>
-      <c r="H108" s="1">
+      <c r="H124" s="1">
         <v>12.8</v>
       </c>
-      <c r="I108" s="1"/>
-      <c r="J108" s="1">
+      <c r="I124" s="1"/>
+      <c r="J124" s="1">
         <v>8.5</v>
       </c>
-      <c r="K108" s="1">
+      <c r="K124" s="1">
         <v>15.5</v>
       </c>
-      <c r="L108" s="1">
+      <c r="L124" s="1">
         <v>18.399999999999999</v>
       </c>
-      <c r="M108" s="1">
+      <c r="M124" s="1">
         <v>25.7</v>
       </c>
-      <c r="N108" s="1">
+      <c r="N124" s="1">
         <v>21.4</v>
       </c>
-      <c r="O108" s="1">
+      <c r="O124" s="1">
         <v>10.3</v>
       </c>
-      <c r="P108" s="1">
+      <c r="P124" s="1">
         <v>21.7</v>
       </c>
-      <c r="Q108" s="1">
+      <c r="Q124" s="1">
         <v>19.600000000000001</v>
       </c>
-      <c r="R108" s="1">
+      <c r="R124" s="1">
         <v>10.4</v>
       </c>
-      <c r="S108" s="1">
+      <c r="S124" s="1">
         <v>10.4</v>
       </c>
-      <c r="T108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="V108" s="1">
+      <c r="T124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="V124" s="1">
         <v>32.799999999999997</v>
       </c>
-      <c r="W108" s="1">
+      <c r="W124" s="1">
         <v>14.8</v>
       </c>
-      <c r="X108" s="1">
+      <c r="X124" s="1">
         <v>16.399999999999999</v>
       </c>
-      <c r="Y108" s="1">
+      <c r="Y124" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:25">
-      <c r="A109">
+    <row r="125" spans="1:26">
+      <c r="A125">
+        <v>1959</v>
+      </c>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
+      <c r="E125" s="1"/>
+      <c r="F125" s="1"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
+      <c r="J125" s="1"/>
+      <c r="K125" s="1"/>
+      <c r="L125" s="1"/>
+      <c r="M125" s="1"/>
+      <c r="N125" s="1"/>
+      <c r="O125" s="1"/>
+      <c r="P125" s="1"/>
+      <c r="Q125" s="1"/>
+      <c r="R125" s="1"/>
+      <c r="S125" s="1"/>
+      <c r="T125" s="1"/>
+      <c r="U125" s="1"/>
+      <c r="V125" s="1"/>
+      <c r="W125" s="1"/>
+      <c r="X125" s="1"/>
+      <c r="Y125" s="1">
+        <v>23.3</v>
+      </c>
+      <c r="Z125" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="126" spans="1:26">
+      <c r="A126">
         <v>1960</v>
       </c>
-      <c r="B109" s="1">
+      <c r="B126" s="1">
         <v>51.6</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1">
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1">
         <v>22</v>
       </c>
-      <c r="E109" s="1">
+      <c r="E126" s="1">
         <v>39.1</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F126" s="1">
         <v>26.5</v>
       </c>
-      <c r="G109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H109" s="1">
+      <c r="G126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H126" s="1">
         <v>17.2</v>
       </c>
-      <c r="I109" s="1">
+      <c r="I126" s="1">
         <v>7.1</v>
       </c>
-      <c r="J109" s="1">
+      <c r="J126" s="1">
         <v>12.1</v>
       </c>
-      <c r="K109" s="1">
+      <c r="K126" s="1">
         <v>29.3</v>
       </c>
-      <c r="L109" s="1">
+      <c r="L126" s="1">
         <v>19.399999999999999</v>
       </c>
-      <c r="M109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N109" s="1">
+      <c r="M126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N126" s="1">
         <v>28</v>
       </c>
-      <c r="O109" s="1">
+      <c r="O126" s="1">
         <v>15.3</v>
       </c>
-      <c r="P109" s="1">
+      <c r="P126" s="1">
         <v>26.9</v>
       </c>
-      <c r="Q109" s="1">
+      <c r="Q126" s="1">
         <v>23</v>
       </c>
-      <c r="R109" s="1">
+      <c r="R126" s="1">
         <v>22.4</v>
       </c>
-      <c r="S109" s="1">
+      <c r="S126" s="1">
         <v>12.9</v>
       </c>
-      <c r="T109" s="1">
+      <c r="T126" s="1">
         <v>30.2</v>
       </c>
-      <c r="U109" s="1">
+      <c r="U126" s="1">
         <v>50.5</v>
       </c>
-      <c r="V109" s="1">
+      <c r="V126" s="1">
         <v>36.799999999999997</v>
       </c>
-      <c r="W109" s="1">
+      <c r="W126" s="1">
         <v>19.2</v>
       </c>
-      <c r="X109" s="1">
+      <c r="X126" s="1">
         <v>23.4</v>
       </c>
     </row>
-    <row r="110" spans="1:25">
-      <c r="A110">
+    <row r="127" spans="1:26">
+      <c r="A127">
         <v>1970</v>
       </c>
-      <c r="B110" s="1">
+      <c r="B127" s="1">
         <v>56.2</v>
       </c>
-      <c r="C110" s="1">
+      <c r="C127" s="1">
         <v>28.5</v>
       </c>
-      <c r="D110" s="1">
+      <c r="D127" s="1">
         <v>32.200000000000003</v>
       </c>
-      <c r="E110" s="1">
+      <c r="E127" s="1">
         <v>49.7</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F127" s="1">
         <v>23.4</v>
       </c>
-      <c r="G110" s="1">
+      <c r="G127" s="1">
         <v>11.5</v>
       </c>
-      <c r="H110" s="1">
+      <c r="H127" s="1">
         <v>19.600000000000001</v>
       </c>
-      <c r="I110" s="1">
+      <c r="I127" s="1">
         <v>16</v>
       </c>
-      <c r="J110" s="1">
+      <c r="J127" s="1">
         <v>20.5</v>
       </c>
-      <c r="K110" s="1">
+      <c r="K127" s="1">
         <v>37.5</v>
       </c>
-      <c r="L110" s="1">
+      <c r="L127" s="1">
         <v>21.8</v>
       </c>
-      <c r="M110" s="1">
+      <c r="M127" s="1">
         <v>31</v>
       </c>
-      <c r="N110" s="1">
+      <c r="N127" s="1">
         <v>37.700000000000003</v>
       </c>
-      <c r="O110" s="1">
+      <c r="O127" s="1">
         <v>20.5</v>
       </c>
-      <c r="P110" s="1">
+      <c r="P127" s="1">
         <v>31.7</v>
       </c>
-      <c r="Q110" s="1">
+      <c r="Q127" s="1">
         <v>24.9</v>
       </c>
-      <c r="R110" s="1">
+      <c r="R127" s="1">
         <v>34.9</v>
       </c>
-      <c r="S110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="T110" s="1">
+      <c r="S127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T127" s="1">
         <v>30.4</v>
       </c>
-      <c r="U110" s="1">
+      <c r="U127" s="1">
         <v>50.3</v>
       </c>
-      <c r="V110" s="1">
+      <c r="V127" s="1">
         <v>43.3</v>
       </c>
-      <c r="W110" s="1">
+      <c r="W127" s="1">
         <v>23.8</v>
       </c>
-      <c r="X110" s="1">
+      <c r="X127" s="1">
         <v>26.1</v>
       </c>
-    </row>
-    <row r="111" spans="1:25">
-      <c r="A111">
+      <c r="Y127" s="1">
+        <v>31.2</v>
+      </c>
+      <c r="Z127" s="1">
+        <v>35.799999999999997</v>
+      </c>
+    </row>
+    <row r="128" spans="1:26">
+      <c r="A128">
+        <v>1979</v>
+      </c>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
+      <c r="E128" s="1"/>
+      <c r="F128" s="1"/>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1"/>
+      <c r="K128" s="1"/>
+      <c r="L128" s="1"/>
+      <c r="M128" s="1"/>
+      <c r="N128" s="1"/>
+      <c r="O128" s="1"/>
+      <c r="P128" s="1"/>
+      <c r="Q128" s="1"/>
+      <c r="R128" s="1"/>
+      <c r="S128" s="1"/>
+      <c r="T128" s="1"/>
+      <c r="U128" s="1"/>
+      <c r="V128" s="1"/>
+      <c r="W128" s="1"/>
+      <c r="X128" s="1"/>
+      <c r="Y128" s="1">
+        <v>40.4</v>
+      </c>
+      <c r="Z128" s="30">
+        <v>42.7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:24">
+      <c r="A129">
         <v>1980</v>
       </c>
-      <c r="B111" s="1">
+      <c r="B129" s="1">
         <v>58.8</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1">
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1">
         <v>42.1</v>
       </c>
-      <c r="E111" s="1">
+      <c r="E129" s="1">
         <v>59.7</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F129" s="1">
         <v>22.1</v>
       </c>
-      <c r="G111" s="1">
+      <c r="G129" s="1">
         <v>14.3</v>
       </c>
-      <c r="H111" s="1">
+      <c r="H129" s="1">
         <v>19.3</v>
       </c>
-      <c r="I111" s="1">
+      <c r="I129" s="1">
         <v>19.100000000000001</v>
       </c>
-      <c r="J111" s="1">
+      <c r="J129" s="1">
         <v>28</v>
       </c>
-      <c r="K111" s="1">
+      <c r="K129" s="1">
         <v>46.2</v>
       </c>
-      <c r="L111" s="1">
+      <c r="L129" s="1">
         <v>25.1</v>
       </c>
-      <c r="M111" s="1">
+      <c r="M129" s="1">
         <v>32.4</v>
       </c>
-      <c r="N111" s="1">
+      <c r="N129" s="1">
         <v>45.3</v>
       </c>
-      <c r="O111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P111" s="1">
+      <c r="O129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P129" s="1">
         <v>33.799999999999997</v>
       </c>
-      <c r="Q111" s="1">
+      <c r="Q129" s="1">
         <v>27.1</v>
       </c>
-      <c r="R111" s="1">
+      <c r="R129" s="1">
         <v>40.9</v>
       </c>
-      <c r="S111" s="1">
+      <c r="S129" s="1">
         <v>14.7</v>
       </c>
-      <c r="T111" s="1">
+      <c r="T129" s="1">
         <v>32.200000000000003</v>
       </c>
-      <c r="U111" s="1">
+      <c r="U129" s="1">
         <v>51.1</v>
       </c>
-      <c r="V111" s="1">
+      <c r="V129" s="1">
         <v>55.8</v>
       </c>
-      <c r="W111" s="1">
+      <c r="W129" s="1">
         <v>32.9</v>
       </c>
-      <c r="X111" s="1">
+      <c r="X129" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
-      <c r="A112">
+    <row r="130" spans="1:24">
+      <c r="A130">
         <v>1990</v>
       </c>
-      <c r="B112" s="1">
+      <c r="B130" s="1">
         <v>61.8</v>
       </c>
-      <c r="C112" s="1">
+      <c r="C130" s="1">
         <v>41.3</v>
       </c>
-      <c r="D112" s="1">
+      <c r="D130" s="1">
         <v>45.6</v>
       </c>
-      <c r="E112" s="1">
+      <c r="E130" s="1">
         <v>59.5</v>
       </c>
-      <c r="F112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H112" s="1">
+      <c r="F130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H130" s="1">
         <v>19</v>
       </c>
-      <c r="I112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J112" s="1">
+      <c r="I130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J130" s="1">
         <v>32.200000000000003</v>
       </c>
-      <c r="K112" s="1">
+      <c r="K130" s="1">
         <v>49.3</v>
       </c>
-      <c r="L112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N112" s="1">
+      <c r="L130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N130" s="1">
         <v>47.5</v>
       </c>
-      <c r="O112" s="1">
+      <c r="O130" s="1">
         <v>22.7</v>
       </c>
-      <c r="P112" s="1">
+      <c r="P130" s="1">
         <v>36.299999999999997</v>
       </c>
-      <c r="Q112" s="1">
+      <c r="Q130" s="1">
         <v>31.6</v>
       </c>
-      <c r="R112" s="1">
+      <c r="R130" s="1">
         <v>48</v>
       </c>
-      <c r="S112" s="1">
+      <c r="S130" s="1">
         <v>28</v>
       </c>
-      <c r="T112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U112" s="1">
+      <c r="T130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U130" s="1">
         <v>50.3</v>
       </c>
-      <c r="V112" s="1">
+      <c r="V130" s="1">
         <v>60.8</v>
       </c>
-      <c r="W112" s="1">
+      <c r="W130" s="1">
         <v>36.4</v>
       </c>
-      <c r="X112" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="113" spans="1:24">
-      <c r="A113">
+      <c r="X130" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24">
+      <c r="A131">
         <v>2000</v>
       </c>
-      <c r="B113" s="1">
+      <c r="B131" s="1">
         <v>62.3</v>
       </c>
-      <c r="C113" s="1">
+      <c r="C131" s="1">
         <v>44.9</v>
       </c>
-      <c r="D113" s="1">
+      <c r="D131" s="1">
         <v>49.6</v>
       </c>
-      <c r="E113" s="1">
+      <c r="E131" s="1">
         <v>61.6</v>
       </c>
-      <c r="F113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G113" s="1">
+      <c r="F131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G131" s="1">
         <v>27.2</v>
       </c>
-      <c r="H113" s="1">
+      <c r="H131" s="1">
         <v>20.2</v>
       </c>
-      <c r="I113" s="1">
+      <c r="I131" s="1">
         <v>24.3</v>
       </c>
-      <c r="J113" s="1">
+      <c r="J131" s="1">
         <v>41.4</v>
       </c>
-      <c r="K113" s="1">
+      <c r="K131" s="1">
         <v>53.9</v>
       </c>
-      <c r="L113" s="1">
+      <c r="L131" s="1">
         <v>33.9</v>
       </c>
-      <c r="M113" s="1">
+      <c r="M131" s="1">
         <v>39.5</v>
       </c>
-      <c r="N113" s="1">
+      <c r="N131" s="1">
         <v>50.2</v>
       </c>
-      <c r="O113" s="1">
+      <c r="O131" s="1">
         <v>21.9</v>
       </c>
-      <c r="P113" s="1">
+      <c r="P131" s="1">
         <v>51.2</v>
       </c>
-      <c r="Q113" s="1">
+      <c r="Q131" s="1">
         <v>35.299999999999997</v>
       </c>
-      <c r="R113" s="1">
+      <c r="R131" s="1">
         <v>53.5</v>
       </c>
-      <c r="S113" s="1">
+      <c r="S131" s="1">
         <v>29.9</v>
       </c>
-      <c r="T113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U113" s="1">
+      <c r="T131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U131" s="1">
         <v>47.4</v>
       </c>
-      <c r="V113" s="1">
+      <c r="V131" s="1">
         <v>63.6</v>
       </c>
-      <c r="W113" s="1">
+      <c r="W131" s="1">
         <v>44.2</v>
       </c>
-      <c r="X113" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="114" spans="1:24">
-      <c r="A114">
+      <c r="X131" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24">
+      <c r="A132">
         <v>2010</v>
       </c>
-      <c r="B114" s="1">
+      <c r="B132" s="1">
         <v>64.7</v>
       </c>
-      <c r="C114" s="1">
+      <c r="C132" s="1">
         <v>52.2</v>
       </c>
-      <c r="D114" s="1">
+      <c r="D132" s="1">
         <v>56.6</v>
       </c>
-      <c r="E114" s="1">
+      <c r="E132" s="1">
         <v>63.5</v>
       </c>
-      <c r="F114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I114" s="1">
+      <c r="F132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I132" s="1">
         <v>29.3</v>
       </c>
-      <c r="J114" s="1">
+      <c r="J132" s="1">
         <v>52.9</v>
       </c>
-      <c r="K114" s="1">
+      <c r="K132" s="1">
         <v>53.9</v>
       </c>
-      <c r="L114" s="1">
+      <c r="L132" s="1">
         <v>46.4</v>
       </c>
-      <c r="M114" s="1">
+      <c r="M132" s="1">
         <v>40.4</v>
       </c>
-      <c r="N114" s="1">
+      <c r="N132" s="1">
         <v>60.7</v>
       </c>
-      <c r="O114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P114" s="1">
+      <c r="O132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P132" s="1">
         <v>52.6</v>
       </c>
-      <c r="Q114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="R114" s="1">
+      <c r="Q132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R132" s="1">
         <v>59</v>
       </c>
-      <c r="S114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="T114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U114" s="1">
+      <c r="S132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U132" s="1">
         <v>54</v>
       </c>
-      <c r="V114" s="1">
+      <c r="V132" s="1">
         <v>72.5</v>
       </c>
-      <c r="W114" s="1">
+      <c r="W132" s="1">
         <v>52</v>
       </c>
-      <c r="X114" s="1" t="s">
+      <c r="X132" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -8581,19 +9301,19 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15">
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="L4" s="17" t="s">
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="L4" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="M4" s="17"/>
+      <c r="M4" s="29"/>
     </row>
     <row r="5" spans="1:13" ht="15">
       <c r="A5" s="2" t="s">
@@ -12235,13 +12955,13 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="15">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>88</v>
       </c>
     </row>
@@ -12844,7 +13564,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>95</v>
       </c>
     </row>
@@ -13008,7 +13728,7 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="15">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="17" t="s">
         <v>96</v>
       </c>
     </row>
@@ -13018,630 +13738,630 @@
       </c>
     </row>
     <row r="24" spans="1:15" ht="15">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="21" t="s">
+      <c r="D24" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="F24" s="21" t="s">
+      <c r="F24" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="G24" s="21" t="s">
+      <c r="G24" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="H24" s="21" t="s">
+      <c r="H24" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="I24" s="21" t="s">
+      <c r="I24" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="J24" s="21" t="s">
+      <c r="J24" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="K24" s="29" t="s">
+      <c r="K24" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="L24" s="28" t="s">
+      <c r="L24" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="M24" s="28" t="s">
+      <c r="M24" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="N24" s="28" t="s">
+      <c r="N24" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="O24" s="28" t="s">
+      <c r="O24" s="27" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="22">
+      <c r="A25" s="21">
         <v>1900</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B25" s="22">
         <v>13607272</v>
       </c>
-      <c r="C25" s="23">
+      <c r="C25" s="22">
         <v>1003646</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="22">
         <v>1985468</v>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="22">
         <v>3330153</v>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="22">
         <v>4366941</v>
       </c>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="26">
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="25">
         <f>B25-SUM(C25:F25)</f>
         <v>2921064</v>
       </c>
-      <c r="M25" s="22"/>
-      <c r="N25" s="27">
+      <c r="M25" s="21"/>
+      <c r="N25" s="26">
         <f>100*L25/B25</f>
         <v>21.466933269210756</v>
       </c>
-      <c r="O25" s="27"/>
+      <c r="O25" s="26"/>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="22">
+      <c r="A26" s="21">
         <v>1910</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B26" s="22">
         <v>15160369</v>
       </c>
-      <c r="C26" s="23">
+      <c r="C26" s="22">
         <v>945632</v>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="22">
         <v>2053154</v>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="22">
         <v>3339000</v>
       </c>
-      <c r="F26" s="23">
+      <c r="F26" s="22">
         <v>5078967</v>
       </c>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="26">
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="25">
         <f t="shared" ref="L26:L28" si="0">B26-SUM(C26:F26)</f>
         <v>3743616</v>
       </c>
-      <c r="M26" s="22"/>
-      <c r="N26" s="27">
+      <c r="M26" s="21"/>
+      <c r="N26" s="26">
         <f t="shared" ref="N26:N38" si="1">100*L26/B26</f>
         <v>24.693435891962789</v>
       </c>
-      <c r="O26" s="27"/>
+      <c r="O26" s="26"/>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="22">
+      <c r="A27" s="21">
         <v>1921</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="22">
         <v>14330780</v>
       </c>
-      <c r="C27" s="23">
+      <c r="C27" s="22">
         <v>843464</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="22">
         <v>1846928</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="22">
         <v>3103658</v>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="22">
         <v>4149139</v>
       </c>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="26">
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="25">
         <f t="shared" si="0"/>
         <v>4387591</v>
       </c>
-      <c r="M27" s="22"/>
-      <c r="N27" s="27">
+      <c r="M27" s="21"/>
+      <c r="N27" s="26">
         <f t="shared" si="1"/>
         <v>30.616554018692632</v>
       </c>
-      <c r="O27" s="27"/>
+      <c r="O27" s="26"/>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" s="22">
+      <c r="A28" s="21">
         <v>1930</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B28" s="22">
         <v>16552722</v>
       </c>
-      <c r="C28" s="23">
+      <c r="C28" s="22">
         <v>805014</v>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="22">
         <v>2171814</v>
       </c>
-      <c r="E28" s="23">
+      <c r="E28" s="22">
         <v>3655794</v>
       </c>
-      <c r="F28" s="23">
+      <c r="F28" s="22">
         <v>5210646</v>
       </c>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="26">
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="25">
         <f t="shared" si="0"/>
         <v>4709454</v>
       </c>
-      <c r="M28" s="22"/>
-      <c r="N28" s="27">
+      <c r="M28" s="21"/>
+      <c r="N28" s="26">
         <f t="shared" si="1"/>
         <v>28.451235996109883</v>
       </c>
-      <c r="O28" s="27"/>
+      <c r="O28" s="26"/>
     </row>
     <row r="29" spans="1:15">
-      <c r="A29" s="22">
+      <c r="A29" s="21">
         <v>1940</v>
       </c>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="22"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
     </row>
     <row r="30" spans="1:15">
-      <c r="A30" s="22">
+      <c r="A30" s="21">
         <v>1950</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B30" s="22">
         <v>25791017</v>
       </c>
-      <c r="C30" s="23">
+      <c r="C30" s="22">
         <v>14790299</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="22">
         <v>2063467</v>
       </c>
-      <c r="E30" s="23">
+      <c r="E30" s="22">
         <v>1472397</v>
       </c>
-      <c r="F30" s="23">
+      <c r="F30" s="22">
         <v>1281299</v>
       </c>
-      <c r="G30" s="24">
+      <c r="G30" s="23">
         <v>1258428</v>
       </c>
-      <c r="H30" s="24">
+      <c r="H30" s="23">
         <v>725296</v>
       </c>
-      <c r="I30" s="24">
+      <c r="I30" s="23">
         <v>1406204</v>
       </c>
-      <c r="J30" s="24">
+      <c r="J30" s="23">
         <v>2234795</v>
       </c>
-      <c r="K30" s="23"/>
-      <c r="L30" s="26">
+      <c r="K30" s="22"/>
+      <c r="L30" s="25">
         <f t="shared" ref="L30:L38" si="2">B30-SUM(C30:F30)</f>
         <v>6183555</v>
       </c>
-      <c r="M30" s="26">
+      <c r="M30" s="25">
         <f>SUM(I30:K30)</f>
         <v>3640999</v>
       </c>
-      <c r="N30" s="27">
+      <c r="N30" s="26">
         <f t="shared" si="1"/>
         <v>23.975615230682838</v>
       </c>
-      <c r="O30" s="27">
+      <c r="O30" s="26">
         <f>M30/B30*100</f>
         <v>14.117314567316209</v>
       </c>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31" s="22">
+      <c r="A31" s="21">
         <v>1960</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B31" s="22">
         <v>34923129</v>
       </c>
-      <c r="C31" s="23">
+      <c r="C31" s="22">
         <v>17218011</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="22">
         <v>2959460</v>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="22">
         <v>2366431</v>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="22">
         <v>2027511</v>
       </c>
-      <c r="G31" s="24">
+      <c r="G31" s="23">
         <v>2108551</v>
       </c>
-      <c r="H31" s="25">
+      <c r="H31" s="24">
         <v>1730933</v>
       </c>
-      <c r="I31" s="24">
+      <c r="I31" s="23">
         <v>2346360</v>
       </c>
-      <c r="J31" s="25">
+      <c r="J31" s="24">
         <v>4165872</v>
       </c>
-      <c r="K31" s="23"/>
-      <c r="L31" s="26">
+      <c r="K31" s="22"/>
+      <c r="L31" s="25">
         <f t="shared" si="2"/>
         <v>10351716</v>
       </c>
-      <c r="M31" s="26">
+      <c r="M31" s="25">
         <f t="shared" ref="M31:M32" si="3">SUM(I31:K31)</f>
         <v>6512232</v>
       </c>
-      <c r="N31" s="27">
+      <c r="N31" s="26">
         <f t="shared" si="1"/>
         <v>29.641433332047651</v>
       </c>
-      <c r="O31" s="27">
+      <c r="O31" s="26">
         <f t="shared" ref="O31:O38" si="4">M31/B31*100</f>
         <v>18.647332545717767</v>
       </c>
     </row>
     <row r="32" spans="1:15">
-      <c r="A32" s="22">
+      <c r="A32" s="21">
         <v>1970</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="23">
         <v>48225238</v>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="24">
         <v>19916682</v>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="23">
         <v>4129872</v>
       </c>
-      <c r="E32" s="24">
+      <c r="E32" s="23">
         <v>3764208</v>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="23">
         <v>3409846</v>
       </c>
-      <c r="G32" s="24">
+      <c r="G32" s="23">
         <v>3405818</v>
       </c>
-      <c r="H32" s="25">
+      <c r="H32" s="24">
         <v>2356569</v>
       </c>
-      <c r="I32" s="25">
+      <c r="I32" s="24">
         <v>5707130</v>
       </c>
-      <c r="J32" s="24">
+      <c r="J32" s="23">
         <v>4341512</v>
       </c>
-      <c r="K32" s="24">
+      <c r="K32" s="23">
         <v>1193601</v>
       </c>
-      <c r="L32" s="26">
+      <c r="L32" s="25">
         <f t="shared" si="2"/>
         <v>17004630</v>
       </c>
-      <c r="M32" s="26">
+      <c r="M32" s="25">
         <f t="shared" si="3"/>
         <v>11242243</v>
       </c>
-      <c r="N32" s="27">
+      <c r="N32" s="26">
         <f t="shared" si="1"/>
         <v>35.260852419224967</v>
       </c>
-      <c r="O32" s="27">
+      <c r="O32" s="26">
         <f t="shared" si="4"/>
         <v>23.311949232889219</v>
       </c>
     </row>
     <row r="33" spans="1:15">
-      <c r="A33" s="22">
+      <c r="A33" s="21">
         <v>1980</v>
       </c>
-      <c r="B33" s="24"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="24"/>
-      <c r="K33" s="24"/>
-      <c r="L33" s="26"/>
-      <c r="M33" s="22"/>
-      <c r="N33" s="27"/>
-      <c r="O33" s="27"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="23"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
     </row>
     <row r="34" spans="1:15">
-      <c r="A34" s="22">
+      <c r="A34" s="21">
         <v>1990</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="24">
         <v>81249645</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="23">
         <v>23289924</v>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="23">
         <v>4647566</v>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="23">
         <v>6636745</v>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="23">
         <v>1675566</v>
       </c>
-      <c r="G34" s="24">
+      <c r="G34" s="23">
         <v>5075188</v>
       </c>
-      <c r="H34" s="24">
+      <c r="H34" s="23">
         <v>3854850</v>
       </c>
-      <c r="I34" s="24">
+      <c r="I34" s="23">
         <v>18233313</v>
       </c>
-      <c r="J34" s="24">
+      <c r="J34" s="23">
         <v>8878127</v>
       </c>
-      <c r="K34" s="24">
+      <c r="K34" s="23">
         <v>8958366</v>
       </c>
-      <c r="L34" s="26">
+      <c r="L34" s="25">
         <f t="shared" si="2"/>
         <v>44999844</v>
       </c>
-      <c r="M34" s="26">
+      <c r="M34" s="25">
         <f t="shared" ref="M34:M38" si="5">SUM(I34:K34)</f>
         <v>36069806</v>
       </c>
-      <c r="N34" s="27">
+      <c r="N34" s="26">
         <f t="shared" si="1"/>
         <v>55.384665372999478</v>
       </c>
-      <c r="O34" s="27">
+      <c r="O34" s="26">
         <f t="shared" si="4"/>
         <v>44.393801351378215</v>
       </c>
     </row>
     <row r="35" spans="1:15">
-      <c r="A35" s="22">
+      <c r="A35" s="21">
         <v>1995</v>
       </c>
-      <c r="B35" s="24">
+      <c r="B35" s="23">
         <v>91158290</v>
       </c>
-      <c r="C35" s="24">
+      <c r="C35" s="23">
         <v>24154775</v>
       </c>
-      <c r="D35" s="24">
+      <c r="D35" s="23">
         <v>4996974</v>
       </c>
-      <c r="E35" s="24">
+      <c r="E35" s="23">
         <v>7373112</v>
       </c>
-      <c r="F35" s="24">
+      <c r="F35" s="23">
         <v>1859302</v>
       </c>
-      <c r="G35" s="24">
+      <c r="G35" s="23">
         <v>6146276</v>
       </c>
-      <c r="H35" s="24">
+      <c r="H35" s="23">
         <v>4340532</v>
       </c>
-      <c r="I35" s="24">
+      <c r="I35" s="23">
         <v>19000266</v>
       </c>
-      <c r="J35" s="24">
+      <c r="J35" s="23">
         <v>13765240</v>
       </c>
-      <c r="K35" s="24">
+      <c r="K35" s="23">
         <v>9521813</v>
       </c>
-      <c r="L35" s="26">
+      <c r="L35" s="25">
         <f t="shared" si="2"/>
         <v>52774127</v>
       </c>
-      <c r="M35" s="26">
+      <c r="M35" s="25">
         <f t="shared" si="5"/>
         <v>42287319</v>
       </c>
-      <c r="N35" s="27">
+      <c r="N35" s="26">
         <f t="shared" si="1"/>
         <v>57.89284441382128</v>
       </c>
-      <c r="O35" s="27">
+      <c r="O35" s="26">
         <f t="shared" si="4"/>
         <v>46.388890138241948</v>
       </c>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="22">
+      <c r="A36" s="21">
         <v>2000</v>
       </c>
-      <c r="B36" s="25">
+      <c r="B36" s="24">
         <v>97483412</v>
       </c>
-      <c r="C36" s="24">
+      <c r="C36" s="23">
         <v>24723590</v>
       </c>
-      <c r="D36" s="24">
+      <c r="D36" s="23">
         <v>5462305</v>
       </c>
-      <c r="E36" s="24">
+      <c r="E36" s="23">
         <v>7878309</v>
       </c>
-      <c r="F36" s="24">
+      <c r="F36" s="23">
         <v>1888466</v>
       </c>
-      <c r="G36" s="24">
+      <c r="G36" s="23">
         <v>6847942</v>
       </c>
-      <c r="H36" s="24">
+      <c r="H36" s="23">
         <v>4549492</v>
       </c>
-      <c r="I36" s="24">
+      <c r="I36" s="23">
         <v>20430268</v>
       </c>
-      <c r="J36" s="24">
+      <c r="J36" s="23">
         <v>12461706</v>
       </c>
-      <c r="K36" s="24">
+      <c r="K36" s="23">
         <v>13241334</v>
       </c>
-      <c r="L36" s="26">
+      <c r="L36" s="25">
         <f t="shared" si="2"/>
         <v>57530742</v>
       </c>
-      <c r="M36" s="26">
+      <c r="M36" s="25">
         <f t="shared" si="5"/>
         <v>46133308</v>
       </c>
-      <c r="N36" s="27">
+      <c r="N36" s="26">
         <f t="shared" si="1"/>
         <v>59.015929807627167</v>
       </c>
-      <c r="O36" s="27">
+      <c r="O36" s="26">
         <f t="shared" si="4"/>
         <v>47.324264768245904</v>
       </c>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="22">
+      <c r="A37" s="21">
         <v>2005</v>
       </c>
-      <c r="B37" s="24">
+      <c r="B37" s="23">
         <v>103263388</v>
       </c>
-      <c r="C37" s="24">
+      <c r="C37" s="23">
         <v>24276536</v>
       </c>
-      <c r="D37" s="24">
+      <c r="D37" s="23">
         <v>5663750</v>
       </c>
-      <c r="E37" s="24">
+      <c r="E37" s="23">
         <v>8466969</v>
       </c>
-      <c r="F37" s="24">
+      <c r="F37" s="23">
         <v>1837560</v>
       </c>
-      <c r="G37" s="24">
+      <c r="G37" s="23">
         <v>7444004</v>
       </c>
-      <c r="H37" s="24">
+      <c r="H37" s="23">
         <v>5082771</v>
       </c>
-      <c r="I37" s="24">
+      <c r="I37" s="23">
         <v>21370547</v>
       </c>
-      <c r="J37" s="24">
+      <c r="J37" s="23">
         <v>14398274</v>
       </c>
-      <c r="K37" s="24">
+      <c r="K37" s="23">
         <v>14722977</v>
       </c>
-      <c r="L37" s="26">
+      <c r="L37" s="25">
         <f t="shared" si="2"/>
         <v>63018573</v>
       </c>
-      <c r="M37" s="26">
+      <c r="M37" s="25">
         <f t="shared" si="5"/>
         <v>50491798</v>
       </c>
-      <c r="N37" s="27">
+      <c r="N37" s="26">
         <f t="shared" si="1"/>
         <v>61.027024408689748</v>
       </c>
-      <c r="O37" s="27">
+      <c r="O37" s="26">
         <f t="shared" si="4"/>
         <v>48.896127638190606</v>
       </c>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="22">
+      <c r="A38" s="21">
         <v>2010</v>
       </c>
-      <c r="B38" s="24">
+      <c r="B38" s="23">
         <v>112336538</v>
       </c>
-      <c r="C38" s="24">
+      <c r="C38" s="23">
         <v>26049769</v>
       </c>
-      <c r="D38" s="24">
+      <c r="D38" s="23">
         <v>6360949</v>
       </c>
-      <c r="E38" s="24">
+      <c r="E38" s="23">
         <v>9746684</v>
       </c>
-      <c r="F38" s="24">
+      <c r="F38" s="23">
         <v>6417488</v>
       </c>
-      <c r="G38" s="24">
+      <c r="G38" s="23">
         <v>4150450</v>
       </c>
-      <c r="H38" s="24">
+      <c r="H38" s="23">
         <v>5946088</v>
       </c>
-      <c r="I38" s="24">
+      <c r="I38" s="23">
         <v>22472661</v>
       </c>
-      <c r="J38" s="24">
+      <c r="J38" s="23">
         <v>16363103</v>
       </c>
-      <c r="K38" s="24">
+      <c r="K38" s="23">
         <v>14829346</v>
       </c>
-      <c r="L38" s="26">
+      <c r="L38" s="25">
         <f t="shared" si="2"/>
         <v>63761648</v>
       </c>
-      <c r="M38" s="26">
+      <c r="M38" s="25">
         <f t="shared" si="5"/>
         <v>53665110</v>
       </c>
-      <c r="N38" s="27">
+      <c r="N38" s="26">
         <f t="shared" si="1"/>
         <v>56.759491733669059</v>
       </c>
-      <c r="O38" s="27">
+      <c r="O38" s="26">
         <f t="shared" si="4"/>
         <v>47.771732114443481</v>
       </c>

--- a/rtss-mexico/src/main/resources/latinamerica/Latin-America-Urbanization.xlsx
+++ b/rtss-mexico/src/main/resources/latinamerica/Latin-America-Urbanization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-mexico\src\main\resources\latinamerica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D971E15-B926-4DA6-B8D6-2E0641B8FE32}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4C60C3-DBC3-4CE1-AAA8-8659F1F6047B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13605" yWindow="1065" windowWidth="26520" windowHeight="22275" activeTab="9" xr2:uid="{CF6A2AB8-34C5-4CDB-9A0B-0A9EB6FB1FEF}"/>
+    <workbookView xWindow="17595" yWindow="900" windowWidth="19965" windowHeight="22275" activeTab="9" xr2:uid="{CF6A2AB8-34C5-4CDB-9A0B-0A9EB6FB1FEF}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -510,7 +510,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -558,11 +558,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -917,7 +920,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC336925-0078-4AF9-986A-8BA8236BAFF3}">
-  <dimension ref="A1:AF132"/>
+  <dimension ref="A1:AF133"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:28" ht="15">
@@ -2564,7 +2567,7 @@
       </c>
     </row>
     <row r="45" spans="1:28" ht="15">
-      <c r="A45" s="31">
+      <c r="A45" s="30">
         <v>1926</v>
       </c>
       <c r="B45" s="16"/>
@@ -2599,659 +2602,654 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="46" spans="1:28">
-      <c r="A46">
-        <v>1950</v>
-      </c>
-      <c r="B46" s="1">
-        <v>64.3</v>
-      </c>
-      <c r="C46" s="1">
-        <v>56.5</v>
-      </c>
-      <c r="D46" s="1">
-        <v>25.6</v>
-      </c>
-      <c r="E46" s="1">
-        <v>30.1</v>
-      </c>
-      <c r="F46" s="1">
-        <v>51.8</v>
-      </c>
-      <c r="G46" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="H46" s="1">
-        <v>26.8</v>
-      </c>
-      <c r="I46" s="1">
-        <v>28.1</v>
-      </c>
-      <c r="J46" s="1">
-        <v>17.2</v>
-      </c>
-      <c r="K46" s="1">
-        <v>21.6</v>
-      </c>
-      <c r="L46" s="1">
-        <v>33.700000000000003</v>
-      </c>
-      <c r="M46" s="1">
-        <v>29.9</v>
-      </c>
-      <c r="N46" s="1">
-        <v>51.4</v>
-      </c>
-      <c r="O46" s="1">
-        <v>42</v>
-      </c>
-      <c r="P46" s="1">
-        <v>28</v>
-      </c>
-      <c r="Q46" s="1">
-        <v>35.5</v>
-      </c>
-      <c r="R46" s="1">
-        <v>31.3</v>
-      </c>
-      <c r="S46" s="1">
-        <v>26.9</v>
-      </c>
-      <c r="T46" s="1">
-        <v>27.9</v>
-      </c>
-      <c r="U46" s="1">
-        <v>47</v>
-      </c>
-      <c r="V46" s="1">
-        <v>78.3</v>
-      </c>
-      <c r="W46" s="1">
-        <v>52</v>
-      </c>
-      <c r="X46" s="1">
-        <v>58.8</v>
-      </c>
-      <c r="Y46" s="1">
-        <v>28.2</v>
-      </c>
-      <c r="Z46" s="1">
-        <v>26.7</v>
-      </c>
+    <row r="46" spans="1:28" ht="15">
+      <c r="A46" s="30">
+        <v>1930</v>
+      </c>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
+      <c r="K46" s="16"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="16"/>
+      <c r="O46" s="32">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="P46" s="16"/>
+      <c r="Q46" s="16"/>
+      <c r="R46" s="16"/>
+      <c r="S46" s="16"/>
+      <c r="T46" s="16"/>
+      <c r="U46" s="16"/>
+      <c r="V46" s="16"/>
+      <c r="W46" s="16"/>
+      <c r="X46" s="16"/>
+      <c r="Y46" s="16"/>
+      <c r="Z46" s="16"/>
+      <c r="AA46" s="1"/>
+      <c r="AB46" s="1"/>
     </row>
     <row r="47" spans="1:28">
       <c r="A47">
-        <v>1959</v>
-      </c>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-      <c r="Q47" s="1"/>
-      <c r="R47" s="1"/>
-      <c r="S47" s="1"/>
-      <c r="T47" s="1"/>
-      <c r="U47" s="1"/>
-      <c r="V47" s="1"/>
-      <c r="W47" s="1"/>
-      <c r="X47" s="1"/>
-      <c r="Y47" s="1"/>
-      <c r="Z47" s="1"/>
-      <c r="AA47" s="1">
-        <v>57.2</v>
-      </c>
-      <c r="AB47" s="1">
-        <v>60.4</v>
+        <v>1950</v>
+      </c>
+      <c r="B47" s="1">
+        <v>64.3</v>
+      </c>
+      <c r="C47" s="1">
+        <v>56.5</v>
+      </c>
+      <c r="D47" s="1">
+        <v>25.6</v>
+      </c>
+      <c r="E47" s="1">
+        <v>30.1</v>
+      </c>
+      <c r="F47" s="1">
+        <v>51.8</v>
+      </c>
+      <c r="G47" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="H47" s="1">
+        <v>26.8</v>
+      </c>
+      <c r="I47" s="1">
+        <v>28.1</v>
+      </c>
+      <c r="J47" s="1">
+        <v>17.2</v>
+      </c>
+      <c r="K47" s="1">
+        <v>21.6</v>
+      </c>
+      <c r="L47" s="1">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="M47" s="1">
+        <v>29.9</v>
+      </c>
+      <c r="N47" s="1">
+        <v>51.4</v>
+      </c>
+      <c r="O47" s="1">
+        <v>42</v>
+      </c>
+      <c r="P47" s="1">
+        <v>28</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>35.5</v>
+      </c>
+      <c r="R47" s="1">
+        <v>31.3</v>
+      </c>
+      <c r="S47" s="1">
+        <v>26.9</v>
+      </c>
+      <c r="T47" s="1">
+        <v>27.9</v>
+      </c>
+      <c r="U47" s="1">
+        <v>47</v>
+      </c>
+      <c r="V47" s="1">
+        <v>78.3</v>
+      </c>
+      <c r="W47" s="1">
+        <v>52</v>
+      </c>
+      <c r="X47" s="1">
+        <v>58.8</v>
+      </c>
+      <c r="Y47" s="1">
+        <v>28.2</v>
+      </c>
+      <c r="Z47" s="1">
+        <v>26.7</v>
       </c>
     </row>
     <row r="48" spans="1:28">
       <c r="A48">
-        <v>1960</v>
-      </c>
-      <c r="B48" s="1">
-        <v>75</v>
-      </c>
-      <c r="C48" s="1">
-        <v>53.8</v>
-      </c>
-      <c r="D48" s="1">
-        <v>39.299999999999997</v>
-      </c>
-      <c r="E48" s="1">
-        <v>38.1</v>
-      </c>
-      <c r="F48" s="1">
-        <v>64.900000000000006</v>
-      </c>
-      <c r="G48" s="1">
-        <v>15.6</v>
-      </c>
-      <c r="H48" s="1">
-        <v>31.5</v>
-      </c>
-      <c r="I48" s="1">
-        <v>29</v>
-      </c>
-      <c r="J48" s="1">
-        <v>22</v>
-      </c>
-      <c r="K48" s="1">
-        <v>29.1</v>
-      </c>
-      <c r="L48" s="1">
-        <v>50.3</v>
-      </c>
-      <c r="M48" s="1">
-        <v>32.200000000000003</v>
-      </c>
-      <c r="N48" s="1">
-        <v>54.9</v>
-      </c>
-      <c r="O48" s="1">
-        <v>49.6</v>
-      </c>
-      <c r="P48" s="1">
-        <v>35.6</v>
-      </c>
-      <c r="Q48" s="1">
-        <v>41.5</v>
-      </c>
-      <c r="R48" s="1">
-        <v>35.1</v>
-      </c>
-      <c r="S48" s="1">
-        <v>40.6</v>
-      </c>
-      <c r="T48" s="1">
-        <v>31.8</v>
-      </c>
-      <c r="U48" s="1">
-        <v>47.2</v>
-      </c>
-      <c r="V48" s="1">
-        <v>78.3</v>
-      </c>
-      <c r="W48" s="1">
-        <v>63.6</v>
-      </c>
-      <c r="X48" s="1">
-        <v>64.7</v>
-      </c>
-      <c r="Y48" s="1">
-        <v>36</v>
-      </c>
-      <c r="Z48" s="1">
-        <v>33.799999999999997</v>
+        <v>1959</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1"/>
+      <c r="V48" s="1"/>
+      <c r="W48" s="1"/>
+      <c r="X48" s="1"/>
+      <c r="Y48" s="1"/>
+      <c r="Z48" s="1"/>
+      <c r="AA48" s="1">
+        <v>57.2</v>
+      </c>
+      <c r="AB48" s="1">
+        <v>60.4</v>
       </c>
     </row>
     <row r="49" spans="1:32">
       <c r="A49">
-        <v>1970</v>
+        <v>1960</v>
       </c>
       <c r="B49" s="1">
-        <v>79.2</v>
+        <v>75</v>
       </c>
       <c r="C49" s="1">
-        <v>51.2</v>
+        <v>53.8</v>
       </c>
       <c r="D49" s="1">
-        <v>43.5</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="E49" s="1">
-        <v>51.1</v>
+        <v>38.1</v>
       </c>
       <c r="F49" s="1">
-        <v>74.599999999999994</v>
+        <v>64.900000000000006</v>
       </c>
       <c r="G49" s="1">
-        <v>18.600000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="H49" s="1">
-        <v>33.700000000000003</v>
+        <v>31.5</v>
       </c>
       <c r="I49" s="1">
-        <v>29.5</v>
+        <v>29</v>
       </c>
       <c r="J49" s="1">
-        <v>32.299999999999997</v>
+        <v>22</v>
       </c>
       <c r="K49" s="1">
-        <v>39</v>
+        <v>29.1</v>
       </c>
       <c r="L49" s="1">
-        <v>57.3</v>
+        <v>50.3</v>
       </c>
       <c r="M49" s="1">
-        <v>39.4</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="N49" s="1">
-        <v>58.3</v>
+        <v>54.9</v>
       </c>
       <c r="O49" s="1">
-        <v>58</v>
+        <v>53.6</v>
       </c>
       <c r="P49" s="1">
-        <v>46.2</v>
+        <v>35.6</v>
       </c>
       <c r="Q49" s="1">
-        <v>47.3</v>
+        <v>41.5</v>
       </c>
       <c r="R49" s="1">
-        <v>36.5</v>
+        <v>35.1</v>
       </c>
       <c r="S49" s="1">
-        <v>52.4</v>
+        <v>40.6</v>
       </c>
       <c r="T49" s="1">
-        <v>34.6</v>
+        <v>31.8</v>
       </c>
       <c r="U49" s="1">
-        <v>46</v>
+        <v>47.2</v>
       </c>
       <c r="V49" s="1">
-        <v>81.599999999999994</v>
+        <v>78.3</v>
       </c>
       <c r="W49" s="1">
-        <v>67.3</v>
+        <v>63.6</v>
       </c>
       <c r="X49" s="1">
-        <v>71.8</v>
+        <v>64.7</v>
       </c>
       <c r="Y49" s="1">
-        <v>42.1</v>
+        <v>36</v>
       </c>
       <c r="Z49" s="1">
-        <v>41.5</v>
-      </c>
-      <c r="AA49" s="1">
-        <v>65.7</v>
-      </c>
-      <c r="AB49" s="1">
-        <v>69.7</v>
+        <v>33.799999999999997</v>
       </c>
     </row>
     <row r="50" spans="1:32">
       <c r="A50">
-        <v>1980</v>
+        <v>1970</v>
       </c>
       <c r="B50" s="1">
-        <v>83.5</v>
+        <v>79.2</v>
       </c>
       <c r="C50" s="1">
-        <v>49.3</v>
+        <v>51.2</v>
       </c>
       <c r="D50" s="1">
-        <v>50.5</v>
+        <v>43.5</v>
       </c>
       <c r="E50" s="1">
-        <v>64.900000000000006</v>
+        <v>51.1</v>
       </c>
       <c r="F50" s="1">
-        <v>81.900000000000006</v>
+        <v>74.599999999999994</v>
       </c>
       <c r="G50" s="1">
-        <v>23.1</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="H50" s="1">
-        <v>35.9</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="I50" s="1">
-        <v>30.6</v>
+        <v>29.5</v>
       </c>
       <c r="J50" s="1">
-        <v>39.700000000000003</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="K50" s="1">
-        <v>51.4</v>
+        <v>39</v>
       </c>
       <c r="L50" s="1">
-        <v>65.8</v>
+        <v>57.3</v>
       </c>
       <c r="M50" s="1">
-        <v>43.4</v>
+        <v>39.4</v>
       </c>
       <c r="N50" s="1">
-        <v>66.099999999999994</v>
+        <v>58.3</v>
       </c>
       <c r="O50" s="1">
-        <v>65.3</v>
+        <v>61.4</v>
       </c>
       <c r="P50" s="1">
-        <v>50.3</v>
+        <v>46.2</v>
       </c>
       <c r="Q50" s="1">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="R50" s="1">
-        <v>42.9</v>
+        <v>36.5</v>
       </c>
       <c r="S50" s="1">
-        <v>59.2</v>
+        <v>52.4</v>
       </c>
       <c r="T50" s="1">
-        <v>41.6</v>
+        <v>34.6</v>
       </c>
       <c r="U50" s="1">
-        <v>54.9</v>
+        <v>46</v>
       </c>
       <c r="V50" s="1">
-        <v>84.4</v>
+        <v>81.599999999999994</v>
       </c>
       <c r="W50" s="1">
-        <v>70.599999999999994</v>
+        <v>67.3</v>
       </c>
       <c r="X50" s="1">
-        <v>78.599999999999994</v>
+        <v>71.8</v>
       </c>
       <c r="Y50" s="1">
-        <v>51.1</v>
+        <v>42.1</v>
       </c>
       <c r="Z50" s="1">
-        <v>46.8</v>
+        <v>41.5</v>
+      </c>
+      <c r="AA50" s="1">
+        <v>65.7</v>
+      </c>
+      <c r="AB50" s="1">
+        <v>69.7</v>
       </c>
     </row>
     <row r="51" spans="1:32">
       <c r="A51">
-        <v>1990</v>
+        <v>1980</v>
       </c>
       <c r="B51" s="1">
-        <v>87.2</v>
+        <v>83.5</v>
       </c>
       <c r="C51" s="1">
-        <v>47.6</v>
+        <v>49.3</v>
       </c>
       <c r="D51" s="1">
-        <v>57.5</v>
+        <v>50.5</v>
       </c>
       <c r="E51" s="1">
-        <v>73.099999999999994</v>
+        <v>64.900000000000006</v>
       </c>
       <c r="F51" s="1">
-        <v>85.7</v>
+        <v>81.900000000000006</v>
       </c>
       <c r="G51" s="1">
         <v>23.1</v>
       </c>
       <c r="H51" s="1">
-        <v>38.1</v>
+        <v>35.9</v>
       </c>
       <c r="I51" s="1">
-        <v>33.200000000000003</v>
+        <v>30.6</v>
       </c>
       <c r="J51" s="1">
-        <v>39.4</v>
+        <v>39.700000000000003</v>
       </c>
       <c r="K51" s="1">
-        <v>55.9</v>
+        <v>51.4</v>
       </c>
       <c r="L51" s="1">
-        <v>70</v>
+        <v>65.8</v>
       </c>
       <c r="M51" s="1">
-        <v>58.8</v>
+        <v>43.4</v>
       </c>
       <c r="N51" s="1">
         <v>66.099999999999994</v>
       </c>
       <c r="O51" s="1">
-        <v>71.400000000000006</v>
+        <v>65.3</v>
       </c>
       <c r="P51" s="1">
-        <v>53.4</v>
+        <v>50.3</v>
       </c>
       <c r="Q51" s="1">
-        <v>53.5</v>
+        <v>50</v>
       </c>
       <c r="R51" s="1">
-        <v>48.5</v>
+        <v>42.9</v>
       </c>
       <c r="S51" s="1">
-        <v>66</v>
+        <v>59.2</v>
       </c>
       <c r="T51" s="1">
-        <v>47.6</v>
+        <v>41.6</v>
       </c>
       <c r="U51" s="1">
-        <v>65.400000000000006</v>
+        <v>54.9</v>
       </c>
       <c r="V51" s="1">
-        <v>84.7</v>
+        <v>84.4</v>
       </c>
       <c r="W51" s="1">
-        <v>74.400000000000006</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="X51" s="1">
-        <v>83.9</v>
+        <v>78.599999999999994</v>
       </c>
       <c r="Y51" s="1">
-        <v>56.3</v>
+        <v>51.1</v>
       </c>
       <c r="Z51" s="1">
-        <v>51.5</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="52" spans="1:32">
       <c r="A52">
+        <v>1990</v>
+      </c>
+      <c r="B52" s="1">
+        <v>87.2</v>
+      </c>
+      <c r="C52" s="1">
+        <v>47.6</v>
+      </c>
+      <c r="D52" s="1">
+        <v>57.5</v>
+      </c>
+      <c r="E52" s="1">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="F52" s="1">
+        <v>85.7</v>
+      </c>
+      <c r="G52" s="1">
+        <v>23.1</v>
+      </c>
+      <c r="H52" s="1">
+        <v>38.1</v>
+      </c>
+      <c r="I52" s="1">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="J52" s="1">
+        <v>39.4</v>
+      </c>
+      <c r="K52" s="1">
+        <v>55.9</v>
+      </c>
+      <c r="L52" s="1">
+        <v>70</v>
+      </c>
+      <c r="M52" s="1">
+        <v>58.8</v>
+      </c>
+      <c r="N52" s="1">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="O52" s="1">
+        <v>73.400000000000006</v>
+      </c>
+      <c r="P52" s="1">
+        <v>53.4</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>53.5</v>
+      </c>
+      <c r="R52" s="1">
+        <v>48.5</v>
+      </c>
+      <c r="S52" s="1">
+        <v>66</v>
+      </c>
+      <c r="T52" s="1">
+        <v>47.6</v>
+      </c>
+      <c r="U52" s="1">
+        <v>65.400000000000006</v>
+      </c>
+      <c r="V52" s="1">
+        <v>84.7</v>
+      </c>
+      <c r="W52" s="1">
+        <v>74.400000000000006</v>
+      </c>
+      <c r="X52" s="1">
+        <v>83.9</v>
+      </c>
+      <c r="Y52" s="1">
+        <v>56.3</v>
+      </c>
+      <c r="Z52" s="1">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:32">
+      <c r="A53">
         <v>2000</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B53" s="1">
         <v>89.1</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C53" s="1">
         <v>49.6</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D53" s="1">
         <v>62.7</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E53" s="1">
         <v>79.5</v>
       </c>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1">
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1">
         <v>47.7</v>
       </c>
-      <c r="I52" s="1">
+      <c r="I53" s="1">
         <v>36.200000000000003</v>
       </c>
-      <c r="J52" s="1">
+      <c r="J53" s="1">
         <v>43.9</v>
       </c>
-      <c r="K52" s="1">
+      <c r="K53" s="1">
         <v>63</v>
       </c>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1">
+      <c r="L53" s="1"/>
+      <c r="M53" s="1">
         <v>54.2</v>
       </c>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1">
+      <c r="N53" s="1"/>
+      <c r="O53" s="1">
         <v>74.5</v>
       </c>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1">
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1">
         <v>61.6</v>
       </c>
-      <c r="R52" s="1">
+      <c r="R53" s="1">
         <v>54.2</v>
       </c>
-      <c r="S52" s="1"/>
-      <c r="T52" s="1"/>
-      <c r="U52" s="1">
+      <c r="S53" s="1"/>
+      <c r="T53" s="1"/>
+      <c r="U53" s="1">
         <v>74.099999999999994</v>
       </c>
-      <c r="V52" s="1"/>
-      <c r="W52" s="1">
+      <c r="V53" s="1"/>
+      <c r="W53" s="1">
         <v>75</v>
       </c>
-      <c r="X52" s="1">
+      <c r="X53" s="1">
         <v>86</v>
       </c>
-      <c r="Y52" s="1">
+      <c r="Y53" s="1">
         <v>61.6</v>
       </c>
-      <c r="Z52" s="1">
+      <c r="Z53" s="1">
         <v>52.1</v>
       </c>
     </row>
-    <row r="56" spans="1:32" ht="15">
-      <c r="A56" s="11" t="s">
+    <row r="57" spans="1:32" ht="15">
+      <c r="A57" s="11" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="58" spans="1:32" ht="15">
-      <c r="A58" s="16" t="s">
+    <row r="59" spans="1:32" ht="15">
+      <c r="A59" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B59" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C59" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D58" s="16" t="s">
+      <c r="D59" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E58" s="16" t="s">
+      <c r="E59" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="F58" s="16" t="s">
+      <c r="F59" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G58" s="16" t="s">
+      <c r="G59" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="H58" s="16" t="s">
+      <c r="H59" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I58" s="16" t="s">
+      <c r="I59" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="J58" s="16" t="s">
+      <c r="J59" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="K58" s="16" t="s">
+      <c r="K59" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="L58" s="16" t="s">
+      <c r="L59" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="M58" s="16" t="s">
+      <c r="M59" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="N58" s="16" t="s">
+      <c r="N59" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="O58" s="16" t="s">
+      <c r="O59" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="P58" s="16" t="s">
+      <c r="P59" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="Q58" s="16" t="s">
+      <c r="Q59" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="R58" s="16" t="s">
+      <c r="R59" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="S58" s="16" t="s">
+      <c r="S59" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="T58" s="16" t="s">
+      <c r="T59" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="U58" s="16" t="s">
+      <c r="U59" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="V58" s="16" t="s">
+      <c r="V59" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="W58" s="16" t="s">
+      <c r="W59" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="X58" s="16" t="s">
+      <c r="X59" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="Y58" s="16" t="s">
+      <c r="Y59" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="Z58" s="16" t="s">
+      <c r="Z59" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="AA58" s="16" t="s">
+      <c r="AA59" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="AB58" s="16" t="s">
+      <c r="AB59" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="AC58" s="16" t="s">
+      <c r="AC59" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="AD58" s="16" t="s">
+      <c r="AD59" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AE58" s="16" t="s">
+      <c r="AE59" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="AF58" s="16" t="s">
+      <c r="AF59" s="16" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="59" spans="1:32">
-      <c r="A59" s="12">
-        <v>1865</v>
-      </c>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
-      <c r="I59" s="12"/>
-      <c r="J59" s="12"/>
-      <c r="K59" s="12"/>
-      <c r="L59" s="12"/>
-      <c r="M59" s="12"/>
-      <c r="N59" s="12"/>
-      <c r="O59" s="12"/>
-      <c r="P59" s="12"/>
-      <c r="Q59" s="12"/>
-      <c r="R59" s="12"/>
-      <c r="S59" s="12"/>
-      <c r="T59" s="12"/>
-      <c r="U59" s="12"/>
-      <c r="V59" s="12"/>
-      <c r="W59" s="12"/>
-      <c r="X59" s="12"/>
-      <c r="Y59" s="12"/>
-      <c r="Z59" s="12"/>
-      <c r="AA59" s="12"/>
-      <c r="AB59" s="13">
-        <v>15.973962510368438</v>
-      </c>
-      <c r="AC59" s="12"/>
-      <c r="AD59" s="12"/>
-      <c r="AE59" s="12"/>
     </row>
     <row r="60" spans="1:32">
       <c r="A60" s="12">
-        <v>1869</v>
-      </c>
-      <c r="B60" s="13">
-        <v>24.82533867257391</v>
-      </c>
+        <v>1865</v>
+      </c>
+      <c r="B60" s="12"/>
       <c r="C60" s="12"/>
       <c r="D60" s="12"/>
       <c r="E60" s="12"/>
@@ -3277,16 +3275,20 @@
       <c r="Y60" s="12"/>
       <c r="Z60" s="12"/>
       <c r="AA60" s="12"/>
-      <c r="AB60" s="12"/>
+      <c r="AB60" s="13">
+        <v>15.973962510368438</v>
+      </c>
       <c r="AC60" s="12"/>
       <c r="AD60" s="12"/>
       <c r="AE60" s="12"/>
     </row>
     <row r="61" spans="1:32">
       <c r="A61" s="12">
-        <v>1875</v>
-      </c>
-      <c r="B61" s="13"/>
+        <v>1869</v>
+      </c>
+      <c r="B61" s="13">
+        <v>24.82533867257391</v>
+      </c>
       <c r="C61" s="12"/>
       <c r="D61" s="12"/>
       <c r="E61" s="12"/>
@@ -3312,16 +3314,14 @@
       <c r="Y61" s="12"/>
       <c r="Z61" s="12"/>
       <c r="AA61" s="12"/>
-      <c r="AB61" s="13">
-        <v>17.277987023903513</v>
-      </c>
+      <c r="AB61" s="12"/>
       <c r="AC61" s="12"/>
       <c r="AD61" s="12"/>
       <c r="AE61" s="12"/>
     </row>
     <row r="62" spans="1:32">
       <c r="A62" s="12">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="B62" s="13"/>
       <c r="C62" s="12"/>
@@ -3343,22 +3343,22 @@
       <c r="S62" s="12"/>
       <c r="T62" s="12"/>
       <c r="U62" s="12"/>
-      <c r="V62" s="13">
-        <v>7.4535049753510974</v>
-      </c>
+      <c r="V62" s="12"/>
       <c r="W62" s="12"/>
       <c r="X62" s="12"/>
       <c r="Y62" s="12"/>
       <c r="Z62" s="12"/>
       <c r="AA62" s="12"/>
-      <c r="AB62" s="13"/>
+      <c r="AB62" s="13">
+        <v>17.277987023903513</v>
+      </c>
       <c r="AC62" s="12"/>
       <c r="AD62" s="12"/>
       <c r="AE62" s="12"/>
     </row>
     <row r="63" spans="1:32">
       <c r="A63" s="12">
-        <v>1885</v>
+        <v>1876</v>
       </c>
       <c r="B63" s="13"/>
       <c r="C63" s="12"/>
@@ -3380,26 +3380,24 @@
       <c r="S63" s="12"/>
       <c r="T63" s="12"/>
       <c r="U63" s="12"/>
-      <c r="V63" s="12"/>
+      <c r="V63" s="13">
+        <v>7.4535049753510974</v>
+      </c>
       <c r="W63" s="12"/>
       <c r="X63" s="12"/>
       <c r="Y63" s="12"/>
       <c r="Z63" s="12"/>
       <c r="AA63" s="12"/>
-      <c r="AB63" s="13">
-        <v>19.212369940391472</v>
-      </c>
+      <c r="AB63" s="13"/>
       <c r="AC63" s="12"/>
       <c r="AD63" s="12"/>
       <c r="AE63" s="12"/>
     </row>
     <row r="64" spans="1:32">
       <c r="A64" s="12">
-        <v>1895</v>
-      </c>
-      <c r="B64" s="13">
-        <v>31.833737851496533</v>
-      </c>
+        <v>1885</v>
+      </c>
+      <c r="B64" s="13"/>
       <c r="C64" s="12"/>
       <c r="D64" s="12"/>
       <c r="E64" s="12"/>
@@ -3426,7 +3424,7 @@
       <c r="Z64" s="12"/>
       <c r="AA64" s="12"/>
       <c r="AB64" s="13">
-        <v>24.121981380841554</v>
+        <v>19.212369940391472</v>
       </c>
       <c r="AC64" s="12"/>
       <c r="AD64" s="12"/>
@@ -3434,15 +3432,15 @@
     </row>
     <row r="65" spans="1:32">
       <c r="A65" s="12">
-        <v>1900</v>
-      </c>
-      <c r="B65" s="13"/>
+        <v>1895</v>
+      </c>
+      <c r="B65" s="13">
+        <v>31.833737851496533</v>
+      </c>
       <c r="C65" s="12"/>
       <c r="D65" s="12"/>
       <c r="E65" s="12"/>
-      <c r="F65" s="13">
-        <v>8.5972647960386706</v>
-      </c>
+      <c r="F65" s="12"/>
       <c r="G65" s="12"/>
       <c r="H65" s="12"/>
       <c r="I65" s="12"/>
@@ -3454,9 +3452,7 @@
       <c r="O65" s="12"/>
       <c r="P65" s="12"/>
       <c r="Q65" s="12"/>
-      <c r="R65" s="1">
-        <v>21.466933269210756</v>
-      </c>
+      <c r="R65" s="12"/>
       <c r="S65" s="12"/>
       <c r="T65" s="12"/>
       <c r="U65" s="12"/>
@@ -3466,20 +3462,24 @@
       <c r="Y65" s="12"/>
       <c r="Z65" s="12"/>
       <c r="AA65" s="12"/>
-      <c r="AB65" s="13"/>
+      <c r="AB65" s="13">
+        <v>24.121981380841554</v>
+      </c>
       <c r="AC65" s="12"/>
       <c r="AD65" s="12"/>
       <c r="AE65" s="12"/>
     </row>
     <row r="66" spans="1:32">
       <c r="A66" s="12">
-        <v>1907</v>
+        <v>1900</v>
       </c>
       <c r="B66" s="13"/>
       <c r="C66" s="12"/>
       <c r="D66" s="12"/>
       <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
+      <c r="F66" s="13">
+        <v>8.5972647960386706</v>
+      </c>
       <c r="G66" s="12"/>
       <c r="H66" s="12"/>
       <c r="I66" s="12"/>
@@ -3491,7 +3491,9 @@
       <c r="O66" s="12"/>
       <c r="P66" s="12"/>
       <c r="Q66" s="12"/>
-      <c r="R66" s="12"/>
+      <c r="R66" s="1">
+        <v>21.466933269210756</v>
+      </c>
       <c r="S66" s="12"/>
       <c r="T66" s="12"/>
       <c r="U66" s="12"/>
@@ -3501,16 +3503,14 @@
       <c r="Y66" s="12"/>
       <c r="Z66" s="12"/>
       <c r="AA66" s="12"/>
-      <c r="AB66" s="13">
-        <v>27.698910521277391</v>
-      </c>
+      <c r="AB66" s="13"/>
       <c r="AC66" s="12"/>
       <c r="AD66" s="12"/>
       <c r="AE66" s="12"/>
     </row>
     <row r="67" spans="1:32">
       <c r="A67" s="12">
-        <v>1910</v>
+        <v>1907</v>
       </c>
       <c r="B67" s="13"/>
       <c r="C67" s="12"/>
@@ -3528,9 +3528,7 @@
       <c r="O67" s="12"/>
       <c r="P67" s="12"/>
       <c r="Q67" s="12"/>
-      <c r="R67" s="12">
-        <v>24.7</v>
-      </c>
+      <c r="R67" s="12"/>
       <c r="S67" s="12"/>
       <c r="T67" s="12"/>
       <c r="U67" s="12"/>
@@ -3540,14 +3538,16 @@
       <c r="Y67" s="12"/>
       <c r="Z67" s="12"/>
       <c r="AA67" s="12"/>
-      <c r="AB67" s="13"/>
+      <c r="AB67" s="13">
+        <v>27.698910521277391</v>
+      </c>
       <c r="AC67" s="12"/>
       <c r="AD67" s="12"/>
       <c r="AE67" s="12"/>
     </row>
     <row r="68" spans="1:32">
       <c r="A68" s="12">
-        <v>1913</v>
+        <v>1910</v>
       </c>
       <c r="B68" s="13"/>
       <c r="C68" s="12"/>
@@ -3565,7 +3565,9 @@
       <c r="O68" s="12"/>
       <c r="P68" s="12"/>
       <c r="Q68" s="12"/>
-      <c r="R68" s="12"/>
+      <c r="R68" s="12">
+        <v>24.7</v>
+      </c>
       <c r="S68" s="12"/>
       <c r="T68" s="12"/>
       <c r="U68" s="12"/>
@@ -3582,11 +3584,9 @@
     </row>
     <row r="69" spans="1:32">
       <c r="A69" s="12">
-        <v>1914</v>
-      </c>
-      <c r="B69" s="13">
-        <v>38.26516565069636</v>
-      </c>
+        <v>1913</v>
+      </c>
+      <c r="B69" s="13"/>
       <c r="C69" s="12"/>
       <c r="D69" s="12"/>
       <c r="E69" s="12"/>
@@ -3612,16 +3612,18 @@
       <c r="Y69" s="12"/>
       <c r="Z69" s="12"/>
       <c r="AA69" s="12"/>
-      <c r="AB69" s="12"/>
+      <c r="AB69" s="13"/>
       <c r="AC69" s="12"/>
       <c r="AD69" s="12"/>
       <c r="AE69" s="12"/>
     </row>
-    <row r="70" spans="1:32" ht="13.5" customHeight="1">
+    <row r="70" spans="1:32">
       <c r="A70" s="12">
-        <v>1919</v>
-      </c>
-      <c r="B70" s="12"/>
+        <v>1914</v>
+      </c>
+      <c r="B70" s="13">
+        <v>38.26516565069636</v>
+      </c>
       <c r="C70" s="12"/>
       <c r="D70" s="12"/>
       <c r="E70" s="12"/>
@@ -3636,9 +3638,7 @@
       <c r="N70" s="12"/>
       <c r="O70" s="12"/>
       <c r="P70" s="12"/>
-      <c r="Q70" s="13">
-        <v>27.859047616410361</v>
-      </c>
+      <c r="Q70" s="12"/>
       <c r="R70" s="12"/>
       <c r="S70" s="12"/>
       <c r="T70" s="12"/>
@@ -3654,103 +3654,101 @@
       <c r="AD70" s="12"/>
       <c r="AE70" s="12"/>
     </row>
-    <row r="71" spans="1:32">
-      <c r="A71" s="14">
-        <v>1920</v>
-      </c>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14">
-        <v>13</v>
-      </c>
-      <c r="H71" s="14">
-        <v>11</v>
-      </c>
-      <c r="I71" s="14"/>
-      <c r="J71" s="14"/>
-      <c r="K71" s="14"/>
-      <c r="L71" s="14"/>
-      <c r="M71" s="14"/>
-      <c r="N71" s="15">
-        <v>5.3757551709299012</v>
-      </c>
-      <c r="O71" s="14">
-        <v>7</v>
-      </c>
-      <c r="P71" s="14"/>
-      <c r="Q71" s="14"/>
-      <c r="R71" s="14"/>
-      <c r="S71" s="15">
-        <v>4.3936290090937495</v>
-      </c>
-      <c r="T71" s="14"/>
-      <c r="U71" s="14"/>
-      <c r="V71" s="14">
-        <v>6</v>
-      </c>
-      <c r="W71" s="14"/>
-      <c r="X71" s="14"/>
-      <c r="Y71" s="14"/>
-      <c r="Z71" s="14"/>
-      <c r="AA71" s="14">
-        <v>30</v>
-      </c>
-      <c r="AB71" s="15">
-        <v>27.96247421409107</v>
-      </c>
-      <c r="AC71" s="14">
-        <v>10</v>
-      </c>
-      <c r="AD71" s="14"/>
-      <c r="AE71" s="14">
-        <v>10</v>
-      </c>
+    <row r="71" spans="1:32" ht="13.5" customHeight="1">
+      <c r="A71" s="12">
+        <v>1919</v>
+      </c>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="12"/>
+      <c r="K71" s="12"/>
+      <c r="L71" s="12"/>
+      <c r="M71" s="12"/>
+      <c r="N71" s="12"/>
+      <c r="O71" s="12"/>
+      <c r="P71" s="12"/>
+      <c r="Q71" s="13">
+        <v>27.859047616410361</v>
+      </c>
+      <c r="R71" s="12"/>
+      <c r="S71" s="12"/>
+      <c r="T71" s="12"/>
+      <c r="U71" s="12"/>
+      <c r="V71" s="12"/>
+      <c r="W71" s="12"/>
+      <c r="X71" s="12"/>
+      <c r="Y71" s="12"/>
+      <c r="Z71" s="12"/>
+      <c r="AA71" s="12"/>
+      <c r="AB71" s="12"/>
+      <c r="AC71" s="12"/>
+      <c r="AD71" s="12"/>
+      <c r="AE71" s="12"/>
     </row>
     <row r="72" spans="1:32">
       <c r="A72" s="14">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
       <c r="D72" s="14"/>
       <c r="E72" s="14"/>
       <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
+      <c r="G72" s="14">
+        <v>13</v>
+      </c>
+      <c r="H72" s="14">
+        <v>11</v>
+      </c>
       <c r="I72" s="14"/>
       <c r="J72" s="14"/>
       <c r="K72" s="14"/>
       <c r="L72" s="14"/>
       <c r="M72" s="14"/>
-      <c r="N72" s="15"/>
-      <c r="O72" s="14"/>
+      <c r="N72" s="15">
+        <v>5.3757551709299012</v>
+      </c>
+      <c r="O72" s="14">
+        <v>7</v>
+      </c>
       <c r="P72" s="14"/>
       <c r="Q72" s="14"/>
-      <c r="R72" s="1">
-        <v>30.616554018692632</v>
-      </c>
-      <c r="S72" s="15"/>
+      <c r="R72" s="14"/>
+      <c r="S72" s="15">
+        <v>4.3936290090937495</v>
+      </c>
       <c r="T72" s="14"/>
       <c r="U72" s="14"/>
-      <c r="V72" s="14"/>
+      <c r="V72" s="14">
+        <v>6</v>
+      </c>
       <c r="W72" s="14"/>
       <c r="X72" s="14"/>
       <c r="Y72" s="14"/>
       <c r="Z72" s="14"/>
-      <c r="AA72" s="14"/>
-      <c r="AB72" s="15"/>
-      <c r="AC72" s="14"/>
-      <c r="AD72" s="14">
-        <v>10.3</v>
-      </c>
-      <c r="AE72" s="14"/>
+      <c r="AA72" s="14">
+        <v>30</v>
+      </c>
+      <c r="AB72" s="15">
+        <v>27.96247421409107</v>
+      </c>
+      <c r="AC72" s="14">
+        <v>10</v>
+      </c>
+      <c r="AD72" s="14"/>
+      <c r="AE72" s="14">
+        <v>10</v>
+      </c>
     </row>
     <row r="73" spans="1:32">
       <c r="A73" s="14">
-        <v>1926</v>
+        <v>1921</v>
       </c>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
@@ -3768,7 +3766,9 @@
       <c r="O73" s="14"/>
       <c r="P73" s="14"/>
       <c r="Q73" s="14"/>
-      <c r="R73" s="1"/>
+      <c r="R73" s="1">
+        <v>30.616554018692632</v>
+      </c>
       <c r="S73" s="15"/>
       <c r="T73" s="14"/>
       <c r="U73" s="14"/>
@@ -3780,17 +3780,14 @@
       <c r="AA73" s="14"/>
       <c r="AB73" s="15"/>
       <c r="AC73" s="14"/>
-      <c r="AD73" s="14"/>
-      <c r="AE73" s="14">
-        <v>12.1</v>
-      </c>
-      <c r="AF73">
-        <v>11.8</v>
-      </c>
+      <c r="AD73" s="14">
+        <v>10.3</v>
+      </c>
+      <c r="AE73" s="14"/>
     </row>
     <row r="74" spans="1:32">
       <c r="A74" s="14">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -3804,14 +3801,12 @@
       <c r="K74" s="14"/>
       <c r="L74" s="14"/>
       <c r="M74" s="14"/>
-      <c r="N74" s="14"/>
+      <c r="N74" s="15"/>
       <c r="O74" s="14"/>
-      <c r="P74" s="15">
-        <v>18.87623959756025</v>
-      </c>
+      <c r="P74" s="14"/>
       <c r="Q74" s="14"/>
-      <c r="R74" s="14"/>
-      <c r="S74" s="14"/>
+      <c r="R74" s="1"/>
+      <c r="S74" s="15"/>
       <c r="T74" s="14"/>
       <c r="U74" s="14"/>
       <c r="V74" s="14"/>
@@ -3820,108 +3815,113 @@
       <c r="Y74" s="14"/>
       <c r="Z74" s="14"/>
       <c r="AA74" s="14"/>
-      <c r="AB74" s="14"/>
+      <c r="AB74" s="15"/>
       <c r="AC74" s="14"/>
       <c r="AD74" s="14"/>
-      <c r="AE74" s="14"/>
+      <c r="AE74" s="14">
+        <v>12.1</v>
+      </c>
+      <c r="AF74">
+        <v>11.8</v>
+      </c>
     </row>
     <row r="75" spans="1:32">
       <c r="A75" s="14">
-        <v>1930</v>
+        <v>1927</v>
       </c>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>
       <c r="E75" s="14"/>
       <c r="F75" s="14"/>
-      <c r="G75" s="14">
-        <v>14</v>
-      </c>
-      <c r="H75" s="14">
-        <v>13</v>
-      </c>
+      <c r="G75" s="14"/>
+      <c r="H75" s="14"/>
       <c r="I75" s="14"/>
       <c r="J75" s="14"/>
       <c r="K75" s="14"/>
       <c r="L75" s="14"/>
       <c r="M75" s="14"/>
       <c r="N75" s="14"/>
-      <c r="O75" s="14">
-        <v>10</v>
-      </c>
-      <c r="P75" s="14"/>
+      <c r="O75" s="14"/>
+      <c r="P75" s="15">
+        <v>18.87623959756025</v>
+      </c>
       <c r="Q75" s="14"/>
-      <c r="R75" s="14">
-        <v>28.5</v>
-      </c>
+      <c r="R75" s="14"/>
       <c r="S75" s="14"/>
-      <c r="T75" s="15">
-        <v>24.338525446181379</v>
-      </c>
+      <c r="T75" s="14"/>
       <c r="U75" s="14"/>
-      <c r="V75" s="14">
-        <v>10</v>
-      </c>
-      <c r="W75" s="15">
-        <v>10.216396011882644</v>
-      </c>
+      <c r="V75" s="14"/>
+      <c r="W75" s="14"/>
       <c r="X75" s="14"/>
       <c r="Y75" s="14"/>
       <c r="Z75" s="14"/>
-      <c r="AA75" s="14">
-        <v>35</v>
-      </c>
-      <c r="AB75" s="15">
-        <v>32.849564250969983</v>
-      </c>
-      <c r="AC75" s="14">
-        <v>13</v>
-      </c>
+      <c r="AA75" s="14"/>
+      <c r="AB75" s="14"/>
+      <c r="AC75" s="14"/>
       <c r="AD75" s="14"/>
-      <c r="AE75" s="14">
-        <v>13</v>
-      </c>
+      <c r="AE75" s="14"/>
     </row>
     <row r="76" spans="1:32">
       <c r="A76" s="14">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="14"/>
       <c r="E76" s="14"/>
       <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
+      <c r="G76" s="14">
+        <v>14</v>
+      </c>
+      <c r="H76" s="14">
+        <v>13</v>
+      </c>
       <c r="I76" s="14"/>
       <c r="J76" s="14"/>
       <c r="K76" s="14"/>
       <c r="L76" s="14"/>
       <c r="M76" s="14"/>
       <c r="N76" s="14"/>
-      <c r="O76" s="14"/>
+      <c r="O76" s="14">
+        <v>10</v>
+      </c>
       <c r="P76" s="14"/>
-      <c r="Q76" s="15">
-        <v>29.864393399462539</v>
-      </c>
-      <c r="R76" s="14"/>
+      <c r="Q76" s="14"/>
+      <c r="R76" s="14">
+        <v>28.5</v>
+      </c>
       <c r="S76" s="14"/>
-      <c r="T76" s="14"/>
+      <c r="T76" s="15">
+        <v>24.338525446181379</v>
+      </c>
       <c r="U76" s="14"/>
-      <c r="V76" s="14"/>
-      <c r="W76" s="14"/>
+      <c r="V76" s="14">
+        <v>10</v>
+      </c>
+      <c r="W76" s="15">
+        <v>10.216396011882644</v>
+      </c>
       <c r="X76" s="14"/>
       <c r="Y76" s="14"/>
       <c r="Z76" s="14"/>
-      <c r="AA76" s="14"/>
-      <c r="AB76" s="14"/>
-      <c r="AC76" s="14"/>
+      <c r="AA76" s="14">
+        <v>35</v>
+      </c>
+      <c r="AB76" s="15">
+        <v>32.849564250969983</v>
+      </c>
+      <c r="AC76" s="14">
+        <v>13</v>
+      </c>
       <c r="AD76" s="14"/>
-      <c r="AE76" s="14"/>
+      <c r="AE76" s="14">
+        <v>13</v>
+      </c>
     </row>
     <row r="77" spans="1:32">
       <c r="A77" s="14">
-        <v>1935</v>
+        <v>1931</v>
       </c>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -3935,12 +3935,12 @@
       <c r="K77" s="14"/>
       <c r="L77" s="14"/>
       <c r="M77" s="14"/>
-      <c r="N77" s="15">
-        <v>7.1153704466016006</v>
-      </c>
+      <c r="N77" s="14"/>
       <c r="O77" s="14"/>
       <c r="P77" s="14"/>
-      <c r="Q77" s="14"/>
+      <c r="Q77" s="15">
+        <v>29.864393399462539</v>
+      </c>
       <c r="R77" s="14"/>
       <c r="S77" s="14"/>
       <c r="T77" s="14"/>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="78" spans="1:32">
       <c r="A78" s="14">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
@@ -3966,15 +3966,15 @@
       <c r="E78" s="14"/>
       <c r="F78" s="14"/>
       <c r="G78" s="14"/>
-      <c r="H78" s="15">
-        <v>19.091253072290105</v>
-      </c>
+      <c r="H78" s="14"/>
       <c r="I78" s="14"/>
       <c r="J78" s="14"/>
       <c r="K78" s="14"/>
       <c r="L78" s="14"/>
       <c r="M78" s="14"/>
-      <c r="N78" s="14"/>
+      <c r="N78" s="15">
+        <v>7.1153704466016006</v>
+      </c>
       <c r="O78" s="14"/>
       <c r="P78" s="14"/>
       <c r="Q78" s="14"/>
@@ -3995,7 +3995,7 @@
     </row>
     <row r="79" spans="1:32">
       <c r="A79" s="14">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
@@ -4003,7 +4003,9 @@
       <c r="E79" s="14"/>
       <c r="F79" s="14"/>
       <c r="G79" s="14"/>
-      <c r="H79" s="15"/>
+      <c r="H79" s="15">
+        <v>19.091253072290105</v>
+      </c>
       <c r="I79" s="14"/>
       <c r="J79" s="14"/>
       <c r="K79" s="14"/>
@@ -4016,9 +4018,7 @@
       <c r="R79" s="14"/>
       <c r="S79" s="14"/>
       <c r="T79" s="14"/>
-      <c r="U79" s="15">
-        <v>11.197210631902117</v>
-      </c>
+      <c r="U79" s="14"/>
       <c r="V79" s="14"/>
       <c r="W79" s="14"/>
       <c r="X79" s="14"/>
@@ -4032,7 +4032,7 @@
     </row>
     <row r="80" spans="1:32">
       <c r="A80" s="14">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
@@ -4040,22 +4040,22 @@
       <c r="E80" s="14"/>
       <c r="F80" s="14"/>
       <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
+      <c r="H80" s="15"/>
       <c r="I80" s="14"/>
       <c r="J80" s="14"/>
       <c r="K80" s="14"/>
       <c r="L80" s="14"/>
       <c r="M80" s="14"/>
       <c r="N80" s="14"/>
-      <c r="O80" s="15">
-        <v>14.737441012312832</v>
-      </c>
+      <c r="O80" s="14"/>
       <c r="P80" s="14"/>
       <c r="Q80" s="14"/>
       <c r="R80" s="14"/>
       <c r="S80" s="14"/>
       <c r="T80" s="14"/>
-      <c r="U80" s="14"/>
+      <c r="U80" s="15">
+        <v>11.197210631902117</v>
+      </c>
       <c r="V80" s="14"/>
       <c r="W80" s="14"/>
       <c r="X80" s="14"/>
@@ -4069,7 +4069,7 @@
     </row>
     <row r="81" spans="1:32">
       <c r="A81" s="14">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
@@ -4084,7 +4084,9 @@
       <c r="L81" s="14"/>
       <c r="M81" s="14"/>
       <c r="N81" s="14"/>
-      <c r="O81" s="15"/>
+      <c r="O81" s="15">
+        <v>14.737441012312832</v>
+      </c>
       <c r="P81" s="14"/>
       <c r="Q81" s="14"/>
       <c r="R81" s="14"/>
@@ -4104,103 +4106,101 @@
     </row>
     <row r="82" spans="1:32">
       <c r="A82" s="14">
-        <v>1940</v>
-      </c>
-      <c r="B82" s="14">
-        <v>41</v>
-      </c>
+        <v>1939</v>
+      </c>
+      <c r="B82" s="14"/>
       <c r="C82" s="14"/>
       <c r="D82" s="14"/>
       <c r="E82" s="14"/>
       <c r="F82" s="14"/>
-      <c r="G82" s="15">
-        <v>14.979631374994044</v>
-      </c>
+      <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="14"/>
       <c r="J82" s="14"/>
-      <c r="K82" s="15">
-        <v>5.7838535408498206</v>
-      </c>
-      <c r="L82" s="14">
-        <v>6.1</v>
-      </c>
+      <c r="K82" s="14"/>
+      <c r="L82" s="14"/>
       <c r="M82" s="14"/>
       <c r="N82" s="14"/>
-      <c r="O82" s="14"/>
+      <c r="O82" s="15"/>
       <c r="P82" s="14"/>
-      <c r="Q82" s="14">
-        <v>30</v>
-      </c>
+      <c r="Q82" s="14"/>
       <c r="R82" s="14"/>
-      <c r="S82" s="15">
-        <v>7.5335821390138475</v>
-      </c>
-      <c r="T82" s="15">
-        <v>27.583662937332001</v>
-      </c>
+      <c r="S82" s="14"/>
+      <c r="T82" s="14"/>
       <c r="U82" s="14"/>
-      <c r="V82" s="15">
-        <v>14.12009761005495</v>
-      </c>
+      <c r="V82" s="14"/>
       <c r="W82" s="14"/>
       <c r="X82" s="14"/>
       <c r="Y82" s="14"/>
       <c r="Z82" s="14"/>
-      <c r="AA82" s="14">
-        <v>38</v>
-      </c>
-      <c r="AB82" s="15">
-        <v>36.418648287591672</v>
-      </c>
-      <c r="AC82" s="14">
-        <v>16</v>
-      </c>
+      <c r="AA82" s="14"/>
+      <c r="AB82" s="14"/>
+      <c r="AC82" s="14"/>
       <c r="AD82" s="14"/>
-      <c r="AE82" s="14">
-        <v>24</v>
-      </c>
+      <c r="AE82" s="14"/>
     </row>
     <row r="83" spans="1:32">
       <c r="A83" s="14">
-        <v>1941</v>
-      </c>
-      <c r="B83" s="14"/>
+        <v>1940</v>
+      </c>
+      <c r="B83" s="14">
+        <v>41</v>
+      </c>
       <c r="C83" s="14"/>
       <c r="D83" s="14"/>
       <c r="E83" s="14"/>
       <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="15">
-        <v>18.100000000000001</v>
-      </c>
+      <c r="G83" s="15">
+        <v>14.979631374994044</v>
+      </c>
+      <c r="H83" s="14"/>
       <c r="I83" s="14"/>
       <c r="J83" s="14"/>
-      <c r="K83" s="14"/>
-      <c r="L83" s="14"/>
+      <c r="K83" s="15">
+        <v>5.7838535408498206</v>
+      </c>
+      <c r="L83" s="14">
+        <v>6.1</v>
+      </c>
       <c r="M83" s="14"/>
       <c r="N83" s="14"/>
       <c r="O83" s="14"/>
       <c r="P83" s="14"/>
-      <c r="Q83" s="14"/>
+      <c r="Q83" s="14">
+        <v>30</v>
+      </c>
       <c r="R83" s="14"/>
-      <c r="S83" s="14"/>
-      <c r="T83" s="14"/>
+      <c r="S83" s="15">
+        <v>7.5335821390138475</v>
+      </c>
+      <c r="T83" s="15">
+        <v>27.583662937332001</v>
+      </c>
       <c r="U83" s="14"/>
-      <c r="V83" s="14"/>
+      <c r="V83" s="15">
+        <v>14.12009761005495</v>
+      </c>
       <c r="W83" s="14"/>
       <c r="X83" s="14"/>
       <c r="Y83" s="14"/>
       <c r="Z83" s="14"/>
-      <c r="AA83" s="14"/>
-      <c r="AB83" s="14"/>
-      <c r="AC83" s="14"/>
+      <c r="AA83" s="14">
+        <v>38</v>
+      </c>
+      <c r="AB83" s="15">
+        <v>36.418648287591672</v>
+      </c>
+      <c r="AC83" s="14">
+        <v>16</v>
+      </c>
       <c r="AD83" s="14"/>
-      <c r="AE83" s="14"/>
+      <c r="AE83" s="14">
+        <v>24</v>
+      </c>
     </row>
     <row r="84" spans="1:32">
       <c r="A84" s="14">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -4208,7 +4208,9 @@
       <c r="E84" s="14"/>
       <c r="F84" s="14"/>
       <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
+      <c r="H84" s="15">
+        <v>18.100000000000001</v>
+      </c>
       <c r="I84" s="14"/>
       <c r="J84" s="14"/>
       <c r="K84" s="14"/>
@@ -4217,9 +4219,7 @@
       <c r="N84" s="14"/>
       <c r="O84" s="14"/>
       <c r="P84" s="14"/>
-      <c r="Q84" s="15">
-        <v>33.361821561291613</v>
-      </c>
+      <c r="Q84" s="14"/>
       <c r="R84" s="14"/>
       <c r="S84" s="14"/>
       <c r="T84" s="14"/>
@@ -4232,18 +4232,14 @@
       <c r="AA84" s="14"/>
       <c r="AB84" s="14"/>
       <c r="AC84" s="14"/>
-      <c r="AD84" s="14">
-        <v>16.3</v>
-      </c>
+      <c r="AD84" s="14"/>
       <c r="AE84" s="14"/>
     </row>
     <row r="85" spans="1:32">
       <c r="A85" s="14">
-        <v>1947</v>
-      </c>
-      <c r="B85" s="15">
-        <v>49.068352134448176</v>
-      </c>
+        <v>1943</v>
+      </c>
+      <c r="B85" s="14"/>
       <c r="C85" s="14"/>
       <c r="D85" s="14"/>
       <c r="E85" s="14"/>
@@ -4258,7 +4254,9 @@
       <c r="N85" s="14"/>
       <c r="O85" s="14"/>
       <c r="P85" s="14"/>
-      <c r="Q85" s="14"/>
+      <c r="Q85" s="15">
+        <v>33.361821561291613</v>
+      </c>
       <c r="R85" s="14"/>
       <c r="S85" s="14"/>
       <c r="T85" s="14"/>
@@ -4271,601 +4269,548 @@
       <c r="AA85" s="14"/>
       <c r="AB85" s="14"/>
       <c r="AC85" s="14"/>
-      <c r="AD85" s="14"/>
+      <c r="AD85" s="14">
+        <v>16.3</v>
+      </c>
       <c r="AE85" s="14"/>
     </row>
     <row r="86" spans="1:32">
       <c r="A86" s="14">
-        <v>1950</v>
+        <v>1947</v>
       </c>
       <c r="B86" s="15">
-        <v>50.7</v>
-      </c>
-      <c r="C86" s="15">
-        <v>54.4</v>
-      </c>
-      <c r="D86" s="15">
-        <v>45.5</v>
-      </c>
-      <c r="E86" s="15">
-        <v>37</v>
-      </c>
-      <c r="F86" s="15">
-        <v>19.7</v>
-      </c>
-      <c r="G86" s="15">
-        <v>22</v>
-      </c>
-      <c r="H86" s="15">
-        <v>38.700000000000003</v>
-      </c>
-      <c r="I86" s="15">
-        <v>24.5</v>
-      </c>
-      <c r="J86" s="15">
-        <v>5.5</v>
-      </c>
-      <c r="K86" s="15">
-        <v>13.8</v>
-      </c>
-      <c r="L86" s="15">
-        <v>6.8</v>
-      </c>
-      <c r="M86" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="N86" s="15">
-        <v>11.1</v>
-      </c>
-      <c r="O86" s="15">
-        <v>22.5</v>
-      </c>
-      <c r="P86" s="15">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="Q86" s="15">
-        <v>38.299999999999997</v>
-      </c>
-      <c r="R86" s="15">
-        <v>29.3</v>
-      </c>
-      <c r="S86" s="15">
-        <v>15.2</v>
-      </c>
-      <c r="T86" s="15">
-        <v>28.2</v>
-      </c>
-      <c r="U86" s="15">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="V86" s="15">
-        <v>15.9</v>
-      </c>
-      <c r="W86" s="15">
-        <v>14.7</v>
-      </c>
-      <c r="X86" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y86" s="15">
-        <v>32</v>
-      </c>
-      <c r="Z86" s="15">
-        <v>22.1</v>
-      </c>
-      <c r="AA86" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB86" s="15">
-        <v>47.1</v>
-      </c>
-      <c r="AC86" s="15">
-        <v>18</v>
-      </c>
-      <c r="AD86" s="15">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="AE86" s="15">
-        <v>31</v>
-      </c>
+        <v>49.068352134448176</v>
+      </c>
+      <c r="C86" s="14"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="14"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="14"/>
+      <c r="K86" s="14"/>
+      <c r="L86" s="14"/>
+      <c r="M86" s="14"/>
+      <c r="N86" s="14"/>
+      <c r="O86" s="14"/>
+      <c r="P86" s="14"/>
+      <c r="Q86" s="14"/>
+      <c r="R86" s="14"/>
+      <c r="S86" s="14"/>
+      <c r="T86" s="14"/>
+      <c r="U86" s="14"/>
+      <c r="V86" s="14"/>
+      <c r="W86" s="14"/>
+      <c r="X86" s="14"/>
+      <c r="Y86" s="14"/>
+      <c r="Z86" s="14"/>
+      <c r="AA86" s="14"/>
+      <c r="AB86" s="14"/>
+      <c r="AC86" s="14"/>
+      <c r="AD86" s="14"/>
+      <c r="AE86" s="14"/>
     </row>
     <row r="87" spans="1:32">
       <c r="A87" s="14">
-        <v>1959</v>
-      </c>
-      <c r="B87" s="15"/>
-      <c r="C87" s="15"/>
-      <c r="D87" s="15"/>
-      <c r="E87" s="15"/>
-      <c r="F87" s="15"/>
-      <c r="G87" s="15"/>
-      <c r="H87" s="15"/>
-      <c r="I87" s="15"/>
-      <c r="J87" s="15"/>
-      <c r="K87" s="15"/>
-      <c r="L87" s="15"/>
-      <c r="M87" s="15"/>
-      <c r="N87" s="15"/>
-      <c r="O87" s="15"/>
-      <c r="P87" s="15"/>
-      <c r="Q87" s="15"/>
-      <c r="R87" s="15"/>
-      <c r="S87" s="15"/>
-      <c r="T87" s="15"/>
-      <c r="U87" s="15"/>
-      <c r="V87" s="15"/>
-      <c r="W87" s="15"/>
-      <c r="X87" s="15"/>
-      <c r="Y87" s="15"/>
-      <c r="Z87" s="15"/>
-      <c r="AA87" s="15"/>
-      <c r="AB87" s="15"/>
-      <c r="AC87" s="15"/>
-      <c r="AD87" s="15"/>
+        <v>1950</v>
+      </c>
+      <c r="B87" s="15">
+        <v>50.7</v>
+      </c>
+      <c r="C87" s="15">
+        <v>54.4</v>
+      </c>
+      <c r="D87" s="15">
+        <v>45.5</v>
+      </c>
+      <c r="E87" s="15">
+        <v>37</v>
+      </c>
+      <c r="F87" s="15">
+        <v>19.7</v>
+      </c>
+      <c r="G87" s="15">
+        <v>22</v>
+      </c>
+      <c r="H87" s="15">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="I87" s="15">
+        <v>24.5</v>
+      </c>
+      <c r="J87" s="15">
+        <v>5.5</v>
+      </c>
+      <c r="K87" s="15">
+        <v>13.8</v>
+      </c>
+      <c r="L87" s="15">
+        <v>6.8</v>
+      </c>
+      <c r="M87" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="N87" s="15">
+        <v>11.1</v>
+      </c>
+      <c r="O87" s="15">
+        <v>22.5</v>
+      </c>
+      <c r="P87" s="15">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="Q87" s="15">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="R87" s="15">
+        <v>29.3</v>
+      </c>
+      <c r="S87" s="15">
+        <v>15.2</v>
+      </c>
+      <c r="T87" s="15">
+        <v>28.2</v>
+      </c>
+      <c r="U87" s="15">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="V87" s="15">
+        <v>15.9</v>
+      </c>
+      <c r="W87" s="15">
+        <v>14.7</v>
+      </c>
+      <c r="X87" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y87" s="15">
+        <v>32</v>
+      </c>
+      <c r="Z87" s="15">
+        <v>22.1</v>
+      </c>
+      <c r="AA87" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB87" s="15">
+        <v>47.1</v>
+      </c>
+      <c r="AC87" s="15">
+        <v>18</v>
+      </c>
+      <c r="AD87" s="15">
+        <v>16.399999999999999</v>
+      </c>
       <c r="AE87" s="15">
-        <v>35.6</v>
-      </c>
-      <c r="AF87" s="1">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="1:32">
       <c r="A88" s="14">
+        <v>1959</v>
+      </c>
+      <c r="B88" s="15"/>
+      <c r="C88" s="15"/>
+      <c r="D88" s="15"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="15"/>
+      <c r="G88" s="15"/>
+      <c r="H88" s="15"/>
+      <c r="I88" s="15"/>
+      <c r="J88" s="15"/>
+      <c r="K88" s="15"/>
+      <c r="L88" s="15"/>
+      <c r="M88" s="15"/>
+      <c r="N88" s="15"/>
+      <c r="O88" s="15"/>
+      <c r="P88" s="15"/>
+      <c r="Q88" s="15"/>
+      <c r="R88" s="15"/>
+      <c r="S88" s="15"/>
+      <c r="T88" s="15"/>
+      <c r="U88" s="15"/>
+      <c r="V88" s="15"/>
+      <c r="W88" s="15"/>
+      <c r="X88" s="15"/>
+      <c r="Y88" s="15"/>
+      <c r="Z88" s="15"/>
+      <c r="AA88" s="15"/>
+      <c r="AB88" s="15"/>
+      <c r="AC88" s="15"/>
+      <c r="AD88" s="15"/>
+      <c r="AE88" s="15">
+        <v>35.6</v>
+      </c>
+      <c r="AF88" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="89" spans="1:32">
+      <c r="A89" s="14">
         <v>1960</v>
       </c>
-      <c r="B88" s="15">
+      <c r="B89" s="15">
         <v>60</v>
       </c>
-      <c r="C88" s="15">
+      <c r="C89" s="15">
         <v>62.1</v>
       </c>
-      <c r="D88" s="15">
+      <c r="D89" s="15">
         <v>46.2</v>
       </c>
-      <c r="E88" s="15">
+      <c r="E89" s="15">
         <v>44.3</v>
       </c>
-      <c r="F88" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="G88" s="15">
+      <c r="F89" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="15">
         <v>29</v>
       </c>
-      <c r="H88" s="15">
+      <c r="H89" s="15">
         <v>52.7</v>
       </c>
-      <c r="I88" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="J88" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="K88" s="15">
+      <c r="I89" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="15">
         <v>19.3</v>
       </c>
-      <c r="L88" s="15">
+      <c r="L89" s="15">
         <v>11.5</v>
       </c>
-      <c r="M88" s="15">
+      <c r="M89" s="15">
         <v>30.3</v>
       </c>
-      <c r="N88" s="15">
+      <c r="N89" s="15">
         <v>18.7</v>
       </c>
-      <c r="O88" s="15">
+      <c r="O89" s="15">
         <v>37.200000000000003</v>
       </c>
-      <c r="P88" s="15">
+      <c r="P89" s="15">
         <v>22.8</v>
       </c>
-      <c r="Q88" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="R88" s="15">
+      <c r="Q89" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="15">
         <v>37</v>
       </c>
-      <c r="S88" s="15">
+      <c r="S89" s="15">
         <v>23</v>
       </c>
-      <c r="T88" s="15">
+      <c r="T89" s="15">
         <v>34.6</v>
       </c>
-      <c r="U88" s="15">
+      <c r="U89" s="15">
         <v>23</v>
       </c>
-      <c r="V88" s="15">
+      <c r="V89" s="15">
         <v>30.7</v>
       </c>
-      <c r="W88" s="15">
+      <c r="W89" s="15">
         <v>19.5</v>
       </c>
-      <c r="X88" s="15">
+      <c r="X89" s="15">
         <v>25.6</v>
       </c>
-      <c r="Y88" s="15">
+      <c r="Y89" s="15">
         <v>37.6</v>
       </c>
-      <c r="Z88" s="15">
+      <c r="Z89" s="15">
         <v>36.799999999999997</v>
       </c>
-      <c r="AA88" s="15">
+      <c r="AA89" s="15">
         <v>66.900000000000006</v>
       </c>
-      <c r="AB88" s="15">
+      <c r="AB89" s="15">
         <v>55.1</v>
       </c>
-      <c r="AC88" s="15">
+      <c r="AC89" s="15">
         <v>27.7</v>
       </c>
-      <c r="AD88" s="15">
+      <c r="AD89" s="15">
         <v>24.9</v>
       </c>
-      <c r="AE88" s="15">
+      <c r="AE89" s="15">
         <v>36</v>
-      </c>
-    </row>
-    <row r="89" spans="1:32">
-      <c r="A89">
-        <v>1970</v>
-      </c>
-      <c r="B89" s="1">
-        <v>66.900000000000006</v>
-      </c>
-      <c r="C89" s="1">
-        <v>60.1</v>
-      </c>
-      <c r="D89" s="1">
-        <v>47</v>
-      </c>
-      <c r="E89" s="1">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="F89" s="1">
-        <v>34.1</v>
-      </c>
-      <c r="G89" s="1">
-        <v>40.700000000000003</v>
-      </c>
-      <c r="H89" s="1">
-        <v>63.3</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="1">
-        <v>13.7</v>
-      </c>
-      <c r="K89" s="1">
-        <v>22.2</v>
-      </c>
-      <c r="L89" s="1">
-        <v>20.5</v>
-      </c>
-      <c r="M89" s="1">
-        <v>31.9</v>
-      </c>
-      <c r="N89" s="1">
-        <v>30.5</v>
-      </c>
-      <c r="O89" s="1">
-        <v>45.6</v>
-      </c>
-      <c r="P89" s="1">
-        <v>30.8</v>
-      </c>
-      <c r="Q89" s="1">
-        <v>43.8</v>
-      </c>
-      <c r="R89" s="1">
-        <v>45.7</v>
-      </c>
-      <c r="S89" s="1">
-        <v>29.6</v>
-      </c>
-      <c r="T89" s="1">
-        <v>39.1</v>
-      </c>
-      <c r="U89" s="1">
-        <v>27.6</v>
-      </c>
-      <c r="V89" s="1">
-        <v>43</v>
-      </c>
-      <c r="W89" s="1">
-        <v>21.9</v>
-      </c>
-      <c r="X89" s="1">
-        <v>27</v>
-      </c>
-      <c r="Y89" s="1">
-        <v>40.5</v>
-      </c>
-      <c r="Z89" s="1">
-        <v>37.4</v>
-      </c>
-      <c r="AA89" s="1">
-        <v>69.900000000000006</v>
-      </c>
-      <c r="AB89" s="1">
-        <v>62</v>
-      </c>
-      <c r="AC89" s="1">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="AD89" s="1">
-        <v>32.1</v>
-      </c>
-      <c r="AE89" s="1">
-        <v>44.3</v>
-      </c>
-      <c r="AF89" s="1">
-        <v>50.8</v>
       </c>
     </row>
     <row r="90" spans="1:32">
       <c r="A90">
-        <v>1979</v>
-      </c>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
-      <c r="K90" s="1"/>
-      <c r="L90" s="1"/>
-      <c r="M90" s="1"/>
-      <c r="N90" s="1"/>
-      <c r="O90" s="1"/>
-      <c r="P90" s="1"/>
-      <c r="Q90" s="1"/>
-      <c r="R90" s="1"/>
-      <c r="S90" s="1"/>
-      <c r="T90" s="1"/>
-      <c r="U90" s="1"/>
-      <c r="V90" s="1"/>
-      <c r="W90" s="1"/>
-      <c r="X90" s="1"/>
-      <c r="Y90" s="1"/>
-      <c r="Z90" s="1"/>
-      <c r="AA90" s="1"/>
-      <c r="AB90" s="1"/>
-      <c r="AC90" s="1"/>
-      <c r="AD90" s="1"/>
+        <v>1970</v>
+      </c>
+      <c r="B90" s="1">
+        <v>66.900000000000006</v>
+      </c>
+      <c r="C90" s="1">
+        <v>60.1</v>
+      </c>
+      <c r="D90" s="1">
+        <v>47</v>
+      </c>
+      <c r="E90" s="1">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="F90" s="1">
+        <v>34.1</v>
+      </c>
+      <c r="G90" s="1">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="H90" s="1">
+        <v>63.3</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J90" s="1">
+        <v>13.7</v>
+      </c>
+      <c r="K90" s="1">
+        <v>22.2</v>
+      </c>
+      <c r="L90" s="1">
+        <v>20.5</v>
+      </c>
+      <c r="M90" s="1">
+        <v>31.9</v>
+      </c>
+      <c r="N90" s="1">
+        <v>30.5</v>
+      </c>
+      <c r="O90" s="1">
+        <v>45.6</v>
+      </c>
+      <c r="P90" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="Q90" s="1">
+        <v>43.8</v>
+      </c>
+      <c r="R90" s="1">
+        <v>45.7</v>
+      </c>
+      <c r="S90" s="1">
+        <v>29.6</v>
+      </c>
+      <c r="T90" s="1">
+        <v>39.1</v>
+      </c>
+      <c r="U90" s="1">
+        <v>27.6</v>
+      </c>
+      <c r="V90" s="1">
+        <v>43</v>
+      </c>
+      <c r="W90" s="1">
+        <v>21.9</v>
+      </c>
+      <c r="X90" s="1">
+        <v>27</v>
+      </c>
+      <c r="Y90" s="1">
+        <v>40.5</v>
+      </c>
+      <c r="Z90" s="1">
+        <v>37.4</v>
+      </c>
+      <c r="AA90" s="1">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="AB90" s="1">
+        <v>62</v>
+      </c>
+      <c r="AC90" s="1">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="AD90" s="1">
+        <v>32.1</v>
+      </c>
       <c r="AE90" s="1">
-        <v>54.9</v>
-      </c>
-      <c r="AF90" s="30">
-        <v>58</v>
+        <v>44.3</v>
+      </c>
+      <c r="AF90" s="1">
+        <v>50.8</v>
       </c>
     </row>
     <row r="91" spans="1:32">
       <c r="A91">
-        <v>1980</v>
-      </c>
-      <c r="B91" s="1">
-        <v>71.2</v>
-      </c>
-      <c r="C91" s="1">
-        <v>64.599999999999994</v>
-      </c>
-      <c r="D91" s="1">
-        <v>46.6</v>
-      </c>
-      <c r="E91" s="1">
-        <v>27.9</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="1">
-        <v>52.3</v>
-      </c>
-      <c r="H91" s="1">
-        <v>70.5</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="1">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="K91" s="1">
-        <v>22</v>
-      </c>
-      <c r="L91" s="1">
-        <v>28</v>
-      </c>
-      <c r="M91" s="1">
-        <v>33</v>
-      </c>
-      <c r="N91" s="1">
-        <v>41.9</v>
-      </c>
-      <c r="O91" s="1">
-        <v>55.1</v>
-      </c>
-      <c r="P91" s="1">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="Q91" s="1">
-        <v>47.9</v>
-      </c>
-      <c r="R91" s="1">
-        <v>52.8</v>
-      </c>
-      <c r="S91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="1">
-        <v>43.8</v>
-      </c>
-      <c r="U91" s="1">
-        <v>33.1</v>
-      </c>
-      <c r="V91" s="1">
-        <v>51.1</v>
-      </c>
-      <c r="W91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="X91" s="1">
-        <v>25.7</v>
-      </c>
-      <c r="Y91" s="1">
-        <v>37.9</v>
-      </c>
-      <c r="Z91" s="1">
-        <v>40.799999999999997</v>
-      </c>
-      <c r="AA91" s="1">
-        <v>71.8</v>
-      </c>
-      <c r="AB91" s="1">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="AC91" s="1">
-        <v>42.5</v>
-      </c>
-      <c r="AD91" s="1">
-        <v>38</v>
+        <v>1979</v>
+      </c>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="1"/>
+      <c r="M91" s="1"/>
+      <c r="N91" s="1"/>
+      <c r="O91" s="1"/>
+      <c r="P91" s="1"/>
+      <c r="Q91" s="1"/>
+      <c r="R91" s="1"/>
+      <c r="S91" s="1"/>
+      <c r="T91" s="1"/>
+      <c r="U91" s="1"/>
+      <c r="V91" s="1"/>
+      <c r="W91" s="1"/>
+      <c r="X91" s="1"/>
+      <c r="Y91" s="1"/>
+      <c r="Z91" s="1"/>
+      <c r="AA91" s="1"/>
+      <c r="AB91" s="1"/>
+      <c r="AC91" s="1"/>
+      <c r="AD91" s="1"/>
+      <c r="AE91" s="1">
+        <v>54.9</v>
+      </c>
+      <c r="AF91" s="29">
+        <v>58</v>
       </c>
     </row>
     <row r="92" spans="1:32">
       <c r="A92">
-        <v>1989</v>
-      </c>
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
-      <c r="K92" s="1"/>
-      <c r="L92" s="1"/>
-      <c r="M92" s="1"/>
-      <c r="N92" s="1"/>
-      <c r="O92" s="1"/>
-      <c r="P92" s="1"/>
-      <c r="Q92" s="1"/>
-      <c r="R92" s="1"/>
-      <c r="S92" s="1"/>
-      <c r="T92" s="1"/>
-      <c r="U92" s="1"/>
-      <c r="V92" s="1"/>
-      <c r="W92" s="1"/>
-      <c r="X92" s="1"/>
-      <c r="Y92" s="1"/>
-      <c r="Z92" s="1"/>
-      <c r="AA92" s="1"/>
-      <c r="AB92" s="1"/>
-      <c r="AC92" s="1"/>
-      <c r="AD92" s="1"/>
+        <v>1980</v>
+      </c>
+      <c r="B92" s="1">
+        <v>71.2</v>
+      </c>
+      <c r="C92" s="1">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="D92" s="1">
+        <v>46.6</v>
+      </c>
+      <c r="E92" s="1">
+        <v>27.9</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G92" s="1">
+        <v>52.3</v>
+      </c>
+      <c r="H92" s="1">
+        <v>70.5</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J92" s="1">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="K92" s="1">
+        <v>22</v>
+      </c>
+      <c r="L92" s="1">
+        <v>28</v>
+      </c>
+      <c r="M92" s="1">
+        <v>33</v>
+      </c>
+      <c r="N92" s="1">
+        <v>41.9</v>
+      </c>
+      <c r="O92" s="1">
+        <v>55.1</v>
+      </c>
+      <c r="P92" s="1">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="Q92" s="1">
+        <v>47.9</v>
+      </c>
+      <c r="R92" s="1">
+        <v>52.8</v>
+      </c>
+      <c r="S92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T92" s="1">
+        <v>43.8</v>
+      </c>
+      <c r="U92" s="1">
+        <v>33.1</v>
+      </c>
+      <c r="V92" s="1">
+        <v>51.1</v>
+      </c>
+      <c r="W92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X92" s="1">
+        <v>25.7</v>
+      </c>
+      <c r="Y92" s="1">
+        <v>37.9</v>
+      </c>
+      <c r="Z92" s="1">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="AA92" s="1">
+        <v>71.8</v>
+      </c>
+      <c r="AB92" s="1">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="AC92" s="1">
+        <v>42.5</v>
+      </c>
+      <c r="AD92" s="1">
+        <v>38</v>
+      </c>
     </row>
     <row r="93" spans="1:32">
       <c r="A93">
-        <v>1990</v>
-      </c>
-      <c r="B93" s="1">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F93" s="1">
-        <v>49.6</v>
-      </c>
-      <c r="G93" s="1">
-        <v>58.9</v>
-      </c>
-      <c r="H93" s="1">
-        <v>71.7</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K93" s="1">
-        <v>23.7</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N93" s="1">
-        <v>45.2</v>
-      </c>
-      <c r="O93" s="1">
-        <v>59.2</v>
-      </c>
-      <c r="P93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="R93" s="1">
-        <v>57.1</v>
-      </c>
-      <c r="S93" s="1">
-        <v>41</v>
-      </c>
-      <c r="T93" s="1">
-        <v>47</v>
-      </c>
-      <c r="U93" s="1">
-        <v>39</v>
-      </c>
-      <c r="V93" s="1">
-        <v>56.8</v>
-      </c>
-      <c r="W93" s="1">
-        <v>35.5</v>
-      </c>
-      <c r="X93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA93" s="1">
-        <v>74.3</v>
-      </c>
-      <c r="AB93" s="1">
-        <v>72.5</v>
-      </c>
-      <c r="AC93" s="1">
-        <v>48</v>
-      </c>
-      <c r="AD93" s="1" t="s">
-        <v>3</v>
-      </c>
+        <v>1989</v>
+      </c>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+      <c r="M93" s="1"/>
+      <c r="N93" s="1"/>
+      <c r="O93" s="1"/>
+      <c r="P93" s="1"/>
+      <c r="Q93" s="1"/>
+      <c r="R93" s="1"/>
+      <c r="S93" s="1"/>
+      <c r="T93" s="1"/>
+      <c r="U93" s="1"/>
+      <c r="V93" s="1"/>
+      <c r="W93" s="1"/>
+      <c r="X93" s="1"/>
+      <c r="Y93" s="1"/>
+      <c r="Z93" s="1"/>
+      <c r="AA93" s="1"/>
+      <c r="AB93" s="1"/>
+      <c r="AC93" s="1"/>
+      <c r="AD93" s="1"/>
     </row>
     <row r="94" spans="1:32">
       <c r="A94">
-        <v>2000</v>
+        <v>1990</v>
       </c>
       <c r="B94" s="1">
-        <v>76.599999999999994</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -4877,76 +4822,76 @@
         <v>3</v>
       </c>
       <c r="F94" s="1">
-        <v>54.4</v>
+        <v>49.6</v>
       </c>
       <c r="G94" s="1">
-        <v>64.599999999999994</v>
+        <v>58.9</v>
       </c>
       <c r="H94" s="1">
+        <v>71.7</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="1">
+        <v>23.7</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="1">
+        <v>45.2</v>
+      </c>
+      <c r="O94" s="1">
+        <v>59.2</v>
+      </c>
+      <c r="P94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="1">
+        <v>57.1</v>
+      </c>
+      <c r="S94" s="1">
+        <v>41</v>
+      </c>
+      <c r="T94" s="1">
+        <v>47</v>
+      </c>
+      <c r="U94" s="1">
+        <v>39</v>
+      </c>
+      <c r="V94" s="1">
+        <v>56.8</v>
+      </c>
+      <c r="W94" s="1">
+        <v>35.5</v>
+      </c>
+      <c r="X94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA94" s="1">
         <v>74.3</v>
       </c>
-      <c r="I94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="1">
-        <v>34.1</v>
-      </c>
-      <c r="K94" s="1">
-        <v>30.7</v>
-      </c>
-      <c r="L94" s="1">
-        <v>32.5</v>
-      </c>
-      <c r="M94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="1">
-        <v>52.6</v>
-      </c>
-      <c r="O94" s="1">
-        <v>65</v>
-      </c>
-      <c r="P94" s="1">
-        <v>49.2</v>
-      </c>
-      <c r="Q94" s="1">
-        <v>54.5</v>
-      </c>
-      <c r="R94" s="1">
-        <v>60.5</v>
-      </c>
-      <c r="S94" s="1">
-        <v>41.4</v>
-      </c>
-      <c r="T94" s="1">
-        <v>57.3</v>
-      </c>
-      <c r="U94" s="1">
-        <v>44.8</v>
-      </c>
-      <c r="V94" s="1">
-        <v>62.1</v>
-      </c>
-      <c r="W94" s="1">
-        <v>44</v>
-      </c>
-      <c r="X94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA94" s="1">
-        <v>72</v>
-      </c>
       <c r="AB94" s="1">
-        <v>76.900000000000006</v>
+        <v>72.5</v>
       </c>
       <c r="AC94" s="1">
-        <v>54.3</v>
+        <v>48</v>
       </c>
       <c r="AD94" s="1" t="s">
         <v>3</v>
@@ -4954,219 +4899,278 @@
     </row>
     <row r="95" spans="1:32">
       <c r="A95">
+        <v>2000</v>
+      </c>
+      <c r="B95" s="1">
+        <v>76.599999999999994</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F95" s="1">
+        <v>54.4</v>
+      </c>
+      <c r="G95" s="1">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="H95" s="1">
+        <v>74.3</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J95" s="1">
+        <v>34.1</v>
+      </c>
+      <c r="K95" s="1">
+        <v>30.7</v>
+      </c>
+      <c r="L95" s="1">
+        <v>32.5</v>
+      </c>
+      <c r="M95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N95" s="1">
+        <v>52.6</v>
+      </c>
+      <c r="O95" s="1">
+        <v>65</v>
+      </c>
+      <c r="P95" s="1">
+        <v>49.2</v>
+      </c>
+      <c r="Q95" s="1">
+        <v>54.5</v>
+      </c>
+      <c r="R95" s="1">
+        <v>60.5</v>
+      </c>
+      <c r="S95" s="1">
+        <v>41.4</v>
+      </c>
+      <c r="T95" s="1">
+        <v>57.3</v>
+      </c>
+      <c r="U95" s="1">
+        <v>44.8</v>
+      </c>
+      <c r="V95" s="1">
+        <v>62.1</v>
+      </c>
+      <c r="W95" s="1">
+        <v>44</v>
+      </c>
+      <c r="X95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA95" s="1">
+        <v>72</v>
+      </c>
+      <c r="AB95" s="1">
+        <v>76.900000000000006</v>
+      </c>
+      <c r="AC95" s="1">
+        <v>54.3</v>
+      </c>
+      <c r="AD95" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:32">
+      <c r="A96">
         <v>2010</v>
       </c>
-      <c r="B95" s="1">
+      <c r="B96" s="1">
         <v>79.8</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F95" s="1">
+      <c r="C96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="1">
         <v>59.4</v>
       </c>
-      <c r="G95" s="1">
+      <c r="G96" s="1">
         <v>70.599999999999994</v>
       </c>
-      <c r="H95" s="1">
+      <c r="H96" s="1">
         <v>78</v>
       </c>
-      <c r="I95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L95" s="1">
+      <c r="I96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="1">
         <v>42.4</v>
       </c>
-      <c r="M95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N95" s="1">
+      <c r="M96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="1">
         <v>64.2</v>
       </c>
-      <c r="O95" s="1">
+      <c r="O96" s="1">
         <v>64.900000000000006</v>
       </c>
-      <c r="P95" s="1">
+      <c r="P96" s="1">
         <v>58.7</v>
       </c>
-      <c r="Q95" s="1">
+      <c r="Q96" s="1">
         <v>55.2</v>
       </c>
-      <c r="R95" s="1">
+      <c r="R96" s="1">
         <v>70.2</v>
       </c>
-      <c r="S95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="T95" s="1">
+      <c r="S96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T96" s="1">
         <v>60.1</v>
       </c>
-      <c r="U95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="V95" s="1">
+      <c r="U96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="V96" s="1">
         <v>69.3</v>
       </c>
-      <c r="W95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="X95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA95" s="1">
+      <c r="W96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA96" s="1">
         <v>77.8</v>
       </c>
-      <c r="AB95" s="1">
+      <c r="AB96" s="1">
         <v>80.3</v>
       </c>
-      <c r="AC95" s="1">
+      <c r="AC96" s="1">
         <v>64.400000000000006</v>
       </c>
-      <c r="AD95" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99" spans="1:26" ht="15">
-      <c r="A99" s="11" t="s">
+      <c r="AD96" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:26" ht="15">
+      <c r="A100" s="11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="101" spans="1:26" ht="15">
-      <c r="A101" s="16" t="s">
+    <row r="102" spans="1:26" ht="15">
+      <c r="A102" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B101" s="16" t="s">
+      <c r="B102" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C101" s="16" t="s">
+      <c r="C102" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D101" s="16" t="s">
+      <c r="D102" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="16" t="s">
+      <c r="E102" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F101" s="16" t="s">
+      <c r="F102" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="G101" s="16" t="s">
+      <c r="G102" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H101" s="16" t="s">
+      <c r="H102" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="I101" s="16" t="s">
+      <c r="I102" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="J101" s="16" t="s">
+      <c r="J102" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="K101" s="16" t="s">
+      <c r="K102" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="L101" s="16" t="s">
+      <c r="L102" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="M101" s="16" t="s">
+      <c r="M102" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="N101" s="16" t="s">
+      <c r="N102" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="O101" s="16" t="s">
+      <c r="O102" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="P101" s="16" t="s">
+      <c r="P102" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="Q101" s="16" t="s">
+      <c r="Q102" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="R101" s="16" t="s">
+      <c r="R102" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="S101" s="16" t="s">
+      <c r="S102" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="T101" s="16" t="s">
+      <c r="T102" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="U101" s="16" t="s">
+      <c r="U102" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="V101" s="16" t="s">
+      <c r="V102" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="W101" s="16" t="s">
+      <c r="W102" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="X101" s="16" t="s">
+      <c r="X102" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="Y101" s="16" t="s">
+      <c r="Y102" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="Z101" s="16" t="s">
+      <c r="Z102" s="16" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="102" spans="1:26" ht="15">
-      <c r="A102" s="12">
-        <v>1865</v>
-      </c>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="2"/>
-      <c r="J102" s="2"/>
-      <c r="K102" s="2"/>
-      <c r="L102" s="2"/>
-      <c r="M102" s="2"/>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
-      <c r="P102" s="2"/>
-      <c r="Q102" s="2"/>
-      <c r="R102" s="2"/>
-      <c r="S102" s="2"/>
-      <c r="T102" s="2"/>
-      <c r="U102" s="2"/>
-      <c r="V102" s="1">
-        <v>10.981226600587174</v>
-      </c>
-      <c r="W102" s="2"/>
-      <c r="X102" s="2"/>
-      <c r="Y102" s="2"/>
     </row>
     <row r="103" spans="1:26" ht="15">
       <c r="A103" s="12">
-        <v>1869</v>
-      </c>
-      <c r="B103" s="1">
-        <v>16.412235273528619</v>
-      </c>
+        <v>1865</v>
+      </c>
+      <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
@@ -5186,16 +5190,20 @@
       <c r="S103" s="2"/>
       <c r="T103" s="2"/>
       <c r="U103" s="2"/>
-      <c r="V103" s="2"/>
+      <c r="V103" s="1">
+        <v>10.981226600587174</v>
+      </c>
       <c r="W103" s="2"/>
       <c r="X103" s="2"/>
       <c r="Y103" s="2"/>
     </row>
     <row r="104" spans="1:26" ht="15">
       <c r="A104" s="12">
-        <v>1875</v>
-      </c>
-      <c r="B104" s="2"/>
+        <v>1869</v>
+      </c>
+      <c r="B104" s="1">
+        <v>16.412235273528619</v>
+      </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
@@ -5215,16 +5223,14 @@
       <c r="S104" s="2"/>
       <c r="T104" s="2"/>
       <c r="U104" s="2"/>
-      <c r="V104" s="1">
-        <v>11.841254044492914</v>
-      </c>
+      <c r="V104" s="2"/>
       <c r="W104" s="2"/>
       <c r="X104" s="2"/>
       <c r="Y104" s="2"/>
     </row>
     <row r="105" spans="1:26" ht="15">
       <c r="A105" s="12">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -5242,20 +5248,20 @@
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
       <c r="Q105" s="2"/>
-      <c r="R105" s="1">
-        <v>3.760059812397142</v>
-      </c>
+      <c r="R105" s="2"/>
       <c r="S105" s="2"/>
       <c r="T105" s="2"/>
       <c r="U105" s="2"/>
-      <c r="V105" s="2"/>
+      <c r="V105" s="1">
+        <v>11.841254044492914</v>
+      </c>
       <c r="W105" s="2"/>
       <c r="X105" s="2"/>
       <c r="Y105" s="2"/>
     </row>
     <row r="106" spans="1:26" ht="15">
       <c r="A106" s="12">
-        <v>1885</v>
+        <v>1876</v>
       </c>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -5273,24 +5279,22 @@
       <c r="O106" s="2"/>
       <c r="P106" s="2"/>
       <c r="Q106" s="2"/>
-      <c r="R106" s="2"/>
+      <c r="R106" s="1">
+        <v>3.760059812397142</v>
+      </c>
       <c r="S106" s="2"/>
       <c r="T106" s="2"/>
       <c r="U106" s="2"/>
-      <c r="V106" s="1">
-        <v>12.749795119459268</v>
-      </c>
+      <c r="V106" s="2"/>
       <c r="W106" s="2"/>
       <c r="X106" s="2"/>
       <c r="Y106" s="2"/>
     </row>
     <row r="107" spans="1:26" ht="15">
       <c r="A107" s="12">
-        <v>1895</v>
-      </c>
-      <c r="B107" s="1">
-        <v>24.590995853004024</v>
-      </c>
+        <v>1885</v>
+      </c>
+      <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
@@ -5311,7 +5315,7 @@
       <c r="T107" s="2"/>
       <c r="U107" s="2"/>
       <c r="V107" s="1">
-        <v>15.576245989559462</v>
+        <v>12.749795119459268</v>
       </c>
       <c r="W107" s="2"/>
       <c r="X107" s="2"/>
@@ -5319,12 +5323,12 @@
     </row>
     <row r="108" spans="1:26" ht="15">
       <c r="A108" s="12">
-        <v>1900</v>
-      </c>
-      <c r="B108" s="1"/>
-      <c r="C108" s="1">
-        <v>3.1064017920301814</v>
-      </c>
+        <v>1895</v>
+      </c>
+      <c r="B108" s="1">
+        <v>24.590995853004024</v>
+      </c>
+      <c r="C108" s="2"/>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
@@ -5335,7 +5339,7 @@
       <c r="K108" s="2"/>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
-      <c r="N108" s="19"/>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" s="2"/>
       <c r="Q108" s="2"/>
@@ -5343,49 +5347,49 @@
       <c r="S108" s="2"/>
       <c r="T108" s="2"/>
       <c r="U108" s="2"/>
-      <c r="V108" s="2"/>
+      <c r="V108" s="1">
+        <v>15.576245989559462</v>
+      </c>
       <c r="W108" s="2"/>
       <c r="X108" s="2"/>
       <c r="Y108" s="2"/>
     </row>
     <row r="109" spans="1:26" ht="15">
       <c r="A109" s="12">
-        <v>1907</v>
-      </c>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
+        <v>1900</v>
+      </c>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1">
+        <v>3.1064017920301814</v>
+      </c>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
-      <c r="J109" s="12"/>
-      <c r="K109" s="12"/>
-      <c r="L109" s="12"/>
-      <c r="M109" s="12"/>
-      <c r="N109" s="12"/>
-      <c r="O109" s="12"/>
-      <c r="P109" s="12"/>
+      <c r="J109" s="2"/>
+      <c r="K109" s="2"/>
+      <c r="L109" s="2"/>
+      <c r="M109" s="2"/>
+      <c r="N109" s="19"/>
+      <c r="O109" s="2"/>
+      <c r="P109" s="2"/>
       <c r="Q109" s="2"/>
       <c r="R109" s="2"/>
       <c r="S109" s="2"/>
       <c r="T109" s="2"/>
       <c r="U109" s="2"/>
-      <c r="V109" s="1">
-        <v>17.093485515276829</v>
-      </c>
+      <c r="V109" s="2"/>
       <c r="W109" s="2"/>
       <c r="X109" s="2"/>
       <c r="Y109" s="2"/>
     </row>
     <row r="110" spans="1:26" ht="15">
-      <c r="A110">
-        <v>1914</v>
-      </c>
-      <c r="B110" s="1">
-        <v>32.61908297746789</v>
-      </c>
+      <c r="A110" s="12">
+        <v>1907</v>
+      </c>
+      <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
@@ -5406,16 +5410,19 @@
       <c r="T110" s="2"/>
       <c r="U110" s="2"/>
       <c r="V110" s="1">
-        <v>18.489934280279929</v>
+        <v>17.093485515276829</v>
       </c>
       <c r="W110" s="2"/>
       <c r="X110" s="2"/>
+      <c r="Y110" s="2"/>
     </row>
     <row r="111" spans="1:26" ht="15">
       <c r="A111">
-        <v>1919</v>
-      </c>
-      <c r="B111" s="2"/>
+        <v>1914</v>
+      </c>
+      <c r="B111" s="1">
+        <v>32.61908297746789</v>
+      </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
       <c r="E111" s="2"/>
@@ -5426,9 +5433,7 @@
       <c r="J111" s="12"/>
       <c r="K111" s="12"/>
       <c r="L111" s="12"/>
-      <c r="M111" s="13">
-        <v>16.136633940278379</v>
-      </c>
+      <c r="M111" s="12"/>
       <c r="N111" s="12"/>
       <c r="O111" s="12"/>
       <c r="P111" s="12"/>
@@ -5437,87 +5442,85 @@
       <c r="S111" s="2"/>
       <c r="T111" s="2"/>
       <c r="U111" s="2"/>
-      <c r="V111" s="2"/>
+      <c r="V111" s="1">
+        <v>18.489934280279929</v>
+      </c>
       <c r="W111" s="2"/>
       <c r="X111" s="2"/>
     </row>
     <row r="112" spans="1:26" ht="15">
       <c r="A112">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
-      <c r="D112" s="1">
-        <v>8.6999999999999993</v>
-      </c>
+      <c r="D112" s="2"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
-      <c r="J112" s="12">
-        <v>3.5</v>
-      </c>
+      <c r="J112" s="12"/>
       <c r="K112" s="12"/>
       <c r="L112" s="12"/>
-      <c r="M112" s="12"/>
+      <c r="M112" s="13">
+        <v>16.136633940278379</v>
+      </c>
       <c r="N112" s="12"/>
-      <c r="O112" s="12">
-        <v>4.4000000000000004</v>
-      </c>
+      <c r="O112" s="12"/>
       <c r="P112" s="12"/>
       <c r="Q112" s="2"/>
       <c r="R112" s="2"/>
       <c r="S112" s="2"/>
       <c r="T112" s="2"/>
       <c r="U112" s="2"/>
-      <c r="V112" s="1">
-        <v>20.291115180623258</v>
-      </c>
+      <c r="V112" s="2"/>
       <c r="W112" s="2"/>
       <c r="X112" s="2"/>
     </row>
     <row r="113" spans="1:26" ht="15">
       <c r="A113">
-        <v>1926</v>
+        <v>1920</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
-      <c r="D113" s="1"/>
+      <c r="D113" s="1">
+        <v>8.6999999999999993</v>
+      </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
-      <c r="J113" s="12"/>
+      <c r="J113" s="12">
+        <v>3.5</v>
+      </c>
       <c r="K113" s="12"/>
       <c r="L113" s="12"/>
       <c r="M113" s="12"/>
       <c r="N113" s="12"/>
-      <c r="O113" s="12"/>
+      <c r="O113" s="12">
+        <v>4.4000000000000004</v>
+      </c>
       <c r="P113" s="12"/>
       <c r="Q113" s="2"/>
       <c r="R113" s="2"/>
       <c r="S113" s="2"/>
       <c r="T113" s="2"/>
       <c r="U113" s="2"/>
-      <c r="V113" s="1"/>
+      <c r="V113" s="1">
+        <v>20.291115180623258</v>
+      </c>
       <c r="W113" s="2"/>
       <c r="X113" s="2"/>
-      <c r="Y113" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="Z113" s="1">
-        <v>6.4</v>
-      </c>
     </row>
     <row r="114" spans="1:26" ht="15">
       <c r="A114">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
+      <c r="D114" s="1"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -5525,9 +5528,7 @@
       <c r="I114" s="2"/>
       <c r="J114" s="12"/>
       <c r="K114" s="12"/>
-      <c r="L114" s="13">
-        <v>15.938107074083186</v>
-      </c>
+      <c r="L114" s="12"/>
       <c r="M114" s="12"/>
       <c r="N114" s="12"/>
       <c r="O114" s="12"/>
@@ -5537,13 +5538,19 @@
       <c r="S114" s="2"/>
       <c r="T114" s="2"/>
       <c r="U114" s="2"/>
-      <c r="V114" s="2"/>
+      <c r="V114" s="1"/>
       <c r="W114" s="2"/>
       <c r="X114" s="2"/>
+      <c r="Y114" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="Z114" s="1">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="115" spans="1:26" ht="15">
       <c r="A115">
-        <v>1930</v>
+        <v>1927</v>
       </c>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -5555,29 +5562,25 @@
       <c r="I115" s="2"/>
       <c r="J115" s="12"/>
       <c r="K115" s="12"/>
-      <c r="L115" s="12"/>
+      <c r="L115" s="13">
+        <v>15.938107074083186</v>
+      </c>
       <c r="M115" s="12"/>
       <c r="N115" s="12"/>
       <c r="O115" s="12"/>
-      <c r="P115" s="13">
-        <v>17.399999999999999</v>
-      </c>
+      <c r="P115" s="12"/>
       <c r="Q115" s="2"/>
       <c r="R115" s="2"/>
-      <c r="S115" s="1">
-        <v>6.2</v>
-      </c>
+      <c r="S115" s="2"/>
       <c r="T115" s="2"/>
       <c r="U115" s="2"/>
-      <c r="V115" s="1">
-        <v>22.93503473513946</v>
-      </c>
+      <c r="V115" s="2"/>
       <c r="W115" s="2"/>
       <c r="X115" s="2"/>
     </row>
     <row r="116" spans="1:26" ht="15">
       <c r="A116">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -5590,24 +5593,28 @@
       <c r="J116" s="12"/>
       <c r="K116" s="12"/>
       <c r="L116" s="12"/>
-      <c r="M116" s="13">
-        <v>20.751529902502156</v>
-      </c>
+      <c r="M116" s="12"/>
       <c r="N116" s="12"/>
       <c r="O116" s="12"/>
-      <c r="P116" s="12"/>
+      <c r="P116" s="13">
+        <v>17.399999999999999</v>
+      </c>
       <c r="Q116" s="2"/>
       <c r="R116" s="2"/>
-      <c r="S116" s="2"/>
+      <c r="S116" s="1">
+        <v>6.2</v>
+      </c>
       <c r="T116" s="2"/>
       <c r="U116" s="2"/>
-      <c r="V116" s="2"/>
+      <c r="V116" s="1">
+        <v>22.93503473513946</v>
+      </c>
       <c r="W116" s="2"/>
       <c r="X116" s="2"/>
     </row>
     <row r="117" spans="1:26" ht="15">
       <c r="A117">
-        <v>1935</v>
+        <v>1931</v>
       </c>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -5617,12 +5624,12 @@
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
-      <c r="J117" s="12">
-        <v>4.7</v>
-      </c>
+      <c r="J117" s="12"/>
       <c r="K117" s="12"/>
       <c r="L117" s="12"/>
-      <c r="M117" s="12"/>
+      <c r="M117" s="13">
+        <v>20.751529902502156</v>
+      </c>
       <c r="N117" s="12"/>
       <c r="O117" s="12"/>
       <c r="P117" s="12"/>
@@ -5637,19 +5644,19 @@
     </row>
     <row r="118" spans="1:26" ht="15">
       <c r="A118">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
-      <c r="E118" s="1">
-        <v>10.959868289448146</v>
-      </c>
+      <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
-      <c r="J118" s="12"/>
+      <c r="J118" s="12">
+        <v>4.7</v>
+      </c>
       <c r="K118" s="12"/>
       <c r="L118" s="12"/>
       <c r="M118" s="12"/>
@@ -5667,20 +5674,20 @@
     </row>
     <row r="119" spans="1:26" ht="15">
       <c r="A119">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
+      <c r="E119" s="1">
+        <v>10.959868289448146</v>
+      </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
-      <c r="J119" s="13"/>
-      <c r="K119" s="13">
-        <v>9.4609561958101622</v>
-      </c>
+      <c r="J119" s="12"/>
+      <c r="K119" s="12"/>
       <c r="L119" s="12"/>
       <c r="M119" s="12"/>
       <c r="N119" s="12"/>
@@ -5697,84 +5704,86 @@
     </row>
     <row r="120" spans="1:26" ht="15">
       <c r="A120">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
-      <c r="D120" s="1">
-        <v>10.943696108636283</v>
-      </c>
+      <c r="D120" s="2"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
-      <c r="H120" s="1">
-        <v>5.6620215161447227</v>
-      </c>
+      <c r="H120" s="2"/>
       <c r="I120" s="2"/>
-      <c r="J120" s="12"/>
-      <c r="K120" s="12"/>
+      <c r="J120" s="13"/>
+      <c r="K120" s="13">
+        <v>9.4609561958101622</v>
+      </c>
       <c r="L120" s="12"/>
       <c r="M120" s="12"/>
-      <c r="N120" s="12">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="O120" s="12">
-        <v>7.5</v>
-      </c>
-      <c r="P120" s="13">
-        <v>19.7</v>
-      </c>
+      <c r="N120" s="12"/>
+      <c r="O120" s="12"/>
+      <c r="P120" s="12"/>
       <c r="Q120" s="2"/>
-      <c r="R120" s="1">
-        <v>8.3848383858999256</v>
-      </c>
+      <c r="R120" s="2"/>
       <c r="S120" s="2"/>
       <c r="T120" s="2"/>
       <c r="U120" s="2"/>
-      <c r="V120" s="1">
-        <v>24.839719568216751</v>
-      </c>
+      <c r="V120" s="2"/>
       <c r="W120" s="2"/>
       <c r="X120" s="2"/>
     </row>
     <row r="121" spans="1:26" ht="15">
       <c r="A121">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
-      <c r="E121" s="1">
-        <v>12.354575557604816</v>
-      </c>
+      <c r="D121" s="1">
+        <v>10.943696108636283</v>
+      </c>
+      <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
-      <c r="H121" s="2"/>
+      <c r="H121" s="1">
+        <v>5.6620215161447227</v>
+      </c>
       <c r="I121" s="2"/>
       <c r="J121" s="12"/>
       <c r="K121" s="12"/>
       <c r="L121" s="12"/>
       <c r="M121" s="12"/>
-      <c r="N121" s="12"/>
-      <c r="O121" s="12"/>
-      <c r="P121" s="12"/>
+      <c r="N121" s="12">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="O121" s="12">
+        <v>7.5</v>
+      </c>
+      <c r="P121" s="13">
+        <v>19.7</v>
+      </c>
       <c r="Q121" s="2"/>
-      <c r="R121" s="2"/>
+      <c r="R121" s="1">
+        <v>8.3848383858999256</v>
+      </c>
       <c r="S121" s="2"/>
       <c r="T121" s="2"/>
       <c r="U121" s="2"/>
-      <c r="V121" s="2"/>
+      <c r="V121" s="1">
+        <v>24.839719568216751</v>
+      </c>
       <c r="W121" s="2"/>
       <c r="X121" s="2"/>
     </row>
     <row r="122" spans="1:26" ht="15">
       <c r="A122">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
-      <c r="E122" s="2"/>
+      <c r="E122" s="1">
+        <v>12.354575557604816</v>
+      </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
@@ -5782,9 +5791,7 @@
       <c r="J122" s="12"/>
       <c r="K122" s="12"/>
       <c r="L122" s="12"/>
-      <c r="M122" s="13">
-        <v>22.055413091163864</v>
-      </c>
+      <c r="M122" s="12"/>
       <c r="N122" s="12"/>
       <c r="O122" s="12"/>
       <c r="P122" s="12"/>
@@ -5799,11 +5806,9 @@
     </row>
     <row r="123" spans="1:26" ht="15">
       <c r="A123">
-        <v>1947</v>
-      </c>
-      <c r="B123" s="1">
-        <v>39.999919465588746</v>
-      </c>
+        <v>1943</v>
+      </c>
+      <c r="B123" s="2"/>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
@@ -5811,13 +5816,15 @@
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
-      <c r="J123" s="2"/>
-      <c r="K123" s="2"/>
-      <c r="L123" s="2"/>
-      <c r="M123" s="2"/>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
-      <c r="P123" s="2"/>
+      <c r="J123" s="12"/>
+      <c r="K123" s="12"/>
+      <c r="L123" s="12"/>
+      <c r="M123" s="13">
+        <v>22.055413091163864</v>
+      </c>
+      <c r="N123" s="12"/>
+      <c r="O123" s="12"/>
+      <c r="P123" s="12"/>
       <c r="Q123" s="2"/>
       <c r="R123" s="2"/>
       <c r="S123" s="2"/>
@@ -5827,601 +5834,632 @@
       <c r="W123" s="2"/>
       <c r="X123" s="2"/>
     </row>
-    <row r="124" spans="1:26">
+    <row r="124" spans="1:26" ht="15">
       <c r="A124">
-        <v>1950</v>
+        <v>1947</v>
       </c>
       <c r="B124" s="1">
-        <v>43.2</v>
-      </c>
-      <c r="C124" s="1">
-        <v>10.6</v>
-      </c>
-      <c r="D124" s="1">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="E124" s="1">
-        <v>24.9</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G124" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="H124" s="1">
-        <v>12.8</v>
-      </c>
-      <c r="I124" s="1"/>
-      <c r="J124" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="K124" s="1">
-        <v>15.5</v>
-      </c>
-      <c r="L124" s="1">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="M124" s="1">
-        <v>25.7</v>
-      </c>
-      <c r="N124" s="1">
-        <v>21.4</v>
-      </c>
-      <c r="O124" s="1">
-        <v>10.3</v>
-      </c>
-      <c r="P124" s="1">
-        <v>21.7</v>
-      </c>
-      <c r="Q124" s="1">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="R124" s="1">
-        <v>10.4</v>
-      </c>
-      <c r="S124" s="1">
-        <v>10.4</v>
-      </c>
-      <c r="T124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="V124" s="1">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="W124" s="1">
-        <v>14.8</v>
-      </c>
-      <c r="X124" s="1">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="Y124" s="1">
-        <v>18</v>
-      </c>
+        <v>39.999919465588746</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
+      <c r="F124" s="2"/>
+      <c r="G124" s="2"/>
+      <c r="H124" s="2"/>
+      <c r="I124" s="2"/>
+      <c r="J124" s="2"/>
+      <c r="K124" s="2"/>
+      <c r="L124" s="2"/>
+      <c r="M124" s="2"/>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
+      <c r="P124" s="2"/>
+      <c r="Q124" s="2"/>
+      <c r="R124" s="2"/>
+      <c r="S124" s="2"/>
+      <c r="T124" s="2"/>
+      <c r="U124" s="2"/>
+      <c r="V124" s="2"/>
+      <c r="W124" s="2"/>
+      <c r="X124" s="2"/>
     </row>
     <row r="125" spans="1:26">
       <c r="A125">
-        <v>1959</v>
-      </c>
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
-      <c r="E125" s="1"/>
-      <c r="F125" s="1"/>
-      <c r="G125" s="1"/>
-      <c r="H125" s="1"/>
+        <v>1950</v>
+      </c>
+      <c r="B125" s="1">
+        <v>43.2</v>
+      </c>
+      <c r="C125" s="1">
+        <v>10.6</v>
+      </c>
+      <c r="D125" s="1">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="E125" s="1">
+        <v>24.9</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G125" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="H125" s="1">
+        <v>12.8</v>
+      </c>
       <c r="I125" s="1"/>
-      <c r="J125" s="1"/>
-      <c r="K125" s="1"/>
-      <c r="L125" s="1"/>
-      <c r="M125" s="1"/>
-      <c r="N125" s="1"/>
-      <c r="O125" s="1"/>
-      <c r="P125" s="1"/>
-      <c r="Q125" s="1"/>
-      <c r="R125" s="1"/>
-      <c r="S125" s="1"/>
-      <c r="T125" s="1"/>
-      <c r="U125" s="1"/>
-      <c r="V125" s="1"/>
-      <c r="W125" s="1"/>
-      <c r="X125" s="1"/>
+      <c r="J125" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="K125" s="1">
+        <v>15.5</v>
+      </c>
+      <c r="L125" s="1">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="M125" s="1">
+        <v>25.7</v>
+      </c>
+      <c r="N125" s="1">
+        <v>21.4</v>
+      </c>
+      <c r="O125" s="1">
+        <v>10.3</v>
+      </c>
+      <c r="P125" s="1">
+        <v>21.7</v>
+      </c>
+      <c r="Q125" s="1">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="R125" s="1">
+        <v>10.4</v>
+      </c>
+      <c r="S125" s="1">
+        <v>10.4</v>
+      </c>
+      <c r="T125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="V125" s="1">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="W125" s="1">
+        <v>14.8</v>
+      </c>
+      <c r="X125" s="1">
+        <v>16.399999999999999</v>
+      </c>
       <c r="Y125" s="1">
-        <v>23.3</v>
-      </c>
-      <c r="Z125" s="1">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="126" spans="1:26">
       <c r="A126">
-        <v>1960</v>
-      </c>
-      <c r="B126" s="1">
-        <v>51.6</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1">
-        <v>22</v>
-      </c>
-      <c r="E126" s="1">
-        <v>39.1</v>
-      </c>
-      <c r="F126" s="1">
-        <v>26.5</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H126" s="1">
-        <v>17.2</v>
-      </c>
-      <c r="I126" s="1">
-        <v>7.1</v>
-      </c>
-      <c r="J126" s="1">
-        <v>12.1</v>
-      </c>
-      <c r="K126" s="1">
-        <v>29.3</v>
-      </c>
-      <c r="L126" s="1">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="M126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N126" s="1">
-        <v>28</v>
-      </c>
-      <c r="O126" s="1">
-        <v>15.3</v>
-      </c>
-      <c r="P126" s="1">
-        <v>26.9</v>
-      </c>
-      <c r="Q126" s="1">
-        <v>23</v>
-      </c>
-      <c r="R126" s="1">
-        <v>22.4</v>
-      </c>
-      <c r="S126" s="1">
-        <v>12.9</v>
-      </c>
-      <c r="T126" s="1">
-        <v>30.2</v>
-      </c>
-      <c r="U126" s="1">
-        <v>50.5</v>
-      </c>
-      <c r="V126" s="1">
-        <v>36.799999999999997</v>
-      </c>
-      <c r="W126" s="1">
-        <v>19.2</v>
-      </c>
-      <c r="X126" s="1">
-        <v>23.4</v>
+        <v>1959</v>
+      </c>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+      <c r="E126" s="1"/>
+      <c r="F126" s="1"/>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1"/>
+      <c r="K126" s="1"/>
+      <c r="L126" s="1"/>
+      <c r="M126" s="1"/>
+      <c r="N126" s="1"/>
+      <c r="O126" s="1"/>
+      <c r="P126" s="1"/>
+      <c r="Q126" s="1"/>
+      <c r="R126" s="1"/>
+      <c r="S126" s="1"/>
+      <c r="T126" s="1"/>
+      <c r="U126" s="1"/>
+      <c r="V126" s="1"/>
+      <c r="W126" s="1"/>
+      <c r="X126" s="1"/>
+      <c r="Y126" s="1">
+        <v>23.3</v>
+      </c>
+      <c r="Z126" s="1">
+        <v>27</v>
       </c>
     </row>
     <row r="127" spans="1:26">
       <c r="A127">
-        <v>1970</v>
+        <v>1960</v>
       </c>
       <c r="B127" s="1">
-        <v>56.2</v>
-      </c>
-      <c r="C127" s="1">
-        <v>28.5</v>
+        <v>51.6</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="D127" s="1">
-        <v>32.200000000000003</v>
+        <v>22</v>
       </c>
       <c r="E127" s="1">
-        <v>49.7</v>
+        <v>39.1</v>
       </c>
       <c r="F127" s="1">
+        <v>26.5</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H127" s="1">
+        <v>17.2</v>
+      </c>
+      <c r="I127" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="J127" s="1">
+        <v>12.1</v>
+      </c>
+      <c r="K127" s="1">
+        <v>29.3</v>
+      </c>
+      <c r="L127" s="1">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="M127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N127" s="1">
+        <v>28</v>
+      </c>
+      <c r="O127" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="P127" s="1">
+        <v>26.9</v>
+      </c>
+      <c r="Q127" s="1">
+        <v>23</v>
+      </c>
+      <c r="R127" s="1">
+        <v>22.4</v>
+      </c>
+      <c r="S127" s="1">
+        <v>12.9</v>
+      </c>
+      <c r="T127" s="1">
+        <v>30.2</v>
+      </c>
+      <c r="U127" s="1">
+        <v>50.5</v>
+      </c>
+      <c r="V127" s="1">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="W127" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="X127" s="1">
         <v>23.4</v>
-      </c>
-      <c r="G127" s="1">
-        <v>11.5</v>
-      </c>
-      <c r="H127" s="1">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="I127" s="1">
-        <v>16</v>
-      </c>
-      <c r="J127" s="1">
-        <v>20.5</v>
-      </c>
-      <c r="K127" s="1">
-        <v>37.5</v>
-      </c>
-      <c r="L127" s="1">
-        <v>21.8</v>
-      </c>
-      <c r="M127" s="1">
-        <v>31</v>
-      </c>
-      <c r="N127" s="1">
-        <v>37.700000000000003</v>
-      </c>
-      <c r="O127" s="1">
-        <v>20.5</v>
-      </c>
-      <c r="P127" s="1">
-        <v>31.7</v>
-      </c>
-      <c r="Q127" s="1">
-        <v>24.9</v>
-      </c>
-      <c r="R127" s="1">
-        <v>34.9</v>
-      </c>
-      <c r="S127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="T127" s="1">
-        <v>30.4</v>
-      </c>
-      <c r="U127" s="1">
-        <v>50.3</v>
-      </c>
-      <c r="V127" s="1">
-        <v>43.3</v>
-      </c>
-      <c r="W127" s="1">
-        <v>23.8</v>
-      </c>
-      <c r="X127" s="1">
-        <v>26.1</v>
-      </c>
-      <c r="Y127" s="1">
-        <v>31.2</v>
-      </c>
-      <c r="Z127" s="1">
-        <v>35.799999999999997</v>
       </c>
     </row>
     <row r="128" spans="1:26">
       <c r="A128">
+        <v>1970</v>
+      </c>
+      <c r="B128" s="1">
+        <v>56.2</v>
+      </c>
+      <c r="C128" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="D128" s="1">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="E128" s="1">
+        <v>49.7</v>
+      </c>
+      <c r="F128" s="1">
+        <v>23.4</v>
+      </c>
+      <c r="G128" s="1">
+        <v>11.5</v>
+      </c>
+      <c r="H128" s="1">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="I128" s="1">
+        <v>16</v>
+      </c>
+      <c r="J128" s="1">
+        <v>20.5</v>
+      </c>
+      <c r="K128" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="L128" s="1">
+        <v>21.8</v>
+      </c>
+      <c r="M128" s="1">
+        <v>31</v>
+      </c>
+      <c r="N128" s="1">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="O128" s="1">
+        <v>20.5</v>
+      </c>
+      <c r="P128" s="1">
+        <v>31.7</v>
+      </c>
+      <c r="Q128" s="1">
+        <v>24.9</v>
+      </c>
+      <c r="R128" s="1">
+        <v>34.9</v>
+      </c>
+      <c r="S128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T128" s="1">
+        <v>30.4</v>
+      </c>
+      <c r="U128" s="1">
+        <v>50.3</v>
+      </c>
+      <c r="V128" s="1">
+        <v>43.3</v>
+      </c>
+      <c r="W128" s="1">
+        <v>23.8</v>
+      </c>
+      <c r="X128" s="1">
+        <v>26.1</v>
+      </c>
+      <c r="Y128" s="1">
+        <v>31.2</v>
+      </c>
+      <c r="Z128" s="1">
+        <v>35.799999999999997</v>
+      </c>
+    </row>
+    <row r="129" spans="1:26">
+      <c r="A129">
         <v>1979</v>
       </c>
-      <c r="B128" s="1"/>
-      <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
-      <c r="E128" s="1"/>
-      <c r="F128" s="1"/>
-      <c r="G128" s="1"/>
-      <c r="H128" s="1"/>
-      <c r="I128" s="1"/>
-      <c r="J128" s="1"/>
-      <c r="K128" s="1"/>
-      <c r="L128" s="1"/>
-      <c r="M128" s="1"/>
-      <c r="N128" s="1"/>
-      <c r="O128" s="1"/>
-      <c r="P128" s="1"/>
-      <c r="Q128" s="1"/>
-      <c r="R128" s="1"/>
-      <c r="S128" s="1"/>
-      <c r="T128" s="1"/>
-      <c r="U128" s="1"/>
-      <c r="V128" s="1"/>
-      <c r="W128" s="1"/>
-      <c r="X128" s="1"/>
-      <c r="Y128" s="1">
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1"/>
+      <c r="K129" s="1"/>
+      <c r="L129" s="1"/>
+      <c r="M129" s="1"/>
+      <c r="N129" s="1"/>
+      <c r="O129" s="1"/>
+      <c r="P129" s="1"/>
+      <c r="Q129" s="1"/>
+      <c r="R129" s="1"/>
+      <c r="S129" s="1"/>
+      <c r="T129" s="1"/>
+      <c r="U129" s="1"/>
+      <c r="V129" s="1"/>
+      <c r="W129" s="1"/>
+      <c r="X129" s="1"/>
+      <c r="Y129" s="1">
         <v>40.4</v>
       </c>
-      <c r="Z128" s="30">
+      <c r="Z129" s="29">
         <v>42.7</v>
       </c>
     </row>
-    <row r="129" spans="1:24">
-      <c r="A129">
+    <row r="130" spans="1:26">
+      <c r="A130">
         <v>1980</v>
       </c>
-      <c r="B129" s="1">
+      <c r="B130" s="1">
         <v>58.8</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1">
         <v>42.1</v>
       </c>
-      <c r="E129" s="1">
+      <c r="E130" s="1">
         <v>59.7</v>
       </c>
-      <c r="F129" s="1">
+      <c r="F130" s="1">
         <v>22.1</v>
       </c>
-      <c r="G129" s="1">
+      <c r="G130" s="1">
         <v>14.3</v>
       </c>
-      <c r="H129" s="1">
+      <c r="H130" s="1">
         <v>19.3</v>
       </c>
-      <c r="I129" s="1">
+      <c r="I130" s="1">
         <v>19.100000000000001</v>
       </c>
-      <c r="J129" s="1">
+      <c r="J130" s="1">
         <v>28</v>
       </c>
-      <c r="K129" s="1">
+      <c r="K130" s="1">
         <v>46.2</v>
       </c>
-      <c r="L129" s="1">
+      <c r="L130" s="1">
         <v>25.1</v>
       </c>
-      <c r="M129" s="1">
+      <c r="M130" s="1">
         <v>32.4</v>
       </c>
-      <c r="N129" s="1">
+      <c r="N130" s="1">
         <v>45.3</v>
       </c>
-      <c r="O129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P129" s="1">
+      <c r="O130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P130" s="1">
         <v>33.799999999999997</v>
       </c>
-      <c r="Q129" s="1">
+      <c r="Q130" s="1">
         <v>27.1</v>
       </c>
-      <c r="R129" s="1">
+      <c r="R130" s="1">
         <v>40.9</v>
       </c>
-      <c r="S129" s="1">
+      <c r="S130" s="1">
         <v>14.7</v>
       </c>
-      <c r="T129" s="1">
+      <c r="T130" s="1">
         <v>32.200000000000003</v>
       </c>
-      <c r="U129" s="1">
+      <c r="U130" s="1">
         <v>51.1</v>
       </c>
-      <c r="V129" s="1">
+      <c r="V130" s="1">
         <v>55.8</v>
       </c>
-      <c r="W129" s="1">
+      <c r="W130" s="1">
         <v>32.9</v>
       </c>
-      <c r="X129" s="1">
+      <c r="X130" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="130" spans="1:24">
-      <c r="A130">
+    <row r="131" spans="1:26">
+      <c r="A131">
         <v>1990</v>
       </c>
-      <c r="B130" s="1">
+      <c r="B131" s="1">
         <v>61.8</v>
       </c>
-      <c r="C130" s="1">
+      <c r="C131" s="1">
         <v>41.3</v>
       </c>
-      <c r="D130" s="1">
+      <c r="D131" s="1">
         <v>45.6</v>
       </c>
-      <c r="E130" s="1">
+      <c r="E131" s="1">
         <v>59.5</v>
       </c>
-      <c r="F130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H130" s="1">
+      <c r="F131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H131" s="1">
         <v>19</v>
       </c>
-      <c r="I130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J130" s="1">
+      <c r="I131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J131" s="1">
         <v>32.200000000000003</v>
       </c>
-      <c r="K130" s="1">
+      <c r="K131" s="1">
         <v>49.3</v>
       </c>
-      <c r="L130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N130" s="1">
+      <c r="L131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N131" s="1">
         <v>47.5</v>
       </c>
-      <c r="O130" s="1">
+      <c r="O131" s="1">
         <v>22.7</v>
       </c>
-      <c r="P130" s="1">
+      <c r="P131" s="1">
         <v>36.299999999999997</v>
       </c>
-      <c r="Q130" s="1">
+      <c r="Q131" s="1">
         <v>31.6</v>
       </c>
-      <c r="R130" s="1">
+      <c r="R131" s="1">
         <v>48</v>
       </c>
-      <c r="S130" s="1">
+      <c r="S131" s="1">
         <v>28</v>
       </c>
-      <c r="T130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U130" s="1">
+      <c r="T131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U131" s="1">
         <v>50.3</v>
       </c>
-      <c r="V130" s="1">
+      <c r="V131" s="1">
         <v>60.8</v>
       </c>
-      <c r="W130" s="1">
+      <c r="W131" s="1">
         <v>36.4</v>
       </c>
-      <c r="X130" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="131" spans="1:24">
-      <c r="A131">
+      <c r="X131" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:26">
+      <c r="A132">
         <v>2000</v>
       </c>
-      <c r="B131" s="1">
+      <c r="B132" s="1">
         <v>62.3</v>
       </c>
-      <c r="C131" s="1">
+      <c r="C132" s="1">
         <v>44.9</v>
       </c>
-      <c r="D131" s="1">
+      <c r="D132" s="1">
         <v>49.6</v>
       </c>
-      <c r="E131" s="1">
+      <c r="E132" s="1">
         <v>61.6</v>
       </c>
-      <c r="F131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G131" s="1">
+      <c r="F132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G132" s="1">
         <v>27.2</v>
       </c>
-      <c r="H131" s="1">
+      <c r="H132" s="1">
         <v>20.2</v>
       </c>
-      <c r="I131" s="1">
+      <c r="I132" s="1">
         <v>24.3</v>
       </c>
-      <c r="J131" s="1">
+      <c r="J132" s="1">
         <v>41.4</v>
-      </c>
-      <c r="K131" s="1">
-        <v>53.9</v>
-      </c>
-      <c r="L131" s="1">
-        <v>33.9</v>
-      </c>
-      <c r="M131" s="1">
-        <v>39.5</v>
-      </c>
-      <c r="N131" s="1">
-        <v>50.2</v>
-      </c>
-      <c r="O131" s="1">
-        <v>21.9</v>
-      </c>
-      <c r="P131" s="1">
-        <v>51.2</v>
-      </c>
-      <c r="Q131" s="1">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="R131" s="1">
-        <v>53.5</v>
-      </c>
-      <c r="S131" s="1">
-        <v>29.9</v>
-      </c>
-      <c r="T131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U131" s="1">
-        <v>47.4</v>
-      </c>
-      <c r="V131" s="1">
-        <v>63.6</v>
-      </c>
-      <c r="W131" s="1">
-        <v>44.2</v>
-      </c>
-      <c r="X131" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="132" spans="1:24">
-      <c r="A132">
-        <v>2010</v>
-      </c>
-      <c r="B132" s="1">
-        <v>64.7</v>
-      </c>
-      <c r="C132" s="1">
-        <v>52.2</v>
-      </c>
-      <c r="D132" s="1">
-        <v>56.6</v>
-      </c>
-      <c r="E132" s="1">
-        <v>63.5</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I132" s="1">
-        <v>29.3</v>
-      </c>
-      <c r="J132" s="1">
-        <v>52.9</v>
       </c>
       <c r="K132" s="1">
         <v>53.9</v>
       </c>
       <c r="L132" s="1">
+        <v>33.9</v>
+      </c>
+      <c r="M132" s="1">
+        <v>39.5</v>
+      </c>
+      <c r="N132" s="1">
+        <v>50.2</v>
+      </c>
+      <c r="O132" s="1">
+        <v>21.9</v>
+      </c>
+      <c r="P132" s="1">
+        <v>51.2</v>
+      </c>
+      <c r="Q132" s="1">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="R132" s="1">
+        <v>53.5</v>
+      </c>
+      <c r="S132" s="1">
+        <v>29.9</v>
+      </c>
+      <c r="T132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U132" s="1">
+        <v>47.4</v>
+      </c>
+      <c r="V132" s="1">
+        <v>63.6</v>
+      </c>
+      <c r="W132" s="1">
+        <v>44.2</v>
+      </c>
+      <c r="X132" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:26">
+      <c r="A133">
+        <v>2010</v>
+      </c>
+      <c r="B133" s="1">
+        <v>64.7</v>
+      </c>
+      <c r="C133" s="1">
+        <v>52.2</v>
+      </c>
+      <c r="D133" s="1">
+        <v>56.6</v>
+      </c>
+      <c r="E133" s="1">
+        <v>63.5</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I133" s="1">
+        <v>29.3</v>
+      </c>
+      <c r="J133" s="1">
+        <v>52.9</v>
+      </c>
+      <c r="K133" s="1">
+        <v>53.9</v>
+      </c>
+      <c r="L133" s="1">
         <v>46.4</v>
       </c>
-      <c r="M132" s="1">
+      <c r="M133" s="1">
         <v>40.4</v>
       </c>
-      <c r="N132" s="1">
+      <c r="N133" s="1">
         <v>60.7</v>
       </c>
-      <c r="O132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P132" s="1">
+      <c r="O133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P133" s="1">
         <v>52.6</v>
       </c>
-      <c r="Q132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="R132" s="1">
+      <c r="Q133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R133" s="1">
         <v>59</v>
       </c>
-      <c r="S132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="T132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U132" s="1">
+      <c r="S133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U133" s="1">
         <v>54</v>
       </c>
-      <c r="V132" s="1">
+      <c r="V133" s="1">
         <v>72.5</v>
       </c>
-      <c r="W132" s="1">
+      <c r="W133" s="1">
         <v>52</v>
       </c>
-      <c r="X132" s="1" t="s">
+      <c r="X133" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9301,19 +9339,19 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15">
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="L4" s="29" t="s">
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="L4" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="M4" s="29"/>
+      <c r="M4" s="31"/>
     </row>
     <row r="5" spans="1:13" ht="15">
       <c r="A5" s="2" t="s">

--- a/rtss-mexico/src/main/resources/latinamerica/Latin-America-Urbanization.xlsx
+++ b/rtss-mexico/src/main/resources/latinamerica/Latin-America-Urbanization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-mexico\src\main\resources\latinamerica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4C60C3-DBC3-4CE1-AAA8-8659F1F6047B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1F322D-0800-403A-849C-761EDC697843}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17595" yWindow="900" windowWidth="19965" windowHeight="22275" activeTab="9" xr2:uid="{CF6A2AB8-34C5-4CDB-9A0B-0A9EB6FB1FEF}"/>
+    <workbookView xWindow="14805" yWindow="1035" windowWidth="14655" windowHeight="22275" activeTab="9" xr2:uid="{CF6A2AB8-34C5-4CDB-9A0B-0A9EB6FB1FEF}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -560,11 +560,11 @@
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1602,11 +1602,11 @@
       <c r="X21" s="16"/>
       <c r="Y21" s="16"/>
       <c r="Z21" s="16"/>
-      <c r="AA21">
-        <v>31.2</v>
+      <c r="AA21" s="1">
+        <v>27</v>
       </c>
       <c r="AB21">
-        <v>33.1</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="22" spans="1:28" ht="15">
@@ -1671,10 +1671,10 @@
       <c r="Y23" s="16"/>
       <c r="Z23" s="16"/>
       <c r="AA23">
-        <v>31.7</v>
+        <v>28.3</v>
       </c>
       <c r="AB23">
-        <v>33.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="24" spans="1:28" ht="15">
@@ -2619,7 +2619,7 @@
       <c r="L46" s="16"/>
       <c r="M46" s="16"/>
       <c r="N46" s="16"/>
-      <c r="O46" s="32">
+      <c r="O46" s="31">
         <v>37.200000000000003</v>
       </c>
       <c r="P46" s="16"/>
@@ -9339,19 +9339,19 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15">
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="L4" s="31" t="s">
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="L4" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="M4" s="31"/>
+      <c r="M4" s="32"/>
     </row>
     <row r="5" spans="1:13" ht="15">
       <c r="A5" s="2" t="s">

--- a/rtss-mexico/src/main/resources/latinamerica/Latin-America-Urbanization.xlsx
+++ b/rtss-mexico/src/main/resources/latinamerica/Latin-America-Urbanization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-mexico\src\main\resources\latinamerica\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-mexico\src\main\resources\latinamerica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1F322D-0800-403A-849C-761EDC697843}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802ED2EB-8FAA-4136-AF4A-7EFD45E3E00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14805" yWindow="1035" windowWidth="14655" windowHeight="22275" activeTab="9" xr2:uid="{CF6A2AB8-34C5-4CDB-9A0B-0A9EB6FB1FEF}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="9" xr2:uid="{CF6A2AB8-34C5-4CDB-9A0B-0A9EB6FB1FEF}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="Data-8" sheetId="11" r:id="rId9"/>
     <sheet name="UR" sheetId="9" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +32,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -388,7 +393,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,7 +515,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -529,10 +534,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -552,14 +553,10 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -903,14 +900,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A5BC77-576E-4DC4-B117-3E379681AD07}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3"/>
     </row>
   </sheetData>
@@ -920,161 +917,161 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC336925-0078-4AF9-986A-8BA8236BAFF3}">
-  <dimension ref="A1:AF133"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:AF134"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:28" ht="15">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="11" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="15">
-      <c r="A3" s="16" t="s">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="L3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="N3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="O3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="16" t="s">
+      <c r="P3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="Q3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="R3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="S3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="T3" s="16" t="s">
+      <c r="T3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="U3" s="16" t="s">
+      <c r="U3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="V3" s="16" t="s">
+      <c r="V3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="16" t="s">
+      <c r="W3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="X3" s="16" t="s">
+      <c r="X3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="Y3" s="16" t="s">
+      <c r="Y3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="Z3" s="16" t="s">
+      <c r="Z3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AA3" s="16" t="s">
+      <c r="AA3" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="AB3" s="16" t="s">
+      <c r="AB3" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="15">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>1895</v>
       </c>
       <c r="B4" s="1">
         <v>37.4</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="16"/>
-      <c r="W4" s="16"/>
-      <c r="X4" s="16"/>
-      <c r="Y4" s="16"/>
-      <c r="Z4" s="16"/>
-    </row>
-    <row r="5" spans="1:28" ht="15">
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="12"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="12"/>
+      <c r="Y4" s="12"/>
+      <c r="Z4" s="12"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>1897</v>
       </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
-      <c r="T5" s="16"/>
-      <c r="U5" s="16"/>
-      <c r="V5" s="16"/>
-      <c r="W5" s="16"/>
-      <c r="X5" s="16"/>
-      <c r="Y5" s="16"/>
-      <c r="Z5" s="16"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="12"/>
       <c r="AA5">
         <v>15</v>
       </c>
@@ -1082,288 +1079,288 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="15">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>1899</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="16"/>
-      <c r="Z6" s="16"/>
-    </row>
-    <row r="7" spans="1:28" ht="15">
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>1900</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
       <c r="D7" s="1">
         <v>26.9</v>
       </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="16"/>
-      <c r="Z7" s="16"/>
-    </row>
-    <row r="8" spans="1:28" ht="15">
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>1901</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="16"/>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="16"/>
-    </row>
-    <row r="9" spans="1:28" ht="15">
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="12"/>
+      <c r="Y8" s="12"/>
+      <c r="Z8" s="12"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>1906</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
       <c r="P9" s="1">
         <v>33</v>
       </c>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="16"/>
-    </row>
-    <row r="10" spans="1:28" ht="15">
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="12"/>
+      <c r="V9" s="12"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="12"/>
+      <c r="Y9" s="12"/>
+      <c r="Z9" s="12"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>1910</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
-      <c r="Y10" s="16"/>
-      <c r="Z10" s="16"/>
-    </row>
-    <row r="11" spans="1:28" ht="15">
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
+      <c r="V10" s="12"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="12"/>
+      <c r="Y10" s="12"/>
+      <c r="Z10" s="12"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>1911</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="16"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-    </row>
-    <row r="12" spans="1:28" ht="15">
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="12"/>
+      <c r="V11" s="12"/>
+      <c r="W11" s="12"/>
+      <c r="X11" s="12"/>
+      <c r="Y11" s="12"/>
+      <c r="Z11" s="12"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>1913</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="16"/>
-      <c r="Y12" s="16"/>
-      <c r="Z12" s="16"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="12"/>
+      <c r="V12" s="12"/>
+      <c r="W12" s="12"/>
+      <c r="X12" s="12"/>
+      <c r="Y12" s="12"/>
+      <c r="Z12" s="12"/>
       <c r="AA12">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="15">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>1914</v>
       </c>
       <c r="B13" s="1">
         <v>52.7</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="16"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
-      <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
-    </row>
-    <row r="14" spans="1:28" ht="15">
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="12"/>
+      <c r="V13" s="12"/>
+      <c r="W13" s="12"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12"/>
+      <c r="Z13" s="12"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>1920</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
       <c r="K14" s="1">
         <v>16.100000000000001</v>
       </c>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
       <c r="P14" s="1">
         <v>34.200000000000003</v>
       </c>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="16"/>
-      <c r="Y14" s="16"/>
-      <c r="Z14" s="16"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="12"/>
+      <c r="V14" s="12"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="12"/>
+      <c r="Z14" s="12"/>
       <c r="AA14">
         <v>15</v>
       </c>
@@ -1371,67 +1368,67 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="15">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>1921</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
       <c r="H15" s="1">
         <v>26.6</v>
       </c>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="16"/>
-      <c r="Z15" s="16"/>
-    </row>
-    <row r="16" spans="1:28" ht="15">
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="12"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>1926</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
       <c r="H16" s="1"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
-      <c r="Y16" s="16"/>
-      <c r="Z16" s="16"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="12"/>
+      <c r="V16" s="12"/>
+      <c r="W16" s="12"/>
+      <c r="X16" s="12"/>
+      <c r="Y16" s="12"/>
+      <c r="Z16" s="12"/>
       <c r="AA16">
         <v>17.899999999999999</v>
       </c>
@@ -1439,169 +1436,169 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="15">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>1930</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
       <c r="O17" s="1">
         <v>33.5</v>
       </c>
-      <c r="P17" s="16"/>
+      <c r="P17" s="12"/>
       <c r="Q17" s="1">
         <v>30.1</v>
       </c>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="12"/>
       <c r="T17" s="1">
         <v>38.299999999999997</v>
       </c>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
+      <c r="U17" s="12"/>
+      <c r="V17" s="12"/>
+      <c r="W17" s="12"/>
       <c r="X17" s="1">
         <v>49.4</v>
       </c>
       <c r="Y17" s="1">
         <v>30.3</v>
       </c>
-      <c r="Z17" s="16"/>
-    </row>
-    <row r="18" spans="1:28" ht="15">
+      <c r="Z17" s="12"/>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>1931</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="16"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
-      <c r="Y18" s="16"/>
-      <c r="Z18" s="16"/>
-    </row>
-    <row r="19" spans="1:28" ht="15">
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="12"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="12"/>
+      <c r="Z18" s="12"/>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>1935</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
       <c r="K19" s="1">
         <v>18</v>
       </c>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="16"/>
-      <c r="Y19" s="16"/>
-      <c r="Z19" s="16"/>
-    </row>
-    <row r="20" spans="1:28" ht="15">
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="12"/>
+      <c r="T19" s="12"/>
+      <c r="U19" s="12"/>
+      <c r="V19" s="12"/>
+      <c r="W19" s="12"/>
+      <c r="X19" s="12"/>
+      <c r="Y19" s="12"/>
+      <c r="Z19" s="12"/>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>1936</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
       <c r="F20" s="1">
         <v>35</v>
       </c>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="16"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="16"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="16"/>
-      <c r="Y20" s="16"/>
-      <c r="Z20" s="16"/>
-    </row>
-    <row r="21" spans="1:28" ht="15">
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+      <c r="U20" s="12"/>
+      <c r="V20" s="12"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="12"/>
+      <c r="Z20" s="12"/>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>1937</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="16"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="16"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
-      <c r="X21" s="16"/>
-      <c r="Y21" s="16"/>
-      <c r="Z21" s="16"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="12"/>
+      <c r="Z21" s="12"/>
       <c r="AA21" s="1">
         <v>27</v>
       </c>
@@ -1609,67 +1606,67 @@
         <v>28.9</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="15">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>1938</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
       <c r="L22" s="1">
         <v>29.1</v>
       </c>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
-      <c r="S22" s="16"/>
-      <c r="T22" s="16"/>
-      <c r="U22" s="16"/>
-      <c r="V22" s="16"/>
-      <c r="W22" s="16"/>
-      <c r="X22" s="16"/>
-      <c r="Y22" s="16"/>
-      <c r="Z22" s="16"/>
-    </row>
-    <row r="23" spans="1:28" ht="15">
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="12"/>
+      <c r="S22" s="12"/>
+      <c r="T22" s="12"/>
+      <c r="U22" s="12"/>
+      <c r="V22" s="12"/>
+      <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="12"/>
+      <c r="Z22" s="12"/>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>1939</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="16"/>
-      <c r="S23" s="16"/>
-      <c r="T23" s="16"/>
-      <c r="U23" s="16"/>
-      <c r="V23" s="16"/>
-      <c r="W23" s="16"/>
-      <c r="X23" s="16"/>
-      <c r="Y23" s="16"/>
-      <c r="Z23" s="16"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="12"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="12"/>
+      <c r="T23" s="12"/>
+      <c r="U23" s="12"/>
+      <c r="V23" s="12"/>
+      <c r="W23" s="12"/>
+      <c r="X23" s="12"/>
+      <c r="Y23" s="12"/>
+      <c r="Z23" s="12"/>
       <c r="AA23">
         <v>28.3</v>
       </c>
@@ -1677,8 +1674,8 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="15">
-      <c r="A24" s="12">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24">
         <v>1940</v>
       </c>
       <c r="B24" s="2"/>
@@ -1708,7 +1705,7 @@
         <v>33.799999999999997</v>
       </c>
       <c r="R24" s="2"/>
-      <c r="S24" s="12">
+      <c r="S24">
         <v>36.1</v>
       </c>
       <c r="T24" s="2"/>
@@ -1721,7 +1718,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:28" ht="15">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>1941</v>
       </c>
@@ -1744,7 +1741,6 @@
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
-      <c r="S25" s="12"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
       <c r="V25" s="2"/>
@@ -1753,7 +1749,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:28" ht="15">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>1943</v>
       </c>
@@ -1776,7 +1772,6 @@
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
-      <c r="S26" s="12"/>
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
       <c r="V26" s="2"/>
@@ -1787,7 +1782,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="15">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>1945</v>
       </c>
@@ -1810,7 +1805,6 @@
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
-      <c r="S27" s="12"/>
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
       <c r="V27" s="2"/>
@@ -1819,7 +1813,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:28" ht="15">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>1946</v>
       </c>
@@ -1840,7 +1834,6 @@
       <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
-      <c r="S28" s="12"/>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
@@ -1849,7 +1842,7 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" spans="1:28" ht="15">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>1947</v>
       </c>
@@ -1872,7 +1865,6 @@
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
-      <c r="S29" s="12"/>
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
       <c r="V29" s="2"/>
@@ -1881,7 +1873,7 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30" spans="1:28">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>1950</v>
       </c>
@@ -1925,7 +1917,7 @@
         <v>55.1</v>
       </c>
       <c r="O30" s="1">
-        <v>36.200000000000003</v>
+        <v>40.5</v>
       </c>
       <c r="P30" s="1">
         <v>34.9</v>
@@ -1961,7 +1953,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="31" spans="1:28">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>1959</v>
       </c>
@@ -1997,7 +1989,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="32" spans="1:28">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>1960</v>
       </c>
@@ -2041,7 +2033,7 @@
         <v>54.9</v>
       </c>
       <c r="O32" s="1">
-        <v>43.7</v>
+        <v>50.7</v>
       </c>
       <c r="P32" s="1">
         <v>40.9</v>
@@ -2077,7 +2069,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:28">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>1970</v>
       </c>
@@ -2121,7 +2113,7 @@
         <v>60.7</v>
       </c>
       <c r="O33" s="1">
-        <v>51.4</v>
+        <v>58.7</v>
       </c>
       <c r="P33" s="1">
         <v>47.7</v>
@@ -2163,7 +2155,7 @@
         <v>62.3</v>
       </c>
     </row>
-    <row r="34" spans="1:28">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>1979</v>
       </c>
@@ -2199,7 +2191,7 @@
         <v>69.3</v>
       </c>
     </row>
-    <row r="35" spans="1:28">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>1980</v>
       </c>
@@ -2243,7 +2235,7 @@
         <v>69</v>
       </c>
       <c r="O35" s="1">
-        <v>58.4</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="P35" s="1">
         <v>50.3</v>
@@ -2279,7 +2271,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="36" spans="1:28">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>1989</v>
       </c>
@@ -2315,7 +2307,7 @@
         <v>73.599999999999994</v>
       </c>
     </row>
-    <row r="37" spans="1:28">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>1990</v>
       </c>
@@ -2359,7 +2351,7 @@
         <v>73.599999999999994</v>
       </c>
       <c r="O37" s="1">
-        <v>65.599999999999994</v>
+        <v>71.3</v>
       </c>
       <c r="P37" s="1">
         <v>54.4</v>
@@ -2395,7 +2387,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="38" spans="1:28">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>2000</v>
       </c>
@@ -2475,126 +2467,126 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="42" spans="1:28" ht="15">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:28" ht="15">
-      <c r="A44" s="16" t="s">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D44" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="16" t="s">
+      <c r="E44" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="16" t="s">
+      <c r="F44" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G44" s="16" t="s">
+      <c r="G44" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H44" s="16" t="s">
+      <c r="H44" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I44" s="16" t="s">
+      <c r="I44" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="J44" s="16" t="s">
+      <c r="J44" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K44" s="16" t="s">
+      <c r="K44" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L44" s="16" t="s">
+      <c r="L44" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M44" s="16" t="s">
+      <c r="M44" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="N44" s="16" t="s">
+      <c r="N44" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="O44" s="16" t="s">
+      <c r="O44" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="P44" s="16" t="s">
+      <c r="P44" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="Q44" s="16" t="s">
+      <c r="Q44" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="R44" s="16" t="s">
+      <c r="R44" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="S44" s="16" t="s">
+      <c r="S44" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="T44" s="16" t="s">
+      <c r="T44" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="U44" s="16" t="s">
+      <c r="U44" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="V44" s="16" t="s">
+      <c r="V44" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="W44" s="16" t="s">
+      <c r="W44" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="X44" s="16" t="s">
+      <c r="X44" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="Y44" s="16" t="s">
+      <c r="Y44" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="Z44" s="16" t="s">
+      <c r="Z44" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AA44" s="16" t="s">
+      <c r="AA44" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="AB44" s="16" t="s">
+      <c r="AB44" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:28" ht="15">
-      <c r="A45" s="30">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="15">
         <v>1926</v>
       </c>
-      <c r="B45" s="16"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="16"/>
-      <c r="J45" s="16"/>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="16"/>
-      <c r="O45" s="16"/>
-      <c r="P45" s="16"/>
-      <c r="Q45" s="16"/>
-      <c r="R45" s="16"/>
-      <c r="S45" s="16"/>
-      <c r="T45" s="16"/>
-      <c r="U45" s="16"/>
-      <c r="V45" s="16"/>
-      <c r="W45" s="16"/>
-      <c r="X45" s="16"/>
-      <c r="Y45" s="16"/>
-      <c r="Z45" s="16"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="12"/>
+      <c r="L45" s="12"/>
+      <c r="M45" s="12"/>
+      <c r="N45" s="12"/>
+      <c r="O45" s="12"/>
+      <c r="P45" s="12"/>
+      <c r="Q45" s="12"/>
+      <c r="R45" s="12"/>
+      <c r="S45" s="12"/>
+      <c r="T45" s="12"/>
+      <c r="U45" s="12"/>
+      <c r="V45" s="12"/>
+      <c r="W45" s="12"/>
+      <c r="X45" s="12"/>
+      <c r="Y45" s="12"/>
+      <c r="Z45" s="12"/>
       <c r="AA45" s="1">
         <v>36</v>
       </c>
@@ -2602,41 +2594,41 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="46" spans="1:28" ht="15">
-      <c r="A46" s="30">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="15">
         <v>1930</v>
       </c>
-      <c r="B46" s="16"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-      <c r="H46" s="16"/>
-      <c r="I46" s="16"/>
-      <c r="J46" s="16"/>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="16"/>
-      <c r="O46" s="31">
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="25">
         <v>37.200000000000003</v>
       </c>
-      <c r="P46" s="16"/>
-      <c r="Q46" s="16"/>
-      <c r="R46" s="16"/>
-      <c r="S46" s="16"/>
-      <c r="T46" s="16"/>
-      <c r="U46" s="16"/>
-      <c r="V46" s="16"/>
-      <c r="W46" s="16"/>
-      <c r="X46" s="16"/>
-      <c r="Y46" s="16"/>
-      <c r="Z46" s="16"/>
+      <c r="P46" s="12"/>
+      <c r="Q46" s="12"/>
+      <c r="R46" s="12"/>
+      <c r="S46" s="12"/>
+      <c r="T46" s="12"/>
+      <c r="U46" s="12"/>
+      <c r="V46" s="12"/>
+      <c r="W46" s="12"/>
+      <c r="X46" s="12"/>
+      <c r="Y46" s="12"/>
+      <c r="Z46" s="12"/>
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
     </row>
-    <row r="47" spans="1:28">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
         <v>1950</v>
       </c>
@@ -2680,7 +2672,7 @@
         <v>51.4</v>
       </c>
       <c r="O47" s="1">
-        <v>42</v>
+        <v>44.1</v>
       </c>
       <c r="P47" s="1">
         <v>28</v>
@@ -2716,7 +2708,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="48" spans="1:28">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
         <v>1959</v>
       </c>
@@ -2752,7 +2744,7 @@
         <v>60.4</v>
       </c>
     </row>
-    <row r="49" spans="1:32">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
         <v>1960</v>
       </c>
@@ -2796,7 +2788,7 @@
         <v>54.9</v>
       </c>
       <c r="O49" s="1">
-        <v>53.6</v>
+        <v>53.8</v>
       </c>
       <c r="P49" s="1">
         <v>35.6</v>
@@ -2832,7 +2824,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="50" spans="1:32">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
         <v>1970</v>
       </c>
@@ -2876,7 +2868,7 @@
         <v>58.3</v>
       </c>
       <c r="O50" s="1">
-        <v>61.4</v>
+        <v>61.7</v>
       </c>
       <c r="P50" s="1">
         <v>46.2</v>
@@ -2918,7 +2910,7 @@
         <v>69.7</v>
       </c>
     </row>
-    <row r="51" spans="1:32">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
         <v>1980</v>
       </c>
@@ -2962,7 +2954,7 @@
         <v>66.099999999999994</v>
       </c>
       <c r="O51" s="1">
-        <v>65.3</v>
+        <v>68.8</v>
       </c>
       <c r="P51" s="1">
         <v>50.3</v>
@@ -2998,7 +2990,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="52" spans="1:32">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
         <v>1990</v>
       </c>
@@ -3078,7 +3070,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="53" spans="1:32">
+    <row r="53" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A53">
         <v>2000</v>
       </c>
@@ -3142,1406 +3134,675 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="57" spans="1:32" ht="15">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="11" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="59" spans="1:32" ht="15">
-      <c r="A59" s="16" t="s">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="B59" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="C59" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D59" s="16" t="s">
+      <c r="D59" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E59" s="16" t="s">
+      <c r="E59" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F59" s="16" t="s">
+      <c r="F59" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G59" s="16" t="s">
+      <c r="G59" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H59" s="16" t="s">
+      <c r="H59" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I59" s="16" t="s">
+      <c r="I59" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="J59" s="16" t="s">
+      <c r="J59" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K59" s="16" t="s">
+      <c r="K59" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="L59" s="16" t="s">
+      <c r="L59" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="M59" s="16" t="s">
+      <c r="M59" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="N59" s="16" t="s">
+      <c r="N59" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="O59" s="16" t="s">
+      <c r="O59" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="P59" s="16" t="s">
+      <c r="P59" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="Q59" s="16" t="s">
+      <c r="Q59" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="R59" s="16" t="s">
+      <c r="R59" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="S59" s="16" t="s">
+      <c r="S59" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="T59" s="16" t="s">
+      <c r="T59" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="U59" s="16" t="s">
+      <c r="U59" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="V59" s="16" t="s">
+      <c r="V59" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="W59" s="16" t="s">
+      <c r="W59" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="X59" s="16" t="s">
+      <c r="X59" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="Y59" s="16" t="s">
+      <c r="Y59" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="Z59" s="16" t="s">
+      <c r="Z59" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="AA59" s="16" t="s">
+      <c r="AA59" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="AB59" s="16" t="s">
+      <c r="AB59" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AC59" s="16" t="s">
+      <c r="AC59" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="AD59" s="16" t="s">
+      <c r="AD59" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AE59" s="16" t="s">
+      <c r="AE59" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="AF59" s="16" t="s">
+      <c r="AF59" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="60" spans="1:32">
-      <c r="A60" s="12">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60">
         <v>1865</v>
       </c>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="12"/>
-      <c r="I60" s="12"/>
-      <c r="J60" s="12"/>
-      <c r="K60" s="12"/>
-      <c r="L60" s="12"/>
-      <c r="M60" s="12"/>
-      <c r="N60" s="12"/>
-      <c r="O60" s="12"/>
-      <c r="P60" s="12"/>
-      <c r="Q60" s="12"/>
-      <c r="R60" s="12"/>
-      <c r="S60" s="12"/>
-      <c r="T60" s="12"/>
-      <c r="U60" s="12"/>
-      <c r="V60" s="12"/>
-      <c r="W60" s="12"/>
-      <c r="X60" s="12"/>
-      <c r="Y60" s="12"/>
-      <c r="Z60" s="12"/>
-      <c r="AA60" s="12"/>
-      <c r="AB60" s="13">
+      <c r="AB60" s="1">
         <v>15.973962510368438</v>
       </c>
-      <c r="AC60" s="12"/>
-      <c r="AD60" s="12"/>
-      <c r="AE60" s="12"/>
-    </row>
-    <row r="61" spans="1:32">
-      <c r="A61" s="12">
+    </row>
+    <row r="61" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61">
         <v>1869</v>
       </c>
-      <c r="B61" s="13">
+      <c r="B61" s="1">
         <v>24.82533867257391</v>
       </c>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-      <c r="I61" s="12"/>
-      <c r="J61" s="12"/>
-      <c r="K61" s="12"/>
-      <c r="L61" s="12"/>
-      <c r="M61" s="12"/>
-      <c r="N61" s="12"/>
-      <c r="O61" s="12"/>
-      <c r="P61" s="12"/>
-      <c r="Q61" s="12"/>
-      <c r="R61" s="12"/>
-      <c r="S61" s="12"/>
-      <c r="T61" s="12"/>
-      <c r="U61" s="12"/>
-      <c r="V61" s="12"/>
-      <c r="W61" s="12"/>
-      <c r="X61" s="12"/>
-      <c r="Y61" s="12"/>
-      <c r="Z61" s="12"/>
-      <c r="AA61" s="12"/>
-      <c r="AB61" s="12"/>
-      <c r="AC61" s="12"/>
-      <c r="AD61" s="12"/>
-      <c r="AE61" s="12"/>
-    </row>
-    <row r="62" spans="1:32">
-      <c r="A62" s="12">
+    </row>
+    <row r="62" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62">
         <v>1875</v>
       </c>
-      <c r="B62" s="13"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
-      <c r="I62" s="12"/>
-      <c r="J62" s="12"/>
-      <c r="K62" s="12"/>
-      <c r="L62" s="12"/>
-      <c r="M62" s="12"/>
-      <c r="N62" s="12"/>
-      <c r="O62" s="12"/>
-      <c r="P62" s="12"/>
-      <c r="Q62" s="12"/>
-      <c r="R62" s="12"/>
-      <c r="S62" s="12"/>
-      <c r="T62" s="12"/>
-      <c r="U62" s="12"/>
-      <c r="V62" s="12"/>
-      <c r="W62" s="12"/>
-      <c r="X62" s="12"/>
-      <c r="Y62" s="12"/>
-      <c r="Z62" s="12"/>
-      <c r="AA62" s="12"/>
-      <c r="AB62" s="13">
+      <c r="B62" s="1"/>
+      <c r="AB62" s="1">
         <v>17.277987023903513</v>
       </c>
-      <c r="AC62" s="12"/>
-      <c r="AD62" s="12"/>
-      <c r="AE62" s="12"/>
-    </row>
-    <row r="63" spans="1:32">
-      <c r="A63" s="12">
+    </row>
+    <row r="63" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63">
         <v>1876</v>
       </c>
-      <c r="B63" s="13"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12"/>
-      <c r="E63" s="12"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12"/>
-      <c r="I63" s="12"/>
-      <c r="J63" s="12"/>
-      <c r="K63" s="12"/>
-      <c r="L63" s="12"/>
-      <c r="M63" s="12"/>
-      <c r="N63" s="12"/>
-      <c r="O63" s="12"/>
-      <c r="P63" s="12"/>
-      <c r="Q63" s="12"/>
-      <c r="R63" s="12"/>
-      <c r="S63" s="12"/>
-      <c r="T63" s="12"/>
-      <c r="U63" s="12"/>
-      <c r="V63" s="13">
+      <c r="B63" s="1"/>
+      <c r="V63" s="1">
         <v>7.4535049753510974</v>
       </c>
-      <c r="W63" s="12"/>
-      <c r="X63" s="12"/>
-      <c r="Y63" s="12"/>
-      <c r="Z63" s="12"/>
-      <c r="AA63" s="12"/>
-      <c r="AB63" s="13"/>
-      <c r="AC63" s="12"/>
-      <c r="AD63" s="12"/>
-      <c r="AE63" s="12"/>
-    </row>
-    <row r="64" spans="1:32">
-      <c r="A64" s="12">
+      <c r="AB63" s="1"/>
+    </row>
+    <row r="64" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64">
         <v>1885</v>
       </c>
-      <c r="B64" s="13"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12"/>
-      <c r="I64" s="12"/>
-      <c r="J64" s="12"/>
-      <c r="K64" s="12"/>
-      <c r="L64" s="12"/>
-      <c r="M64" s="12"/>
-      <c r="N64" s="12"/>
-      <c r="O64" s="12"/>
-      <c r="P64" s="12"/>
-      <c r="Q64" s="12"/>
-      <c r="R64" s="12"/>
-      <c r="S64" s="12"/>
-      <c r="T64" s="12"/>
-      <c r="U64" s="12"/>
-      <c r="V64" s="12"/>
-      <c r="W64" s="12"/>
-      <c r="X64" s="12"/>
-      <c r="Y64" s="12"/>
-      <c r="Z64" s="12"/>
-      <c r="AA64" s="12"/>
-      <c r="AB64" s="13">
+      <c r="B64" s="1"/>
+      <c r="AB64" s="1">
         <v>19.212369940391472</v>
       </c>
-      <c r="AC64" s="12"/>
-      <c r="AD64" s="12"/>
-      <c r="AE64" s="12"/>
-    </row>
-    <row r="65" spans="1:32">
-      <c r="A65" s="12">
+    </row>
+    <row r="65" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65">
         <v>1895</v>
       </c>
-      <c r="B65" s="13">
+      <c r="B65" s="1">
         <v>31.833737851496533</v>
       </c>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="12"/>
-      <c r="I65" s="12"/>
-      <c r="J65" s="12"/>
-      <c r="K65" s="12"/>
-      <c r="L65" s="12"/>
-      <c r="M65" s="12"/>
-      <c r="N65" s="12"/>
-      <c r="O65" s="12"/>
-      <c r="P65" s="12"/>
-      <c r="Q65" s="12"/>
-      <c r="R65" s="12"/>
-      <c r="S65" s="12"/>
-      <c r="T65" s="12"/>
-      <c r="U65" s="12"/>
-      <c r="V65" s="12"/>
-      <c r="W65" s="12"/>
-      <c r="X65" s="12"/>
-      <c r="Y65" s="12"/>
-      <c r="Z65" s="12"/>
-      <c r="AA65" s="12"/>
-      <c r="AB65" s="13">
+      <c r="AB65" s="1">
         <v>24.121981380841554</v>
       </c>
-      <c r="AC65" s="12"/>
-      <c r="AD65" s="12"/>
-      <c r="AE65" s="12"/>
-    </row>
-    <row r="66" spans="1:32">
-      <c r="A66" s="12">
+    </row>
+    <row r="66" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66">
         <v>1900</v>
       </c>
-      <c r="B66" s="13"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="13">
+      <c r="B66" s="1"/>
+      <c r="F66" s="1">
         <v>8.5972647960386706</v>
       </c>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12"/>
-      <c r="I66" s="12"/>
-      <c r="J66" s="12"/>
-      <c r="K66" s="12"/>
-      <c r="L66" s="12"/>
-      <c r="M66" s="12"/>
-      <c r="N66" s="12"/>
-      <c r="O66" s="12"/>
-      <c r="P66" s="12"/>
-      <c r="Q66" s="12"/>
       <c r="R66" s="1">
         <v>21.466933269210756</v>
       </c>
-      <c r="S66" s="12"/>
-      <c r="T66" s="12"/>
-      <c r="U66" s="12"/>
-      <c r="V66" s="12"/>
-      <c r="W66" s="12"/>
-      <c r="X66" s="12"/>
-      <c r="Y66" s="12"/>
-      <c r="Z66" s="12"/>
-      <c r="AA66" s="12"/>
-      <c r="AB66" s="13"/>
-      <c r="AC66" s="12"/>
-      <c r="AD66" s="12"/>
-      <c r="AE66" s="12"/>
-    </row>
-    <row r="67" spans="1:32">
-      <c r="A67" s="12">
+      <c r="AB66" s="1"/>
+    </row>
+    <row r="67" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67">
         <v>1907</v>
       </c>
-      <c r="B67" s="13"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="12"/>
-      <c r="I67" s="12"/>
-      <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="12"/>
-      <c r="M67" s="12"/>
-      <c r="N67" s="12"/>
-      <c r="O67" s="12"/>
-      <c r="P67" s="12"/>
-      <c r="Q67" s="12"/>
-      <c r="R67" s="12"/>
-      <c r="S67" s="12"/>
-      <c r="T67" s="12"/>
-      <c r="U67" s="12"/>
-      <c r="V67" s="12"/>
-      <c r="W67" s="12"/>
-      <c r="X67" s="12"/>
-      <c r="Y67" s="12"/>
-      <c r="Z67" s="12"/>
-      <c r="AA67" s="12"/>
-      <c r="AB67" s="13">
+      <c r="B67" s="1"/>
+      <c r="AB67" s="1">
         <v>27.698910521277391</v>
       </c>
-      <c r="AC67" s="12"/>
-      <c r="AD67" s="12"/>
-      <c r="AE67" s="12"/>
-    </row>
-    <row r="68" spans="1:32">
-      <c r="A68" s="12">
+    </row>
+    <row r="68" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68">
         <v>1910</v>
       </c>
-      <c r="B68" s="13"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12"/>
-      <c r="I68" s="12"/>
-      <c r="J68" s="12"/>
-      <c r="K68" s="12"/>
-      <c r="L68" s="12"/>
-      <c r="M68" s="12"/>
-      <c r="N68" s="12"/>
-      <c r="O68" s="12"/>
-      <c r="P68" s="12"/>
-      <c r="Q68" s="12"/>
-      <c r="R68" s="12">
+      <c r="B68" s="1"/>
+      <c r="R68">
         <v>24.7</v>
       </c>
-      <c r="S68" s="12"/>
-      <c r="T68" s="12"/>
-      <c r="U68" s="12"/>
-      <c r="V68" s="12"/>
-      <c r="W68" s="12"/>
-      <c r="X68" s="12"/>
-      <c r="Y68" s="12"/>
-      <c r="Z68" s="12"/>
-      <c r="AA68" s="12"/>
-      <c r="AB68" s="13"/>
-      <c r="AC68" s="12"/>
-      <c r="AD68" s="12"/>
-      <c r="AE68" s="12"/>
-    </row>
-    <row r="69" spans="1:32">
-      <c r="A69" s="12">
+      <c r="AB68" s="1"/>
+    </row>
+    <row r="69" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69">
         <v>1913</v>
       </c>
-      <c r="B69" s="13"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="12"/>
-      <c r="I69" s="12"/>
-      <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="12"/>
-      <c r="M69" s="12"/>
-      <c r="N69" s="12"/>
-      <c r="O69" s="12"/>
-      <c r="P69" s="12"/>
-      <c r="Q69" s="12"/>
-      <c r="R69" s="12"/>
-      <c r="S69" s="12"/>
-      <c r="T69" s="12"/>
-      <c r="U69" s="12"/>
-      <c r="V69" s="12"/>
-      <c r="W69" s="12"/>
-      <c r="X69" s="12"/>
-      <c r="Y69" s="12"/>
-      <c r="Z69" s="12"/>
-      <c r="AA69" s="12"/>
-      <c r="AB69" s="13"/>
-      <c r="AC69" s="12"/>
-      <c r="AD69" s="12"/>
-      <c r="AE69" s="12"/>
-    </row>
-    <row r="70" spans="1:32">
-      <c r="A70" s="12">
+      <c r="B69" s="1"/>
+      <c r="AB69" s="1"/>
+    </row>
+    <row r="70" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70">
         <v>1914</v>
       </c>
-      <c r="B70" s="13">
+      <c r="B70" s="1">
         <v>38.26516565069636</v>
       </c>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="12"/>
-      <c r="I70" s="12"/>
-      <c r="J70" s="12"/>
-      <c r="K70" s="12"/>
-      <c r="L70" s="12"/>
-      <c r="M70" s="12"/>
-      <c r="N70" s="12"/>
-      <c r="O70" s="12"/>
-      <c r="P70" s="12"/>
-      <c r="Q70" s="12"/>
-      <c r="R70" s="12"/>
-      <c r="S70" s="12"/>
-      <c r="T70" s="12"/>
-      <c r="U70" s="12"/>
-      <c r="V70" s="12"/>
-      <c r="W70" s="12"/>
-      <c r="X70" s="12"/>
-      <c r="Y70" s="12"/>
-      <c r="Z70" s="12"/>
-      <c r="AA70" s="12"/>
-      <c r="AB70" s="12"/>
-      <c r="AC70" s="12"/>
-      <c r="AD70" s="12"/>
-      <c r="AE70" s="12"/>
-    </row>
-    <row r="71" spans="1:32" ht="13.5" customHeight="1">
-      <c r="A71" s="12">
+    </row>
+    <row r="71" spans="1:32" ht="13.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71">
         <v>1919</v>
       </c>
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="12"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="12"/>
-      <c r="I71" s="12"/>
-      <c r="J71" s="12"/>
-      <c r="K71" s="12"/>
-      <c r="L71" s="12"/>
-      <c r="M71" s="12"/>
-      <c r="N71" s="12"/>
-      <c r="O71" s="12"/>
-      <c r="P71" s="12"/>
-      <c r="Q71" s="13">
+      <c r="Q71" s="1">
         <v>27.859047616410361</v>
       </c>
-      <c r="R71" s="12"/>
-      <c r="S71" s="12"/>
-      <c r="T71" s="12"/>
-      <c r="U71" s="12"/>
-      <c r="V71" s="12"/>
-      <c r="W71" s="12"/>
-      <c r="X71" s="12"/>
-      <c r="Y71" s="12"/>
-      <c r="Z71" s="12"/>
-      <c r="AA71" s="12"/>
-      <c r="AB71" s="12"/>
-      <c r="AC71" s="12"/>
-      <c r="AD71" s="12"/>
-      <c r="AE71" s="12"/>
-    </row>
-    <row r="72" spans="1:32">
-      <c r="A72" s="14">
+    </row>
+    <row r="72" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72">
         <v>1920</v>
       </c>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14">
+      <c r="G72">
         <v>13</v>
       </c>
-      <c r="H72" s="14">
+      <c r="H72">
         <v>11</v>
       </c>
-      <c r="I72" s="14"/>
-      <c r="J72" s="14"/>
-      <c r="K72" s="14"/>
-      <c r="L72" s="14"/>
-      <c r="M72" s="14"/>
-      <c r="N72" s="15">
+      <c r="N72" s="1">
         <v>5.3757551709299012</v>
       </c>
-      <c r="O72" s="14">
+      <c r="O72">
         <v>7</v>
       </c>
-      <c r="P72" s="14"/>
-      <c r="Q72" s="14"/>
-      <c r="R72" s="14"/>
-      <c r="S72" s="15">
+      <c r="S72" s="1">
         <v>4.3936290090937495</v>
       </c>
-      <c r="T72" s="14"/>
-      <c r="U72" s="14"/>
-      <c r="V72" s="14">
+      <c r="V72">
         <v>6</v>
       </c>
-      <c r="W72" s="14"/>
-      <c r="X72" s="14"/>
-      <c r="Y72" s="14"/>
-      <c r="Z72" s="14"/>
-      <c r="AA72" s="14">
+      <c r="AA72">
         <v>30</v>
       </c>
-      <c r="AB72" s="15">
+      <c r="AB72" s="1">
         <v>27.96247421409107</v>
       </c>
-      <c r="AC72" s="14">
+      <c r="AC72">
         <v>10</v>
       </c>
-      <c r="AD72" s="14"/>
-      <c r="AE72" s="14">
+      <c r="AE72">
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:32">
-      <c r="A73" s="14">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73">
         <v>1921</v>
       </c>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="14"/>
-      <c r="J73" s="14"/>
-      <c r="K73" s="14"/>
-      <c r="L73" s="14"/>
-      <c r="M73" s="14"/>
-      <c r="N73" s="15"/>
-      <c r="O73" s="14"/>
-      <c r="P73" s="14"/>
-      <c r="Q73" s="14"/>
+      <c r="N73" s="1"/>
       <c r="R73" s="1">
         <v>30.616554018692632</v>
       </c>
-      <c r="S73" s="15"/>
-      <c r="T73" s="14"/>
-      <c r="U73" s="14"/>
-      <c r="V73" s="14"/>
-      <c r="W73" s="14"/>
-      <c r="X73" s="14"/>
-      <c r="Y73" s="14"/>
-      <c r="Z73" s="14"/>
-      <c r="AA73" s="14"/>
-      <c r="AB73" s="15"/>
-      <c r="AC73" s="14"/>
-      <c r="AD73" s="14">
+      <c r="S73" s="1"/>
+      <c r="AB73" s="1"/>
+      <c r="AD73">
         <v>10.3</v>
       </c>
-      <c r="AE73" s="14"/>
-    </row>
-    <row r="74" spans="1:32">
-      <c r="A74" s="14">
+    </row>
+    <row r="74" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74">
         <v>1926</v>
       </c>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="14"/>
-      <c r="J74" s="14"/>
-      <c r="K74" s="14"/>
-      <c r="L74" s="14"/>
-      <c r="M74" s="14"/>
-      <c r="N74" s="15"/>
-      <c r="O74" s="14"/>
-      <c r="P74" s="14"/>
-      <c r="Q74" s="14"/>
+      <c r="N74" s="1"/>
       <c r="R74" s="1"/>
-      <c r="S74" s="15"/>
-      <c r="T74" s="14"/>
-      <c r="U74" s="14"/>
-      <c r="V74" s="14"/>
-      <c r="W74" s="14"/>
-      <c r="X74" s="14"/>
-      <c r="Y74" s="14"/>
-      <c r="Z74" s="14"/>
-      <c r="AA74" s="14"/>
-      <c r="AB74" s="15"/>
-      <c r="AC74" s="14"/>
-      <c r="AD74" s="14"/>
-      <c r="AE74" s="14">
+      <c r="S74" s="1"/>
+      <c r="AB74" s="1"/>
+      <c r="AE74">
         <v>12.1</v>
       </c>
       <c r="AF74">
         <v>11.8</v>
       </c>
     </row>
-    <row r="75" spans="1:32">
-      <c r="A75" s="14">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75">
         <v>1927</v>
       </c>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="14"/>
-      <c r="J75" s="14"/>
-      <c r="K75" s="14"/>
-      <c r="L75" s="14"/>
-      <c r="M75" s="14"/>
-      <c r="N75" s="14"/>
-      <c r="O75" s="14"/>
-      <c r="P75" s="15">
+      <c r="P75" s="1">
         <v>18.87623959756025</v>
       </c>
-      <c r="Q75" s="14"/>
-      <c r="R75" s="14"/>
-      <c r="S75" s="14"/>
-      <c r="T75" s="14"/>
-      <c r="U75" s="14"/>
-      <c r="V75" s="14"/>
-      <c r="W75" s="14"/>
-      <c r="X75" s="14"/>
-      <c r="Y75" s="14"/>
-      <c r="Z75" s="14"/>
-      <c r="AA75" s="14"/>
-      <c r="AB75" s="14"/>
-      <c r="AC75" s="14"/>
-      <c r="AD75" s="14"/>
-      <c r="AE75" s="14"/>
-    </row>
-    <row r="76" spans="1:32">
-      <c r="A76" s="14">
+    </row>
+    <row r="76" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76">
         <v>1930</v>
       </c>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14">
+      <c r="G76">
         <v>14</v>
       </c>
-      <c r="H76" s="14">
+      <c r="H76">
         <v>13</v>
       </c>
-      <c r="I76" s="14"/>
-      <c r="J76" s="14"/>
-      <c r="K76" s="14"/>
-      <c r="L76" s="14"/>
-      <c r="M76" s="14"/>
-      <c r="N76" s="14"/>
-      <c r="O76" s="14">
+      <c r="O76">
         <v>10</v>
       </c>
-      <c r="P76" s="14"/>
-      <c r="Q76" s="14"/>
-      <c r="R76" s="14">
+      <c r="R76">
         <v>28.5</v>
       </c>
-      <c r="S76" s="14"/>
-      <c r="T76" s="15">
+      <c r="T76" s="1">
         <v>24.338525446181379</v>
       </c>
-      <c r="U76" s="14"/>
-      <c r="V76" s="14">
+      <c r="V76">
         <v>10</v>
       </c>
-      <c r="W76" s="15">
+      <c r="W76" s="1">
         <v>10.216396011882644</v>
       </c>
-      <c r="X76" s="14"/>
-      <c r="Y76" s="14"/>
-      <c r="Z76" s="14"/>
-      <c r="AA76" s="14">
+      <c r="AA76">
         <v>35</v>
       </c>
-      <c r="AB76" s="15">
+      <c r="AB76" s="1">
         <v>32.849564250969983</v>
       </c>
-      <c r="AC76" s="14">
+      <c r="AC76">
         <v>13</v>
       </c>
-      <c r="AD76" s="14"/>
-      <c r="AE76" s="14">
+      <c r="AE76">
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:32">
-      <c r="A77" s="14">
+    <row r="77" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77">
         <v>1931</v>
       </c>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="14"/>
-      <c r="J77" s="14"/>
-      <c r="K77" s="14"/>
-      <c r="L77" s="14"/>
-      <c r="M77" s="14"/>
-      <c r="N77" s="14"/>
-      <c r="O77" s="14"/>
-      <c r="P77" s="14"/>
-      <c r="Q77" s="15">
+      <c r="Q77" s="1">
         <v>29.864393399462539</v>
       </c>
-      <c r="R77" s="14"/>
-      <c r="S77" s="14"/>
-      <c r="T77" s="14"/>
-      <c r="U77" s="14"/>
-      <c r="V77" s="14"/>
-      <c r="W77" s="14"/>
-      <c r="X77" s="14"/>
-      <c r="Y77" s="14"/>
-      <c r="Z77" s="14"/>
-      <c r="AA77" s="14"/>
-      <c r="AB77" s="14"/>
-      <c r="AC77" s="14"/>
-      <c r="AD77" s="14"/>
-      <c r="AE77" s="14"/>
-    </row>
-    <row r="78" spans="1:32">
-      <c r="A78" s="14">
+    </row>
+    <row r="78" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78">
         <v>1935</v>
       </c>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="14"/>
-      <c r="J78" s="14"/>
-      <c r="K78" s="14"/>
-      <c r="L78" s="14"/>
-      <c r="M78" s="14"/>
-      <c r="N78" s="15">
+      <c r="N78" s="1">
         <v>7.1153704466016006</v>
       </c>
-      <c r="O78" s="14"/>
-      <c r="P78" s="14"/>
-      <c r="Q78" s="14"/>
-      <c r="R78" s="14"/>
-      <c r="S78" s="14"/>
-      <c r="T78" s="14"/>
-      <c r="U78" s="14"/>
-      <c r="V78" s="14"/>
-      <c r="W78" s="14"/>
-      <c r="X78" s="14"/>
-      <c r="Y78" s="14"/>
-      <c r="Z78" s="14"/>
-      <c r="AA78" s="14"/>
-      <c r="AB78" s="14"/>
-      <c r="AC78" s="14"/>
-      <c r="AD78" s="14"/>
-      <c r="AE78" s="14"/>
-    </row>
-    <row r="79" spans="1:32">
-      <c r="A79" s="14">
+    </row>
+    <row r="79" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79">
         <v>1936</v>
       </c>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="15">
+      <c r="H79" s="1">
         <v>19.091253072290105</v>
       </c>
-      <c r="I79" s="14"/>
-      <c r="J79" s="14"/>
-      <c r="K79" s="14"/>
-      <c r="L79" s="14"/>
-      <c r="M79" s="14"/>
-      <c r="N79" s="14"/>
-      <c r="O79" s="14"/>
-      <c r="P79" s="14"/>
-      <c r="Q79" s="14"/>
-      <c r="R79" s="14"/>
-      <c r="S79" s="14"/>
-      <c r="T79" s="14"/>
-      <c r="U79" s="14"/>
-      <c r="V79" s="14"/>
-      <c r="W79" s="14"/>
-      <c r="X79" s="14"/>
-      <c r="Y79" s="14"/>
-      <c r="Z79" s="14"/>
-      <c r="AA79" s="14"/>
-      <c r="AB79" s="14"/>
-      <c r="AC79" s="14"/>
-      <c r="AD79" s="14"/>
-      <c r="AE79" s="14"/>
-    </row>
-    <row r="80" spans="1:32">
-      <c r="A80" s="14">
+    </row>
+    <row r="80" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80">
         <v>1937</v>
       </c>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="15"/>
-      <c r="I80" s="14"/>
-      <c r="J80" s="14"/>
-      <c r="K80" s="14"/>
-      <c r="L80" s="14"/>
-      <c r="M80" s="14"/>
-      <c r="N80" s="14"/>
-      <c r="O80" s="14"/>
-      <c r="P80" s="14"/>
-      <c r="Q80" s="14"/>
-      <c r="R80" s="14"/>
-      <c r="S80" s="14"/>
-      <c r="T80" s="14"/>
-      <c r="U80" s="15">
+      <c r="H80" s="1"/>
+      <c r="U80" s="1">
         <v>11.197210631902117</v>
       </c>
-      <c r="V80" s="14"/>
-      <c r="W80" s="14"/>
-      <c r="X80" s="14"/>
-      <c r="Y80" s="14"/>
-      <c r="Z80" s="14"/>
-      <c r="AA80" s="14"/>
-      <c r="AB80" s="14"/>
-      <c r="AC80" s="14"/>
-      <c r="AD80" s="14"/>
-      <c r="AE80" s="14"/>
-    </row>
-    <row r="81" spans="1:32">
-      <c r="A81" s="14">
+    </row>
+    <row r="81" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81">
         <v>1938</v>
       </c>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="14"/>
-      <c r="J81" s="14"/>
-      <c r="K81" s="14"/>
-      <c r="L81" s="14"/>
-      <c r="M81" s="14"/>
-      <c r="N81" s="14"/>
-      <c r="O81" s="15">
+      <c r="O81" s="1">
         <v>14.737441012312832</v>
       </c>
-      <c r="P81" s="14"/>
-      <c r="Q81" s="14"/>
-      <c r="R81" s="14"/>
-      <c r="S81" s="14"/>
-      <c r="T81" s="14"/>
-      <c r="U81" s="14"/>
-      <c r="V81" s="14"/>
-      <c r="W81" s="14"/>
-      <c r="X81" s="14"/>
-      <c r="Y81" s="14"/>
-      <c r="Z81" s="14"/>
-      <c r="AA81" s="14"/>
-      <c r="AB81" s="14"/>
-      <c r="AC81" s="14"/>
-      <c r="AD81" s="14"/>
-      <c r="AE81" s="14"/>
-    </row>
-    <row r="82" spans="1:32">
-      <c r="A82" s="14">
+    </row>
+    <row r="82" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82">
         <v>1939</v>
       </c>
-      <c r="B82" s="14"/>
-      <c r="C82" s="14"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="14"/>
-      <c r="J82" s="14"/>
-      <c r="K82" s="14"/>
-      <c r="L82" s="14"/>
-      <c r="M82" s="14"/>
-      <c r="N82" s="14"/>
-      <c r="O82" s="15"/>
-      <c r="P82" s="14"/>
-      <c r="Q82" s="14"/>
-      <c r="R82" s="14"/>
-      <c r="S82" s="14"/>
-      <c r="T82" s="14"/>
-      <c r="U82" s="14"/>
-      <c r="V82" s="14"/>
-      <c r="W82" s="14"/>
-      <c r="X82" s="14"/>
-      <c r="Y82" s="14"/>
-      <c r="Z82" s="14"/>
-      <c r="AA82" s="14"/>
-      <c r="AB82" s="14"/>
-      <c r="AC82" s="14"/>
-      <c r="AD82" s="14"/>
-      <c r="AE82" s="14"/>
-    </row>
-    <row r="83" spans="1:32">
-      <c r="A83" s="14">
+      <c r="O82" s="1"/>
+    </row>
+    <row r="83" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83">
         <v>1940</v>
       </c>
-      <c r="B83" s="14">
+      <c r="B83">
         <v>41</v>
       </c>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="15">
+      <c r="G83" s="1">
         <v>14.979631374994044</v>
       </c>
-      <c r="H83" s="14"/>
-      <c r="I83" s="14"/>
-      <c r="J83" s="14"/>
-      <c r="K83" s="15">
+      <c r="K83" s="1">
         <v>5.7838535408498206</v>
       </c>
-      <c r="L83" s="14">
+      <c r="L83">
         <v>6.1</v>
       </c>
-      <c r="M83" s="14"/>
-      <c r="N83" s="14"/>
-      <c r="O83" s="14"/>
-      <c r="P83" s="14"/>
-      <c r="Q83" s="14">
+      <c r="Q83">
         <v>30</v>
       </c>
-      <c r="R83" s="14"/>
-      <c r="S83" s="15">
+      <c r="S83" s="1">
         <v>7.5335821390138475</v>
       </c>
-      <c r="T83" s="15">
+      <c r="T83" s="1">
         <v>27.583662937332001</v>
       </c>
-      <c r="U83" s="14"/>
-      <c r="V83" s="15">
+      <c r="V83" s="1">
         <v>14.12009761005495</v>
       </c>
-      <c r="W83" s="14"/>
-      <c r="X83" s="14"/>
-      <c r="Y83" s="14"/>
-      <c r="Z83" s="14"/>
-      <c r="AA83" s="14">
+      <c r="AA83">
         <v>38</v>
       </c>
-      <c r="AB83" s="15">
+      <c r="AB83" s="1">
         <v>36.418648287591672</v>
       </c>
-      <c r="AC83" s="14">
+      <c r="AC83">
         <v>16</v>
       </c>
-      <c r="AD83" s="14"/>
-      <c r="AE83" s="14">
+      <c r="AE83">
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:32">
-      <c r="A84" s="14">
+    <row r="84" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84">
         <v>1941</v>
       </c>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="15">
+      <c r="H84" s="1">
         <v>18.100000000000001</v>
       </c>
-      <c r="I84" s="14"/>
-      <c r="J84" s="14"/>
-      <c r="K84" s="14"/>
-      <c r="L84" s="14"/>
-      <c r="M84" s="14"/>
-      <c r="N84" s="14"/>
-      <c r="O84" s="14"/>
-      <c r="P84" s="14"/>
-      <c r="Q84" s="14"/>
-      <c r="R84" s="14"/>
-      <c r="S84" s="14"/>
-      <c r="T84" s="14"/>
-      <c r="U84" s="14"/>
-      <c r="V84" s="14"/>
-      <c r="W84" s="14"/>
-      <c r="X84" s="14"/>
-      <c r="Y84" s="14"/>
-      <c r="Z84" s="14"/>
-      <c r="AA84" s="14"/>
-      <c r="AB84" s="14"/>
-      <c r="AC84" s="14"/>
-      <c r="AD84" s="14"/>
-      <c r="AE84" s="14"/>
-    </row>
-    <row r="85" spans="1:32">
-      <c r="A85" s="14">
+    </row>
+    <row r="85" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85">
         <v>1943</v>
       </c>
-      <c r="B85" s="14"/>
-      <c r="C85" s="14"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="14"/>
-      <c r="I85" s="14"/>
-      <c r="J85" s="14"/>
-      <c r="K85" s="14"/>
-      <c r="L85" s="14"/>
-      <c r="M85" s="14"/>
-      <c r="N85" s="14"/>
-      <c r="O85" s="14"/>
-      <c r="P85" s="14"/>
-      <c r="Q85" s="15">
+      <c r="Q85" s="1">
         <v>33.361821561291613</v>
       </c>
-      <c r="R85" s="14"/>
-      <c r="S85" s="14"/>
-      <c r="T85" s="14"/>
-      <c r="U85" s="14"/>
-      <c r="V85" s="14"/>
-      <c r="W85" s="14"/>
-      <c r="X85" s="14"/>
-      <c r="Y85" s="14"/>
-      <c r="Z85" s="14"/>
-      <c r="AA85" s="14"/>
-      <c r="AB85" s="14"/>
-      <c r="AC85" s="14"/>
-      <c r="AD85" s="14">
+      <c r="AD85">
         <v>16.3</v>
       </c>
-      <c r="AE85" s="14"/>
-    </row>
-    <row r="86" spans="1:32">
-      <c r="A86" s="14">
+    </row>
+    <row r="86" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86">
         <v>1947</v>
       </c>
-      <c r="B86" s="15">
+      <c r="B86" s="1">
         <v>49.068352134448176</v>
       </c>
-      <c r="C86" s="14"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
-      <c r="H86" s="14"/>
-      <c r="I86" s="14"/>
-      <c r="J86" s="14"/>
-      <c r="K86" s="14"/>
-      <c r="L86" s="14"/>
-      <c r="M86" s="14"/>
-      <c r="N86" s="14"/>
-      <c r="O86" s="14"/>
-      <c r="P86" s="14"/>
-      <c r="Q86" s="14"/>
-      <c r="R86" s="14"/>
-      <c r="S86" s="14"/>
-      <c r="T86" s="14"/>
-      <c r="U86" s="14"/>
-      <c r="V86" s="14"/>
-      <c r="W86" s="14"/>
-      <c r="X86" s="14"/>
-      <c r="Y86" s="14"/>
-      <c r="Z86" s="14"/>
-      <c r="AA86" s="14"/>
-      <c r="AB86" s="14"/>
-      <c r="AC86" s="14"/>
-      <c r="AD86" s="14"/>
-      <c r="AE86" s="14"/>
-    </row>
-    <row r="87" spans="1:32">
-      <c r="A87" s="14">
+    </row>
+    <row r="87" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87">
         <v>1950</v>
       </c>
-      <c r="B87" s="15">
+      <c r="B87" s="1">
         <v>50.7</v>
       </c>
-      <c r="C87" s="15">
+      <c r="C87" s="1">
         <v>54.4</v>
       </c>
-      <c r="D87" s="15">
+      <c r="D87" s="1">
         <v>45.5</v>
       </c>
-      <c r="E87" s="15">
+      <c r="E87" s="1">
         <v>37</v>
       </c>
-      <c r="F87" s="15">
+      <c r="F87" s="1">
         <v>19.7</v>
       </c>
-      <c r="G87" s="15">
+      <c r="G87" s="1">
         <v>22</v>
       </c>
-      <c r="H87" s="15">
+      <c r="H87" s="1">
         <v>38.700000000000003</v>
       </c>
-      <c r="I87" s="15">
+      <c r="I87" s="1">
         <v>24.5</v>
       </c>
-      <c r="J87" s="15">
+      <c r="J87" s="1">
         <v>5.5</v>
       </c>
-      <c r="K87" s="15">
+      <c r="K87" s="1">
         <v>13.8</v>
       </c>
-      <c r="L87" s="15">
+      <c r="L87" s="1">
         <v>6.8</v>
       </c>
-      <c r="M87" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="N87" s="15">
+      <c r="M87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N87" s="1">
         <v>11.1</v>
       </c>
-      <c r="O87" s="15">
+      <c r="O87" s="1">
         <v>22.5</v>
       </c>
-      <c r="P87" s="15">
+      <c r="P87" s="1">
         <v>18.399999999999999</v>
       </c>
-      <c r="Q87" s="15">
+      <c r="Q87" s="1">
         <v>38.299999999999997</v>
       </c>
-      <c r="R87" s="15">
-        <v>29.3</v>
-      </c>
-      <c r="S87" s="15">
+      <c r="R87" s="1">
+        <v>21.8</v>
+      </c>
+      <c r="S87" s="1">
         <v>15.2</v>
       </c>
-      <c r="T87" s="15">
+      <c r="T87" s="1">
         <v>28.2</v>
       </c>
-      <c r="U87" s="15">
+      <c r="U87" s="1">
         <v>19.600000000000001</v>
       </c>
-      <c r="V87" s="15">
+      <c r="V87" s="1">
         <v>15.9</v>
       </c>
-      <c r="W87" s="15">
+      <c r="W87" s="1">
         <v>14.7</v>
       </c>
-      <c r="X87" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y87" s="15">
+      <c r="X87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y87" s="1">
         <v>32</v>
       </c>
-      <c r="Z87" s="15">
+      <c r="Z87" s="1">
         <v>22.1</v>
       </c>
-      <c r="AA87" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB87" s="15">
+      <c r="AA87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB87" s="1">
         <v>47.1</v>
       </c>
-      <c r="AC87" s="15">
+      <c r="AC87" s="1">
         <v>18</v>
       </c>
-      <c r="AD87" s="15">
+      <c r="AD87" s="1">
         <v>16.399999999999999</v>
       </c>
-      <c r="AE87" s="15">
+      <c r="AE87" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:32">
-      <c r="A88" s="14">
+    <row r="88" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88">
         <v>1959</v>
       </c>
-      <c r="B88" s="15"/>
-      <c r="C88" s="15"/>
-      <c r="D88" s="15"/>
-      <c r="E88" s="15"/>
-      <c r="F88" s="15"/>
-      <c r="G88" s="15"/>
-      <c r="H88" s="15"/>
-      <c r="I88" s="15"/>
-      <c r="J88" s="15"/>
-      <c r="K88" s="15"/>
-      <c r="L88" s="15"/>
-      <c r="M88" s="15"/>
-      <c r="N88" s="15"/>
-      <c r="O88" s="15"/>
-      <c r="P88" s="15"/>
-      <c r="Q88" s="15"/>
-      <c r="R88" s="15"/>
-      <c r="S88" s="15"/>
-      <c r="T88" s="15"/>
-      <c r="U88" s="15"/>
-      <c r="V88" s="15"/>
-      <c r="W88" s="15"/>
-      <c r="X88" s="15"/>
-      <c r="Y88" s="15"/>
-      <c r="Z88" s="15"/>
-      <c r="AA88" s="15"/>
-      <c r="AB88" s="15"/>
-      <c r="AC88" s="15"/>
-      <c r="AD88" s="15"/>
-      <c r="AE88" s="15">
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="1"/>
+      <c r="N88" s="1"/>
+      <c r="O88" s="1"/>
+      <c r="P88" s="1"/>
+      <c r="Q88" s="1"/>
+      <c r="R88" s="1"/>
+      <c r="S88" s="1"/>
+      <c r="T88" s="1"/>
+      <c r="U88" s="1"/>
+      <c r="V88" s="1"/>
+      <c r="W88" s="1"/>
+      <c r="X88" s="1"/>
+      <c r="Y88" s="1"/>
+      <c r="Z88" s="1"/>
+      <c r="AA88" s="1"/>
+      <c r="AB88" s="1"/>
+      <c r="AC88" s="1"/>
+      <c r="AD88" s="1"/>
+      <c r="AE88" s="1">
         <v>35.6</v>
       </c>
       <c r="AF88" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="89" spans="1:32">
-      <c r="A89" s="14">
+    <row r="89" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89">
         <v>1960</v>
       </c>
-      <c r="B89" s="15">
+      <c r="B89" s="1">
         <v>60</v>
       </c>
-      <c r="C89" s="15">
+      <c r="C89" s="1">
         <v>62.1</v>
       </c>
-      <c r="D89" s="15">
+      <c r="D89" s="1">
         <v>46.2</v>
       </c>
-      <c r="E89" s="15">
+      <c r="E89" s="1">
         <v>44.3</v>
       </c>
-      <c r="F89" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="15">
+      <c r="F89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="1">
         <v>29</v>
       </c>
-      <c r="H89" s="15">
+      <c r="H89" s="1">
         <v>52.7</v>
       </c>
-      <c r="I89" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="15">
+      <c r="I89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="1">
         <v>19.3</v>
       </c>
-      <c r="L89" s="15">
+      <c r="L89" s="1">
         <v>11.5</v>
       </c>
-      <c r="M89" s="15">
+      <c r="M89" s="1">
         <v>30.3</v>
       </c>
-      <c r="N89" s="15">
+      <c r="N89" s="1">
         <v>18.7</v>
       </c>
-      <c r="O89" s="15">
+      <c r="O89" s="1">
         <v>37.200000000000003</v>
       </c>
-      <c r="P89" s="15">
+      <c r="P89" s="1">
         <v>22.8</v>
       </c>
-      <c r="Q89" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="15">
-        <v>37</v>
-      </c>
-      <c r="S89" s="15">
+      <c r="Q89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="1">
+        <v>29.6</v>
+      </c>
+      <c r="S89" s="1">
         <v>23</v>
       </c>
-      <c r="T89" s="15">
+      <c r="T89" s="1">
         <v>34.6</v>
       </c>
-      <c r="U89" s="15">
+      <c r="U89" s="1">
         <v>23</v>
       </c>
-      <c r="V89" s="15">
+      <c r="V89" s="1">
         <v>30.7</v>
       </c>
-      <c r="W89" s="15">
+      <c r="W89" s="1">
         <v>19.5</v>
       </c>
-      <c r="X89" s="15">
+      <c r="X89" s="1">
         <v>25.6</v>
       </c>
-      <c r="Y89" s="15">
+      <c r="Y89" s="1">
         <v>37.6</v>
       </c>
-      <c r="Z89" s="15">
+      <c r="Z89" s="1">
         <v>36.799999999999997</v>
       </c>
-      <c r="AA89" s="15">
+      <c r="AA89" s="1">
         <v>66.900000000000006</v>
       </c>
-      <c r="AB89" s="15">
+      <c r="AB89" s="1">
         <v>55.1</v>
       </c>
-      <c r="AC89" s="15">
+      <c r="AC89" s="1">
         <v>27.7</v>
       </c>
-      <c r="AD89" s="15">
+      <c r="AD89" s="1">
         <v>24.9</v>
       </c>
-      <c r="AE89" s="15">
+      <c r="AE89" s="1">
         <v>36</v>
       </c>
     </row>
-    <row r="90" spans="1:32">
+    <row r="90" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A90">
         <v>1970</v>
       </c>
@@ -4594,7 +3855,7 @@
         <v>43.8</v>
       </c>
       <c r="R90" s="1">
-        <v>45.7</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="S90" s="1">
         <v>29.6</v>
@@ -4639,7 +3900,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="91" spans="1:32">
+    <row r="91" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A91">
         <v>1979</v>
       </c>
@@ -4675,11 +3936,11 @@
       <c r="AE91" s="1">
         <v>54.9</v>
       </c>
-      <c r="AF91" s="29">
+      <c r="AF91" s="24">
         <v>58</v>
       </c>
     </row>
-    <row r="92" spans="1:32">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A92">
         <v>1980</v>
       </c>
@@ -4732,7 +3993,7 @@
         <v>47.9</v>
       </c>
       <c r="R92" s="1">
-        <v>52.8</v>
+        <v>40.9</v>
       </c>
       <c r="S92" s="1" t="s">
         <v>3</v>
@@ -4771,7 +4032,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:32">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A93">
         <v>1989</v>
       </c>
@@ -4804,8 +4065,11 @@
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
       <c r="AD93" s="1"/>
-    </row>
-    <row r="94" spans="1:32">
+      <c r="AF93">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A94">
         <v>1990</v>
       </c>
@@ -4858,7 +4122,7 @@
         <v>3</v>
       </c>
       <c r="R94" s="1">
-        <v>57.1</v>
+        <v>44.4</v>
       </c>
       <c r="S94" s="1">
         <v>41</v>
@@ -4897,7 +4161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:32">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A95">
         <v>2000</v>
       </c>
@@ -4989,7 +4253,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:32">
+    <row r="96" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="A96">
         <v>2010</v>
       </c>
@@ -5081,93 +4345,93 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:26" ht="15">
+    <row r="100" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="102" spans="1:26" ht="15">
-      <c r="A102" s="16" t="s">
+    <row r="102" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B102" s="16" t="s">
+      <c r="B102" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C102" s="16" t="s">
+      <c r="C102" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D102" s="16" t="s">
+      <c r="D102" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E102" s="16" t="s">
+      <c r="E102" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F102" s="16" t="s">
+      <c r="F102" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G102" s="16" t="s">
+      <c r="G102" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H102" s="16" t="s">
+      <c r="H102" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I102" s="16" t="s">
+      <c r="I102" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="J102" s="16" t="s">
+      <c r="J102" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K102" s="16" t="s">
+      <c r="K102" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L102" s="16" t="s">
+      <c r="L102" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="M102" s="16" t="s">
+      <c r="M102" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="N102" s="16" t="s">
+      <c r="N102" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="O102" s="16" t="s">
+      <c r="O102" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="P102" s="16" t="s">
+      <c r="P102" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="Q102" s="16" t="s">
+      <c r="Q102" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="R102" s="16" t="s">
+      <c r="R102" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="S102" s="16" t="s">
+      <c r="S102" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="T102" s="16" t="s">
+      <c r="T102" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="U102" s="16" t="s">
+      <c r="U102" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="V102" s="16" t="s">
+      <c r="V102" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="W102" s="16" t="s">
+      <c r="W102" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="X102" s="16" t="s">
+      <c r="X102" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="Y102" s="16" t="s">
+      <c r="Y102" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="Z102" s="16" t="s">
+      <c r="Z102" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="103" spans="1:26" ht="15">
-      <c r="A103" s="12">
+    <row r="103" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103">
         <v>1865</v>
       </c>
       <c r="B103" s="2"/>
@@ -5197,8 +4461,8 @@
       <c r="X103" s="2"/>
       <c r="Y103" s="2"/>
     </row>
-    <row r="104" spans="1:26" ht="15">
-      <c r="A104" s="12">
+    <row r="104" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104">
         <v>1869</v>
       </c>
       <c r="B104" s="1">
@@ -5228,8 +4492,8 @@
       <c r="X104" s="2"/>
       <c r="Y104" s="2"/>
     </row>
-    <row r="105" spans="1:26" ht="15">
-      <c r="A105" s="12">
+    <row r="105" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105">
         <v>1875</v>
       </c>
       <c r="B105" s="2"/>
@@ -5259,8 +4523,8 @@
       <c r="X105" s="2"/>
       <c r="Y105" s="2"/>
     </row>
-    <row r="106" spans="1:26" ht="15">
-      <c r="A106" s="12">
+    <row r="106" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106">
         <v>1876</v>
       </c>
       <c r="B106" s="2"/>
@@ -5290,8 +4554,8 @@
       <c r="X106" s="2"/>
       <c r="Y106" s="2"/>
     </row>
-    <row r="107" spans="1:26" ht="15">
-      <c r="A107" s="12">
+    <row r="107" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107">
         <v>1885</v>
       </c>
       <c r="B107" s="2"/>
@@ -5321,8 +4585,8 @@
       <c r="X107" s="2"/>
       <c r="Y107" s="2"/>
     </row>
-    <row r="108" spans="1:26" ht="15">
-      <c r="A108" s="12">
+    <row r="108" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108">
         <v>1895</v>
       </c>
       <c r="B108" s="1">
@@ -5354,8 +4618,8 @@
       <c r="X108" s="2"/>
       <c r="Y108" s="2"/>
     </row>
-    <row r="109" spans="1:26" ht="15">
-      <c r="A109" s="12">
+    <row r="109" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109">
         <v>1900</v>
       </c>
       <c r="B109" s="1"/>
@@ -5372,7 +4636,7 @@
       <c r="K109" s="2"/>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
-      <c r="N109" s="19"/>
+      <c r="N109" s="15"/>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
       <c r="Q109" s="2"/>
@@ -5385,8 +4649,8 @@
       <c r="X109" s="2"/>
       <c r="Y109" s="2"/>
     </row>
-    <row r="110" spans="1:26" ht="15">
-      <c r="A110" s="12">
+    <row r="110" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110">
         <v>1907</v>
       </c>
       <c r="B110" s="2"/>
@@ -5397,13 +4661,6 @@
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
-      <c r="J110" s="12"/>
-      <c r="K110" s="12"/>
-      <c r="L110" s="12"/>
-      <c r="M110" s="12"/>
-      <c r="N110" s="12"/>
-      <c r="O110" s="12"/>
-      <c r="P110" s="12"/>
       <c r="Q110" s="2"/>
       <c r="R110" s="2"/>
       <c r="S110" s="2"/>
@@ -5416,7 +4673,7 @@
       <c r="X110" s="2"/>
       <c r="Y110" s="2"/>
     </row>
-    <row r="111" spans="1:26" ht="15">
+    <row r="111" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A111">
         <v>1914</v>
       </c>
@@ -5430,13 +4687,6 @@
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
-      <c r="J111" s="12"/>
-      <c r="K111" s="12"/>
-      <c r="L111" s="12"/>
-      <c r="M111" s="12"/>
-      <c r="N111" s="12"/>
-      <c r="O111" s="12"/>
-      <c r="P111" s="12"/>
       <c r="Q111" s="2"/>
       <c r="R111" s="2"/>
       <c r="S111" s="2"/>
@@ -5448,7 +4698,7 @@
       <c r="W111" s="2"/>
       <c r="X111" s="2"/>
     </row>
-    <row r="112" spans="1:26" ht="15">
+    <row r="112" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A112">
         <v>1919</v>
       </c>
@@ -5460,15 +4710,9 @@
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
-      <c r="J112" s="12"/>
-      <c r="K112" s="12"/>
-      <c r="L112" s="12"/>
-      <c r="M112" s="13">
+      <c r="M112" s="1">
         <v>16.136633940278379</v>
       </c>
-      <c r="N112" s="12"/>
-      <c r="O112" s="12"/>
-      <c r="P112" s="12"/>
       <c r="Q112" s="2"/>
       <c r="R112" s="2"/>
       <c r="S112" s="2"/>
@@ -5478,7 +4722,7 @@
       <c r="W112" s="2"/>
       <c r="X112" s="2"/>
     </row>
-    <row r="113" spans="1:26" ht="15">
+    <row r="113" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A113">
         <v>1920</v>
       </c>
@@ -5492,17 +4736,12 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
-      <c r="J113" s="12">
+      <c r="J113">
         <v>3.5</v>
       </c>
-      <c r="K113" s="12"/>
-      <c r="L113" s="12"/>
-      <c r="M113" s="12"/>
-      <c r="N113" s="12"/>
-      <c r="O113" s="12">
+      <c r="O113">
         <v>4.4000000000000004</v>
       </c>
-      <c r="P113" s="12"/>
       <c r="Q113" s="2"/>
       <c r="R113" s="2"/>
       <c r="S113" s="2"/>
@@ -5514,7 +4753,7 @@
       <c r="W113" s="2"/>
       <c r="X113" s="2"/>
     </row>
-    <row r="114" spans="1:26" ht="15">
+    <row r="114" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A114">
         <v>1926</v>
       </c>
@@ -5526,13 +4765,6 @@
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
-      <c r="J114" s="12"/>
-      <c r="K114" s="12"/>
-      <c r="L114" s="12"/>
-      <c r="M114" s="12"/>
-      <c r="N114" s="12"/>
-      <c r="O114" s="12"/>
-      <c r="P114" s="12"/>
       <c r="Q114" s="2"/>
       <c r="R114" s="2"/>
       <c r="S114" s="2"/>
@@ -5548,7 +4780,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="115" spans="1:26" ht="15">
+    <row r="115" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A115">
         <v>1927</v>
       </c>
@@ -5560,15 +4792,9 @@
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
-      <c r="J115" s="12"/>
-      <c r="K115" s="12"/>
-      <c r="L115" s="13">
+      <c r="L115" s="1">
         <v>15.938107074083186</v>
       </c>
-      <c r="M115" s="12"/>
-      <c r="N115" s="12"/>
-      <c r="O115" s="12"/>
-      <c r="P115" s="12"/>
       <c r="Q115" s="2"/>
       <c r="R115" s="2"/>
       <c r="S115" s="2"/>
@@ -5578,7 +4804,7 @@
       <c r="W115" s="2"/>
       <c r="X115" s="2"/>
     </row>
-    <row r="116" spans="1:26" ht="15">
+    <row r="116" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A116">
         <v>1930</v>
       </c>
@@ -5590,13 +4816,7 @@
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
-      <c r="J116" s="12"/>
-      <c r="K116" s="12"/>
-      <c r="L116" s="12"/>
-      <c r="M116" s="12"/>
-      <c r="N116" s="12"/>
-      <c r="O116" s="12"/>
-      <c r="P116" s="13">
+      <c r="P116" s="1">
         <v>17.399999999999999</v>
       </c>
       <c r="Q116" s="2"/>
@@ -5612,7 +4832,7 @@
       <c r="W116" s="2"/>
       <c r="X116" s="2"/>
     </row>
-    <row r="117" spans="1:26" ht="15">
+    <row r="117" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A117">
         <v>1931</v>
       </c>
@@ -5624,15 +4844,9 @@
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
-      <c r="J117" s="12"/>
-      <c r="K117" s="12"/>
-      <c r="L117" s="12"/>
-      <c r="M117" s="13">
+      <c r="M117" s="1">
         <v>20.751529902502156</v>
       </c>
-      <c r="N117" s="12"/>
-      <c r="O117" s="12"/>
-      <c r="P117" s="12"/>
       <c r="Q117" s="2"/>
       <c r="R117" s="2"/>
       <c r="S117" s="2"/>
@@ -5642,7 +4856,7 @@
       <c r="W117" s="2"/>
       <c r="X117" s="2"/>
     </row>
-    <row r="118" spans="1:26" ht="15">
+    <row r="118" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A118">
         <v>1935</v>
       </c>
@@ -5654,15 +4868,9 @@
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
-      <c r="J118" s="12">
+      <c r="J118">
         <v>4.7</v>
       </c>
-      <c r="K118" s="12"/>
-      <c r="L118" s="12"/>
-      <c r="M118" s="12"/>
-      <c r="N118" s="12"/>
-      <c r="O118" s="12"/>
-      <c r="P118" s="12"/>
       <c r="Q118" s="2"/>
       <c r="R118" s="2"/>
       <c r="S118" s="2"/>
@@ -5672,7 +4880,7 @@
       <c r="W118" s="2"/>
       <c r="X118" s="2"/>
     </row>
-    <row r="119" spans="1:26" ht="15">
+    <row r="119" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A119">
         <v>1936</v>
       </c>
@@ -5686,13 +4894,6 @@
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
-      <c r="J119" s="12"/>
-      <c r="K119" s="12"/>
-      <c r="L119" s="12"/>
-      <c r="M119" s="12"/>
-      <c r="N119" s="12"/>
-      <c r="O119" s="12"/>
-      <c r="P119" s="12"/>
       <c r="Q119" s="2"/>
       <c r="R119" s="2"/>
       <c r="S119" s="2"/>
@@ -5702,7 +4903,7 @@
       <c r="W119" s="2"/>
       <c r="X119" s="2"/>
     </row>
-    <row r="120" spans="1:26" ht="15">
+    <row r="120" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A120">
         <v>1938</v>
       </c>
@@ -5714,15 +4915,10 @@
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
-      <c r="J120" s="13"/>
-      <c r="K120" s="13">
+      <c r="J120" s="1"/>
+      <c r="K120" s="1">
         <v>9.4609561958101622</v>
       </c>
-      <c r="L120" s="12"/>
-      <c r="M120" s="12"/>
-      <c r="N120" s="12"/>
-      <c r="O120" s="12"/>
-      <c r="P120" s="12"/>
       <c r="Q120" s="2"/>
       <c r="R120" s="2"/>
       <c r="S120" s="2"/>
@@ -5732,7 +4928,7 @@
       <c r="W120" s="2"/>
       <c r="X120" s="2"/>
     </row>
-    <row r="121" spans="1:26" ht="15">
+    <row r="121" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A121">
         <v>1940</v>
       </c>
@@ -5748,17 +4944,13 @@
         <v>5.6620215161447227</v>
       </c>
       <c r="I121" s="2"/>
-      <c r="J121" s="12"/>
-      <c r="K121" s="12"/>
-      <c r="L121" s="12"/>
-      <c r="M121" s="12"/>
-      <c r="N121" s="12">
+      <c r="N121">
         <v>10.199999999999999</v>
       </c>
-      <c r="O121" s="12">
+      <c r="O121">
         <v>7.5</v>
       </c>
-      <c r="P121" s="13">
+      <c r="P121" s="1">
         <v>19.7</v>
       </c>
       <c r="Q121" s="2"/>
@@ -5774,7 +4966,7 @@
       <c r="W121" s="2"/>
       <c r="X121" s="2"/>
     </row>
-    <row r="122" spans="1:26" ht="15">
+    <row r="122" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A122">
         <v>1941</v>
       </c>
@@ -5788,13 +4980,6 @@
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
       <c r="I122" s="2"/>
-      <c r="J122" s="12"/>
-      <c r="K122" s="12"/>
-      <c r="L122" s="12"/>
-      <c r="M122" s="12"/>
-      <c r="N122" s="12"/>
-      <c r="O122" s="12"/>
-      <c r="P122" s="12"/>
       <c r="Q122" s="2"/>
       <c r="R122" s="2"/>
       <c r="S122" s="2"/>
@@ -5804,7 +4989,7 @@
       <c r="W122" s="2"/>
       <c r="X122" s="2"/>
     </row>
-    <row r="123" spans="1:26" ht="15">
+    <row r="123" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A123">
         <v>1943</v>
       </c>
@@ -5816,15 +5001,9 @@
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
-      <c r="L123" s="12"/>
-      <c r="M123" s="13">
+      <c r="M123" s="1">
         <v>22.055413091163864</v>
       </c>
-      <c r="N123" s="12"/>
-      <c r="O123" s="12"/>
-      <c r="P123" s="12"/>
       <c r="Q123" s="2"/>
       <c r="R123" s="2"/>
       <c r="S123" s="2"/>
@@ -5834,7 +5013,7 @@
       <c r="W123" s="2"/>
       <c r="X123" s="2"/>
     </row>
-    <row r="124" spans="1:26" ht="15">
+    <row r="124" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A124">
         <v>1947</v>
       </c>
@@ -5864,7 +5043,7 @@
       <c r="W124" s="2"/>
       <c r="X124" s="2"/>
     </row>
-    <row r="125" spans="1:26">
+    <row r="125" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A125">
         <v>1950</v>
       </c>
@@ -5903,7 +5082,7 @@
         <v>25.7</v>
       </c>
       <c r="N125" s="1">
-        <v>21.4</v>
+        <v>14.1</v>
       </c>
       <c r="O125" s="1">
         <v>10.3</v>
@@ -5939,7 +5118,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:26">
+    <row r="126" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A126">
         <v>1959</v>
       </c>
@@ -5973,7 +5152,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="127" spans="1:26">
+    <row r="127" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A127">
         <v>1960</v>
       </c>
@@ -6014,7 +5193,7 @@
         <v>3</v>
       </c>
       <c r="N127" s="1">
-        <v>28</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="O127" s="1">
         <v>15.3</v>
@@ -6047,7 +5226,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="128" spans="1:26">
+    <row r="128" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A128">
         <v>1970</v>
       </c>
@@ -6088,7 +5267,7 @@
         <v>31</v>
       </c>
       <c r="N128" s="1">
-        <v>37.700000000000003</v>
+        <v>23.3</v>
       </c>
       <c r="O128" s="1">
         <v>20.5</v>
@@ -6127,7 +5306,7 @@
         <v>35.799999999999997</v>
       </c>
     </row>
-    <row r="129" spans="1:26">
+    <row r="129" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A129">
         <v>1979</v>
       </c>
@@ -6157,11 +5336,11 @@
       <c r="Y129" s="1">
         <v>40.4</v>
       </c>
-      <c r="Z129" s="29">
+      <c r="Z129" s="24">
         <v>42.7</v>
       </c>
     </row>
-    <row r="130" spans="1:26">
+    <row r="130" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A130">
         <v>1980</v>
       </c>
@@ -6202,7 +5381,7 @@
         <v>32.4</v>
       </c>
       <c r="N130" s="1">
-        <v>45.3</v>
+        <v>40.9</v>
       </c>
       <c r="O130" s="1" t="s">
         <v>3</v>
@@ -6235,225 +5414,256 @@
         <v>24</v>
       </c>
     </row>
-    <row r="131" spans="1:26">
+    <row r="131" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="A131">
+        <v>1989</v>
+      </c>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
+      <c r="E131" s="1"/>
+      <c r="F131" s="1"/>
+      <c r="G131" s="1"/>
+      <c r="H131" s="1"/>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1"/>
+      <c r="K131" s="1"/>
+      <c r="L131" s="1"/>
+      <c r="M131" s="1"/>
+      <c r="N131" s="1"/>
+      <c r="O131" s="1"/>
+      <c r="P131" s="1"/>
+      <c r="Q131" s="1"/>
+      <c r="R131" s="1"/>
+      <c r="S131" s="1"/>
+      <c r="T131" s="1"/>
+      <c r="U131" s="1"/>
+      <c r="V131" s="1"/>
+      <c r="W131" s="1"/>
+      <c r="X131" s="1"/>
+      <c r="Z131">
+        <v>45.7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A132">
         <v>1990</v>
       </c>
-      <c r="B131" s="1">
+      <c r="B132" s="1">
         <v>61.8</v>
       </c>
-      <c r="C131" s="1">
+      <c r="C132" s="1">
         <v>41.3</v>
       </c>
-      <c r="D131" s="1">
+      <c r="D132" s="1">
         <v>45.6</v>
       </c>
-      <c r="E131" s="1">
+      <c r="E132" s="1">
         <v>59.5</v>
       </c>
-      <c r="F131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H131" s="1">
+      <c r="F132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H132" s="1">
         <v>19</v>
       </c>
-      <c r="I131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J131" s="1">
+      <c r="I132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J132" s="1">
         <v>32.200000000000003</v>
       </c>
-      <c r="K131" s="1">
+      <c r="K132" s="1">
         <v>49.3</v>
       </c>
-      <c r="L131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N131" s="1">
-        <v>47.5</v>
-      </c>
-      <c r="O131" s="1">
+      <c r="L132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N132" s="1">
+        <v>44.4</v>
+      </c>
+      <c r="O132" s="1">
         <v>22.7</v>
       </c>
-      <c r="P131" s="1">
+      <c r="P132" s="1">
         <v>36.299999999999997</v>
       </c>
-      <c r="Q131" s="1">
+      <c r="Q132" s="1">
         <v>31.6</v>
       </c>
-      <c r="R131" s="1">
+      <c r="R132" s="1">
         <v>48</v>
       </c>
-      <c r="S131" s="1">
+      <c r="S132" s="1">
         <v>28</v>
       </c>
-      <c r="T131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U131" s="1">
+      <c r="T132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U132" s="1">
         <v>50.3</v>
       </c>
-      <c r="V131" s="1">
+      <c r="V132" s="1">
         <v>60.8</v>
       </c>
-      <c r="W131" s="1">
+      <c r="W132" s="1">
         <v>36.4</v>
       </c>
-      <c r="X131" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="132" spans="1:26">
-      <c r="A132">
+      <c r="X132" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A133">
         <v>2000</v>
       </c>
-      <c r="B132" s="1">
+      <c r="B133" s="1">
         <v>62.3</v>
       </c>
-      <c r="C132" s="1">
+      <c r="C133" s="1">
         <v>44.9</v>
       </c>
-      <c r="D132" s="1">
+      <c r="D133" s="1">
         <v>49.6</v>
       </c>
-      <c r="E132" s="1">
+      <c r="E133" s="1">
         <v>61.6</v>
       </c>
-      <c r="F132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G132" s="1">
+      <c r="F133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G133" s="1">
         <v>27.2</v>
       </c>
-      <c r="H132" s="1">
+      <c r="H133" s="1">
         <v>20.2</v>
       </c>
-      <c r="I132" s="1">
+      <c r="I133" s="1">
         <v>24.3</v>
       </c>
-      <c r="J132" s="1">
+      <c r="J133" s="1">
         <v>41.4</v>
-      </c>
-      <c r="K132" s="1">
-        <v>53.9</v>
-      </c>
-      <c r="L132" s="1">
-        <v>33.9</v>
-      </c>
-      <c r="M132" s="1">
-        <v>39.5</v>
-      </c>
-      <c r="N132" s="1">
-        <v>50.2</v>
-      </c>
-      <c r="O132" s="1">
-        <v>21.9</v>
-      </c>
-      <c r="P132" s="1">
-        <v>51.2</v>
-      </c>
-      <c r="Q132" s="1">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="R132" s="1">
-        <v>53.5</v>
-      </c>
-      <c r="S132" s="1">
-        <v>29.9</v>
-      </c>
-      <c r="T132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U132" s="1">
-        <v>47.4</v>
-      </c>
-      <c r="V132" s="1">
-        <v>63.6</v>
-      </c>
-      <c r="W132" s="1">
-        <v>44.2</v>
-      </c>
-      <c r="X132" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="133" spans="1:26">
-      <c r="A133">
-        <v>2010</v>
-      </c>
-      <c r="B133" s="1">
-        <v>64.7</v>
-      </c>
-      <c r="C133" s="1">
-        <v>52.2</v>
-      </c>
-      <c r="D133" s="1">
-        <v>56.6</v>
-      </c>
-      <c r="E133" s="1">
-        <v>63.5</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I133" s="1">
-        <v>29.3</v>
-      </c>
-      <c r="J133" s="1">
-        <v>52.9</v>
       </c>
       <c r="K133" s="1">
         <v>53.9</v>
       </c>
       <c r="L133" s="1">
+        <v>33.9</v>
+      </c>
+      <c r="M133" s="1">
+        <v>39.5</v>
+      </c>
+      <c r="N133" s="1">
+        <v>50.2</v>
+      </c>
+      <c r="O133" s="1">
+        <v>21.9</v>
+      </c>
+      <c r="P133" s="1">
+        <v>51.2</v>
+      </c>
+      <c r="Q133" s="1">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="R133" s="1">
+        <v>53.5</v>
+      </c>
+      <c r="S133" s="1">
+        <v>29.9</v>
+      </c>
+      <c r="T133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U133" s="1">
+        <v>47.4</v>
+      </c>
+      <c r="V133" s="1">
+        <v>63.6</v>
+      </c>
+      <c r="W133" s="1">
+        <v>44.2</v>
+      </c>
+      <c r="X133" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A134">
+        <v>2010</v>
+      </c>
+      <c r="B134" s="1">
+        <v>64.7</v>
+      </c>
+      <c r="C134" s="1">
+        <v>52.2</v>
+      </c>
+      <c r="D134" s="1">
+        <v>56.6</v>
+      </c>
+      <c r="E134" s="1">
+        <v>63.5</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I134" s="1">
+        <v>29.3</v>
+      </c>
+      <c r="J134" s="1">
+        <v>52.9</v>
+      </c>
+      <c r="K134" s="1">
+        <v>53.9</v>
+      </c>
+      <c r="L134" s="1">
         <v>46.4</v>
       </c>
-      <c r="M133" s="1">
+      <c r="M134" s="1">
         <v>40.4</v>
       </c>
-      <c r="N133" s="1">
+      <c r="N134" s="1">
         <v>60.7</v>
       </c>
-      <c r="O133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P133" s="1">
+      <c r="O134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P134" s="1">
         <v>52.6</v>
       </c>
-      <c r="Q133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="R133" s="1">
+      <c r="Q134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R134" s="1">
         <v>59</v>
       </c>
-      <c r="S133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="T133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U133" s="1">
+      <c r="S134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U134" s="1">
         <v>54</v>
       </c>
-      <c r="V133" s="1">
+      <c r="V134" s="1">
         <v>72.5</v>
       </c>
-      <c r="W133" s="1">
+      <c r="W134" s="1">
         <v>52</v>
       </c>
-      <c r="X133" s="1" t="s">
+      <c r="X134" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -6466,22 +5676,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13506065-263E-4E0E-AA1C-6A8B756E2690}">
   <dimension ref="A1:O124"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="31.375" customWidth="1"/>
+    <col min="1" max="1" width="31.3671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="11" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
@@ -6504,7 +5714,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -6527,7 +5737,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -6550,7 +5760,7 @@
         <v>47.9</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -6573,7 +5783,7 @@
         <v>62.4</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -6596,7 +5806,7 @@
         <v>81.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -6619,7 +5829,7 @@
         <v>86.9</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -6642,7 +5852,7 @@
         <v>35.6</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -6665,7 +5875,7 @@
         <v>46.1</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -6688,7 +5898,7 @@
         <v>36.200000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -6711,7 +5921,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -6734,7 +5944,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -6757,7 +5967,7 @@
         <v>74.900000000000006</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -6780,7 +5990,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -6803,7 +6013,7 @@
         <v>75.2</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -6826,7 +6036,7 @@
         <v>69.8</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -6849,7 +6059,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -6872,7 +6082,7 @@
         <v>65.599999999999994</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -6895,7 +6105,7 @@
         <v>58.7</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -6918,7 +6128,7 @@
         <v>72.8</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -6941,7 +6151,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -6964,7 +6174,7 @@
         <v>74.099999999999994</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -6987,7 +6197,7 @@
         <v>91.9</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -7010,7 +6220,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -7033,7 +6243,7 @@
         <v>86.6</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -7056,7 +6266,7 @@
         <v>61.4</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>26</v>
       </c>
@@ -7079,17 +6289,17 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="2" t="s">
         <v>38</v>
       </c>
@@ -7112,7 +6322,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -7135,7 +6345,7 @@
         <v>89.1</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -7158,7 +6368,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -7181,7 +6391,7 @@
         <v>62.7</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -7204,7 +6414,7 @@
         <v>79.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -7225,7 +6435,7 @@
       </c>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -7246,7 +6456,7 @@
       </c>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>23</v>
       </c>
@@ -7269,7 +6479,7 @@
         <v>47.7</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -7292,7 +6502,7 @@
         <v>36.200000000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>25</v>
       </c>
@@ -7315,7 +6525,7 @@
         <v>43.9</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>30</v>
       </c>
@@ -7338,7 +6548,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>10</v>
       </c>
@@ -7359,7 +6569,7 @@
       </c>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -7382,7 +6592,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>21</v>
       </c>
@@ -7403,7 +6613,7 @@
       </c>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -7426,7 +6636,7 @@
         <v>74.5</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>28</v>
       </c>
@@ -7447,7 +6657,7 @@
       </c>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>29</v>
       </c>
@@ -7470,7 +6680,7 @@
         <v>61.6</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -7493,7 +6703,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -7514,7 +6724,7 @@
       </c>
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>22</v>
       </c>
@@ -7535,7 +6745,7 @@
       </c>
       <c r="G53" s="1"/>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>16</v>
       </c>
@@ -7558,7 +6768,7 @@
         <v>74.099999999999994</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>17</v>
       </c>
@@ -7579,7 +6789,7 @@
       </c>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>13</v>
       </c>
@@ -7602,7 +6812,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -7625,7 +6835,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -7648,7 +6858,7 @@
         <v>61.6</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>26</v>
       </c>
@@ -7671,22 +6881,22 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="15">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="15">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="5"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -7703,7 +6913,7 @@
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
     </row>
-    <row r="65" spans="1:15" ht="15">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="2" t="s">
         <v>38</v>
       </c>
@@ -7736,7 +6946,7 @@
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
     </row>
-    <row r="66" spans="1:15" ht="15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="5" t="s">
         <v>6</v>
       </c>
@@ -7769,7 +6979,7 @@
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
     </row>
-    <row r="67" spans="1:15" ht="15">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="5" t="s">
         <v>31</v>
       </c>
@@ -7802,7 +7012,7 @@
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
     </row>
-    <row r="68" spans="1:15" ht="15">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="5" t="s">
         <v>32</v>
       </c>
@@ -7835,7 +7045,7 @@
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
     </row>
-    <row r="69" spans="1:15" ht="15">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="5" t="s">
         <v>19</v>
       </c>
@@ -7868,7 +7078,7 @@
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
     </row>
-    <row r="70" spans="1:15" ht="15">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="5" t="s">
         <v>7</v>
       </c>
@@ -7901,7 +7111,7 @@
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
     </row>
-    <row r="71" spans="1:15" ht="15">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="5" t="s">
         <v>8</v>
       </c>
@@ -7934,7 +7144,7 @@
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
     </row>
-    <row r="72" spans="1:15" ht="15">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="5" t="s">
         <v>18</v>
       </c>
@@ -7967,7 +7177,7 @@
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
     </row>
-    <row r="73" spans="1:15" ht="15">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="5" t="s">
         <v>34</v>
       </c>
@@ -8000,7 +7210,7 @@
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
     </row>
-    <row r="74" spans="1:15" ht="15">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="5" t="s">
         <v>24</v>
       </c>
@@ -8033,7 +7243,7 @@
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
     </row>
-    <row r="75" spans="1:15" ht="15">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="5" t="s">
         <v>23</v>
       </c>
@@ -8066,7 +7276,7 @@
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
     </row>
-    <row r="76" spans="1:15" ht="15">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="5" t="s">
         <v>25</v>
       </c>
@@ -8099,7 +7309,7 @@
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
     </row>
-    <row r="77" spans="1:15" ht="15">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="5" t="s">
         <v>33</v>
       </c>
@@ -8132,7 +7342,7 @@
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
     </row>
-    <row r="78" spans="1:15" ht="15">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="5" t="s">
         <v>30</v>
       </c>
@@ -8165,7 +7375,7 @@
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
     </row>
-    <row r="79" spans="1:15" ht="15">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="5" t="s">
         <v>10</v>
       </c>
@@ -8198,7 +7408,7 @@
       <c r="N79" s="4"/>
       <c r="O79" s="4"/>
     </row>
-    <row r="80" spans="1:15" ht="15">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="5" t="s">
         <v>20</v>
       </c>
@@ -8231,7 +7441,7 @@
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
     </row>
-    <row r="81" spans="1:15" ht="15">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="5" t="s">
         <v>21</v>
       </c>
@@ -8264,7 +7474,7 @@
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
     </row>
-    <row r="82" spans="1:15" ht="15">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="5" t="s">
         <v>27</v>
       </c>
@@ -8297,7 +7507,7 @@
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
     </row>
-    <row r="83" spans="1:15" ht="15">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="5" t="s">
         <v>28</v>
       </c>
@@ -8330,7 +7540,7 @@
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
     </row>
-    <row r="84" spans="1:15" ht="15">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="5" t="s">
         <v>29</v>
       </c>
@@ -8363,7 +7573,7 @@
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
     </row>
-    <row r="85" spans="1:15" ht="15">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="5" t="s">
         <v>14</v>
       </c>
@@ -8396,7 +7606,7 @@
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
     </row>
-    <row r="86" spans="1:15" ht="15">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="5" t="s">
         <v>15</v>
       </c>
@@ -8429,7 +7639,7 @@
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
     </row>
-    <row r="87" spans="1:15" ht="15">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="5" t="s">
         <v>22</v>
       </c>
@@ -8462,7 +7672,7 @@
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
     </row>
-    <row r="88" spans="1:15" ht="15">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="5" t="s">
         <v>35</v>
       </c>
@@ -8495,7 +7705,7 @@
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
     </row>
-    <row r="89" spans="1:15" ht="15">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="5" t="s">
         <v>36</v>
       </c>
@@ -8528,7 +7738,7 @@
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
     </row>
-    <row r="90" spans="1:15" ht="15">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="5" t="s">
         <v>37</v>
       </c>
@@ -8561,7 +7771,7 @@
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
     </row>
-    <row r="91" spans="1:15" ht="15">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="5" t="s">
         <v>17</v>
       </c>
@@ -8587,7 +7797,7 @@
         <v>77.8</v>
       </c>
     </row>
-    <row r="92" spans="1:15" ht="15">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="5" t="s">
         <v>9</v>
       </c>
@@ -8613,7 +7823,7 @@
         <v>80.3</v>
       </c>
     </row>
-    <row r="93" spans="1:15" ht="15">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="5" t="s">
         <v>11</v>
       </c>
@@ -8639,7 +7849,7 @@
         <v>64.400000000000006</v>
       </c>
     </row>
-    <row r="94" spans="1:15" ht="15">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="5" t="s">
         <v>26</v>
       </c>
@@ -8665,17 +7875,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:15" ht="15">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="2" t="s">
         <v>38</v>
       </c>
@@ -8701,7 +7911,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="5" t="s">
         <v>6</v>
       </c>
@@ -8727,7 +7937,7 @@
         <v>64.7</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="5" t="s">
         <v>7</v>
       </c>
@@ -8753,7 +7963,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="5" t="s">
         <v>8</v>
       </c>
@@ -8779,7 +7989,7 @@
         <v>56.6</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="5" t="s">
         <v>18</v>
       </c>
@@ -8805,7 +8015,7 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="5" t="s">
         <v>34</v>
       </c>
@@ -8831,7 +8041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="5" t="s">
         <v>24</v>
       </c>
@@ -8857,7 +8067,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="5" t="s">
         <v>23</v>
       </c>
@@ -8883,7 +8093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="5" t="s">
         <v>25</v>
       </c>
@@ -8909,7 +8119,7 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="5" t="s">
         <v>30</v>
       </c>
@@ -8935,7 +8145,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="5" t="s">
         <v>10</v>
       </c>
@@ -8961,7 +8171,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="5" t="s">
         <v>20</v>
       </c>
@@ -8987,7 +8197,7 @@
         <v>46.4</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="5" t="s">
         <v>21</v>
       </c>
@@ -9013,7 +8223,7 @@
         <v>40.4</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="5" t="s">
         <v>27</v>
       </c>
@@ -9039,7 +8249,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="5" t="s">
         <v>28</v>
       </c>
@@ -9065,7 +8275,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="5" t="s">
         <v>29</v>
       </c>
@@ -9091,7 +8301,7 @@
         <v>52.6</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="15">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="5" t="s">
         <v>14</v>
       </c>
@@ -9117,7 +8327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="5" t="s">
         <v>15</v>
       </c>
@@ -9143,7 +8353,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="5" t="s">
         <v>22</v>
       </c>
@@ -9169,7 +8379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="5" t="s">
         <v>37</v>
       </c>
@@ -9195,7 +8405,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="5" t="s">
         <v>17</v>
       </c>
@@ -9221,7 +8431,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="5" t="s">
         <v>9</v>
       </c>
@@ -9247,7 +8457,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="5" t="s">
         <v>11</v>
       </c>
@@ -9273,7 +8483,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="5" t="s">
         <v>26</v>
       </c>
@@ -9299,7 +8509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="5"/>
     </row>
   </sheetData>
@@ -9313,47 +8523,47 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{963BF401-935F-4B94-9C82-FE672CD446F7}">
   <dimension ref="A1:M46"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="7.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.62890625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.47265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.3671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="7.26171875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.26171875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.26171875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.3671875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.62890625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="11" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15">
-      <c r="D4" s="32" t="s">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="D4" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="L4" s="32" t="s">
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="L4" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="M4" s="32"/>
-    </row>
-    <row r="5" spans="1:13" ht="15">
+      <c r="M4" s="26"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>38</v>
       </c>
@@ -9391,7 +8601,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -9430,7 +8640,7 @@
         <v>39.999919465588746</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -9469,7 +8679,7 @@
         <v>31.501729117336613</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -9508,7 +8718,7 @@
         <v>10.702575393983178</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -9545,7 +8755,7 @@
         <v>12.354575557604816</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -9580,7 +8790,7 @@
         <v>10.959868289448146</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -9613,7 +8823,7 @@
         <v>5.6620215161447227</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -9648,7 +8858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -9685,7 +8895,7 @@
         <v>7.4679699042130974</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -9718,7 +8928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -9757,7 +8967,7 @@
         <v>22.055413091163864</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -9796,7 +9006,7 @@
         <v>20.751529902502156</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -9833,7 +9043,7 @@
         <v>16.136633940278379</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -9866,7 +9076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -9899,7 +9109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -9934,7 +9144,7 @@
         <v>17.97258487317211</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -9969,7 +9179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -10006,7 +9216,7 @@
         <v>8.3848383858999256</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -10041,7 +9251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -10080,7 +9290,7 @@
         <v>23.131501517157528</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -10119,7 +9329,7 @@
         <v>21.125355543919515</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -10158,7 +9368,7 @@
         <v>18.489934280279929</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
@@ -10168,7 +9378,7 @@
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
@@ -10178,7 +9388,7 @@
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
@@ -10188,7 +9398,7 @@
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
@@ -10198,7 +9408,7 @@
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
@@ -10208,7 +9418,7 @@
       <c r="I31" s="7"/>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
@@ -10218,7 +9428,7 @@
       <c r="I32" s="7"/>
       <c r="J32" s="7"/>
     </row>
-    <row r="33" spans="3:10">
+    <row r="33" spans="3:10" x14ac:dyDescent="0.55000000000000004">
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
@@ -10228,7 +9438,7 @@
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
     </row>
-    <row r="34" spans="3:10">
+    <row r="34" spans="3:10" x14ac:dyDescent="0.55000000000000004">
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
@@ -10238,7 +9448,7 @@
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" spans="3:10">
+    <row r="35" spans="3:10" x14ac:dyDescent="0.55000000000000004">
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -10248,7 +9458,7 @@
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
     </row>
-    <row r="36" spans="3:10">
+    <row r="36" spans="3:10" x14ac:dyDescent="0.55000000000000004">
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -10258,7 +9468,7 @@
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
     </row>
-    <row r="37" spans="3:10">
+    <row r="37" spans="3:10" x14ac:dyDescent="0.55000000000000004">
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -10268,7 +9478,7 @@
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
     </row>
-    <row r="38" spans="3:10">
+    <row r="38" spans="3:10" x14ac:dyDescent="0.55000000000000004">
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
@@ -10278,7 +9488,7 @@
       <c r="I38" s="7"/>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" spans="3:10">
+    <row r="39" spans="3:10" x14ac:dyDescent="0.55000000000000004">
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -10288,7 +9498,7 @@
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" spans="3:10">
+    <row r="40" spans="3:10" x14ac:dyDescent="0.55000000000000004">
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
@@ -10298,7 +9508,7 @@
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
     </row>
-    <row r="41" spans="3:10">
+    <row r="41" spans="3:10" x14ac:dyDescent="0.55000000000000004">
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
@@ -10308,7 +9518,7 @@
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" spans="3:10">
+    <row r="42" spans="3:10" x14ac:dyDescent="0.55000000000000004">
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
@@ -10318,7 +9528,7 @@
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" spans="3:10">
+    <row r="43" spans="3:10" x14ac:dyDescent="0.55000000000000004">
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
@@ -10328,7 +9538,7 @@
       <c r="I43" s="7"/>
       <c r="J43" s="7"/>
     </row>
-    <row r="44" spans="3:10">
+    <row r="44" spans="3:10" x14ac:dyDescent="0.55000000000000004">
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
@@ -10338,7 +9548,7 @@
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
     </row>
-    <row r="45" spans="3:10">
+    <row r="45" spans="3:10" x14ac:dyDescent="0.55000000000000004">
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
@@ -10347,7 +9557,7 @@
       <c r="H45" s="7"/>
       <c r="I45" s="7"/>
     </row>
-    <row r="46" spans="3:10">
+    <row r="46" spans="3:10" x14ac:dyDescent="0.55000000000000004">
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
@@ -10371,28 +9581,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C7C1AA-F6CE-4B15-A1F0-6B51B5CB852A}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="3" max="3" width="13.875" customWidth="1"/>
-    <col min="5" max="5" width="24.625" customWidth="1"/>
+    <col min="3" max="3" width="13.89453125" customWidth="1"/>
+    <col min="5" max="5" width="24.62890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8" t="s">
         <v>38</v>
       </c>
@@ -10411,7 +9621,7 @@
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -10428,7 +9638,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -10450,38 +9660,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E826B6E2-6891-4E9F-99E3-F5829E93EAFA}">
   <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="5.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.62890625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.25" customWidth="1"/>
+    <col min="5" max="5" width="12.89453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.47265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.3671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.26171875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="9" t="s">
         <v>38</v>
       </c>
@@ -10511,7 +9721,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>67</v>
       </c>
@@ -10542,7 +9752,7 @@
         <v>16.412235273528619</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -10573,7 +9783,7 @@
         <v>24.590995853004024</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>67</v>
       </c>
@@ -10604,7 +9814,7 @@
         <v>32.61908297746789</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>67</v>
       </c>
@@ -10635,7 +9845,7 @@
         <v>38.944534881372498</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -10666,7 +9876,7 @@
         <v>3.1064017920301814</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -10697,7 +9907,7 @@
         <v>10.634968637287924</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -10728,7 +9938,7 @@
         <v>10.943696108636283</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -10759,7 +9969,7 @@
         <v>13.231908342299171</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -10790,7 +10000,7 @@
         <v>10.981226600587174</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -10821,7 +10031,7 @@
         <v>11.841254044492914</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -10852,7 +10062,7 @@
         <v>12.749795119459268</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -10883,7 +10093,7 @@
         <v>15.576245989559462</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -10914,7 +10124,7 @@
         <v>17.093485515276829</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -10945,7 +10155,7 @@
         <v>20.291115180623258</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -10976,7 +10186,7 @@
         <v>22.93503473513946</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -11007,7 +10217,7 @@
         <v>24.839719568216751</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -11038,7 +10248,7 @@
         <v>28.524008531947185</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -11069,7 +10279,7 @@
         <v>9.4609561958101622</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -11100,7 +10310,7 @@
         <v>14.708734854312873</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>14</v>
       </c>
@@ -11128,7 +10338,7 @@
         <v>11.197210631902117</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>14</v>
       </c>
@@ -11156,7 +10366,7 @@
         <v>15.155986064983907</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -11187,7 +10397,7 @@
         <v>3.760059812397142</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -11218,7 +10428,7 @@
         <v>8.3848383858999256</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -11249,7 +10459,7 @@
         <v>10.396698081381023</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -11280,7 +10490,7 @@
         <v>11.551115348069256</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -11311,7 +10521,7 @@
         <v>16.602758619045936</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>20</v>
       </c>
@@ -11339,7 +10549,7 @@
         <v>15.938107074083186</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>20</v>
       </c>
@@ -11367,7 +10577,7 @@
         <v>19.183518027157795</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -11398,7 +10608,7 @@
         <v>15.794024515023171</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -11429,7 +10639,7 @@
         <v>17.498682597977361</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>21</v>
       </c>
@@ -11460,7 +10670,7 @@
         <v>18.798710831223399</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -11491,7 +10701,7 @@
         <v>3.4586130003967965</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -11522,7 +10732,7 @@
         <v>4.7377446656351792</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -11553,7 +10763,7 @@
         <v>8.5001816588259977</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -11584,7 +10794,7 @@
         <v>6.2316948104417227</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>22</v>
       </c>
@@ -11615,7 +10825,7 @@
         <v>8.7261984237441652</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>28</v>
       </c>
@@ -11643,7 +10853,7 @@
         <v>4.3626658977400767</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>28</v>
       </c>
@@ -11672,7 +10882,7 @@
         <v>7.4808002048616347</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>28</v>
       </c>
@@ -11700,7 +10910,7 @@
         <v>10.345281039296212</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>29</v>
       </c>
@@ -11731,7 +10941,7 @@
         <v>17.384427399590209</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>29</v>
       </c>
@@ -11762,7 +10972,7 @@
         <v>19.748530239732858</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>29</v>
       </c>
@@ -11801,32 +11011,32 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719B9C8C-E4AF-49FE-9EFA-970A258833D5}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="9" t="s">
         <v>38</v>
       </c>
@@ -11846,7 +11056,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -11866,7 +11076,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -11886,7 +11096,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -11906,7 +11116,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -11926,7 +11136,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -11946,7 +11156,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -11966,7 +11176,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -11986,7 +11196,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -12006,7 +11216,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -12026,7 +11236,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -12046,7 +11256,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -12077,47 +11287,47 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9A27944-A9ED-4A44-B000-67DEAE444E0B}">
   <dimension ref="A1:D70"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="9" t="s">
         <v>38</v>
       </c>
@@ -12131,7 +11341,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -12145,7 +11355,7 @@
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -12159,7 +11369,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -12173,7 +11383,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -12187,7 +11397,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -12201,7 +11411,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -12215,7 +11425,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -12229,7 +11439,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -12243,7 +11453,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -12257,7 +11467,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -12271,7 +11481,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -12285,7 +11495,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -12299,7 +11509,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -12313,7 +11523,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -12325,7 +11535,7 @@
       </c>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -12337,7 +11547,7 @@
       </c>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -12351,7 +11561,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -12363,7 +11573,7 @@
       </c>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>50</v>
       </c>
@@ -12375,7 +11585,7 @@
       </c>
       <c r="D27" s="1"/>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -12389,7 +11599,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -12403,7 +11613,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -12417,7 +11627,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -12431,7 +11641,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -12443,7 +11653,7 @@
       </c>
       <c r="D32" s="1"/>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -12457,7 +11667,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -12471,7 +11681,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>21</v>
       </c>
@@ -12485,7 +11695,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -12499,7 +11709,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -12513,7 +11723,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -12527,7 +11737,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -12541,7 +11751,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -12555,7 +11765,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -12569,7 +11779,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>28</v>
       </c>
@@ -12583,7 +11793,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>28</v>
       </c>
@@ -12597,7 +11807,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>29</v>
       </c>
@@ -12609,7 +11819,7 @@
       </c>
       <c r="D44" s="1"/>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>29</v>
       </c>
@@ -12623,7 +11833,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>29</v>
       </c>
@@ -12637,7 +11847,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>29</v>
       </c>
@@ -12651,7 +11861,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -12665,7 +11875,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -12679,7 +11889,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>76</v>
       </c>
@@ -12691,7 +11901,7 @@
       </c>
       <c r="D50" s="1"/>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>76</v>
       </c>
@@ -12705,7 +11915,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>76</v>
       </c>
@@ -12719,7 +11929,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>76</v>
       </c>
@@ -12733,7 +11943,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>76</v>
       </c>
@@ -12747,7 +11957,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>22</v>
       </c>
@@ -12759,7 +11969,7 @@
       </c>
       <c r="D55" s="1"/>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>22</v>
       </c>
@@ -12773,7 +11983,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>22</v>
       </c>
@@ -12787,7 +11997,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -12797,7 +12007,7 @@
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>9</v>
       </c>
@@ -12811,7 +12021,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>9</v>
       </c>
@@ -12825,7 +12035,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -12839,7 +12049,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>9</v>
       </c>
@@ -12853,7 +12063,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -12867,7 +12077,7 @@
         <v>33.299999999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>11</v>
       </c>
@@ -12881,7 +12091,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>11</v>
       </c>
@@ -12895,7 +12105,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>11</v>
       </c>
@@ -12909,7 +12119,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -12921,7 +12131,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>26</v>
       </c>
@@ -12933,7 +12143,7 @@
       </c>
       <c r="D68" s="1"/>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>26</v>
       </c>
@@ -12947,7 +12157,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>26</v>
       </c>
@@ -12972,38 +12182,38 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2107AC6-D071-4E3A-BD12-A1ED8E64132A}">
   <dimension ref="A1:C57"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="31.375" customWidth="1"/>
+    <col min="1" max="1" width="31.3671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="11" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -13014,7 +12224,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -13025,7 +12235,7 @@
         <v>52.7</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -13036,7 +12246,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -13047,7 +12257,7 @@
         <v>39.6</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>89</v>
       </c>
@@ -13058,7 +12268,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -13069,7 +12279,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -13080,7 +12290,7 @@
         <v>33.6</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -13091,7 +12301,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -13102,7 +12312,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -13113,7 +12323,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -13124,7 +12334,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -13135,7 +12345,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -13146,7 +12356,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -13157,7 +12367,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -13168,7 +12378,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -13179,7 +12389,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -13190,7 +12400,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -13201,7 +12411,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -13212,7 +12422,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -13223,7 +12433,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -13234,7 +12444,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -13245,7 +12455,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -13256,7 +12466,7 @@
         <v>54.6</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -13267,7 +12477,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -13278,7 +12488,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>28</v>
       </c>
@@ -13289,7 +12499,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -13300,7 +12510,7 @@
         <v>34.200000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -13311,7 +12521,7 @@
         <v>37.200000000000003</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -13322,7 +12532,7 @@
         <v>34.6</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>29</v>
       </c>
@@ -13333,7 +12543,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -13344,7 +12554,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>29</v>
       </c>
@@ -13355,7 +12565,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -13366,7 +12576,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -13377,7 +12587,7 @@
         <v>35.4</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>76</v>
       </c>
@@ -13388,7 +12598,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>76</v>
       </c>
@@ -13399,7 +12609,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>76</v>
       </c>
@@ -13410,7 +12620,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>76</v>
       </c>
@@ -13421,7 +12631,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>76</v>
       </c>
@@ -13432,7 +12642,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>76</v>
       </c>
@@ -13443,7 +12653,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>76</v>
       </c>
@@ -13454,7 +12664,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -13465,7 +12675,7 @@
         <v>38.299999999999997</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>22</v>
       </c>
@@ -13476,7 +12686,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>37</v>
       </c>
@@ -13487,7 +12697,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>37</v>
       </c>
@@ -13498,7 +12708,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>37</v>
       </c>
@@ -13509,7 +12719,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>37</v>
       </c>
@@ -13520,7 +12730,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>37</v>
       </c>
@@ -13531,7 +12741,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -13542,7 +12752,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -13553,7 +12763,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -13564,7 +12774,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -13586,32 +12796,32 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF0C43D6-0532-4458-BC4D-A9495F82E7F4}">
   <dimension ref="A1:O38"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.89453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1015625" customWidth="1"/>
+    <col min="4" max="4" width="9.1015625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12.125" customWidth="1"/>
-    <col min="7" max="8" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.75" customWidth="1"/>
-    <col min="13" max="13" width="10.5" customWidth="1"/>
-    <col min="14" max="14" width="10.125" customWidth="1"/>
-    <col min="15" max="15" width="10.875" customWidth="1"/>
+    <col min="6" max="6" width="12.1015625" customWidth="1"/>
+    <col min="7" max="8" width="9.1015625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="9.89453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.734375" customWidth="1"/>
+    <col min="13" max="13" width="10.47265625" customWidth="1"/>
+    <col min="14" max="14" width="10.1015625" customWidth="1"/>
+    <col min="15" max="15" width="10.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -13622,7 +12832,7 @@
         <v>28.3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -13633,7 +12843,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -13644,7 +12854,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -13655,7 +12865,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -13666,7 +12876,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -13677,7 +12887,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -13688,7 +12898,7 @@
         <v>50.7</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -13699,7 +12909,7 @@
         <v>57.8</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -13710,7 +12920,7 @@
         <v>66.3</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -13721,7 +12931,7 @@
         <v>71.3</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -13732,7 +12942,7 @@
         <v>73.5</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -13743,7 +12953,7 @@
         <v>74.599999999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -13754,7 +12964,7 @@
         <v>78.5</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -13765,641 +12975,641 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15">
-      <c r="A20" s="17" t="s">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15">
-      <c r="A24" s="20" t="s">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="G24" s="20" t="s">
+      <c r="G24" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="H24" s="20" t="s">
+      <c r="H24" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="I24" s="20" t="s">
+      <c r="I24" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="J24" s="20" t="s">
+      <c r="J24" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="K24" s="28" t="s">
+      <c r="K24" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="L24" s="27" t="s">
+      <c r="L24" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="M24" s="27" t="s">
+      <c r="M24" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="N24" s="27" t="s">
+      <c r="N24" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="O24" s="27" t="s">
+      <c r="O24" s="23" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="21">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="17">
         <v>1900</v>
       </c>
-      <c r="B25" s="22">
+      <c r="B25" s="18">
         <v>13607272</v>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="18">
         <v>1003646</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="18">
         <v>1985468</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="18">
         <v>3330153</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F25" s="18">
         <v>4366941</v>
       </c>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="25">
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="21">
         <f>B25-SUM(C25:F25)</f>
         <v>2921064</v>
       </c>
-      <c r="M25" s="21"/>
-      <c r="N25" s="26">
+      <c r="M25" s="17"/>
+      <c r="N25" s="22">
         <f>100*L25/B25</f>
         <v>21.466933269210756</v>
       </c>
-      <c r="O25" s="26"/>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" s="21">
+      <c r="O25" s="22"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="17">
         <v>1910</v>
       </c>
-      <c r="B26" s="22">
+      <c r="B26" s="18">
         <v>15160369</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="18">
         <v>945632</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="18">
         <v>2053154</v>
       </c>
-      <c r="E26" s="22">
+      <c r="E26" s="18">
         <v>3339000</v>
       </c>
-      <c r="F26" s="22">
+      <c r="F26" s="18">
         <v>5078967</v>
       </c>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="25">
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="21">
         <f t="shared" ref="L26:L28" si="0">B26-SUM(C26:F26)</f>
         <v>3743616</v>
       </c>
-      <c r="M26" s="21"/>
-      <c r="N26" s="26">
+      <c r="M26" s="17"/>
+      <c r="N26" s="22">
         <f t="shared" ref="N26:N38" si="1">100*L26/B26</f>
         <v>24.693435891962789</v>
       </c>
-      <c r="O26" s="26"/>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="A27" s="21">
+      <c r="O26" s="22"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="17">
         <v>1921</v>
       </c>
-      <c r="B27" s="22">
+      <c r="B27" s="18">
         <v>14330780</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="18">
         <v>843464</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="18">
         <v>1846928</v>
       </c>
-      <c r="E27" s="22">
+      <c r="E27" s="18">
         <v>3103658</v>
       </c>
-      <c r="F27" s="22">
+      <c r="F27" s="18">
         <v>4149139</v>
       </c>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="25">
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="21">
         <f t="shared" si="0"/>
         <v>4387591</v>
       </c>
-      <c r="M27" s="21"/>
-      <c r="N27" s="26">
+      <c r="M27" s="17"/>
+      <c r="N27" s="22">
         <f t="shared" si="1"/>
         <v>30.616554018692632</v>
       </c>
-      <c r="O27" s="26"/>
-    </row>
-    <row r="28" spans="1:15">
-      <c r="A28" s="21">
+      <c r="O27" s="22"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="17">
         <v>1930</v>
       </c>
-      <c r="B28" s="22">
+      <c r="B28" s="18">
         <v>16552722</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="18">
         <v>805014</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="18">
         <v>2171814</v>
       </c>
-      <c r="E28" s="22">
+      <c r="E28" s="18">
         <v>3655794</v>
       </c>
-      <c r="F28" s="22">
+      <c r="F28" s="18">
         <v>5210646</v>
       </c>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="25">
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="21">
         <f t="shared" si="0"/>
         <v>4709454</v>
       </c>
-      <c r="M28" s="21"/>
-      <c r="N28" s="26">
+      <c r="M28" s="17"/>
+      <c r="N28" s="22">
         <f t="shared" si="1"/>
         <v>28.451235996109883</v>
       </c>
-      <c r="O28" s="26"/>
-    </row>
-    <row r="29" spans="1:15">
-      <c r="A29" s="21">
+      <c r="O28" s="22"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="17">
         <v>1940</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="26"/>
-      <c r="O29" s="26"/>
-    </row>
-    <row r="30" spans="1:15">
-      <c r="A30" s="21">
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="17">
         <v>1950</v>
       </c>
-      <c r="B30" s="22">
+      <c r="B30" s="18">
         <v>25791017</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="18">
         <v>14790299</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="18">
         <v>2063467</v>
       </c>
-      <c r="E30" s="22">
+      <c r="E30" s="18">
         <v>1472397</v>
       </c>
-      <c r="F30" s="22">
+      <c r="F30" s="18">
         <v>1281299</v>
       </c>
-      <c r="G30" s="23">
+      <c r="G30" s="19">
         <v>1258428</v>
       </c>
-      <c r="H30" s="23">
+      <c r="H30" s="19">
         <v>725296</v>
       </c>
-      <c r="I30" s="23">
+      <c r="I30" s="19">
         <v>1406204</v>
       </c>
-      <c r="J30" s="23">
+      <c r="J30" s="19">
         <v>2234795</v>
       </c>
-      <c r="K30" s="22"/>
-      <c r="L30" s="25">
+      <c r="K30" s="18"/>
+      <c r="L30" s="21">
         <f t="shared" ref="L30:L38" si="2">B30-SUM(C30:F30)</f>
         <v>6183555</v>
       </c>
-      <c r="M30" s="25">
+      <c r="M30" s="21">
         <f>SUM(I30:K30)</f>
         <v>3640999</v>
       </c>
-      <c r="N30" s="26">
+      <c r="N30" s="22">
         <f t="shared" si="1"/>
         <v>23.975615230682838</v>
       </c>
-      <c r="O30" s="26">
+      <c r="O30" s="22">
         <f>M30/B30*100</f>
         <v>14.117314567316209</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
-      <c r="A31" s="21">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="17">
         <v>1960</v>
       </c>
-      <c r="B31" s="22">
+      <c r="B31" s="18">
         <v>34923129</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="18">
         <v>17218011</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="18">
         <v>2959460</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="18">
         <v>2366431</v>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="18">
         <v>2027511</v>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="19">
         <v>2108551</v>
       </c>
-      <c r="H31" s="24">
+      <c r="H31" s="20">
         <v>1730933</v>
       </c>
-      <c r="I31" s="23">
+      <c r="I31" s="19">
         <v>2346360</v>
       </c>
-      <c r="J31" s="24">
+      <c r="J31" s="20">
         <v>4165872</v>
       </c>
-      <c r="K31" s="22"/>
-      <c r="L31" s="25">
+      <c r="K31" s="18"/>
+      <c r="L31" s="21">
         <f t="shared" si="2"/>
         <v>10351716</v>
       </c>
-      <c r="M31" s="25">
+      <c r="M31" s="21">
         <f t="shared" ref="M31:M32" si="3">SUM(I31:K31)</f>
         <v>6512232</v>
       </c>
-      <c r="N31" s="26">
+      <c r="N31" s="22">
         <f t="shared" si="1"/>
         <v>29.641433332047651</v>
       </c>
-      <c r="O31" s="26">
+      <c r="O31" s="22">
         <f t="shared" ref="O31:O38" si="4">M31/B31*100</f>
         <v>18.647332545717767</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
-      <c r="A32" s="21">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="17">
         <v>1970</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B32" s="19">
         <v>48225238</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="20">
         <v>19916682</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="19">
         <v>4129872</v>
       </c>
-      <c r="E32" s="23">
+      <c r="E32" s="19">
         <v>3764208</v>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="19">
         <v>3409846</v>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="19">
         <v>3405818</v>
       </c>
-      <c r="H32" s="24">
+      <c r="H32" s="20">
         <v>2356569</v>
       </c>
-      <c r="I32" s="24">
+      <c r="I32" s="20">
         <v>5707130</v>
       </c>
-      <c r="J32" s="23">
+      <c r="J32" s="19">
         <v>4341512</v>
       </c>
-      <c r="K32" s="23">
+      <c r="K32" s="19">
         <v>1193601</v>
       </c>
-      <c r="L32" s="25">
+      <c r="L32" s="21">
         <f t="shared" si="2"/>
         <v>17004630</v>
       </c>
-      <c r="M32" s="25">
+      <c r="M32" s="21">
         <f t="shared" si="3"/>
         <v>11242243</v>
       </c>
-      <c r="N32" s="26">
+      <c r="N32" s="22">
         <f t="shared" si="1"/>
         <v>35.260852419224967</v>
       </c>
-      <c r="O32" s="26">
+      <c r="O32" s="22">
         <f t="shared" si="4"/>
         <v>23.311949232889219</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
-      <c r="A33" s="21">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="17">
         <v>1980</v>
       </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="26"/>
-      <c r="O33" s="26"/>
-    </row>
-    <row r="34" spans="1:15">
-      <c r="A34" s="21">
+      <c r="B33" s="19"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="17">
         <v>1990</v>
       </c>
-      <c r="B34" s="24">
+      <c r="B34" s="20">
         <v>81249645</v>
       </c>
-      <c r="C34" s="23">
+      <c r="C34" s="19">
         <v>23289924</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="19">
         <v>4647566</v>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="19">
         <v>6636745</v>
       </c>
-      <c r="F34" s="23">
+      <c r="F34" s="19">
         <v>1675566</v>
       </c>
-      <c r="G34" s="23">
+      <c r="G34" s="19">
         <v>5075188</v>
       </c>
-      <c r="H34" s="23">
+      <c r="H34" s="19">
         <v>3854850</v>
       </c>
-      <c r="I34" s="23">
+      <c r="I34" s="19">
         <v>18233313</v>
       </c>
-      <c r="J34" s="23">
+      <c r="J34" s="19">
         <v>8878127</v>
       </c>
-      <c r="K34" s="23">
+      <c r="K34" s="19">
         <v>8958366</v>
       </c>
-      <c r="L34" s="25">
+      <c r="L34" s="21">
         <f t="shared" si="2"/>
         <v>44999844</v>
       </c>
-      <c r="M34" s="25">
+      <c r="M34" s="21">
         <f t="shared" ref="M34:M38" si="5">SUM(I34:K34)</f>
         <v>36069806</v>
       </c>
-      <c r="N34" s="26">
+      <c r="N34" s="22">
         <f t="shared" si="1"/>
         <v>55.384665372999478</v>
       </c>
-      <c r="O34" s="26">
+      <c r="O34" s="22">
         <f t="shared" si="4"/>
         <v>44.393801351378215</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
-      <c r="A35" s="21">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="17">
         <v>1995</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B35" s="19">
         <v>91158290</v>
       </c>
-      <c r="C35" s="23">
+      <c r="C35" s="19">
         <v>24154775</v>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="19">
         <v>4996974</v>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="19">
         <v>7373112</v>
       </c>
-      <c r="F35" s="23">
+      <c r="F35" s="19">
         <v>1859302</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="19">
         <v>6146276</v>
       </c>
-      <c r="H35" s="23">
+      <c r="H35" s="19">
         <v>4340532</v>
       </c>
-      <c r="I35" s="23">
+      <c r="I35" s="19">
         <v>19000266</v>
       </c>
-      <c r="J35" s="23">
+      <c r="J35" s="19">
         <v>13765240</v>
       </c>
-      <c r="K35" s="23">
+      <c r="K35" s="19">
         <v>9521813</v>
       </c>
-      <c r="L35" s="25">
+      <c r="L35" s="21">
         <f t="shared" si="2"/>
         <v>52774127</v>
       </c>
-      <c r="M35" s="25">
+      <c r="M35" s="21">
         <f t="shared" si="5"/>
         <v>42287319</v>
       </c>
-      <c r="N35" s="26">
+      <c r="N35" s="22">
         <f t="shared" si="1"/>
         <v>57.89284441382128</v>
       </c>
-      <c r="O35" s="26">
+      <c r="O35" s="22">
         <f t="shared" si="4"/>
         <v>46.388890138241948</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
-      <c r="A36" s="21">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="17">
         <v>2000</v>
       </c>
-      <c r="B36" s="24">
+      <c r="B36" s="20">
         <v>97483412</v>
       </c>
-      <c r="C36" s="23">
+      <c r="C36" s="19">
         <v>24723590</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="19">
         <v>5462305</v>
       </c>
-      <c r="E36" s="23">
+      <c r="E36" s="19">
         <v>7878309</v>
       </c>
-      <c r="F36" s="23">
+      <c r="F36" s="19">
         <v>1888466</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="19">
         <v>6847942</v>
       </c>
-      <c r="H36" s="23">
+      <c r="H36" s="19">
         <v>4549492</v>
       </c>
-      <c r="I36" s="23">
+      <c r="I36" s="19">
         <v>20430268</v>
       </c>
-      <c r="J36" s="23">
+      <c r="J36" s="19">
         <v>12461706</v>
       </c>
-      <c r="K36" s="23">
+      <c r="K36" s="19">
         <v>13241334</v>
       </c>
-      <c r="L36" s="25">
+      <c r="L36" s="21">
         <f t="shared" si="2"/>
         <v>57530742</v>
       </c>
-      <c r="M36" s="25">
+      <c r="M36" s="21">
         <f t="shared" si="5"/>
         <v>46133308</v>
       </c>
-      <c r="N36" s="26">
+      <c r="N36" s="22">
         <f t="shared" si="1"/>
         <v>59.015929807627167</v>
       </c>
-      <c r="O36" s="26">
+      <c r="O36" s="22">
         <f t="shared" si="4"/>
         <v>47.324264768245904</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
-      <c r="A37" s="21">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="17">
         <v>2005</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B37" s="19">
         <v>103263388</v>
       </c>
-      <c r="C37" s="23">
+      <c r="C37" s="19">
         <v>24276536</v>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="19">
         <v>5663750</v>
       </c>
-      <c r="E37" s="23">
+      <c r="E37" s="19">
         <v>8466969</v>
       </c>
-      <c r="F37" s="23">
+      <c r="F37" s="19">
         <v>1837560</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G37" s="19">
         <v>7444004</v>
       </c>
-      <c r="H37" s="23">
+      <c r="H37" s="19">
         <v>5082771</v>
       </c>
-      <c r="I37" s="23">
+      <c r="I37" s="19">
         <v>21370547</v>
       </c>
-      <c r="J37" s="23">
+      <c r="J37" s="19">
         <v>14398274</v>
       </c>
-      <c r="K37" s="23">
+      <c r="K37" s="19">
         <v>14722977</v>
       </c>
-      <c r="L37" s="25">
+      <c r="L37" s="21">
         <f t="shared" si="2"/>
         <v>63018573</v>
       </c>
-      <c r="M37" s="25">
+      <c r="M37" s="21">
         <f t="shared" si="5"/>
         <v>50491798</v>
       </c>
-      <c r="N37" s="26">
+      <c r="N37" s="22">
         <f t="shared" si="1"/>
         <v>61.027024408689748</v>
       </c>
-      <c r="O37" s="26">
+      <c r="O37" s="22">
         <f t="shared" si="4"/>
         <v>48.896127638190606</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
-      <c r="A38" s="21">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="17">
         <v>2010</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B38" s="19">
         <v>112336538</v>
       </c>
-      <c r="C38" s="23">
+      <c r="C38" s="19">
         <v>26049769</v>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="19">
         <v>6360949</v>
       </c>
-      <c r="E38" s="23">
+      <c r="E38" s="19">
         <v>9746684</v>
       </c>
-      <c r="F38" s="23">
+      <c r="F38" s="19">
         <v>6417488</v>
       </c>
-      <c r="G38" s="23">
+      <c r="G38" s="19">
         <v>4150450</v>
       </c>
-      <c r="H38" s="23">
+      <c r="H38" s="19">
         <v>5946088</v>
       </c>
-      <c r="I38" s="23">
+      <c r="I38" s="19">
         <v>22472661</v>
       </c>
-      <c r="J38" s="23">
+      <c r="J38" s="19">
         <v>16363103</v>
       </c>
-      <c r="K38" s="23">
+      <c r="K38" s="19">
         <v>14829346</v>
       </c>
-      <c r="L38" s="25">
+      <c r="L38" s="21">
         <f t="shared" si="2"/>
         <v>63761648</v>
       </c>
-      <c r="M38" s="25">
+      <c r="M38" s="21">
         <f t="shared" si="5"/>
         <v>53665110</v>
       </c>
-      <c r="N38" s="26">
+      <c r="N38" s="22">
         <f t="shared" si="1"/>
         <v>56.759491733669059</v>
       </c>
-      <c r="O38" s="26">
+      <c r="O38" s="22">
         <f t="shared" si="4"/>
         <v>47.771732114443481</v>
       </c>

--- a/rtss-mexico/src/main/resources/latinamerica/Latin-America-Urbanization.xlsx
+++ b/rtss-mexico/src/main/resources/latinamerica/Latin-America-Urbanization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-mexico\src\main\resources\latinamerica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802ED2EB-8FAA-4136-AF4A-7EFD45E3E00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D74C9B-6B2C-46A7-AE9C-B4ACE7E6FA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="9" xr2:uid="{CF6A2AB8-34C5-4CDB-9A0B-0A9EB6FB1FEF}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="Data-6" sheetId="7" r:id="rId7"/>
     <sheet name="Data-7" sheetId="10" r:id="rId8"/>
     <sheet name="Data-8" sheetId="11" r:id="rId9"/>
-    <sheet name="UR" sheetId="9" r:id="rId10"/>
+    <sheet name="Сводка-все" sheetId="9" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -380,10 +380,10 @@
     <t>100+ тыс</t>
   </si>
   <si>
-    <t>Для СССР и РСФСР см. urbanization.xlsx</t>
+    <t>РСФСР</t>
   </si>
   <si>
-    <t>РСФСР</t>
+    <t>Для СССР, РСФСР и Мексики см. urbanization.xlsx</t>
   </si>
 </sst>
 </file>
@@ -393,7 +393,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -900,14 +900,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A5BC77-576E-4DC4-B117-3E379681AD07}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" s="3"/>
     </row>
   </sheetData>
@@ -918,16 +918,16 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC336925-0078-4AF9-986A-8BA8236BAFF3}">
   <dimension ref="A1:AF134"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:28">
       <c r="A1" s="11" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:28">
       <c r="A3" s="12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>6</v>
@@ -1008,10 +1008,10 @@
         <v>64</v>
       </c>
       <c r="AB3" s="12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28">
       <c r="A4">
         <v>1895</v>
       </c>
@@ -1043,7 +1043,7 @@
       <c r="Y4" s="12"/>
       <c r="Z4" s="12"/>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:28">
       <c r="A5">
         <v>1897</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:28">
       <c r="A6">
         <v>1899</v>
       </c>
@@ -1109,7 +1109,7 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:28">
       <c r="A7">
         <v>1900</v>
       </c>
@@ -1141,7 +1141,7 @@
       <c r="Y7" s="12"/>
       <c r="Z7" s="12"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:28">
       <c r="A8">
         <v>1901</v>
       </c>
@@ -1171,7 +1171,7 @@
       <c r="Y8" s="12"/>
       <c r="Z8" s="12"/>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:28">
       <c r="A9">
         <v>1906</v>
       </c>
@@ -1203,7 +1203,7 @@
       <c r="Y9" s="12"/>
       <c r="Z9" s="12"/>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:28">
       <c r="A10">
         <v>1910</v>
       </c>
@@ -1233,7 +1233,7 @@
       <c r="Y10" s="12"/>
       <c r="Z10" s="12"/>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:28">
       <c r="A11">
         <v>1911</v>
       </c>
@@ -1263,7 +1263,7 @@
       <c r="Y11" s="12"/>
       <c r="Z11" s="12"/>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:28">
       <c r="A12">
         <v>1913</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:28">
       <c r="A13">
         <v>1914</v>
       </c>
@@ -1328,7 +1328,7 @@
       <c r="Y13" s="12"/>
       <c r="Z13" s="12"/>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:28">
       <c r="A14">
         <v>1920</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:28">
       <c r="A15">
         <v>1921</v>
       </c>
@@ -1400,7 +1400,7 @@
       <c r="Y15" s="12"/>
       <c r="Z15" s="12"/>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:28">
       <c r="A16">
         <v>1926</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:28">
       <c r="A17">
         <v>1930</v>
       </c>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z17" s="12"/>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:28">
       <c r="A18">
         <v>1931</v>
       </c>
@@ -1506,7 +1506,7 @@
       <c r="Y18" s="12"/>
       <c r="Z18" s="12"/>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:28">
       <c r="A19">
         <v>1935</v>
       </c>
@@ -1538,7 +1538,7 @@
       <c r="Y19" s="12"/>
       <c r="Z19" s="12"/>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:28">
       <c r="A20">
         <v>1936</v>
       </c>
@@ -1570,7 +1570,7 @@
       <c r="Y20" s="12"/>
       <c r="Z20" s="12"/>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:28">
       <c r="A21">
         <v>1937</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>28.9</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:28">
       <c r="A22">
         <v>1938</v>
       </c>
@@ -1638,7 +1638,7 @@
       <c r="Y22" s="12"/>
       <c r="Z22" s="12"/>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:28">
       <c r="A23">
         <v>1939</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:28">
       <c r="A24">
         <v>1940</v>
       </c>
@@ -1718,7 +1718,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:28">
       <c r="A25">
         <v>1941</v>
       </c>
@@ -1749,7 +1749,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:28">
       <c r="A26">
         <v>1943</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:28">
       <c r="A27">
         <v>1945</v>
       </c>
@@ -1813,7 +1813,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:28">
       <c r="A28">
         <v>1946</v>
       </c>
@@ -1842,7 +1842,7 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:28">
       <c r="A29">
         <v>1947</v>
       </c>
@@ -1873,7 +1873,7 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:28">
       <c r="A30">
         <v>1950</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:28">
       <c r="A31">
         <v>1959</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:28">
       <c r="A32">
         <v>1960</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:28">
       <c r="A33">
         <v>1970</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>62.3</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:28">
       <c r="A34">
         <v>1979</v>
       </c>
@@ -2191,7 +2191,7 @@
         <v>69.3</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:28">
       <c r="A35">
         <v>1980</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:28">
       <c r="A36">
         <v>1989</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>73.599999999999994</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:28">
       <c r="A37">
         <v>1990</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:28">
       <c r="A38">
         <v>2000</v>
       </c>
@@ -2467,14 +2467,14 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:28">
       <c r="A42" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:28">
       <c r="A44" s="12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>6</v>
@@ -2555,10 +2555,10 @@
         <v>84</v>
       </c>
       <c r="AB44" s="12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28">
       <c r="A45" s="15">
         <v>1926</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:28">
       <c r="A46" s="15">
         <v>1930</v>
       </c>
@@ -2628,7 +2628,7 @@
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:28">
       <c r="A47">
         <v>1950</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:28">
       <c r="A48">
         <v>1959</v>
       </c>
@@ -2744,7 +2744,7 @@
         <v>60.4</v>
       </c>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:32">
       <c r="A49">
         <v>1960</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:32">
       <c r="A50">
         <v>1970</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>69.7</v>
       </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:32">
       <c r="A51">
         <v>1980</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:32">
       <c r="A52">
         <v>1990</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:32">
       <c r="A53">
         <v>2000</v>
       </c>
@@ -3134,14 +3134,14 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:32">
       <c r="A57" s="11" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:32">
       <c r="A59" s="12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>6</v>
@@ -3234,10 +3234,10 @@
         <v>84</v>
       </c>
       <c r="AF59" s="12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="1:32">
       <c r="A60">
         <v>1865</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>15.973962510368438</v>
       </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:32">
       <c r="A61">
         <v>1869</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>24.82533867257391</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:32">
       <c r="A62">
         <v>1875</v>
       </c>
@@ -3262,7 +3262,7 @@
         <v>17.277987023903513</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:32">
       <c r="A63">
         <v>1876</v>
       </c>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="AB63" s="1"/>
     </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:32">
       <c r="A64">
         <v>1885</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>19.212369940391472</v>
       </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:32">
       <c r="A65">
         <v>1895</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>24.121981380841554</v>
       </c>
     </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:32">
       <c r="A66">
         <v>1900</v>
       </c>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AB66" s="1"/>
     </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:32">
       <c r="A67">
         <v>1907</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>27.698910521277391</v>
       </c>
     </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:32">
       <c r="A68">
         <v>1910</v>
       </c>
@@ -3324,14 +3324,14 @@
       </c>
       <c r="AB68" s="1"/>
     </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:32">
       <c r="A69">
         <v>1913</v>
       </c>
       <c r="B69" s="1"/>
       <c r="AB69" s="1"/>
     </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:32">
       <c r="A70">
         <v>1914</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>38.26516565069636</v>
       </c>
     </row>
-    <row r="71" spans="1:32" ht="13.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:32" ht="13.5" customHeight="1">
       <c r="A71">
         <v>1919</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>27.859047616410361</v>
       </c>
     </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:32">
       <c r="A72">
         <v>1920</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:32">
       <c r="A73">
         <v>1921</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:32">
       <c r="A74">
         <v>1926</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:32">
       <c r="A75">
         <v>1927</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>18.87623959756025</v>
       </c>
     </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:32">
       <c r="A76">
         <v>1930</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:32">
       <c r="A77">
         <v>1931</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>29.864393399462539</v>
       </c>
     </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:32">
       <c r="A78">
         <v>1935</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>7.1153704466016006</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:32">
       <c r="A79">
         <v>1936</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>19.091253072290105</v>
       </c>
     </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:32">
       <c r="A80">
         <v>1937</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>11.197210631902117</v>
       </c>
     </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:32">
       <c r="A81">
         <v>1938</v>
       </c>
@@ -3498,13 +3498,13 @@
         <v>14.737441012312832</v>
       </c>
     </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:32">
       <c r="A82">
         <v>1939</v>
       </c>
       <c r="O82" s="1"/>
     </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:32">
       <c r="A83">
         <v>1940</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:32">
       <c r="A84">
         <v>1941</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:32">
       <c r="A85">
         <v>1943</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:32">
       <c r="A86">
         <v>1947</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>49.068352134448176</v>
       </c>
     </row>
-    <row r="87" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:32">
       <c r="A87">
         <v>1950</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:32">
       <c r="A88">
         <v>1959</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="89" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:32">
       <c r="A89">
         <v>1960</v>
       </c>
@@ -3802,7 +3802,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="90" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:32">
       <c r="A90">
         <v>1970</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="91" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:32">
       <c r="A91">
         <v>1979</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="92" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:32">
       <c r="A92">
         <v>1980</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:32">
       <c r="A93">
         <v>1989</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>61.9</v>
       </c>
     </row>
-    <row r="94" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:32">
       <c r="A94">
         <v>1990</v>
       </c>
@@ -4161,7 +4161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:32">
       <c r="A95">
         <v>2000</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:32">
       <c r="A96">
         <v>2010</v>
       </c>
@@ -4345,14 +4345,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:26">
       <c r="A100" s="11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:26">
       <c r="A102" s="12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B102" s="12" t="s">
         <v>6</v>
@@ -4427,10 +4427,10 @@
         <v>64</v>
       </c>
       <c r="Z102" s="12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:26">
       <c r="A103">
         <v>1865</v>
       </c>
@@ -4461,7 +4461,7 @@
       <c r="X103" s="2"/>
       <c r="Y103" s="2"/>
     </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:26">
       <c r="A104">
         <v>1869</v>
       </c>
@@ -4492,7 +4492,7 @@
       <c r="X104" s="2"/>
       <c r="Y104" s="2"/>
     </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:26">
       <c r="A105">
         <v>1875</v>
       </c>
@@ -4523,7 +4523,7 @@
       <c r="X105" s="2"/>
       <c r="Y105" s="2"/>
     </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:26">
       <c r="A106">
         <v>1876</v>
       </c>
@@ -4554,7 +4554,7 @@
       <c r="X106" s="2"/>
       <c r="Y106" s="2"/>
     </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:26">
       <c r="A107">
         <v>1885</v>
       </c>
@@ -4585,7 +4585,7 @@
       <c r="X107" s="2"/>
       <c r="Y107" s="2"/>
     </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:26">
       <c r="A108">
         <v>1895</v>
       </c>
@@ -4618,7 +4618,7 @@
       <c r="X108" s="2"/>
       <c r="Y108" s="2"/>
     </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:26">
       <c r="A109">
         <v>1900</v>
       </c>
@@ -4649,7 +4649,7 @@
       <c r="X109" s="2"/>
       <c r="Y109" s="2"/>
     </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:26">
       <c r="A110">
         <v>1907</v>
       </c>
@@ -4673,7 +4673,7 @@
       <c r="X110" s="2"/>
       <c r="Y110" s="2"/>
     </row>
-    <row r="111" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:26">
       <c r="A111">
         <v>1914</v>
       </c>
@@ -4698,7 +4698,7 @@
       <c r="W111" s="2"/>
       <c r="X111" s="2"/>
     </row>
-    <row r="112" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:26">
       <c r="A112">
         <v>1919</v>
       </c>
@@ -4722,7 +4722,7 @@
       <c r="W112" s="2"/>
       <c r="X112" s="2"/>
     </row>
-    <row r="113" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:26">
       <c r="A113">
         <v>1920</v>
       </c>
@@ -4753,7 +4753,7 @@
       <c r="W113" s="2"/>
       <c r="X113" s="2"/>
     </row>
-    <row r="114" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:26">
       <c r="A114">
         <v>1926</v>
       </c>
@@ -4780,7 +4780,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="115" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:26">
       <c r="A115">
         <v>1927</v>
       </c>
@@ -4804,7 +4804,7 @@
       <c r="W115" s="2"/>
       <c r="X115" s="2"/>
     </row>
-    <row r="116" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:26">
       <c r="A116">
         <v>1930</v>
       </c>
@@ -4832,7 +4832,7 @@
       <c r="W116" s="2"/>
       <c r="X116" s="2"/>
     </row>
-    <row r="117" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:26">
       <c r="A117">
         <v>1931</v>
       </c>
@@ -4856,7 +4856,7 @@
       <c r="W117" s="2"/>
       <c r="X117" s="2"/>
     </row>
-    <row r="118" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:26">
       <c r="A118">
         <v>1935</v>
       </c>
@@ -4880,7 +4880,7 @@
       <c r="W118" s="2"/>
       <c r="X118" s="2"/>
     </row>
-    <row r="119" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:26">
       <c r="A119">
         <v>1936</v>
       </c>
@@ -4903,7 +4903,7 @@
       <c r="W119" s="2"/>
       <c r="X119" s="2"/>
     </row>
-    <row r="120" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:26">
       <c r="A120">
         <v>1938</v>
       </c>
@@ -4928,7 +4928,7 @@
       <c r="W120" s="2"/>
       <c r="X120" s="2"/>
     </row>
-    <row r="121" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:26">
       <c r="A121">
         <v>1940</v>
       </c>
@@ -4966,7 +4966,7 @@
       <c r="W121" s="2"/>
       <c r="X121" s="2"/>
     </row>
-    <row r="122" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:26">
       <c r="A122">
         <v>1941</v>
       </c>
@@ -4989,7 +4989,7 @@
       <c r="W122" s="2"/>
       <c r="X122" s="2"/>
     </row>
-    <row r="123" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:26">
       <c r="A123">
         <v>1943</v>
       </c>
@@ -5013,7 +5013,7 @@
       <c r="W123" s="2"/>
       <c r="X123" s="2"/>
     </row>
-    <row r="124" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:26">
       <c r="A124">
         <v>1947</v>
       </c>
@@ -5043,7 +5043,7 @@
       <c r="W124" s="2"/>
       <c r="X124" s="2"/>
     </row>
-    <row r="125" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:26">
       <c r="A125">
         <v>1950</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:26">
       <c r="A126">
         <v>1959</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="127" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:26">
       <c r="A127">
         <v>1960</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="128" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:26">
       <c r="A128">
         <v>1970</v>
       </c>
@@ -5306,7 +5306,7 @@
         <v>35.799999999999997</v>
       </c>
     </row>
-    <row r="129" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:26">
       <c r="A129">
         <v>1979</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>42.7</v>
       </c>
     </row>
-    <row r="130" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:26">
       <c r="A130">
         <v>1980</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="131" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:26">
       <c r="A131">
         <v>1989</v>
       </c>
@@ -5445,7 +5445,7 @@
         <v>45.7</v>
       </c>
     </row>
-    <row r="132" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:26">
       <c r="A132">
         <v>1990</v>
       </c>
@@ -5519,7 +5519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:26">
       <c r="A133">
         <v>2000</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:26">
       <c r="A134">
         <v>2010</v>
       </c>
@@ -5676,22 +5676,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13506065-263E-4E0E-AA1C-6A8B756E2690}">
   <dimension ref="A1:O124"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="31.3671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7">
       <c r="A1" s="11" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
@@ -5714,7 +5714,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -5737,7 +5737,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -5760,7 +5760,7 @@
         <v>47.9</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>62.4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -5806,7 +5806,7 @@
         <v>81.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -5829,7 +5829,7 @@
         <v>86.9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>35.6</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>46.1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -5898,7 +5898,7 @@
         <v>36.200000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -5921,7 +5921,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -5944,7 +5944,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>74.900000000000006</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -5990,7 +5990,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -6013,7 +6013,7 @@
         <v>75.2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -6036,7 +6036,7 @@
         <v>69.8</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -6059,7 +6059,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -6082,7 +6082,7 @@
         <v>65.599999999999994</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -6105,7 +6105,7 @@
         <v>58.7</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -6128,7 +6128,7 @@
         <v>72.8</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -6151,7 +6151,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -6174,7 +6174,7 @@
         <v>74.099999999999994</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -6197,7 +6197,7 @@
         <v>91.9</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>86.6</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>61.4</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>26</v>
       </c>
@@ -6289,17 +6289,17 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:7">
       <c r="A31" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:7">
       <c r="A34" s="2" t="s">
         <v>38</v>
       </c>
@@ -6322,7 +6322,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -6345,7 +6345,7 @@
         <v>89.1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -6391,7 +6391,7 @@
         <v>62.7</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -6414,7 +6414,7 @@
         <v>79.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>23</v>
       </c>
@@ -6479,7 +6479,7 @@
         <v>47.7</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -6502,7 +6502,7 @@
         <v>36.200000000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>25</v>
       </c>
@@ -6525,7 +6525,7 @@
         <v>43.9</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>30</v>
       </c>
@@ -6548,7 +6548,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>10</v>
       </c>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>21</v>
       </c>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -6636,7 +6636,7 @@
         <v>74.5</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:15">
       <c r="A49" t="s">
         <v>28</v>
       </c>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:15">
       <c r="A50" t="s">
         <v>29</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>61.6</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:15">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -6703,7 +6703,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:15">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:15">
       <c r="A53" t="s">
         <v>22</v>
       </c>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="G53" s="1"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:15">
       <c r="A54" t="s">
         <v>16</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>74.099999999999994</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:15">
       <c r="A55" t="s">
         <v>17</v>
       </c>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:15">
       <c r="A56" t="s">
         <v>13</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:15">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -6835,7 +6835,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:15">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>61.6</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:15">
       <c r="A59" t="s">
         <v>26</v>
       </c>
@@ -6881,22 +6881,22 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:15">
       <c r="A61" s="11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:15">
       <c r="A62" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:15">
       <c r="A63" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:15">
       <c r="A64" s="5"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -6913,7 +6913,7 @@
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:15">
       <c r="A65" s="2" t="s">
         <v>38</v>
       </c>
@@ -6946,7 +6946,7 @@
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:15">
       <c r="A66" s="5" t="s">
         <v>6</v>
       </c>
@@ -6979,7 +6979,7 @@
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:15">
       <c r="A67" s="5" t="s">
         <v>31</v>
       </c>
@@ -7012,7 +7012,7 @@
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:15">
       <c r="A68" s="5" t="s">
         <v>32</v>
       </c>
@@ -7045,7 +7045,7 @@
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:15">
       <c r="A69" s="5" t="s">
         <v>19</v>
       </c>
@@ -7078,7 +7078,7 @@
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:15">
       <c r="A70" s="5" t="s">
         <v>7</v>
       </c>
@@ -7111,7 +7111,7 @@
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:15">
       <c r="A71" s="5" t="s">
         <v>8</v>
       </c>
@@ -7144,7 +7144,7 @@
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:15">
       <c r="A72" s="5" t="s">
         <v>18</v>
       </c>
@@ -7177,7 +7177,7 @@
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:15">
       <c r="A73" s="5" t="s">
         <v>34</v>
       </c>
@@ -7210,7 +7210,7 @@
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:15">
       <c r="A74" s="5" t="s">
         <v>24</v>
       </c>
@@ -7243,7 +7243,7 @@
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:15">
       <c r="A75" s="5" t="s">
         <v>23</v>
       </c>
@@ -7276,7 +7276,7 @@
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:15">
       <c r="A76" s="5" t="s">
         <v>25</v>
       </c>
@@ -7309,7 +7309,7 @@
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:15">
       <c r="A77" s="5" t="s">
         <v>33</v>
       </c>
@@ -7342,7 +7342,7 @@
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:15">
       <c r="A78" s="5" t="s">
         <v>30</v>
       </c>
@@ -7375,7 +7375,7 @@
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:15">
       <c r="A79" s="5" t="s">
         <v>10</v>
       </c>
@@ -7408,7 +7408,7 @@
       <c r="N79" s="4"/>
       <c r="O79" s="4"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:15">
       <c r="A80" s="5" t="s">
         <v>20</v>
       </c>
@@ -7441,7 +7441,7 @@
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:15">
       <c r="A81" s="5" t="s">
         <v>21</v>
       </c>
@@ -7474,7 +7474,7 @@
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:15">
       <c r="A82" s="5" t="s">
         <v>27</v>
       </c>
@@ -7507,7 +7507,7 @@
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:15">
       <c r="A83" s="5" t="s">
         <v>28</v>
       </c>
@@ -7540,7 +7540,7 @@
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:15">
       <c r="A84" s="5" t="s">
         <v>29</v>
       </c>
@@ -7573,7 +7573,7 @@
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:15">
       <c r="A85" s="5" t="s">
         <v>14</v>
       </c>
@@ -7606,7 +7606,7 @@
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:15">
       <c r="A86" s="5" t="s">
         <v>15</v>
       </c>
@@ -7639,7 +7639,7 @@
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:15">
       <c r="A87" s="5" t="s">
         <v>22</v>
       </c>
@@ -7672,7 +7672,7 @@
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:15">
       <c r="A88" s="5" t="s">
         <v>35</v>
       </c>
@@ -7705,7 +7705,7 @@
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:15">
       <c r="A89" s="5" t="s">
         <v>36</v>
       </c>
@@ -7738,7 +7738,7 @@
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:15">
       <c r="A90" s="5" t="s">
         <v>37</v>
       </c>
@@ -7771,7 +7771,7 @@
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:15">
       <c r="A91" s="5" t="s">
         <v>17</v>
       </c>
@@ -7797,7 +7797,7 @@
         <v>77.8</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:15">
       <c r="A92" s="5" t="s">
         <v>9</v>
       </c>
@@ -7823,7 +7823,7 @@
         <v>80.3</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:15">
       <c r="A93" s="5" t="s">
         <v>11</v>
       </c>
@@ -7849,7 +7849,7 @@
         <v>64.400000000000006</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:15">
       <c r="A94" s="5" t="s">
         <v>26</v>
       </c>
@@ -7875,17 +7875,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:15">
       <c r="A96" s="11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:8">
       <c r="A97" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:8">
       <c r="A99" s="2" t="s">
         <v>38</v>
       </c>
@@ -7911,7 +7911,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:8">
       <c r="A100" s="5" t="s">
         <v>6</v>
       </c>
@@ -7937,7 +7937,7 @@
         <v>64.7</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:8">
       <c r="A101" s="5" t="s">
         <v>7</v>
       </c>
@@ -7963,7 +7963,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:8">
       <c r="A102" s="5" t="s">
         <v>8</v>
       </c>
@@ -7989,7 +7989,7 @@
         <v>56.6</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:8">
       <c r="A103" s="5" t="s">
         <v>18</v>
       </c>
@@ -8015,7 +8015,7 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:8">
       <c r="A104" s="5" t="s">
         <v>34</v>
       </c>
@@ -8041,7 +8041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:8">
       <c r="A105" s="5" t="s">
         <v>24</v>
       </c>
@@ -8067,7 +8067,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:8">
       <c r="A106" s="5" t="s">
         <v>23</v>
       </c>
@@ -8093,7 +8093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:8">
       <c r="A107" s="5" t="s">
         <v>25</v>
       </c>
@@ -8119,7 +8119,7 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:8">
       <c r="A108" s="5" t="s">
         <v>30</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:8">
       <c r="A109" s="5" t="s">
         <v>10</v>
       </c>
@@ -8171,7 +8171,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:8">
       <c r="A110" s="5" t="s">
         <v>20</v>
       </c>
@@ -8197,7 +8197,7 @@
         <v>46.4</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:8">
       <c r="A111" s="5" t="s">
         <v>21</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>40.4</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:8">
       <c r="A112" s="5" t="s">
         <v>27</v>
       </c>
@@ -8249,7 +8249,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:8">
       <c r="A113" s="5" t="s">
         <v>28</v>
       </c>
@@ -8275,7 +8275,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:8">
       <c r="A114" s="5" t="s">
         <v>29</v>
       </c>
@@ -8301,7 +8301,7 @@
         <v>52.6</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:8">
       <c r="A115" s="5" t="s">
         <v>14</v>
       </c>
@@ -8327,7 +8327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:8">
       <c r="A116" s="5" t="s">
         <v>15</v>
       </c>
@@ -8353,7 +8353,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:8">
       <c r="A117" s="5" t="s">
         <v>22</v>
       </c>
@@ -8379,7 +8379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:8">
       <c r="A118" s="5" t="s">
         <v>37</v>
       </c>
@@ -8405,7 +8405,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:8">
       <c r="A119" s="5" t="s">
         <v>17</v>
       </c>
@@ -8431,7 +8431,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:8">
       <c r="A120" s="5" t="s">
         <v>9</v>
       </c>
@@ -8457,7 +8457,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:8">
       <c r="A121" s="5" t="s">
         <v>11</v>
       </c>
@@ -8483,7 +8483,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:8">
       <c r="A122" s="5" t="s">
         <v>26</v>
       </c>
@@ -8509,7 +8509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:8">
       <c r="A124" s="5"/>
     </row>
   </sheetData>
@@ -8523,7 +8523,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{963BF401-935F-4B94-9C82-FE672CD446F7}">
   <dimension ref="A1:M46"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.62890625" bestFit="1" customWidth="1"/>
@@ -8538,17 +8538,17 @@
     <col min="13" max="13" width="9.62890625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13">
       <c r="A1" s="11" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:13">
       <c r="D4" s="26" t="s">
         <v>55</v>
       </c>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="M4" s="26"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
         <v>38</v>
       </c>
@@ -8601,7 +8601,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -8640,7 +8640,7 @@
         <v>39.999919465588746</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -8679,7 +8679,7 @@
         <v>31.501729117336613</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>10.702575393983178</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>12.354575557604816</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>10.959868289448146</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -8823,7 +8823,7 @@
         <v>5.6620215161447227</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -8858,7 +8858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -8895,7 +8895,7 @@
         <v>7.4679699042130974</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -8928,7 +8928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -8967,7 +8967,7 @@
         <v>22.055413091163864</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -9006,7 +9006,7 @@
         <v>20.751529902502156</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>16.136633940278379</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -9076,7 +9076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -9109,7 +9109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -9144,7 +9144,7 @@
         <v>17.97258487317211</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -9179,7 +9179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -9216,7 +9216,7 @@
         <v>8.3848383858999256</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -9251,7 +9251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -9290,7 +9290,7 @@
         <v>23.131501517157528</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -9329,7 +9329,7 @@
         <v>21.125355543919515</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -9368,7 +9368,7 @@
         <v>18.489934280279929</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:13">
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
@@ -9378,7 +9378,7 @@
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:13">
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
@@ -9388,7 +9388,7 @@
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:13">
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
@@ -9398,7 +9398,7 @@
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:13">
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
@@ -9408,7 +9408,7 @@
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:13">
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
@@ -9418,7 +9418,7 @@
       <c r="I31" s="7"/>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:13">
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
@@ -9428,7 +9428,7 @@
       <c r="I32" s="7"/>
       <c r="J32" s="7"/>
     </row>
-    <row r="33" spans="3:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="3:10">
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
@@ -9438,7 +9438,7 @@
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
     </row>
-    <row r="34" spans="3:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="3:10">
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
@@ -9448,7 +9448,7 @@
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" spans="3:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="3:10">
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -9458,7 +9458,7 @@
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
     </row>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="3:10">
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -9468,7 +9468,7 @@
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
     </row>
-    <row r="37" spans="3:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="3:10">
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -9478,7 +9478,7 @@
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
     </row>
-    <row r="38" spans="3:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="3:10">
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
@@ -9488,7 +9488,7 @@
       <c r="I38" s="7"/>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" spans="3:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="3:10">
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -9498,7 +9498,7 @@
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" spans="3:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="3:10">
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
@@ -9508,7 +9508,7 @@
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
     </row>
-    <row r="41" spans="3:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="3:10">
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
@@ -9518,7 +9518,7 @@
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" spans="3:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="3:10">
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
@@ -9528,7 +9528,7 @@
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" spans="3:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="3:10">
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
@@ -9538,7 +9538,7 @@
       <c r="I43" s="7"/>
       <c r="J43" s="7"/>
     </row>
-    <row r="44" spans="3:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="3:10">
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
@@ -9548,7 +9548,7 @@
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
     </row>
-    <row r="45" spans="3:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="3:10">
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
@@ -9557,7 +9557,7 @@
       <c r="H45" s="7"/>
       <c r="I45" s="7"/>
     </row>
-    <row r="46" spans="3:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="3:10">
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
@@ -9581,28 +9581,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C7C1AA-F6CE-4B15-A1F0-6B51B5CB852A}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="13.89453125" customWidth="1"/>
     <col min="5" max="5" width="24.62890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:7">
       <c r="A5" s="8" t="s">
         <v>38</v>
       </c>
@@ -9621,7 +9621,7 @@
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -9638,7 +9638,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -9660,7 +9660,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E826B6E2-6891-4E9F-99E3-F5829E93EAFA}">
   <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="5.62890625" bestFit="1" customWidth="1"/>
@@ -9671,27 +9671,27 @@
     <col min="9" max="9" width="9.26171875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:10">
       <c r="A8" s="9" t="s">
         <v>38</v>
       </c>
@@ -9721,7 +9721,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>67</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>16.412235273528619</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -9783,7 +9783,7 @@
         <v>24.590995853004024</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>67</v>
       </c>
@@ -9814,7 +9814,7 @@
         <v>32.61908297746789</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>67</v>
       </c>
@@ -9845,7 +9845,7 @@
         <v>38.944534881372498</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -9876,7 +9876,7 @@
         <v>3.1064017920301814</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>10.634968637287924</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -9938,7 +9938,7 @@
         <v>10.943696108636283</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -9969,7 +9969,7 @@
         <v>13.231908342299171</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -10000,7 +10000,7 @@
         <v>10.981226600587174</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -10031,7 +10031,7 @@
         <v>11.841254044492914</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -10062,7 +10062,7 @@
         <v>12.749795119459268</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -10093,7 +10093,7 @@
         <v>15.576245989559462</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -10124,7 +10124,7 @@
         <v>17.093485515276829</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -10155,7 +10155,7 @@
         <v>20.291115180623258</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -10186,7 +10186,7 @@
         <v>22.93503473513946</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -10217,7 +10217,7 @@
         <v>24.839719568216751</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -10248,7 +10248,7 @@
         <v>28.524008531947185</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -10279,7 +10279,7 @@
         <v>9.4609561958101622</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -10310,7 +10310,7 @@
         <v>14.708734854312873</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>14</v>
       </c>
@@ -10338,7 +10338,7 @@
         <v>11.197210631902117</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>14</v>
       </c>
@@ -10366,7 +10366,7 @@
         <v>15.155986064983907</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -10397,7 +10397,7 @@
         <v>3.760059812397142</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -10428,7 +10428,7 @@
         <v>8.3848383858999256</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -10459,7 +10459,7 @@
         <v>10.396698081381023</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -10490,7 +10490,7 @@
         <v>11.551115348069256</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -10521,7 +10521,7 @@
         <v>16.602758619045936</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>20</v>
       </c>
@@ -10549,7 +10549,7 @@
         <v>15.938107074083186</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>20</v>
       </c>
@@ -10577,7 +10577,7 @@
         <v>19.183518027157795</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -10608,7 +10608,7 @@
         <v>15.794024515023171</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -10639,7 +10639,7 @@
         <v>17.498682597977361</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>21</v>
       </c>
@@ -10670,7 +10670,7 @@
         <v>18.798710831223399</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -10701,7 +10701,7 @@
         <v>3.4586130003967965</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -10732,7 +10732,7 @@
         <v>4.7377446656351792</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -10763,7 +10763,7 @@
         <v>8.5001816588259977</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -10794,7 +10794,7 @@
         <v>6.2316948104417227</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
         <v>22</v>
       </c>
@@ -10825,7 +10825,7 @@
         <v>8.7261984237441652</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
         <v>28</v>
       </c>
@@ -10853,7 +10853,7 @@
         <v>4.3626658977400767</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
         <v>28</v>
       </c>
@@ -10882,7 +10882,7 @@
         <v>7.4808002048616347</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
         <v>28</v>
       </c>
@@ -10910,7 +10910,7 @@
         <v>10.345281039296212</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>29</v>
       </c>
@@ -10941,7 +10941,7 @@
         <v>17.384427399590209</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>29</v>
       </c>
@@ -10972,7 +10972,7 @@
         <v>19.748530239732858</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>29</v>
       </c>
@@ -11011,32 +11011,32 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719B9C8C-E4AF-49FE-9EFA-970A258833D5}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:6">
       <c r="A6" s="9" t="s">
         <v>38</v>
       </c>
@@ -11056,7 +11056,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -11076,7 +11076,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -11096,7 +11096,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -11116,7 +11116,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -11136,7 +11136,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -11156,7 +11156,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -11176,7 +11176,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -11196,7 +11196,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -11216,7 +11216,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -11236,7 +11236,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -11256,7 +11256,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -11287,47 +11287,47 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9A27944-A9ED-4A44-B000-67DEAE444E0B}">
   <dimension ref="A1:D70"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4">
       <c r="A9" s="9" t="s">
         <v>38</v>
       </c>
@@ -11341,7 +11341,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -11355,7 +11355,7 @@
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -11369,7 +11369,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -11383,7 +11383,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -11397,7 +11397,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -11411,7 +11411,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -11425,7 +11425,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -11439,7 +11439,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -11453,7 +11453,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -11467,7 +11467,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -11481,7 +11481,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -11495,7 +11495,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -11509,7 +11509,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -11523,7 +11523,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -11561,7 +11561,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>50</v>
       </c>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="D27" s="1"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -11599,7 +11599,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -11613,7 +11613,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -11627,7 +11627,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -11641,7 +11641,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -11653,7 +11653,7 @@
       </c>
       <c r="D32" s="1"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -11667,7 +11667,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -11681,7 +11681,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
         <v>21</v>
       </c>
@@ -11695,7 +11695,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -11709,7 +11709,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -11723,7 +11723,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -11737,7 +11737,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -11751,7 +11751,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -11765,7 +11765,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -11779,7 +11779,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
         <v>28</v>
       </c>
@@ -11793,7 +11793,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
         <v>28</v>
       </c>
@@ -11807,7 +11807,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
         <v>29</v>
       </c>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="D44" s="1"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
         <v>29</v>
       </c>
@@ -11833,7 +11833,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
         <v>29</v>
       </c>
@@ -11847,7 +11847,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:4">
       <c r="A47" t="s">
         <v>29</v>
       </c>
@@ -11861,7 +11861,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:4">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -11875,7 +11875,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -11889,7 +11889,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
         <v>76</v>
       </c>
@@ -11901,7 +11901,7 @@
       </c>
       <c r="D50" s="1"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
         <v>76</v>
       </c>
@@ -11915,7 +11915,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
         <v>76</v>
       </c>
@@ -11929,7 +11929,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>76</v>
       </c>
@@ -11943,7 +11943,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
         <v>76</v>
       </c>
@@ -11957,7 +11957,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
         <v>22</v>
       </c>
@@ -11969,7 +11969,7 @@
       </c>
       <c r="D55" s="1"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
         <v>22</v>
       </c>
@@ -11983,7 +11983,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>22</v>
       </c>
@@ -11997,7 +11997,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -12007,7 +12007,7 @@
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
         <v>9</v>
       </c>
@@ -12021,7 +12021,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>9</v>
       </c>
@@ -12035,7 +12035,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -12049,7 +12049,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
         <v>9</v>
       </c>
@@ -12063,7 +12063,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -12077,7 +12077,7 @@
         <v>33.299999999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
         <v>11</v>
       </c>
@@ -12091,7 +12091,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
         <v>11</v>
       </c>
@@ -12105,7 +12105,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
         <v>11</v>
       </c>
@@ -12119,7 +12119,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -12131,7 +12131,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
         <v>26</v>
       </c>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="D68" s="1"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
         <v>26</v>
       </c>
@@ -12157,7 +12157,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
         <v>26</v>
       </c>
@@ -12182,27 +12182,27 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2107AC6-D071-4E3A-BD12-A1ED8E64132A}">
   <dimension ref="A1:C57"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="31.3671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3">
       <c r="A1" s="11" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:3">
       <c r="A5" s="14" t="s">
         <v>87</v>
       </c>
@@ -12213,7 +12213,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -12224,7 +12224,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -12235,7 +12235,7 @@
         <v>52.7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -12246,7 +12246,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -12257,7 +12257,7 @@
         <v>39.6</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>89</v>
       </c>
@@ -12268,7 +12268,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -12279,7 +12279,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -12290,7 +12290,7 @@
         <v>33.6</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -12301,7 +12301,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -12312,7 +12312,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -12323,7 +12323,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -12334,7 +12334,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -12345,7 +12345,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -12356,7 +12356,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -12367,7 +12367,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -12378,7 +12378,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -12389,7 +12389,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -12400,7 +12400,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -12411,7 +12411,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -12422,7 +12422,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -12433,7 +12433,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -12444,7 +12444,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -12455,7 +12455,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -12466,7 +12466,7 @@
         <v>54.6</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -12477,7 +12477,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -12488,7 +12488,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>28</v>
       </c>
@@ -12499,7 +12499,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -12510,7 +12510,7 @@
         <v>34.200000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -12521,7 +12521,7 @@
         <v>37.200000000000003</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -12532,7 +12532,7 @@
         <v>34.6</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>29</v>
       </c>
@@ -12543,7 +12543,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -12554,7 +12554,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>29</v>
       </c>
@@ -12565,7 +12565,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -12576,7 +12576,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -12587,7 +12587,7 @@
         <v>35.4</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>76</v>
       </c>
@@ -12598,7 +12598,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>76</v>
       </c>
@@ -12609,7 +12609,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>76</v>
       </c>
@@ -12620,7 +12620,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>76</v>
       </c>
@@ -12631,7 +12631,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>76</v>
       </c>
@@ -12642,7 +12642,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>76</v>
       </c>
@@ -12653,7 +12653,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>76</v>
       </c>
@@ -12664,7 +12664,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -12675,7 +12675,7 @@
         <v>38.299999999999997</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>22</v>
       </c>
@@ -12686,7 +12686,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>37</v>
       </c>
@@ -12697,7 +12697,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>37</v>
       </c>
@@ -12708,7 +12708,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>37</v>
       </c>
@@ -12719,7 +12719,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>37</v>
       </c>
@@ -12730,7 +12730,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>37</v>
       </c>
@@ -12741,7 +12741,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -12752,7 +12752,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -12763,7 +12763,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -12774,7 +12774,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -12796,7 +12796,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF0C43D6-0532-4458-BC4D-A9495F82E7F4}">
   <dimension ref="A1:O38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="10.89453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.1015625" customWidth="1"/>
@@ -12811,17 +12811,17 @@
     <col min="15" max="15" width="10.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3">
       <c r="A1" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -12832,7 +12832,7 @@
         <v>28.3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -12843,7 +12843,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -12854,7 +12854,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -12865,7 +12865,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -12876,7 +12876,7 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -12887,7 +12887,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -12898,7 +12898,7 @@
         <v>50.7</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -12909,7 +12909,7 @@
         <v>57.8</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -12920,7 +12920,7 @@
         <v>66.3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -12931,7 +12931,7 @@
         <v>71.3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -12942,7 +12942,7 @@
         <v>73.5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -12953,7 +12953,7 @@
         <v>74.599999999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -12964,7 +12964,7 @@
         <v>78.5</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -12975,17 +12975,17 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:15">
       <c r="A20" s="13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:15">
       <c r="A24" s="16" t="s">
         <v>42</v>
       </c>
@@ -13032,7 +13032,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:15">
       <c r="A25" s="17">
         <v>1900</v>
       </c>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="O25" s="22"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:15">
       <c r="A26" s="17">
         <v>1910</v>
       </c>
@@ -13102,7 +13102,7 @@
       </c>
       <c r="O26" s="22"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:15">
       <c r="A27" s="17">
         <v>1921</v>
       </c>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="O27" s="22"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:15">
       <c r="A28" s="17">
         <v>1930</v>
       </c>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="O28" s="22"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:15">
       <c r="A29" s="17">
         <v>1940</v>
       </c>
@@ -13191,7 +13191,7 @@
       <c r="N29" s="22"/>
       <c r="O29" s="22"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:15">
       <c r="A30" s="17">
         <v>1950</v>
       </c>
@@ -13240,7 +13240,7 @@
         <v>14.117314567316209</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:15">
       <c r="A31" s="17">
         <v>1960</v>
       </c>
@@ -13289,7 +13289,7 @@
         <v>18.647332545717767</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:15">
       <c r="A32" s="17">
         <v>1970</v>
       </c>
@@ -13340,7 +13340,7 @@
         <v>23.311949232889219</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:15">
       <c r="A33" s="17">
         <v>1980</v>
       </c>
@@ -13359,7 +13359,7 @@
       <c r="N33" s="22"/>
       <c r="O33" s="22"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:15">
       <c r="A34" s="17">
         <v>1990</v>
       </c>
@@ -13410,7 +13410,7 @@
         <v>44.393801351378215</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:15">
       <c r="A35" s="17">
         <v>1995</v>
       </c>
@@ -13461,7 +13461,7 @@
         <v>46.388890138241948</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:15">
       <c r="A36" s="17">
         <v>2000</v>
       </c>
@@ -13512,7 +13512,7 @@
         <v>47.324264768245904</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:15">
       <c r="A37" s="17">
         <v>2005</v>
       </c>
@@ -13563,7 +13563,7 @@
         <v>48.896127638190606</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:15">
       <c r="A38" s="17">
         <v>2010</v>
       </c>
